--- a/data/reports/personal-ai-four-year-capability-report-card.xlsx
+++ b/data/reports/personal-ai-four-year-capability-report-card.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rc829119a715c4779"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report Card" sheetId="2" r:id="R28ce804f5f534375"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="R21350ed4522f4830"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog" sheetId="4" r:id="Raed543d991ea4d8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="5" r:id="R51b9d02e6e614a21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" r:id="R8579c35a0b374f06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf406edfcae7447e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report Card" sheetId="2" r:id="Re0f20c91a52a4356"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="R63887f00eaca4d6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog" sheetId="4" r:id="R8a0855d5ac824b1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="5" r:id="R5ec971cd060b4aa9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" r:id="R97928a25773440d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -657,7 +657,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9f46cf3019584d9f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R531620a691b843e4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -667,12 +667,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BenchmarkObservationsTable" displayName="BenchmarkObservationsTable" ref="A5:K45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BenchmarkObservationsTable" displayName="BenchmarkObservationsTable" ref="A5:K43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="Benchmark ID"/>
     <x:tableColumn id="2" name="Benchmark Name"/>
     <x:tableColumn id="3" name="Category"/>
-    <x:tableColumn id="4" name="Observed date"/>
+    <x:tableColumn id="4" name="System release date (x-axis)"/>
     <x:tableColumn id="5" name="Quarter"/>
     <x:tableColumn id="6" name="Quarter index"/>
     <x:tableColumn id="7" name="Score"/>
@@ -1174,7 +1174,7 @@
     <x:row r="6">
       <x:c r="A6" s="55" t="n">
         <x:f>D17</x:f>
-        <x:v>0.4754547162751583</x:v>
+        <x:v>0.45660533834944794</x:v>
       </x:c>
       <x:c r="D6" s="54" t="str">
         <x:f>IF(A6&gt;='Methodology'!$G$7,"A",IF(A6&gt;='Methodology'!$G$8,"B",IF(A6&gt;='Methodology'!$G$9,"C",IF(A6&gt;='Methodology'!$G$10,"D","F"))))</x:f>
@@ -1182,15 +1182,15 @@
       </x:c>
       <x:c r="G6" s="55" t="n">
         <x:f>F17</x:f>
-        <x:v>0.6415123054035713</x:v>
+        <x:v>0.6045222756154646</x:v>
       </x:c>
       <x:c r="J6" s="56" t="n">
         <x:f>H17</x:f>
-        <x:v>0.04706919723433389</x:v>
+        <x:v>0.046536604581876154</x:v>
       </x:c>
       <x:c r="M6" s="54" t="str">
         <x:f>J17</x:f>
-        <x:v>Medium</x:v>
+        <x:v>Low</x:v>
       </x:c>
       <x:c r="P6" s="57" t="n">
         <x:f>I17</x:f>
@@ -1285,15 +1285,15 @@
       </x:c>
       <x:c r="D13" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A13,'Report Card'!$AS$6:$AS$28),"")</x:f>
-        <x:v>0.411119997193754</x:v>
+        <x:v>0.38254856862232545</x:v>
       </x:c>
       <x:c r="E13" s="60" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A13,'Report Card'!$AU$6:$AU$28),"")</x:f>
-        <x:v>1</x:v>
+        <x:v>0.7142857142857143</x:v>
       </x:c>
       <x:c r="F13" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A13,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.41656299325127366</x:v>
+        <x:v>0.3879915646798451</x:v>
       </x:c>
       <x:c r="G13" s="62" t="n">
         <x:f>IFERROR(AVERAGEIFS('Model'!$N$6:$N$28,'Model'!$C$6:$C$28,A13,'Model'!$D$6:$D$28,"&gt;=2"),"")</x:f>
@@ -1330,7 +1330,7 @@
       </x:c>
       <x:c r="D14" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A14,'Report Card'!$AS$6:$AS$28),"")</x:f>
-        <x:v>0.5348571428571428</x:v>
+        <x:v>0.5063285714285714</x:v>
       </x:c>
       <x:c r="E14" s="60" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A14,'Report Card'!$AU$6:$AU$28),"")</x:f>
@@ -1338,11 +1338,11 @@
       </x:c>
       <x:c r="F14" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A14,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.7614002449377768</x:v>
+        <x:v>0.6964852462818304</x:v>
       </x:c>
       <x:c r="G14" s="62" t="n">
         <x:f>IFERROR(AVERAGEIFS('Model'!$N$6:$N$28,'Model'!$C$6:$C$28,A14,'Model'!$D$6:$D$28,"&gt;=2"),"")</x:f>
-        <x:v>0.21231534925022855</x:v>
+        <x:v>0.23660304317034014</x:v>
       </x:c>
       <x:c r="H14" s="62" t="n">
         <x:f>IFERROR(AVERAGEIFS('Model'!$P$6:$P$28,'Model'!$C$6:$C$28,A14,'Model'!$D$6:$D$28,"&gt;=3"),"")</x:f>
@@ -1358,7 +1358,7 @@
       </x:c>
       <x:c r="K14" s="19" t="n">
         <x:f>IFERROR(SUMIF('Model'!$C$6:$C$28,A14,'Model'!$U$6:$U$28)/(3*C14),0)</x:f>
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.625</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -1375,7 +1375,7 @@
       </x:c>
       <x:c r="D15" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A15,'Report Card'!$AS$6:$AS$28),"")</x:f>
-        <x:v>0.4895</x:v>
+        <x:v>0.49477499999999996</x:v>
       </x:c>
       <x:c r="E15" s="60" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A15,'Report Card'!$AU$6:$AU$28),"")</x:f>
@@ -1383,11 +1383,10 @@
       </x:c>
       <x:c r="F15" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A15,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.5390515200198509</x:v>
-      </x:c>
-      <x:c r="G15" s="62" t="n">
+        <x:v>0.49477499999999996</x:v>
+      </x:c>
+      <x:c r="G15" s="62" t="str">
         <x:f>IFERROR(AVERAGEIFS('Model'!$N$6:$N$28,'Model'!$C$6:$C$28,A15,'Model'!$D$6:$D$28,"&gt;=2"),"")</x:f>
-        <x:v>0.060208192614823824</x:v>
       </x:c>
       <x:c r="H15" s="62" t="str">
         <x:f>IFERROR(AVERAGEIFS('Model'!$P$6:$P$28,'Model'!$C$6:$C$28,A15,'Model'!$D$6:$D$28,"&gt;=3"),"")</x:f>
@@ -1402,7 +1401,7 @@
       </x:c>
       <x:c r="K15" s="19" t="n">
         <x:f>IFERROR(SUMIF('Model'!$C$6:$C$28,A15,'Model'!$U$6:$U$28)/(3*C15),0)</x:f>
-        <x:v>0.4166666666666667</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -1464,23 +1463,23 @@
       </x:c>
       <x:c r="D17" s="59" t="n">
         <x:f>IFERROR(SUMPRODUCT(D13:D16,K13:K16)/SUM(K13:K16),"")</x:f>
-        <x:v>0.4754547162751583</x:v>
+        <x:v>0.45660533834944794</x:v>
       </x:c>
       <x:c r="E17" s="61" t="n">
         <x:f>IFERROR(SUMPRODUCT(E13:E16,K13:K16)/SUM(K13:K16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="F17" s="59" t="n">
         <x:f>IFERROR(SUMPRODUCT(F13:F16,K13:K16)/SUM(K13:K16),"")</x:f>
-        <x:v>0.6415123054035713</x:v>
+        <x:v>0.6045222756154646</x:v>
       </x:c>
       <x:c r="G17" s="63" t="n">
         <x:f>IFERROR(SUMPRODUCT(G13:G16,K13:K16)/SUM(K13:K16),"")</x:f>
-        <x:v>0.12254930739429859</x:v>
+        <x:v>0.12060641981551987</x:v>
       </x:c>
       <x:c r="H17" s="63" t="n">
         <x:f>IFERROR((IF(H13="",0,H13*K13)+IF(H14="",0,H14*K14)+IF(H15="",0,H15*K15)+IF(H16="",0,H16*K16))/(IF(H13="",0,K13)+IF(H14="",0,K14)+IF(H15="",0,K15)+IF(H16="",0,K16)),"")</x:f>
-        <x:v>0.04706919723433389</x:v>
+        <x:v>0.046536604581876154</x:v>
       </x:c>
       <x:c r="I17" s="64" t="n">
         <x:f>COUNTIF('Model'!$D$6:$D$28,"&gt;=3")/COUNTIF('Model'!$D$6:$D$28,"&gt;0")</x:f>
@@ -1488,11 +1487,11 @@
       </x:c>
       <x:c r="J17" s="58" t="str">
         <x:f>IF(K17&gt;=0.8,"High",IF(K17&gt;=0.5,"Medium","Low"))</x:f>
-        <x:v>Medium</x:v>
+        <x:v>Low</x:v>
       </x:c>
       <x:c r="K17" s="64" t="n">
         <x:f>IFERROR(SUMPRODUCT(K13:K16,C13:C16)/SUM(C13:C16),0)</x:f>
-        <x:v>0.5072463768115941</x:v>
+        <x:v>0.4782608695652174</x:v>
       </x:c>
     </x:row>
     <x:row r="18"/>
@@ -1587,16 +1586,14 @@
       <x:c r="C24" s="19" t="str">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$I$6:$I$28),"")</x:f>
       </x:c>
-      <x:c r="D24" s="19" t="n">
+      <x:c r="D24" s="19" t="str">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$I$6:$I$28),"")</x:f>
-        <x:v>0.252</x:v>
       </x:c>
       <x:c r="E24" s="19" t="str">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$I$6:$I$28),"")</x:f>
       </x:c>
-      <x:c r="F24" s="19" t="n">
+      <x:c r="F24" s="19" t="str">
         <x:f>IFERROR((IF(B24="",0,B24*$K$13)+IF(C24="",0,C24*$K$14)+IF(D24="",0,D24*$K$15)+IF(E24="",0,E24*$K$16))/(IF(B24="",0,$K$13)+IF(C24="",0,$K$14)+IF(D24="",0,$K$15)+IF(E24="",0,$K$16)),"")</x:f>
-        <x:v>0.252</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -1610,16 +1607,15 @@
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$K$6:$K$28),"")</x:f>
         <x:v>0.24</x:v>
       </x:c>
-      <x:c r="D25" s="19" t="n">
+      <x:c r="D25" s="19" t="str">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$K$6:$K$28),"")</x:f>
-        <x:v>0.252</x:v>
       </x:c>
       <x:c r="E25" s="19" t="str">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$K$6:$K$28),"")</x:f>
       </x:c>
       <x:c r="F25" s="19" t="n">
         <x:f>IFERROR((IF(B25="",0,B25*$K$13)+IF(C25="",0,C25*$K$14)+IF(D25="",0,D25*$K$15)+IF(E25="",0,E25*$K$16))/(IF(B25="",0,$K$13)+IF(C25="",0,$K$14)+IF(D25="",0,$K$15)+IF(E25="",0,$K$16)),"")</x:f>
-        <x:v>0.24461538461538465</x:v>
+        <x:v>0.24</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
@@ -1633,16 +1629,15 @@
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$M$6:$M$28),"")</x:f>
         <x:v>0.24</x:v>
       </x:c>
-      <x:c r="D26" s="19" t="n">
+      <x:c r="D26" s="19" t="str">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$M$6:$M$28),"")</x:f>
-        <x:v>0.252</x:v>
       </x:c>
       <x:c r="E26" s="19" t="str">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$M$6:$M$28),"")</x:f>
       </x:c>
       <x:c r="F26" s="19" t="n">
         <x:f>IFERROR((IF(B26="",0,B26*$K$13)+IF(C26="",0,C26*$K$14)+IF(D26="",0,D26*$K$15)+IF(E26="",0,E26*$K$16))/(IF(B26="",0,$K$13)+IF(C26="",0,$K$14)+IF(D26="",0,$K$15)+IF(E26="",0,$K$16)),"")</x:f>
-        <x:v>0.24461538461538465</x:v>
+        <x:v>0.24</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -1658,14 +1653,14 @@
       </x:c>
       <x:c r="D27" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$O$6:$O$28),"")</x:f>
-        <x:v>0.252</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="E27" s="19" t="str">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$O$6:$O$28),"")</x:f>
       </x:c>
       <x:c r="F27" s="19" t="n">
         <x:f>IFERROR((IF(B27="",0,B27*$K$13)+IF(C27="",0,C27*$K$14)+IF(D27="",0,D27*$K$15)+IF(E27="",0,E27*$K$16))/(IF(B27="",0,$K$13)+IF(C27="",0,$K$14)+IF(D27="",0,$K$15)+IF(E27="",0,$K$16)),"")</x:f>
-        <x:v>0.2516923076923077</x:v>
+        <x:v>0.2990130434782609</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -1681,7 +1676,7 @@
       </x:c>
       <x:c r="D28" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$Q$6:$Q$28),"")</x:f>
-        <x:v>0.367</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="E28" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$Q$6:$Q$28),"")</x:f>
@@ -1689,7 +1684,7 @@
       </x:c>
       <x:c r="F28" s="19" t="n">
         <x:f>IFERROR((IF(B28="",0,B28*$K$13)+IF(C28="",0,C28*$K$14)+IF(D28="",0,D28*$K$15)+IF(E28="",0,E28*$K$16))/(IF(B28="",0,$K$13)+IF(C28="",0,$K$14)+IF(D28="",0,$K$15)+IF(E28="",0,$K$16)),"")</x:f>
-        <x:v>0.2733058823529412</x:v>
+        <x:v>0.2705225806451613</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
@@ -1705,7 +1700,7 @@
       </x:c>
       <x:c r="D29" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$S$6:$S$28),"")</x:f>
-        <x:v>0.367</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="E29" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$S$6:$S$28),"")</x:f>
@@ -1713,7 +1708,7 @@
       </x:c>
       <x:c r="F29" s="19" t="n">
         <x:f>IFERROR((IF(B29="",0,B29*$K$13)+IF(C29="",0,C29*$K$14)+IF(D29="",0,D29*$K$15)+IF(E29="",0,E29*$K$16))/(IF(B29="",0,$K$13)+IF(C29="",0,$K$14)+IF(D29="",0,$K$15)+IF(E29="",0,$K$16)),"")</x:f>
-        <x:v>0.28796470588235296</x:v>
+        <x:v>0.28586451612903224</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -1722,7 +1717,7 @@
       </x:c>
       <x:c r="B30" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$U$6:$U$28),"")</x:f>
-        <x:v>0.46363166666666666</x:v>
+        <x:v>0.3636316666666667</x:v>
       </x:c>
       <x:c r="C30" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$U$6:$U$28),"")</x:f>
@@ -1730,7 +1725,7 @@
       </x:c>
       <x:c r="D30" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$U$6:$U$28),"")</x:f>
-        <x:v>0.5416666666666666</x:v>
+        <x:v>0.5487000000000001</x:v>
       </x:c>
       <x:c r="E30" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$U$6:$U$28),"")</x:f>
@@ -1738,7 +1733,7 @@
       </x:c>
       <x:c r="F30" s="19" t="n">
         <x:f>IFERROR((IF(B30="",0,B30*$K$13)+IF(C30="",0,C30*$K$14)+IF(D30="",0,D30*$K$15)+IF(E30="",0,E30*$K$16))/(IF(B30="",0,$K$13)+IF(C30="",0,$K$14)+IF(D30="",0,$K$15)+IF(E30="",0,$K$16)),"")</x:f>
-        <x:v>0.4608431865828092</x:v>
+        <x:v>0.43162401795735134</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -1747,15 +1742,15 @@
       </x:c>
       <x:c r="B31" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$W$6:$W$28),"")</x:f>
-        <x:v>0.4948350774062049</x:v>
+        <x:v>0.44483507740620487</x:v>
       </x:c>
       <x:c r="C31" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$W$6:$W$28),"")</x:f>
-        <x:v>0.4943857142857143</x:v>
+        <x:v>0.4717571428571428</x:v>
       </x:c>
       <x:c r="D31" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$W$6:$W$28),"")</x:f>
-        <x:v>0.4895</x:v>
+        <x:v>0.49477499999999996</x:v>
       </x:c>
       <x:c r="E31" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$W$6:$W$28),"")</x:f>
@@ -1763,7 +1758,7 @@
       </x:c>
       <x:c r="F31" s="19" t="n">
         <x:f>IFERROR((IF(B31="",0,B31*$K$13)+IF(C31="",0,C31*$K$14)+IF(D31="",0,D31*$K$15)+IF(E31="",0,E31*$K$16))/(IF(B31="",0,$K$13)+IF(C31="",0,$K$14)+IF(D31="",0,$K$15)+IF(E31="",0,$K$16)),"")</x:f>
-        <x:v>0.4822610257625673</x:v>
+        <x:v>0.46116062691076226</x:v>
       </x:c>
       <x:c r="H31" s="13" t="str">
         <x:v>LEGEND / READING RULE</x:v>
@@ -1785,15 +1780,15 @@
       </x:c>
       <x:c r="B32" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$Y$6:$Y$28),"")</x:f>
-        <x:v>0.411119997193754</x:v>
+        <x:v>0.38254856862232545</x:v>
       </x:c>
       <x:c r="C32" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$Y$6:$Y$28),"")</x:f>
-        <x:v>0.5348571428571428</x:v>
+        <x:v>0.5063285714285714</x:v>
       </x:c>
       <x:c r="D32" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$Y$6:$Y$28),"")</x:f>
-        <x:v>0.4895</x:v>
+        <x:v>0.49477499999999996</x:v>
       </x:c>
       <x:c r="E32" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$Y$6:$Y$28),"")</x:f>
@@ -1801,7 +1796,7 @@
       </x:c>
       <x:c r="F32" s="19" t="n">
         <x:f>IFERROR((IF(B32="",0,B32*$K$13)+IF(C32="",0,C32*$K$14)+IF(D32="",0,D32*$K$15)+IF(E32="",0,E32*$K$16))/(IF(B32="",0,$K$13)+IF(C32="",0,$K$14)+IF(D32="",0,$K$15)+IF(E32="",0,$K$16)),"")</x:f>
-        <x:v>0.4754547162751583</x:v>
+        <x:v>0.45660533834944794</x:v>
       </x:c>
       <x:c r="H32" s="42" t="str">
         <x:v>Observed</x:v>
@@ -1825,15 +1820,15 @@
       </x:c>
       <x:c r="B33" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AA$6:$AA$28),"")</x:f>
-        <x:v>0.41173537761105267</x:v>
+        <x:v>0.38316394903962403</x:v>
       </x:c>
       <x:c r="C33" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AA$6:$AA$28),"")</x:f>
-        <x:v>0.585604707113973</x:v>
+        <x:v>0.5516288014851415</x:v>
       </x:c>
       <x:c r="D33" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AA$6:$AA$28),"")</x:f>
-        <x:v>0.49596835802127504</x:v>
+        <x:v>0.49477499999999996</x:v>
       </x:c>
       <x:c r="E33" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AA$6:$AA$28),"")</x:f>
@@ -1841,7 +1836,7 @@
       </x:c>
       <x:c r="F33" s="19" t="n">
         <x:f>IFERROR((IF(B33="",0,B33*$K$13)+IF(C33="",0,C33*$K$14)+IF(D33="",0,D33*$K$15)+IF(E33="",0,E33*$K$16))/(IF(B33="",0,$K$13)+IF(C33="",0,$K$14)+IF(D33="",0,$K$15)+IF(E33="",0,$K$16)),"")</x:f>
-        <x:v>0.5078511456750117</x:v>
+        <x:v>0.48664599978661627</x:v>
       </x:c>
       <x:c r="H33" s="41" t="str">
         <x:v>Carried</x:v>
@@ -1865,15 +1860,15 @@
       </x:c>
       <x:c r="B34" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AC$6:$AC$28),"")</x:f>
-        <x:v>0.41234808035015463</x:v>
+        <x:v>0.38377665177872605</x:v>
       </x:c>
       <x:c r="C34" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AC$6:$AC$28),"")</x:f>
-        <x:v>0.6326578162812213</x:v>
+        <x:v>0.5936525123660638</x:v>
       </x:c>
       <x:c r="D34" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AC$6:$AC$28),"")</x:f>
-        <x:v>0.5021723264343897</x:v>
+        <x:v>0.49477499999999996</x:v>
       </x:c>
       <x:c r="E34" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AC$6:$AC$28),"")</x:f>
@@ -1881,7 +1876,7 @@
       </x:c>
       <x:c r="F34" s="19" t="n">
         <x:f>IFERROR((IF(B34="",0,B34*$K$13)+IF(C34="",0,C34*$K$14)+IF(D34="",0,D34*$K$15)+IF(E34="",0,E34*$K$16))/(IF(B34="",0,$K$13)+IF(C34="",0,$K$14)+IF(D34="",0,$K$15)+IF(E34="",0,$K$16)),"")</x:f>
-        <x:v>0.5425628219693986</x:v>
+        <x:v>0.5194627563134246</x:v>
       </x:c>
       <x:c r="H34" s="43" t="str">
         <x:v>Projected</x:v>
@@ -1905,15 +1900,15 @@
       </x:c>
       <x:c r="B35" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AE$6:$AE$28),"")</x:f>
-        <x:v>0.4129581169304344</x:v>
+        <x:v>0.3843866883590058</x:v>
       </x:c>
       <x:c r="C35" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AE$6:$AE$28),"")</x:f>
-        <x:v>0.6722381094693379</x:v>
+        <x:v>0.6285892778775987</x:v>
       </x:c>
       <x:c r="D35" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AE$6:$AE$28),"")</x:f>
-        <x:v>0.5081227119795819</x:v>
+        <x:v>0.49477499999999996</x:v>
       </x:c>
       <x:c r="E35" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AE$6:$AE$28),"")</x:f>
@@ -1921,7 +1916,7 @@
       </x:c>
       <x:c r="F35" s="19" t="n">
         <x:f>IFERROR((IF(B35="",0,B35*$K$13)+IF(C35="",0,C35*$K$14)+IF(D35="",0,D35*$K$15)+IF(E35="",0,E35*$K$16))/(IF(B35="",0,$K$13)+IF(C35="",0,$K$14)+IF(D35="",0,$K$15)+IF(E35="",0,$K$16)),"")</x:f>
-        <x:v>0.5738876519324834</x:v>
+        <x:v>0.5490255054101908</x:v>
       </x:c>
       <x:c r="H35" s="17" t="str">
         <x:v>Δ score</x:v>
@@ -1945,15 +1940,15 @@
       </x:c>
       <x:c r="B36" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AG$6:$AG$28),"")</x:f>
-        <x:v>0.41356549895360756</x:v>
+        <x:v>0.384994070382179</x:v>
       </x:c>
       <x:c r="C36" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AG$6:$AG$28),"")</x:f>
-        <x:v>0.7031496365481767</x:v>
+        <x:v>0.6552135427322853</x:v>
       </x:c>
       <x:c r="D36" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AG$6:$AG$28),"")</x:f>
-        <x:v>0.5138298796791444</x:v>
+        <x:v>0.49477499999999996</x:v>
       </x:c>
       <x:c r="E36" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AG$6:$AG$28),"")</x:f>
@@ -1961,7 +1956,7 @@
       </x:c>
       <x:c r="F36" s="19" t="n">
         <x:f>IFERROR((IF(B36="",0,B36*$K$13)+IF(C36="",0,C36*$K$14)+IF(D36="",0,D36*$K$15)+IF(E36="",0,E36*$K$16))/(IF(B36="",0,$K$13)+IF(C36="",0,$K$14)+IF(D36="",0,$K$15)+IF(E36="",0,$K$16)),"")</x:f>
-        <x:v>0.5985826142285467</x:v>
+        <x:v>0.571877199174807</x:v>
       </x:c>
       <x:c r="H36" s="17" t="str">
         <x:v>Gap velocity</x:v>
@@ -1985,15 +1980,15 @@
       </x:c>
       <x:c r="B37" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AI$6:$AI$28),"")</x:f>
-        <x:v>0.414170237970905</x:v>
+        <x:v>0.3855988093994764</x:v>
       </x:c>
       <x:c r="C37" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AI$6:$AI$28),"")</x:f>
-        <x:v>0.7247142264089005</x:v>
+        <x:v>0.6728198020609567</x:v>
       </x:c>
       <x:c r="D37" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AI$6:$AI$28),"")</x:f>
-        <x:v>0.5193037708923357</x:v>
+        <x:v>0.49477499999999996</x:v>
       </x:c>
       <x:c r="E37" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AI$6:$AI$28),"")</x:f>
@@ -2001,7 +1996,7 @@
       </x:c>
       <x:c r="F37" s="19" t="n">
         <x:f>IFERROR((IF(B37="",0,B37*$K$13)+IF(C37="",0,C37*$K$14)+IF(D37="",0,D37*$K$15)+IF(E37="",0,E37*$K$16))/(IF(B37="",0,$K$13)+IF(C37="",0,$K$14)+IF(D37="",0,$K$15)+IF(E37="",0,$K$16)),"")</x:f>
-        <x:v>0.6156518281019359</x:v>
+        <x:v>0.5869555183395334</x:v>
       </x:c>
       <x:c r="H37" s="17" t="str">
         <x:v>Gap acceleration</x:v>
@@ -2025,15 +2020,15 @@
       </x:c>
       <x:c r="B38" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AK$6:$AK$28),"")</x:f>
-        <x:v>0.41477234548329284</x:v>
+        <x:v>0.38620091691186426</x:v>
       </x:c>
       <x:c r="C38" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AK$6:$AK$28),"")</x:f>
-        <x:v>0.7391533872186862</x:v>
+        <x:v>0.6836043273990166</x:v>
       </x:c>
       <x:c r="D38" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AK$6:$AK$28),"")</x:f>
-        <x:v>0.524553920632311</x:v>
+        <x:v>0.49477499999999996</x:v>
       </x:c>
       <x:c r="E38" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AK$6:$AK$28),"")</x:f>
@@ -2041,7 +2036,7 @@
       </x:c>
       <x:c r="F38" s="19" t="n">
         <x:f>IFERROR((IF(B38="",0,B38*$K$13)+IF(C38="",0,C38*$K$14)+IF(D38="",0,D38*$K$15)+IF(E38="",0,E38*$K$16))/(IF(B38="",0,$K$13)+IF(C38="",0,$K$14)+IF(D38="",0,$K$15)+IF(E38="",0,$K$16)),"")</x:f>
-        <x:v>0.6265867003180403</x:v>
+        <x:v>0.5957937945439886</x:v>
       </x:c>
       <x:c r="H38" s="17" t="str">
         <x:v>Acceleration coverage</x:v>
@@ -2065,15 +2060,15 @@
       </x:c>
       <x:c r="B39" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AM$6:$AM$28),"")</x:f>
-        <x:v>0.41537183294169105</x:v>
+        <x:v>0.3868004043702625</x:v>
       </x:c>
       <x:c r="C39" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AM$6:$AM$28),"")</x:f>
-        <x:v>0.7489298368839602</x:v>
+        <x:v>0.6900065362516443</x:v>
       </x:c>
       <x:c r="D39" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AM$6:$AM$28),"")</x:f>
-        <x:v>0.5295894741752345</x:v>
+        <x:v>0.49477499999999996</x:v>
       </x:c>
       <x:c r="E39" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AM$6:$AM$28),"")</x:f>
@@ -2081,7 +2076,7 @@
       </x:c>
       <x:c r="F39" s="19" t="n">
         <x:f>IFERROR((IF(B39="",0,B39*$K$13)+IF(C39="",0,C39*$K$14)+IF(D39="",0,D39*$K$15)+IF(E39="",0,E39*$K$16))/(IF(B39="",0,$K$13)+IF(C39="",0,$K$14)+IF(D39="",0,$K$15)+IF(E39="",0,$K$16)),"")</x:f>
-        <x:v>0.6334825742739434</x:v>
+        <x:v>0.6005670899547221</x:v>
       </x:c>
       <x:c r="H39" s="17" t="str">
         <x:v>Confidence</x:v>
@@ -2105,15 +2100,15 @@
       </x:c>
       <x:c r="B40" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AO$6:$AO$28),"")</x:f>
-        <x:v>0.41596871174719136</x:v>
+        <x:v>0.3873972831757628</x:v>
       </x:c>
       <x:c r="C40" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AO$6:$AO$28),"")</x:f>
-        <x:v>0.7559490367936539</x:v>
+        <x:v>0.6939103772836017</x:v>
       </x:c>
       <x:c r="D40" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AO$6:$AO$28),"")</x:f>
-        <x:v>0.5344192029905058</x:v>
+        <x:v>0.49477499999999996</x:v>
       </x:c>
       <x:c r="E40" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AO$6:$AO$28),"")</x:f>
@@ -2121,7 +2116,7 @@
       </x:c>
       <x:c r="F40" s="19" t="n">
         <x:f>IFERROR((IF(B40="",0,B40*$K$13)+IF(C40="",0,C40*$K$14)+IF(D40="",0,D40*$K$15)+IF(E40="",0,E40*$K$16))/(IF(B40="",0,$K$13)+IF(C40="",0,$K$14)+IF(D40="",0,$K$15)+IF(E40="",0,$K$16)),"")</x:f>
-        <x:v>0.6380873837883642</x:v>
+        <x:v>0.6030923469479429</x:v>
       </x:c>
       <x:c r="H40" s="17" t="str">
         <x:v>Direct stewardship</x:v>
@@ -2145,15 +2140,15 @@
       </x:c>
       <x:c r="B41" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.41656299325127366</x:v>
+        <x:v>0.3879915646798451</x:v>
       </x:c>
       <x:c r="C41" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.7614002449377768</x:v>
+        <x:v>0.6964852462818304</x:v>
       </x:c>
       <x:c r="D41" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.5390515200198509</x:v>
+        <x:v>0.49477499999999996</x:v>
       </x:c>
       <x:c r="E41" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
@@ -2161,7 +2156,7 @@
       </x:c>
       <x:c r="F41" s="19" t="n">
         <x:f>IFERROR((IF(B41="",0,B41*$K$13)+IF(C41="",0,C41*$K$14)+IF(D41="",0,D41*$K$15)+IF(E41="",0,E41*$K$16))/(IF(B41="",0,$K$13)+IF(C41="",0,$K$14)+IF(D41="",0,$K$15)+IF(E41="",0,$K$16)),"")</x:f>
-        <x:v>0.6415123054035713</x:v>
+        <x:v>0.6045222756154646</x:v>
       </x:c>
       <x:c r="H41" s="17" t="str">
         <x:v>Caution</x:v>
@@ -2221,7 +2216,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb51204249f4942b1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6218106c435547f6"/>
 </x:worksheet>
 </file>
 
@@ -3219,7 +3214,7 @@
       </x:c>
       <x:c r="AV6" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW6" s="25" t="n">
         <x:f>'Model'!N6</x:f>
@@ -3402,7 +3397,7 @@
       </x:c>
       <x:c r="AV7" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW7" s="25" t="n">
         <x:f>'Model'!N7</x:f>
@@ -3585,7 +3580,7 @@
       </x:c>
       <x:c r="AV8" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW8" s="25" t="n">
         <x:f>'Model'!N8</x:f>
@@ -3766,7 +3761,7 @@
       </x:c>
       <x:c r="AV9" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW9" s="25" t="n">
         <x:f>'Model'!N9</x:f>
@@ -3792,7 +3787,7 @@
         <x:v>EnterpriseArena</x:v>
       </x:c>
       <x:c r="D10" s="17" t="str">
-        <x:v>Best-model full-horizon survival rate</x:v>
+        <x:v>Best-system full-horizon survival rate</x:v>
       </x:c>
       <x:c r="E10" s="44" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
@@ -3844,14 +3839,14 @@
       </x:c>
       <x:c r="U10" s="45" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="V10" s="45" t="str">
         <x:f>IF(OR(U10="",S10=""),"",U10-S10)</x:f>
       </x:c>
       <x:c r="W10" s="44" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="X10" s="44" t="n">
         <x:f>IF(OR(W10="",U10=""),"",W10-U10)</x:f>
@@ -3859,7 +3854,7 @@
       </x:c>
       <x:c r="Y10" s="44" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="Z10" s="44" t="n">
         <x:f>IF(OR(Y10="",W10=""),"",Y10-W10)</x:f>
@@ -3867,7 +3862,7 @@
       </x:c>
       <x:c r="AA10" s="46" t="n">
         <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(12-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AB10" s="46" t="n">
         <x:f>IF(OR(AA10="",Y10=""),"",AA10-Y10)</x:f>
@@ -3875,7 +3870,7 @@
       </x:c>
       <x:c r="AC10" s="46" t="n">
         <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(13-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AD10" s="46" t="n">
         <x:f>IF(OR(AC10="",AA10=""),"",AC10-AA10)</x:f>
@@ -3883,7 +3878,7 @@
       </x:c>
       <x:c r="AE10" s="46" t="n">
         <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(14-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AF10" s="46" t="n">
         <x:f>IF(OR(AE10="",AC10=""),"",AE10-AC10)</x:f>
@@ -3891,7 +3886,7 @@
       </x:c>
       <x:c r="AG10" s="46" t="n">
         <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(15-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AH10" s="46" t="n">
         <x:f>IF(OR(AG10="",AE10=""),"",AG10-AE10)</x:f>
@@ -3899,7 +3894,7 @@
       </x:c>
       <x:c r="AI10" s="46" t="n">
         <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(16-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AJ10" s="46" t="n">
         <x:f>IF(OR(AI10="",AG10=""),"",AI10-AG10)</x:f>
@@ -3907,7 +3902,7 @@
       </x:c>
       <x:c r="AK10" s="46" t="n">
         <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(17-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AL10" s="46" t="n">
         <x:f>IF(OR(AK10="",AI10=""),"",AK10-AI10)</x:f>
@@ -3915,7 +3910,7 @@
       </x:c>
       <x:c r="AM10" s="46" t="n">
         <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(18-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AN10" s="46" t="n">
         <x:f>IF(OR(AM10="",AK10=""),"",AM10-AK10)</x:f>
@@ -3923,7 +3918,7 @@
       </x:c>
       <x:c r="AO10" s="46" t="n">
         <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(19-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AP10" s="46" t="n">
         <x:f>IF(OR(AO10="",AM10=""),"",AO10-AM10)</x:f>
@@ -3931,7 +3926,7 @@
       </x:c>
       <x:c r="AQ10" s="46" t="n">
         <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(20-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AR10" s="46" t="n">
         <x:f>IF(OR(AQ10="",AO10=""),"",AQ10-AO10)</x:f>
@@ -3939,19 +3934,19 @@
       </x:c>
       <x:c r="AS10" s="24" t="n">
         <x:f>IF('Model'!$D10=0,"",Y10)</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AT10" s="17" t="str">
         <x:f>'Model'!S10</x:f>
-        <x:v>B</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="AU10" s="26" t="n">
         <x:f>IF('Model'!$D10=0,"",'Model'!T10)</x:f>
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV10" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW10" s="25" t="n">
         <x:f>'Model'!N10</x:f>
@@ -4132,7 +4127,7 @@
       </x:c>
       <x:c r="AV11" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW11" s="25" t="n">
         <x:f>'Model'!N11</x:f>
@@ -4313,7 +4308,7 @@
       </x:c>
       <x:c r="AV12" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW12" s="25" t="n">
         <x:f>'Model'!N12</x:f>
@@ -4397,94 +4392,94 @@
       </x:c>
       <x:c r="W13" s="45" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
-        <x:v>0.4617</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="X13" s="45" t="str">
         <x:f>IF(OR(W13="",U13=""),"",W13-U13)</x:f>
       </x:c>
-      <x:c r="Y13" s="45" t="n">
+      <x:c r="Y13" s="44" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
-        <x:v>0.503</x:v>
-      </x:c>
-      <x:c r="Z13" s="45" t="n">
+        <x:v>0.3033</x:v>
+      </x:c>
+      <x:c r="Z13" s="44" t="n">
         <x:f>IF(OR(Y13="",W13=""),"",Y13-W13)</x:f>
-        <x:v>0.0413</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AA13" s="46" t="n">
         <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(12-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.5411313394018207</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="AB13" s="46" t="n">
         <x:f>IF(OR(AA13="",Y13=""),"",AA13-Y13)</x:f>
-        <x:v>0.038131339401820674</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AC13" s="46" t="n">
         <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(13-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.5763371274061023</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="AD13" s="46" t="n">
         <x:f>IF(OR(AC13="",AA13=""),"",AC13-AA13)</x:f>
-        <x:v>0.035205788004281646</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AE13" s="46" t="n">
         <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(14-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6088418211421751</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="AF13" s="46" t="n">
         <x:f>IF(OR(AE13="",AC13=""),"",AE13-AC13)</x:f>
-        <x:v>0.03250469373607279</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AG13" s="46" t="n">
         <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(15-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6388526567112411</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="AH13" s="46" t="n">
         <x:f>IF(OR(AG13="",AE13=""),"",AG13-AE13)</x:f>
-        <x:v>0.03001083556906603</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AI13" s="46" t="n">
         <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(16-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6665609704356062</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="AJ13" s="46" t="n">
         <x:f>IF(OR(AI13="",AG13=""),"",AI13-AG13)</x:f>
-        <x:v>0.027708313724365108</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AK13" s="46" t="n">
         <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(17-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6921434187376858</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="AL13" s="46" t="n">
         <x:f>IF(OR(AK13="",AI13=""),"",AK13-AI13)</x:f>
-        <x:v>0.025582448302079563</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AM13" s="46" t="n">
         <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(18-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.7157631044262119</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="AN13" s="46" t="n">
         <x:f>IF(OR(AM13="",AK13=""),"",AM13-AK13)</x:f>
-        <x:v>0.023619685688526126</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AO13" s="46" t="n">
         <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(19-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.7375706165703648</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="AP13" s="46" t="n">
         <x:f>IF(OR(AO13="",AM13=""),"",AO13-AM13)</x:f>
-        <x:v>0.021807512144152885</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AQ13" s="46" t="n">
         <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(20-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.7577049905916242</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="AR13" s="46" t="n">
         <x:f>IF(OR(AQ13="",AO13=""),"",AQ13-AO13)</x:f>
-        <x:v>0.020134374021259394</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AS13" s="24" t="n">
         <x:f>IF('Model'!$D13=0,"",Y13)</x:f>
-        <x:v>0.503</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="AT13" s="17" t="str">
         <x:f>'Model'!S13</x:f>
@@ -4496,11 +4491,11 @@
       </x:c>
       <x:c r="AV13" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW13" s="25" t="n">
         <x:f>'Model'!N13</x:f>
-        <x:v>0.11516457356978227</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AX13" s="25" t="n">
         <x:f>'Model'!P13</x:f>
@@ -4508,7 +4503,7 @@
       </x:c>
       <x:c r="AY13" s="17" t="str">
         <x:f>'Model'!Q13</x:f>
-        <x:v>Constant velocity — two observations</x:v>
+        <x:v>Flat — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="46" hidden="0" customHeight="1">
@@ -4519,7 +4514,7 @@
         <x:v>OPS-02</x:v>
       </x:c>
       <x:c r="C14" s="17" t="str">
-        <x:v>EnterpriseOps-Gym</x:v>
+        <x:v>EnterpriseOps-Gym-AA</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
         <x:v>Strict task success across enterprise workflows</x:v>
@@ -4687,7 +4682,7 @@
       </x:c>
       <x:c r="AV14" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW14" s="25" t="n">
         <x:f>'Model'!N14</x:f>
@@ -4874,7 +4869,7 @@
       </x:c>
       <x:c r="AV15" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW15" s="25" t="n">
         <x:f>'Model'!N15</x:f>
@@ -5059,7 +5054,7 @@
       </x:c>
       <x:c r="AV16" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW16" s="25" t="n">
         <x:f>'Model'!N16</x:f>
@@ -5254,7 +5249,7 @@
       </x:c>
       <x:c r="AV17" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW17" s="25" t="n">
         <x:f>'Model'!N17</x:f>
@@ -5414,7 +5409,7 @@
       </x:c>
       <x:c r="AV18" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW18" s="25" t="n">
         <x:f>'Model'!N18</x:f>
@@ -5601,7 +5596,7 @@
       </x:c>
       <x:c r="AV19" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW19" s="25" t="n">
         <x:f>'Model'!N19</x:f>
@@ -5790,7 +5785,7 @@
       </x:c>
       <x:c r="AV20" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW20" s="25" t="n">
         <x:f>'Model'!N20</x:f>
@@ -5975,7 +5970,7 @@
       </x:c>
       <x:c r="AV21" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW21" s="25" t="n">
         <x:f>'Model'!N21</x:f>
@@ -6160,7 +6155,7 @@
       </x:c>
       <x:c r="AV22" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW22" s="25" t="n">
         <x:f>'Model'!N22</x:f>
@@ -6186,7 +6181,7 @@
         <x:v>ClawBench</x:v>
       </x:c>
       <x:c r="D23" s="17" t="str">
-        <x:v>Standardized personal-agent task score</x:v>
+        <x:v>V1 six-model comparison score</x:v>
       </x:c>
       <x:c r="E23" s="44" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
@@ -6343,7 +6338,7 @@
       </x:c>
       <x:c r="AV23" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW23" s="25" t="n">
         <x:f>'Model'!N23</x:f>
@@ -6366,10 +6361,10 @@
         <x:v>PER-04</x:v>
       </x:c>
       <x:c r="C24" s="17" t="str">
-        <x:v>AssistantBench</x:v>
+        <x:v>AssistantBench (HAL)</x:v>
       </x:c>
       <x:c r="D24" s="17" t="str">
-        <x:v>Assistant task accuracy</x:v>
+        <x:v>Assistant task accuracy on the current HAL configuration</x:v>
       </x:c>
       <x:c r="E24" s="44" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
@@ -6383,48 +6378,42 @@
       <x:c r="H24" s="44" t="str">
         <x:f>IF(OR(G24="",E24=""),"",G24-E24)</x:f>
       </x:c>
-      <x:c r="I24" s="45" t="n">
+      <x:c r="I24" s="44" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
-        <x:v>0.252</x:v>
-      </x:c>
-      <x:c r="J24" s="45" t="str">
+      </x:c>
+      <x:c r="J24" s="44" t="str">
         <x:f>IF(OR(I24="",G24=""),"",I24-G24)</x:f>
       </x:c>
-      <x:c r="K24" s="44" t="n">
+      <x:c r="K24" s="44" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
-        <x:v>0.252</x:v>
-      </x:c>
-      <x:c r="L24" s="44" t="n">
+      </x:c>
+      <x:c r="L24" s="44" t="str">
         <x:f>IF(OR(K24="",I24=""),"",K24-I24)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M24" s="44" t="n">
+      </x:c>
+      <x:c r="M24" s="44" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
-        <x:v>0.252</x:v>
-      </x:c>
-      <x:c r="N24" s="44" t="n">
+      </x:c>
+      <x:c r="N24" s="44" t="str">
         <x:f>IF(OR(M24="",K24=""),"",M24-K24)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O24" s="44" t="n">
+      </x:c>
+      <x:c r="O24" s="45" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
-        <x:v>0.252</x:v>
-      </x:c>
-      <x:c r="P24" s="44" t="n">
+        <x:v>0.3881</x:v>
+      </x:c>
+      <x:c r="P24" s="45" t="str">
         <x:f>IF(OR(O24="",M24=""),"",O24-M24)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q24" s="45" t="n">
+      </x:c>
+      <x:c r="Q24" s="44" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
-        <x:v>0.367</x:v>
-      </x:c>
-      <x:c r="R24" s="45" t="n">
+        <x:v>0.3881</x:v>
+      </x:c>
+      <x:c r="R24" s="44" t="n">
         <x:f>IF(OR(Q24="",O24=""),"",Q24-O24)</x:f>
-        <x:v>0.11499999999999999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S24" s="44" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
-        <x:v>0.367</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="T24" s="44" t="n">
         <x:f>IF(OR(S24="",Q24=""),"",S24-Q24)</x:f>
@@ -6432,7 +6421,7 @@
       </x:c>
       <x:c r="U24" s="44" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
-        <x:v>0.367</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="V24" s="44" t="n">
         <x:f>IF(OR(U24="",S24=""),"",U24-S24)</x:f>
@@ -6440,7 +6429,7 @@
       </x:c>
       <x:c r="W24" s="44" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
-        <x:v>0.367</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="X24" s="44" t="n">
         <x:f>IF(OR(W24="",U24=""),"",W24-U24)</x:f>
@@ -6448,7 +6437,7 @@
       </x:c>
       <x:c r="Y24" s="44" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
-        <x:v>0.367</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="Z24" s="44" t="n">
         <x:f>IF(OR(Y24="",W24=""),"",Y24-W24)</x:f>
@@ -6456,79 +6445,79 @@
       </x:c>
       <x:c r="AA24" s="46" t="n">
         <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(12-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.39287343208510017</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="AB24" s="46" t="n">
         <x:f>IF(OR(AA24="",Y24=""),"",AA24-Y24)</x:f>
-        <x:v>0.02587343208510018</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AC24" s="46" t="n">
         <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(13-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.4176893057375587</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="AD24" s="46" t="n">
         <x:f>IF(OR(AC24="",AA24=""),"",AC24-AA24)</x:f>
-        <x:v>0.02481587365245852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AE24" s="46" t="n">
         <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(14-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.4414908479183278</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="AF24" s="46" t="n">
         <x:f>IF(OR(AE24="",AC24=""),"",AE24-AC24)</x:f>
-        <x:v>0.02380154218076913</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AG24" s="46" t="n">
         <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(15-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.4643195187165775</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="AH24" s="46" t="n">
         <x:f>IF(OR(AG24="",AE24=""),"",AG24-AE24)</x:f>
-        <x:v>0.022828670798249684</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AI24" s="46" t="n">
         <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(16-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.48621508356934284</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="AJ24" s="46" t="n">
         <x:f>IF(OR(AI24="",AG24=""),"",AI24-AG24)</x:f>
-        <x:v>0.021895564852765337</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AK24" s="46" t="n">
         <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(17-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.5072156825292441</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="AL24" s="46" t="n">
         <x:f>IF(OR(AK24="",AI24=""),"",AK24-AI24)</x:f>
-        <x:v>0.02100059895990125</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AM24" s="46" t="n">
         <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(18-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.5273578967009378</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="AN24" s="46" t="n">
         <x:f>IF(OR(AM24="",AK24=""),"",AM24-AK24)</x:f>
-        <x:v>0.020142214171693706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AO24" s="46" t="n">
         <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(19-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.5466768119620233</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="AP24" s="46" t="n">
         <x:f>IF(OR(AO24="",AM24=""),"",AO24-AM24)</x:f>
-        <x:v>0.019318915261085534</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AQ24" s="46" t="n">
         <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(20-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.5652060800794036</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="AR24" s="46" t="n">
         <x:f>IF(OR(AQ24="",AO24=""),"",AQ24-AO24)</x:f>
-        <x:v>0.018529268117380315</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AS24" s="24" t="n">
         <x:f>IF('Model'!$D24=0,"",Y24)</x:f>
-        <x:v>0.367</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="AT24" s="17" t="str">
         <x:f>'Model'!S24</x:f>
@@ -6540,11 +6529,11 @@
       </x:c>
       <x:c r="AV24" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW24" s="25" t="n">
         <x:f>'Model'!N24</x:f>
-        <x:v>0.060208192614823824</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AX24" s="25" t="n">
         <x:f>'Model'!P24</x:f>
@@ -6552,7 +6541,7 @@
       </x:c>
       <x:c r="AY24" s="17" t="str">
         <x:f>'Model'!Q24</x:f>
-        <x:v>Constant velocity — two observations</x:v>
+        <x:v>Flat — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="46" hidden="0" customHeight="1">
@@ -6700,7 +6689,7 @@
       </x:c>
       <x:c r="AV25" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW25" s="25" t="n">
         <x:f>'Model'!N25</x:f>
@@ -6889,7 +6878,7 @@
       </x:c>
       <x:c r="AV26" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW26" s="25" t="n">
         <x:f>'Model'!N26</x:f>
@@ -7049,7 +7038,7 @@
       </x:c>
       <x:c r="AV27" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW27" s="25" t="n">
         <x:f>'Model'!N27</x:f>
@@ -7234,7 +7223,7 @@
       </x:c>
       <x:c r="AV28" s="26" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
-        <x:v>0.6336477987421384</x:v>
+        <x:v>0.5796055796055796</x:v>
       </x:c>
       <x:c r="AW28" s="25" t="n">
         <x:f>'Model'!N28</x:f>
@@ -7389,37 +7378,37 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>Append-only evidence ledger. Raw dollars and Elo enter the report only after conversion against a fixed, sourced target or reference anchor.</x:v>
+        <x:v>Evidence captured by 2026-08-26. The date column is the evaluated system's release date used on the retrospective x-axis—not the date the leaderboard result first became public.</x:v>
       </x:c>
       <x:c r="B3" s="6" t="str">
-        <x:v>Append-only evidence ledger. Raw dollars and Elo enter the report only after conversion against a fixed, sourced target or reference anchor.</x:v>
+        <x:v>Evidence captured by 2026-08-26. The date column is the evaluated system's release date used on the retrospective x-axis—not the date the leaderboard result first became public.</x:v>
       </x:c>
       <x:c r="C3" s="6" t="str">
-        <x:v>Append-only evidence ledger. Raw dollars and Elo enter the report only after conversion against a fixed, sourced target or reference anchor.</x:v>
+        <x:v>Evidence captured by 2026-08-26. The date column is the evaluated system's release date used on the retrospective x-axis—not the date the leaderboard result first became public.</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Append-only evidence ledger. Raw dollars and Elo enter the report only after conversion against a fixed, sourced target or reference anchor.</x:v>
+        <x:v>Evidence captured by 2026-08-26. The date column is the evaluated system's release date used on the retrospective x-axis—not the date the leaderboard result first became public.</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>Append-only evidence ledger. Raw dollars and Elo enter the report only after conversion against a fixed, sourced target or reference anchor.</x:v>
+        <x:v>Evidence captured by 2026-08-26. The date column is the evaluated system's release date used on the retrospective x-axis—not the date the leaderboard result first became public.</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>Append-only evidence ledger. Raw dollars and Elo enter the report only after conversion against a fixed, sourced target or reference anchor.</x:v>
+        <x:v>Evidence captured by 2026-08-26. The date column is the evaluated system's release date used on the retrospective x-axis—not the date the leaderboard result first became public.</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
-        <x:v>Append-only evidence ledger. Raw dollars and Elo enter the report only after conversion against a fixed, sourced target or reference anchor.</x:v>
+        <x:v>Evidence captured by 2026-08-26. The date column is the evaluated system's release date used on the retrospective x-axis—not the date the leaderboard result first became public.</x:v>
       </x:c>
       <x:c r="H3" s="6" t="str">
-        <x:v>Append-only evidence ledger. Raw dollars and Elo enter the report only after conversion against a fixed, sourced target or reference anchor.</x:v>
+        <x:v>Evidence captured by 2026-08-26. The date column is the evaluated system's release date used on the retrospective x-axis—not the date the leaderboard result first became public.</x:v>
       </x:c>
       <x:c r="I3" s="6" t="str">
-        <x:v>Append-only evidence ledger. Raw dollars and Elo enter the report only after conversion against a fixed, sourced target or reference anchor.</x:v>
+        <x:v>Evidence captured by 2026-08-26. The date column is the evaluated system's release date used on the retrospective x-axis—not the date the leaderboard result first became public.</x:v>
       </x:c>
       <x:c r="J3" s="6" t="str">
-        <x:v>Append-only evidence ledger. Raw dollars and Elo enter the report only after conversion against a fixed, sourced target or reference anchor.</x:v>
+        <x:v>Evidence captured by 2026-08-26. The date column is the evaluated system's release date used on the retrospective x-axis—not the date the leaderboard result first became public.</x:v>
       </x:c>
       <x:c r="K3" s="6" t="str">
-        <x:v>Append-only evidence ledger. Raw dollars and Elo enter the report only after conversion against a fixed, sourced target or reference anchor.</x:v>
+        <x:v>Evidence captured by 2026-08-26. The date column is the evaluated system's release date used on the retrospective x-axis—not the date the leaderboard result first became public.</x:v>
       </x:c>
     </x:row>
     <x:row r="4"/>
@@ -7434,7 +7423,7 @@
         <x:v>Category</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>Observed date</x:v>
+        <x:v>System release date (x-axis)</x:v>
       </x:c>
       <x:c r="E5" s="13" t="str">
         <x:v>Quarter</x:v>
@@ -7703,7 +7692,7 @@
         <x:v>Ten matched runs per model; reference strategy uses only agent-visible information.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
+    <x:row r="13" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A13" s="17" t="str">
         <x:v>DES-05</x:v>
       </x:c>
@@ -7723,19 +7712,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="G13" s="24" t="n">
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="H13" s="17" t="str">
-        <x:v>Qwen 3.5 9B</x:v>
+        <x:v>Codex CLI + GPT-5.5 / DeepSeek-V4 + ReAct (tie)</x:v>
       </x:c>
       <x:c r="I13" s="17" t="str">
-        <x:v>Best-model full-horizon survival</x:v>
+        <x:v>Best-system full-horizon survival</x:v>
       </x:c>
       <x:c r="J13" s="17" t="str">
-        <x:v>https://arxiv.org/abs/2603.23638</x:v>
+        <x:v>https://arxiv.org/html/2603.23638v2</x:v>
       </x:c>
       <x:c r="K13" s="17" t="str">
-        <x:v>Single launch-era frontier; flat forecast until another comparable point.</x:v>
+        <x:v>Five seeds per system. The paper reports 60% full survival for both leaders and 20% for Qwen3.5-9B.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -7808,7 +7797,7 @@
         <x:v>Authors' reported ratio; three LLM runs per configuration and three non-expert human participants.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
+    <x:row r="16" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A16" s="17" t="str">
         <x:v>OPS-01</x:v>
       </x:c>
@@ -7819,7 +7808,7 @@
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D16" s="18" t="n">
-        <x:v>46182</x:v>
+        <x:v>46170</x:v>
       </x:c>
       <x:c r="E16" s="17" t="str">
         <x:v>2026-Q2</x:v>
@@ -7828,10 +7817,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G16" s="24" t="n">
-        <x:v>0.4617</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="H16" s="17" t="str">
-        <x:v>Claude Fable 5</x:v>
+        <x:v>Claude Opus 4.8</x:v>
       </x:c>
       <x:c r="I16" s="17" t="str">
         <x:v>Public 600-task pass rate, max reasoning</x:v>
@@ -7840,42 +7829,42 @@
         <x:v>https://github.com/zapier/AutomationBench</x:v>
       </x:c>
       <x:c r="K16" s="17" t="str">
-        <x:v>Score rerun under the July 2026 stricter classifier.</x:v>
+        <x:v>Current public frontier after the July 2026 stricter-classifier rescore; 182/600 tasks. Later private-leaderboard results are not comparable.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="17" t="str">
-        <x:v>OPS-01</x:v>
+        <x:v>OPS-02</x:v>
       </x:c>
       <x:c r="B17" s="17" t="str">
-        <x:v>AutomationBench</x:v>
+        <x:v>EnterpriseOps-Gym-AA</x:v>
       </x:c>
       <x:c r="C17" s="17" t="str">
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D17" s="18" t="n">
-        <x:v>46227</x:v>
+        <x:v>45825</x:v>
       </x:c>
       <x:c r="E17" s="17" t="str">
-        <x:v>2026-Q3</x:v>
+        <x:v>2025-Q2</x:v>
       </x:c>
       <x:c r="F17" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G17" s="24" t="n">
-        <x:v>0.503</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="H17" s="17" t="str">
-        <x:v>Claude Opus 5</x:v>
+        <x:v>Gemini 2.5 Pro + Stirrup</x:v>
       </x:c>
       <x:c r="I17" s="17" t="str">
-        <x:v>Public 600-task pass rate, max reasoning</x:v>
+        <x:v>Strict task success in oracle tool mode</x:v>
       </x:c>
       <x:c r="J17" s="17" t="str">
-        <x:v>https://github.com/zapier/AutomationBench</x:v>
+        <x:v>https://artificialanalysis.ai/evaluations/enterprise-ops-gym-aa</x:v>
       </x:c>
       <x:c r="K17" s="17" t="str">
-        <x:v>Current public frontier.</x:v>
+        <x:v>Retrospective release-date point from the EnterpriseOps-Gym-AA table.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
@@ -7883,34 +7872,34 @@
         <x:v>OPS-02</x:v>
       </x:c>
       <x:c r="B18" s="17" t="str">
-        <x:v>EnterpriseOps-Gym</x:v>
+        <x:v>EnterpriseOps-Gym-AA</x:v>
       </x:c>
       <x:c r="C18" s="17" t="str">
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D18" s="18" t="n">
-        <x:v>45825</x:v>
+        <x:v>45929</x:v>
       </x:c>
       <x:c r="E18" s="17" t="str">
-        <x:v>2025-Q2</x:v>
+        <x:v>2025-Q3</x:v>
       </x:c>
       <x:c r="F18" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G18" s="24" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.341</x:v>
       </x:c>
       <x:c r="H18" s="17" t="str">
-        <x:v>Gemini 2.5 Pro</x:v>
+        <x:v>Claude Sonnet 4.5 + Stirrup</x:v>
       </x:c>
       <x:c r="I18" s="17" t="str">
-        <x:v>Strict task success</x:v>
+        <x:v>Strict task success in oracle tool mode</x:v>
       </x:c>
       <x:c r="J18" s="17" t="str">
-        <x:v>https://enterpriseops-gym.github.io/</x:v>
+        <x:v>https://artificialanalysis.ai/evaluations/enterprise-ops-gym-aa</x:v>
       </x:c>
       <x:c r="K18" s="17" t="str">
-        <x:v>Release-quarter frontier.</x:v>
+        <x:v>Retrospective release-date point from the EnterpriseOps-Gym-AA table.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -7918,34 +7907,34 @@
         <x:v>OPS-02</x:v>
       </x:c>
       <x:c r="B19" s="17" t="str">
-        <x:v>EnterpriseOps-Gym</x:v>
+        <x:v>EnterpriseOps-Gym-AA</x:v>
       </x:c>
       <x:c r="C19" s="17" t="str">
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D19" s="18" t="n">
-        <x:v>45929</x:v>
+        <x:v>45985</x:v>
       </x:c>
       <x:c r="E19" s="17" t="str">
-        <x:v>2025-Q3</x:v>
+        <x:v>2025-Q4</x:v>
       </x:c>
       <x:c r="F19" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G19" s="24" t="n">
-        <x:v>0.341</x:v>
+        <x:v>0.394</x:v>
       </x:c>
       <x:c r="H19" s="17" t="str">
-        <x:v>Claude Sonnet 4.5</x:v>
+        <x:v>Claude Opus 4.5 + Stirrup</x:v>
       </x:c>
       <x:c r="I19" s="17" t="str">
-        <x:v>Strict task success</x:v>
+        <x:v>Strict task success in oracle tool mode</x:v>
       </x:c>
       <x:c r="J19" s="17" t="str">
-        <x:v>https://enterpriseops-gym.github.io/</x:v>
+        <x:v>https://artificialanalysis.ai/evaluations/enterprise-ops-gym-aa</x:v>
       </x:c>
       <x:c r="K19" s="17" t="str">
-        <x:v>Release-quarter frontier.</x:v>
+        <x:v>Retrospective release-date point from the EnterpriseOps-Gym-AA table.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -7953,104 +7942,104 @@
         <x:v>OPS-02</x:v>
       </x:c>
       <x:c r="B20" s="17" t="str">
-        <x:v>EnterpriseOps-Gym</x:v>
+        <x:v>EnterpriseOps-Gym-AA</x:v>
       </x:c>
       <x:c r="C20" s="17" t="str">
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D20" s="18" t="n">
-        <x:v>45985</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="E20" s="17" t="str">
-        <x:v>2025-Q4</x:v>
+        <x:v>2026-Q1</x:v>
       </x:c>
       <x:c r="F20" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G20" s="24" t="n">
-        <x:v>0.394</x:v>
+        <x:v>0.459</x:v>
       </x:c>
       <x:c r="H20" s="17" t="str">
-        <x:v>Claude Opus 4.5</x:v>
+        <x:v>Claude Opus 4.6 + Stirrup</x:v>
       </x:c>
       <x:c r="I20" s="17" t="str">
-        <x:v>Strict task success</x:v>
+        <x:v>Strict task success in oracle tool mode</x:v>
       </x:c>
       <x:c r="J20" s="17" t="str">
-        <x:v>https://enterpriseops-gym.github.io/</x:v>
+        <x:v>https://artificialanalysis.ai/evaluations/enterprise-ops-gym-aa</x:v>
       </x:c>
       <x:c r="K20" s="17" t="str">
-        <x:v>Release-quarter frontier.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="15" hidden="0" customHeight="1">
+        <x:v>Retrospective release-date point from the EnterpriseOps-Gym-AA table.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A21" s="17" t="str">
         <x:v>OPS-02</x:v>
       </x:c>
       <x:c r="B21" s="17" t="str">
-        <x:v>EnterpriseOps-Gym</x:v>
+        <x:v>EnterpriseOps-Gym-AA</x:v>
       </x:c>
       <x:c r="C21" s="17" t="str">
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D21" s="18" t="n">
-        <x:v>46058</x:v>
+        <x:v>46204</x:v>
       </x:c>
       <x:c r="E21" s="17" t="str">
-        <x:v>2026-Q1</x:v>
+        <x:v>2026-Q3</x:v>
       </x:c>
       <x:c r="F21" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G21" s="24" t="n">
-        <x:v>0.459</x:v>
+        <x:v>0.511</x:v>
       </x:c>
       <x:c r="H21" s="17" t="str">
-        <x:v>Claude Opus 4.6</x:v>
+        <x:v>Claude Fable 5 + Stirrup + Opus 4.8 fallback</x:v>
       </x:c>
       <x:c r="I21" s="17" t="str">
-        <x:v>Strict task success</x:v>
+        <x:v>Strict task success in oracle tool mode</x:v>
       </x:c>
       <x:c r="J21" s="17" t="str">
-        <x:v>https://enterpriseops-gym.github.io/</x:v>
+        <x:v>https://artificialanalysis.ai/evaluations/enterprise-ops-gym-aa</x:v>
       </x:c>
       <x:c r="K21" s="17" t="str">
-        <x:v>Release-quarter frontier.</x:v>
+        <x:v>Current 51.1% frontier; adaptive max-effort configuration includes an Opus 4.8 fallback.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="17" t="str">
-        <x:v>OPS-02</x:v>
+        <x:v>OPS-03</x:v>
       </x:c>
       <x:c r="B22" s="17" t="str">
-        <x:v>EnterpriseOps-Gym</x:v>
+        <x:v>Commerce Agent Bench</x:v>
       </x:c>
       <x:c r="C22" s="17" t="str">
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D22" s="18" t="n">
-        <x:v>46204</x:v>
+        <x:v>46008</x:v>
       </x:c>
       <x:c r="E22" s="17" t="str">
-        <x:v>2026-Q3</x:v>
+        <x:v>2025-Q4</x:v>
       </x:c>
       <x:c r="F22" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G22" s="24" t="n">
-        <x:v>0.511</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="H22" s="17" t="str">
-        <x:v>Claude Fable 5 + fallback</x:v>
+        <x:v>Gemini 3 Flash + Pi</x:v>
       </x:c>
       <x:c r="I22" s="17" t="str">
-        <x:v>Strict task success</x:v>
+        <x:v>Pi-harness full-suite pass rate</x:v>
       </x:c>
       <x:c r="J22" s="17" t="str">
-        <x:v>https://enterpriseops-gym.github.io/</x:v>
+        <x:v>https://github.com/Accio-org/CommerceAgentBench</x:v>
       </x:c>
       <x:c r="K22" s="17" t="str">
-        <x:v>Harness includes fallback; pin this configuration for future comparison.</x:v>
+        <x:v>107-task benchmark snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -8064,19 +8053,19 @@
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D23" s="18" t="n">
-        <x:v>46008</x:v>
+        <x:v>46143</x:v>
       </x:c>
       <x:c r="E23" s="17" t="str">
-        <x:v>2025-Q4</x:v>
+        <x:v>2026-Q2</x:v>
       </x:c>
       <x:c r="F23" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G23" s="24" t="n">
-        <x:v>0.29</x:v>
+        <x:v>0.523</x:v>
       </x:c>
       <x:c r="H23" s="17" t="str">
-        <x:v>Gemini 3 Flash + Pi</x:v>
+        <x:v>Claude Opus 4.8 + Pi</x:v>
       </x:c>
       <x:c r="I23" s="17" t="str">
         <x:v>Pi-harness full-suite pass rate</x:v>
@@ -8085,7 +8074,7 @@
         <x:v>https://github.com/Accio-org/CommerceAgentBench</x:v>
       </x:c>
       <x:c r="K23" s="17" t="str">
-        <x:v>107-task benchmark snapshot.</x:v>
+        <x:v>Quarter frontier; fixed Pi harness.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -8099,19 +8088,19 @@
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D24" s="18" t="n">
-        <x:v>46143</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="E24" s="17" t="str">
-        <x:v>2026-Q2</x:v>
+        <x:v>2026-Q3</x:v>
       </x:c>
       <x:c r="F24" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G24" s="24" t="n">
-        <x:v>0.523</x:v>
+        <x:v>0.607</x:v>
       </x:c>
       <x:c r="H24" s="17" t="str">
-        <x:v>Claude Opus 4.8 + Pi</x:v>
+        <x:v>Claude Opus 5 + Pi</x:v>
       </x:c>
       <x:c r="I24" s="17" t="str">
         <x:v>Pi-harness full-suite pass rate</x:v>
@@ -8120,77 +8109,77 @@
         <x:v>https://github.com/Accio-org/CommerceAgentBench</x:v>
       </x:c>
       <x:c r="K24" s="17" t="str">
-        <x:v>Quarter frontier; fixed Pi harness.</x:v>
+        <x:v>65/107 tasks; fixed Pi harness.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="17" t="str">
-        <x:v>OPS-03</x:v>
+        <x:v>OPS-04</x:v>
       </x:c>
       <x:c r="B25" s="17" t="str">
-        <x:v>Commerce Agent Bench</x:v>
+        <x:v>ClawMark</x:v>
       </x:c>
       <x:c r="C25" s="17" t="str">
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D25" s="18" t="n">
-        <x:v>46227</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="E25" s="17" t="str">
-        <x:v>2026-Q3</x:v>
+        <x:v>2026-Q1</x:v>
       </x:c>
       <x:c r="F25" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G25" s="24" t="n">
-        <x:v>0.607</x:v>
+        <x:v>0.758</x:v>
       </x:c>
       <x:c r="H25" s="17" t="str">
-        <x:v>Claude Opus 5 + Pi</x:v>
+        <x:v>Claude Sonnet 4.6</x:v>
       </x:c>
       <x:c r="I25" s="17" t="str">
-        <x:v>Pi-harness full-suite pass rate</x:v>
+        <x:v>Avg@3 weighted deterministic-checker score</x:v>
       </x:c>
       <x:c r="J25" s="17" t="str">
-        <x:v>https://github.com/Accio-org/CommerceAgentBench</x:v>
+        <x:v>https://github.com/evolvent-ai/ClawMark</x:v>
       </x:c>
       <x:c r="K25" s="17" t="str">
-        <x:v>65/107 tasks; fixed Pi harness.</x:v>
+        <x:v>One pinned 100-task repo snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="17" t="str">
-        <x:v>OPS-04</x:v>
+        <x:v>OPS-05</x:v>
       </x:c>
       <x:c r="B26" s="17" t="str">
-        <x:v>ClawMark</x:v>
+        <x:v>TheAgentCompany</x:v>
       </x:c>
       <x:c r="C26" s="17" t="str">
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D26" s="18" t="n">
-        <x:v>46082</x:v>
+        <x:v>45645</x:v>
       </x:c>
       <x:c r="E26" s="17" t="str">
-        <x:v>2026-Q1</x:v>
+        <x:v>2024-Q4</x:v>
       </x:c>
       <x:c r="F26" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G26" s="24" t="n">
-        <x:v>0.758</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="H26" s="17" t="str">
-        <x:v>Claude Sonnet 4.6</x:v>
+        <x:v>Launch-paper best system</x:v>
       </x:c>
       <x:c r="I26" s="17" t="str">
-        <x:v>Avg@3 weighted deterministic-checker score</x:v>
+        <x:v>Fraction of tasks completed</x:v>
       </x:c>
       <x:c r="J26" s="17" t="str">
-        <x:v>https://github.com/evolvent-ai/ClawMark</x:v>
+        <x:v>https://arxiv.org/abs/2412.14161</x:v>
       </x:c>
       <x:c r="K26" s="17" t="str">
-        <x:v>One pinned 100-task repo snapshot.</x:v>
+        <x:v>Primary-paper baseline.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -8204,28 +8193,28 @@
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D27" s="18" t="n">
-        <x:v>45645</x:v>
+        <x:v>45825</x:v>
       </x:c>
       <x:c r="E27" s="17" t="str">
-        <x:v>2024-Q4</x:v>
+        <x:v>2025-Q2</x:v>
       </x:c>
       <x:c r="F27" s="17" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G27" s="24" t="n">
-        <x:v>0.24</x:v>
+        <x:v>0.303</x:v>
       </x:c>
       <x:c r="H27" s="17" t="str">
-        <x:v>Launch-paper best system</x:v>
+        <x:v>Gemini 2.5 Pro</x:v>
       </x:c>
       <x:c r="I27" s="17" t="str">
         <x:v>Fraction of tasks completed</x:v>
       </x:c>
       <x:c r="J27" s="17" t="str">
-        <x:v>https://arxiv.org/abs/2412.14161</x:v>
+        <x:v>https://the-agent-company.com/</x:v>
       </x:c>
       <x:c r="K27" s="17" t="str">
-        <x:v>Primary-paper baseline.</x:v>
+        <x:v>Later leaderboard configuration; comparability caveat.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -8239,19 +8228,19 @@
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D28" s="18" t="n">
-        <x:v>45825</x:v>
+        <x:v>45901</x:v>
       </x:c>
       <x:c r="E28" s="17" t="str">
-        <x:v>2025-Q2</x:v>
+        <x:v>2025-Q3</x:v>
       </x:c>
       <x:c r="F28" s="17" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G28" s="24" t="n">
-        <x:v>0.303</x:v>
+        <x:v>0.429</x:v>
       </x:c>
       <x:c r="H28" s="17" t="str">
-        <x:v>Gemini 2.5 Pro</x:v>
+        <x:v>DeepSeek V3.2 + specialized harness</x:v>
       </x:c>
       <x:c r="I28" s="17" t="str">
         <x:v>Fraction of tasks completed</x:v>
@@ -8260,77 +8249,77 @@
         <x:v>https://the-agent-company.com/</x:v>
       </x:c>
       <x:c r="K28" s="17" t="str">
-        <x:v>Later leaderboard configuration; comparability caveat.</x:v>
+        <x:v>Community/specialized harness; system-level frontier.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="17" t="str">
-        <x:v>OPS-05</x:v>
+        <x:v>OPS-07</x:v>
       </x:c>
       <x:c r="B29" s="17" t="str">
-        <x:v>TheAgentCompany</x:v>
+        <x:v>Finch / FinWorkBench</x:v>
       </x:c>
       <x:c r="C29" s="17" t="str">
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D29" s="18" t="n">
-        <x:v>45901</x:v>
+        <x:v>45974</x:v>
       </x:c>
       <x:c r="E29" s="17" t="str">
-        <x:v>2025-Q3</x:v>
+        <x:v>2025-Q4</x:v>
       </x:c>
       <x:c r="F29" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G29" s="24" t="n">
-        <x:v>0.429</x:v>
+        <x:v>0.384</x:v>
       </x:c>
       <x:c r="H29" s="17" t="str">
-        <x:v>DeepSeek V3.2 + specialized harness</x:v>
+        <x:v>GPT-5.1 Pro</x:v>
       </x:c>
       <x:c r="I29" s="17" t="str">
-        <x:v>Fraction of tasks completed</x:v>
+        <x:v>Strict finance-work task pass rate</x:v>
       </x:c>
       <x:c r="J29" s="17" t="str">
-        <x:v>https://the-agent-company.com/</x:v>
+        <x:v>https://aclanthology.org/2026.findings-acl.523/</x:v>
       </x:c>
       <x:c r="K29" s="17" t="str">
-        <x:v>Community/specialized harness; system-level frontier.</x:v>
+        <x:v>Model release-quarter assignment; publication followed in 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" s="17" t="str">
-        <x:v>OPS-07</x:v>
+        <x:v>OPS-08</x:v>
       </x:c>
       <x:c r="B30" s="17" t="str">
-        <x:v>Finch / FinWorkBench</x:v>
+        <x:v>tau3 Banking</x:v>
       </x:c>
       <x:c r="C30" s="17" t="str">
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D30" s="18" t="n">
-        <x:v>45974</x:v>
+        <x:v>45929</x:v>
       </x:c>
       <x:c r="E30" s="17" t="str">
-        <x:v>2025-Q4</x:v>
+        <x:v>2025-Q3</x:v>
       </x:c>
       <x:c r="F30" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G30" s="24" t="n">
-        <x:v>0.384</x:v>
+        <x:v>0.253</x:v>
       </x:c>
       <x:c r="H30" s="17" t="str">
-        <x:v>GPT-5.1 Pro</x:v>
+        <x:v>Claude Sonnet 4.5</x:v>
       </x:c>
       <x:c r="I30" s="17" t="str">
-        <x:v>Strict finance-work task pass rate</x:v>
+        <x:v>tau3 Banking strict success</x:v>
       </x:c>
       <x:c r="J30" s="17" t="str">
-        <x:v>https://aclanthology.org/2026.findings-acl.523/</x:v>
+        <x:v>https://taubench.com/leaderboard/</x:v>
       </x:c>
       <x:c r="K30" s="17" t="str">
-        <x:v>Model release-quarter assignment; publication followed in 2026.</x:v>
+        <x:v>Release-quarter frontier.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -8344,19 +8333,19 @@
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D31" s="18" t="n">
-        <x:v>45929</x:v>
+        <x:v>46002</x:v>
       </x:c>
       <x:c r="E31" s="17" t="str">
-        <x:v>2025-Q3</x:v>
+        <x:v>2025-Q4</x:v>
       </x:c>
       <x:c r="F31" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G31" s="24" t="n">
-        <x:v>0.253</x:v>
+        <x:v>0.322</x:v>
       </x:c>
       <x:c r="H31" s="17" t="str">
-        <x:v>Claude Sonnet 4.5</x:v>
+        <x:v>GPT-5.2</x:v>
       </x:c>
       <x:c r="I31" s="17" t="str">
         <x:v>tau3 Banking strict success</x:v>
@@ -8379,19 +8368,19 @@
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D32" s="18" t="n">
-        <x:v>46002</x:v>
+        <x:v>46086</x:v>
       </x:c>
       <x:c r="E32" s="17" t="str">
-        <x:v>2025-Q4</x:v>
+        <x:v>2026-Q1</x:v>
       </x:c>
       <x:c r="F32" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G32" s="24" t="n">
-        <x:v>0.322</x:v>
+        <x:v>0.394</x:v>
       </x:c>
       <x:c r="H32" s="17" t="str">
-        <x:v>GPT-5.2</x:v>
+        <x:v>GPT-5.4</x:v>
       </x:c>
       <x:c r="I32" s="17" t="str">
         <x:v>tau3 Banking strict success</x:v>
@@ -8414,19 +8403,19 @@
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D33" s="18" t="n">
-        <x:v>46086</x:v>
+        <x:v>46143</x:v>
       </x:c>
       <x:c r="E33" s="17" t="str">
-        <x:v>2026-Q1</x:v>
+        <x:v>2026-Q2</x:v>
       </x:c>
       <x:c r="F33" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G33" s="24" t="n">
-        <x:v>0.394</x:v>
+        <x:v>0.446</x:v>
       </x:c>
       <x:c r="H33" s="17" t="str">
-        <x:v>GPT-5.4</x:v>
+        <x:v>GPT-5.5</x:v>
       </x:c>
       <x:c r="I33" s="17" t="str">
         <x:v>tau3 Banking strict success</x:v>
@@ -8449,19 +8438,19 @@
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="D34" s="18" t="n">
-        <x:v>46143</x:v>
+        <x:v>46235</x:v>
       </x:c>
       <x:c r="E34" s="17" t="str">
-        <x:v>2026-Q2</x:v>
+        <x:v>2026-Q3</x:v>
       </x:c>
       <x:c r="F34" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G34" s="24" t="n">
-        <x:v>0.446</x:v>
+        <x:v>0.552</x:v>
       </x:c>
       <x:c r="H34" s="17" t="str">
-        <x:v>GPT-5.5</x:v>
+        <x:v>Qwen 3.8 Max</x:v>
       </x:c>
       <x:c r="I34" s="17" t="str">
         <x:v>tau3 Banking strict success</x:v>
@@ -8470,50 +8459,50 @@
         <x:v>https://taubench.com/leaderboard/</x:v>
       </x:c>
       <x:c r="K34" s="17" t="str">
-        <x:v>Release-quarter frontier.</x:v>
+        <x:v>Current quarter frontier.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="17" t="str">
-        <x:v>OPS-08</x:v>
+        <x:v>PER-01</x:v>
       </x:c>
       <x:c r="B35" s="17" t="str">
-        <x:v>tau3 Banking</x:v>
+        <x:v>MyPCBench</x:v>
       </x:c>
       <x:c r="C35" s="17" t="str">
-        <x:v>Operational execution</x:v>
+        <x:v>Personal stewardship transfer</x:v>
       </x:c>
       <x:c r="D35" s="18" t="n">
-        <x:v>46235</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="E35" s="17" t="str">
-        <x:v>2026-Q3</x:v>
+        <x:v>2026-Q1</x:v>
       </x:c>
       <x:c r="F35" s="17" t="n">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G35" s="24" t="n">
-        <x:v>0.552</x:v>
+        <x:v>0.582</x:v>
       </x:c>
       <x:c r="H35" s="17" t="str">
-        <x:v>Qwen 3.8 Max</x:v>
+        <x:v>Claude Opus 4.6</x:v>
       </x:c>
       <x:c r="I35" s="17" t="str">
-        <x:v>tau3 Banking strict success</x:v>
+        <x:v>Perfect task success rate</x:v>
       </x:c>
       <x:c r="J35" s="17" t="str">
-        <x:v>https://taubench.com/leaderboard/</x:v>
+        <x:v>https://mypcbench.com/</x:v>
       </x:c>
       <x:c r="K35" s="17" t="str">
-        <x:v>Current quarter frontier.</x:v>
+        <x:v>Current published frontier; newer models may be missing.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="17" t="str">
-        <x:v>PER-01</x:v>
+        <x:v>PER-02</x:v>
       </x:c>
       <x:c r="B36" s="17" t="str">
-        <x:v>MyPCBench</x:v>
+        <x:v>pi-Bench</x:v>
       </x:c>
       <x:c r="C36" s="17" t="str">
         <x:v>Personal stewardship transfer</x:v>
@@ -8528,159 +8517,159 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="G36" s="24" t="n">
-        <x:v>0.582</x:v>
+        <x:v>0.676</x:v>
       </x:c>
       <x:c r="H36" s="17" t="str">
         <x:v>Claude Opus 4.6</x:v>
       </x:c>
       <x:c r="I36" s="17" t="str">
-        <x:v>Perfect task success rate</x:v>
+        <x:v>Completeness checklist score</x:v>
       </x:c>
       <x:c r="J36" s="17" t="str">
-        <x:v>https://mypcbench.com/</x:v>
+        <x:v>https://arxiv.org/html/2605.14678v3</x:v>
       </x:c>
       <x:c r="K36" s="17" t="str">
-        <x:v>Current published frontier; newer models may be missing.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="15" hidden="0" customHeight="1">
+        <x:v>One comparable frontier point.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A37" s="17" t="str">
-        <x:v>PER-02</x:v>
+        <x:v>PER-03</x:v>
       </x:c>
       <x:c r="B37" s="17" t="str">
-        <x:v>pi-Bench</x:v>
+        <x:v>ClawBench</x:v>
       </x:c>
       <x:c r="C37" s="17" t="str">
         <x:v>Personal stewardship transfer</x:v>
       </x:c>
       <x:c r="D37" s="18" t="n">
-        <x:v>46058</x:v>
+        <x:v>46174</x:v>
       </x:c>
       <x:c r="E37" s="17" t="str">
-        <x:v>2026-Q1</x:v>
+        <x:v>2026-Q2</x:v>
       </x:c>
       <x:c r="F37" s="17" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G37" s="24" t="n">
-        <x:v>0.676</x:v>
+        <x:v>0.333</x:v>
       </x:c>
       <x:c r="H37" s="17" t="str">
-        <x:v>Claude Opus 4.6</x:v>
+        <x:v>Claude Sonnet 4.6</x:v>
       </x:c>
       <x:c r="I37" s="17" t="str">
-        <x:v>Completeness checklist score</x:v>
+        <x:v>ClawBench V1 six-model comparison score</x:v>
       </x:c>
       <x:c r="J37" s="17" t="str">
-        <x:v>https://arxiv.org/html/2605.14678v3</x:v>
+        <x:v>https://github.com/TIGER-AI-Lab/ClawBench</x:v>
       </x:c>
       <x:c r="K37" s="17" t="str">
-        <x:v>One comparable frontier point.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="15" hidden="0" customHeight="1">
+        <x:v>Repository headline/comparison score. Do not mix with its separate original-rubric pass-rate table.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A38" s="17" t="str">
-        <x:v>PER-03</x:v>
+        <x:v>PER-04</x:v>
       </x:c>
       <x:c r="B38" s="17" t="str">
-        <x:v>ClawBench</x:v>
+        <x:v>AssistantBench (HAL)</x:v>
       </x:c>
       <x:c r="C38" s="17" t="str">
         <x:v>Personal stewardship transfer</x:v>
       </x:c>
       <x:c r="D38" s="18" t="n">
-        <x:v>46174</x:v>
+        <x:v>45763</x:v>
       </x:c>
       <x:c r="E38" s="17" t="str">
-        <x:v>2026-Q2</x:v>
+        <x:v>2025-Q2</x:v>
       </x:c>
       <x:c r="F38" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G38" s="24" t="n">
-        <x:v>0.333</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="H38" s="17" t="str">
-        <x:v>Current top system</x:v>
+        <x:v>Browser-Use + o3 Medium</x:v>
       </x:c>
       <x:c r="I38" s="17" t="str">
-        <x:v>Standardized ClawBench score</x:v>
+        <x:v>Assistant task accuracy on current HAL 33-task configuration</x:v>
       </x:c>
       <x:c r="J38" s="17" t="str">
-        <x:v>https://github.com/TIGER-AI-Lab/ClawBench</x:v>
+        <x:v>https://hal.cs.princeton.edu/assistantbench</x:v>
       </x:c>
       <x:c r="K38" s="17" t="str">
-        <x:v>One public frontier point; pin repository version.</x:v>
+        <x:v>Verified HAL leaderboard result. Kept separate from the 2024 full-benchmark configuration and projected flat.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
       <x:c r="A39" s="17" t="str">
-        <x:v>PER-04</x:v>
+        <x:v>VAL-02</x:v>
       </x:c>
       <x:c r="B39" s="17" t="str">
-        <x:v>AssistantBench</x:v>
+        <x:v>Remote Labor Index</x:v>
       </x:c>
       <x:c r="C39" s="17" t="str">
-        <x:v>Personal stewardship transfer</x:v>
+        <x:v>Economic value &amp; governance</x:v>
       </x:c>
       <x:c r="D39" s="18" t="n">
-        <x:v>45545</x:v>
+        <x:v>45929</x:v>
       </x:c>
       <x:c r="E39" s="17" t="str">
-        <x:v>2024-Q3</x:v>
+        <x:v>2025-Q3</x:v>
       </x:c>
       <x:c r="F39" s="17" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G39" s="24" t="n">
-        <x:v>0.252</x:v>
+        <x:v>0.0208</x:v>
       </x:c>
       <x:c r="H39" s="17" t="str">
-        <x:v>Launch-paper top system</x:v>
+        <x:v>Claude Sonnet 4.5</x:v>
       </x:c>
       <x:c r="I39" s="17" t="str">
-        <x:v>Assistant task accuracy</x:v>
+        <x:v>Strict end-to-end automation rate</x:v>
       </x:c>
       <x:c r="J39" s="17" t="str">
-        <x:v>https://assistantbench.github.io/</x:v>
+        <x:v>https://www.remotelabor.ai/</x:v>
       </x:c>
       <x:c r="K39" s="17" t="str">
-        <x:v>Original benchmark configuration.</x:v>
+        <x:v>Quarter frontier.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
       <x:c r="A40" s="17" t="str">
-        <x:v>PER-04</x:v>
+        <x:v>VAL-02</x:v>
       </x:c>
       <x:c r="B40" s="17" t="str">
-        <x:v>AssistantBench</x:v>
+        <x:v>Remote Labor Index</x:v>
       </x:c>
       <x:c r="C40" s="17" t="str">
-        <x:v>Personal stewardship transfer</x:v>
+        <x:v>Economic value &amp; governance</x:v>
       </x:c>
       <x:c r="D40" s="18" t="n">
-        <x:v>45876</x:v>
+        <x:v>45985</x:v>
       </x:c>
       <x:c r="E40" s="17" t="str">
-        <x:v>2025-Q3</x:v>
+        <x:v>2025-Q4</x:v>
       </x:c>
       <x:c r="F40" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G40" s="24" t="n">
-        <x:v>0.367</x:v>
+        <x:v>0.0375</x:v>
       </x:c>
       <x:c r="H40" s="17" t="str">
-        <x:v>GPT-5</x:v>
+        <x:v>Claude Opus 4.5</x:v>
       </x:c>
       <x:c r="I40" s="17" t="str">
-        <x:v>Assistant task accuracy</x:v>
+        <x:v>Strict end-to-end automation rate</x:v>
       </x:c>
       <x:c r="J40" s="17" t="str">
-        <x:v>https://hal.cs.princeton.edu/assistantbench</x:v>
+        <x:v>https://www.remotelabor.ai/</x:v>
       </x:c>
       <x:c r="K40" s="17" t="str">
-        <x:v>Updated HAL leaderboard/configuration; system-level trend only.</x:v>
+        <x:v>Quarter frontier.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="15" hidden="0" customHeight="1">
@@ -8694,19 +8683,19 @@
         <x:v>Economic value &amp; governance</x:v>
       </x:c>
       <x:c r="D41" s="18" t="n">
-        <x:v>45929</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="E41" s="17" t="str">
-        <x:v>2025-Q3</x:v>
+        <x:v>2026-Q1</x:v>
       </x:c>
       <x:c r="F41" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G41" s="24" t="n">
-        <x:v>0.0208</x:v>
+        <x:v>0.0417</x:v>
       </x:c>
       <x:c r="H41" s="17" t="str">
-        <x:v>Claude Sonnet 4.5</x:v>
+        <x:v>Claude Opus 4.6</x:v>
       </x:c>
       <x:c r="I41" s="17" t="str">
         <x:v>Strict end-to-end automation rate</x:v>
@@ -8729,19 +8718,19 @@
         <x:v>Economic value &amp; governance</x:v>
       </x:c>
       <x:c r="D42" s="18" t="n">
-        <x:v>45985</x:v>
+        <x:v>46182</x:v>
       </x:c>
       <x:c r="E42" s="17" t="str">
-        <x:v>2025-Q4</x:v>
+        <x:v>2026-Q2</x:v>
       </x:c>
       <x:c r="F42" s="17" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G42" s="24" t="n">
-        <x:v>0.0375</x:v>
+        <x:v>0.158</x:v>
       </x:c>
       <x:c r="H42" s="17" t="str">
-        <x:v>Claude Opus 4.5</x:v>
+        <x:v>Claude Fable 5</x:v>
       </x:c>
       <x:c r="I42" s="17" t="str">
         <x:v>Strict end-to-end automation rate</x:v>
@@ -8750,15 +8739,15 @@
         <x:v>https://www.remotelabor.ai/</x:v>
       </x:c>
       <x:c r="K42" s="17" t="str">
-        <x:v>Quarter frontier.</x:v>
+        <x:v>Current frontier; large quarter jump merits caution.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
       <x:c r="A43" s="17" t="str">
-        <x:v>VAL-02</x:v>
+        <x:v>VAL-04</x:v>
       </x:c>
       <x:c r="B43" s="17" t="str">
-        <x:v>Remote Labor Index</x:v>
+        <x:v>Claw-Eval</x:v>
       </x:c>
       <x:c r="C43" s="17" t="str">
         <x:v>Economic value &amp; governance</x:v>
@@ -8773,88 +8762,18 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="G43" s="24" t="n">
-        <x:v>0.0417</x:v>
+        <x:v>0.704</x:v>
       </x:c>
       <x:c r="H43" s="17" t="str">
         <x:v>Claude Opus 4.6</x:v>
       </x:c>
       <x:c r="I43" s="17" t="str">
-        <x:v>Strict end-to-end automation rate</x:v>
+        <x:v>Pass^3 governed-agent score</x:v>
       </x:c>
       <x:c r="J43" s="17" t="str">
-        <x:v>https://www.remotelabor.ai/</x:v>
+        <x:v>https://github.com/claw-eval/claw-eval</x:v>
       </x:c>
       <x:c r="K43" s="17" t="str">
-        <x:v>Quarter frontier.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="15" hidden="0" customHeight="1">
-      <x:c r="A44" s="17" t="str">
-        <x:v>VAL-02</x:v>
-      </x:c>
-      <x:c r="B44" s="17" t="str">
-        <x:v>Remote Labor Index</x:v>
-      </x:c>
-      <x:c r="C44" s="17" t="str">
-        <x:v>Economic value &amp; governance</x:v>
-      </x:c>
-      <x:c r="D44" s="18" t="n">
-        <x:v>46182</x:v>
-      </x:c>
-      <x:c r="E44" s="17" t="str">
-        <x:v>2026-Q2</x:v>
-      </x:c>
-      <x:c r="F44" s="17" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G44" s="24" t="n">
-        <x:v>0.158</x:v>
-      </x:c>
-      <x:c r="H44" s="17" t="str">
-        <x:v>Claude Fable 5</x:v>
-      </x:c>
-      <x:c r="I44" s="17" t="str">
-        <x:v>Strict end-to-end automation rate</x:v>
-      </x:c>
-      <x:c r="J44" s="17" t="str">
-        <x:v>https://www.remotelabor.ai/</x:v>
-      </x:c>
-      <x:c r="K44" s="17" t="str">
-        <x:v>Current frontier; large quarter jump merits caution.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="15" hidden="0" customHeight="1">
-      <x:c r="A45" s="17" t="str">
-        <x:v>VAL-04</x:v>
-      </x:c>
-      <x:c r="B45" s="17" t="str">
-        <x:v>Claw-Eval</x:v>
-      </x:c>
-      <x:c r="C45" s="17" t="str">
-        <x:v>Economic value &amp; governance</x:v>
-      </x:c>
-      <x:c r="D45" s="18" t="n">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="E45" s="17" t="str">
-        <x:v>2026-Q1</x:v>
-      </x:c>
-      <x:c r="F45" s="17" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G45" s="24" t="n">
-        <x:v>0.704</x:v>
-      </x:c>
-      <x:c r="H45" s="17" t="str">
-        <x:v>Claude Opus 4.6</x:v>
-      </x:c>
-      <x:c r="I45" s="17" t="str">
-        <x:v>Pass^3 governed-agent score</x:v>
-      </x:c>
-      <x:c r="J45" s="17" t="str">
-        <x:v>https://github.com/claw-eval/claw-eval</x:v>
-      </x:c>
-      <x:c r="K45" s="17" t="str">
         <x:v>One current frontier point.</x:v>
       </x:c>
     </x:row>
@@ -8864,18 +8783,18 @@
     <x:mergeCell ref="A3:K3"/>
   </x:mergeCells>
   <x:dataValidations count="2">
-    <x:dataValidation operator="between" sqref="F6:F45">
+    <x:dataValidation operator="between" sqref="F6:F43">
       <x:formula1>1</x:formula1>
       <x:formula2>20</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="G6:G45">
+    <x:dataValidation type="decimal" operator="between" sqref="G6:G43">
       <x:formula1>0</x:formula1>
       <x:formula2>1</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8918cccbdbf4e71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f0c1b5e2b4d484e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9128,7 +9047,7 @@
         <x:v>Ten-run model mean divided by the strongest published expert-designed strategy outcome.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
+    <x:row r="10" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A10" s="17" t="str">
         <x:v>DES-05</x:v>
       </x:c>
@@ -9139,10 +9058,10 @@
         <x:v>EnterpriseArena</x:v>
       </x:c>
       <x:c r="D10" s="17" t="str">
-        <x:v>Best-model full-horizon survival rate</x:v>
+        <x:v>Best-system full-horizon survival rate</x:v>
       </x:c>
       <x:c r="E10" s="17" t="str">
-        <x:v>Already a 0–100% rate; use frontier survival</x:v>
+        <x:v>Already a 0–100% rate; use the best published full-survival result</x:v>
       </x:c>
       <x:c r="F10" s="17" t="str">
         <x:v>Graded</x:v>
@@ -9151,10 +9070,10 @@
         <x:v>2026-Q1</x:v>
       </x:c>
       <x:c r="H10" s="17" t="str">
-        <x:v>https://arxiv.org/abs/2603.23638</x:v>
+        <x:v>https://arxiv.org/html/2603.23638v2</x:v>
       </x:c>
       <x:c r="I10" s="17" t="str">
-        <x:v>132-month CFO simulator; current point has limited-run uncertainty.</x:v>
+        <x:v>132-month CFO simulator; only five seeds per system and the best published result is a tie.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -9215,7 +9134,7 @@
         <x:v>Three runs per model-framework pairing; human reference is three non-expert participants.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
+    <x:row r="13" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A13" s="17" t="str">
         <x:v>OPS-01</x:v>
       </x:c>
@@ -9229,7 +9148,7 @@
         <x:v>Public 600-task pass rate, max reasoning</x:v>
       </x:c>
       <x:c r="E13" s="17" t="str">
-        <x:v>Already a 0–100% pass rate; compare within the public task version</x:v>
+        <x:v>Already a 0–100% pass rate; compare only within the public 600-task version</x:v>
       </x:c>
       <x:c r="F13" s="17" t="str">
         <x:v>Graded</x:v>
@@ -9241,10 +9160,10 @@
         <x:v>https://github.com/zapier/AutomationBench</x:v>
       </x:c>
       <x:c r="I13" s="17" t="str">
-        <x:v>Private leaderboard differs; this report uses the public 600-task table.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
+        <x:v>Pinned to the current public 600-task table after the July 2026 stricter-classifier rescore; the private leaderboard is a different evaluation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A14" s="17" t="str">
         <x:v>OPS-02</x:v>
       </x:c>
@@ -9252,7 +9171,7 @@
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="C14" s="17" t="str">
-        <x:v>EnterpriseOps-Gym</x:v>
+        <x:v>EnterpriseOps-Gym-AA</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
         <x:v>Strict task success across enterprise workflows</x:v>
@@ -9267,10 +9186,10 @@
         <x:v>2025-Q2</x:v>
       </x:c>
       <x:c r="H14" s="17" t="str">
-        <x:v>https://github.com/ServiceNow/EnterpriseOps-Gym</x:v>
+        <x:v>https://artificialanalysis.ai/evaluations/enterprise-ops-gym-aa</x:v>
       </x:c>
       <x:c r="I14" s="17" t="str">
-        <x:v>Stateful planning, policy, side effects, and safe refusal.</x:v>
+        <x:v>Artificial Analysis implementation using the Stirrup harness, ServiceNow dataset, oracle tool mode, and three repeats per task.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -9505,7 +9424,7 @@
         <x:v>Personal-computing workflows scored for completion.</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="15" hidden="0" customHeight="1">
+    <x:row r="23" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A23" s="17" t="str">
         <x:v>PER-03</x:v>
       </x:c>
@@ -9516,10 +9435,10 @@
         <x:v>ClawBench</x:v>
       </x:c>
       <x:c r="D23" s="17" t="str">
-        <x:v>Standardized personal-agent task score</x:v>
+        <x:v>V1 six-model comparison score</x:v>
       </x:c>
       <x:c r="E23" s="17" t="str">
-        <x:v>Already a 0–100% score; pin benchmark repo/version</x:v>
+        <x:v>Already a 0–100% score; pin benchmark repo/version and scoring table</x:v>
       </x:c>
       <x:c r="F23" s="17" t="str">
         <x:v>Graded</x:v>
@@ -9531,7 +9450,7 @@
         <x:v>https://github.com/TIGER-AI-Lab/ClawBench</x:v>
       </x:c>
       <x:c r="I23" s="17" t="str">
-        <x:v>Personal-agent and computer-use signal; one public frontier point.</x:v>
+        <x:v>Uses the repository's 33.3 headline/comparison score, not the separately reported 61.4% original-rubric pass rate.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -9542,25 +9461,25 @@
         <x:v>Personal stewardship transfer</x:v>
       </x:c>
       <x:c r="C24" s="17" t="str">
-        <x:v>AssistantBench</x:v>
+        <x:v>AssistantBench (HAL)</x:v>
       </x:c>
       <x:c r="D24" s="17" t="str">
-        <x:v>Assistant task accuracy</x:v>
+        <x:v>Assistant task accuracy on the current HAL configuration</x:v>
       </x:c>
       <x:c r="E24" s="17" t="str">
-        <x:v>Already a 0–100% score; later HAL result marked as updated configuration</x:v>
+        <x:v>Already a 0–100% score; do not splice the 33-task HAL configuration to the 2024 full benchmark</x:v>
       </x:c>
       <x:c r="F24" s="17" t="str">
         <x:v>Graded</x:v>
       </x:c>
       <x:c r="G24" s="17" t="str">
-        <x:v>2024-Q3</x:v>
+        <x:v>2025-Q2</x:v>
       </x:c>
       <x:c r="H24" s="17" t="str">
-        <x:v>https://assistantbench.github.io/</x:v>
+        <x:v>https://hal.cs.princeton.edu/assistantbench</x:v>
       </x:c>
       <x:c r="I24" s="17" t="str">
-        <x:v>Realistic web research and personal-assistant tasks.</x:v>
+        <x:v>Current HAL result covers 33 tasks and is treated as a one-point series, so it projects flat.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -9691,7 +9610,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c2c60fdc13d47b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c7b77da95ff4712"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10333,7 +10252,7 @@
       </x:c>
       <x:c r="J10" s="24" t="n">
         <x:f>IF(G10="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A10,'Observations'!$F$6:$F$500,G10))</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="K10" s="25" t="str">
         <x:f>IF(H10="","",IF(H10&gt;=1,30,-LN(1-H10)/LN(2)))</x:f>
@@ -10343,7 +10262,7 @@
       </x:c>
       <x:c r="M10" s="25" t="n">
         <x:f>IF(J10="","",IF(J10&gt;=1,30,-LN(1-J10)/LN(2)))</x:f>
-        <x:v>2.3219280948873626</x:v>
+        <x:v>1.3219280948873622</x:v>
       </x:c>
       <x:c r="N10" s="25" t="n">
         <x:f>IF(D10&lt;2,0,(M10-L10)/(G10-F10))</x:f>
@@ -10363,15 +10282,15 @@
       </x:c>
       <x:c r="R10" s="24" t="n">
         <x:f>IF(D10=0,"",J10)</x:f>
-        <x:v>0.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="S10" s="17" t="str">
         <x:f>IF(R10="","N/A",IF(R10&gt;='Methodology'!$G$7,"A",IF(R10&gt;='Methodology'!$G$8,"B",IF(R10&gt;='Methodology'!$G$9,"C",IF(R10&gt;='Methodology'!$G$10,"D","F")))))</x:f>
-        <x:v>B</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="T10" s="26" t="n">
         <x:f>IF(R10="","",IF(R10&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R10&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R10&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R10&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U10" s="27" t="n">
         <x:f>MIN(D10,3)</x:f>
@@ -10544,44 +10463,41 @@
       </x:c>
       <x:c r="D13" s="17" t="n">
         <x:f>COUNTIF('Observations'!$A$6:$A$500,A13)</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E13" s="17" t="str">
         <x:f>IF(D13&lt;3,"",MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,A13,'Observations'!$F$6:$F$500,"&lt;"&amp;F13))</x:f>
       </x:c>
-      <x:c r="F13" s="17" t="n">
+      <x:c r="F13" s="17" t="str">
         <x:f>IF(D13&lt;2,"",MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,A13,'Observations'!$F$6:$F$500,"&lt;"&amp;G13))</x:f>
-        <x:v>10</x:v>
       </x:c>
       <x:c r="G13" s="17" t="n">
         <x:f>IF(D13=0,"",MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,A13))</x:f>
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H13" s="24" t="str">
         <x:f>IF(E13="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A13,'Observations'!$F$6:$F$500,E13))</x:f>
       </x:c>
-      <x:c r="I13" s="24" t="n">
+      <x:c r="I13" s="24" t="str">
         <x:f>IF(F13="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A13,'Observations'!$F$6:$F$500,F13))</x:f>
-        <x:v>0.4617</x:v>
       </x:c>
       <x:c r="J13" s="24" t="n">
         <x:f>IF(G13="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A13,'Observations'!$F$6:$F$500,G13))</x:f>
-        <x:v>0.503</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="K13" s="25" t="str">
         <x:f>IF(H13="","",IF(H13&gt;=1,30,-LN(1-H13)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L13" s="25" t="n">
+      <x:c r="L13" s="25" t="str">
         <x:f>IF(I13="","",IF(I13&gt;=1,30,-LN(1-I13)/LN(2)))</x:f>
-        <x:v>0.8935176695300188</x:v>
       </x:c>
       <x:c r="M13" s="25" t="n">
         <x:f>IF(J13="","",IF(J13&gt;=1,30,-LN(1-J13)/LN(2)))</x:f>
-        <x:v>1.008682243099801</x:v>
+        <x:v>0.5213905315954884</x:v>
       </x:c>
       <x:c r="N13" s="25" t="n">
         <x:f>IF(D13&lt;2,0,(M13-L13)/(G13-F13))</x:f>
-        <x:v>0.11516457356978227</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="O13" s="25" t="n">
         <x:f>IF(D13&lt;3,0,(L13-K13)/(F13-E13))</x:f>
@@ -10593,11 +10509,11 @@
       </x:c>
       <x:c r="Q13" s="17" t="str">
         <x:f>IF(D13=0,"Ungraded — no normalized observation",IF(D13=1,"Flat — one observation",IF(D13=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Constant velocity — two observations</x:v>
+        <x:v>Flat — one observation</x:v>
       </x:c>
       <x:c r="R13" s="24" t="n">
         <x:f>IF(D13=0,"",J13)</x:f>
-        <x:v>0.503</x:v>
+        <x:v>0.3033</x:v>
       </x:c>
       <x:c r="S13" s="17" t="str">
         <x:f>IF(R13="","N/A",IF(R13&gt;='Methodology'!$G$7,"A",IF(R13&gt;='Methodology'!$G$8,"B",IF(R13&gt;='Methodology'!$G$9,"C",IF(R13&gt;='Methodology'!$G$10,"D","F")))))</x:f>
@@ -10609,7 +10525,7 @@
       </x:c>
       <x:c r="U13" s="27" t="n">
         <x:f>MIN(D13,3)</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -10617,7 +10533,7 @@
         <x:v>OPS-02</x:v>
       </x:c>
       <x:c r="B14" s="17" t="str">
-        <x:v>EnterpriseOps-Gym</x:v>
+        <x:v>EnterpriseOps-Gym-AA</x:v>
       </x:c>
       <x:c r="C14" s="17" t="str">
         <x:v>Operational execution</x:v>
@@ -11406,51 +11322,48 @@
         <x:v>PER-04</x:v>
       </x:c>
       <x:c r="B24" s="17" t="str">
-        <x:v>AssistantBench</x:v>
+        <x:v>AssistantBench (HAL)</x:v>
       </x:c>
       <x:c r="C24" s="17" t="str">
         <x:v>Personal stewardship transfer</x:v>
       </x:c>
       <x:c r="D24" s="17" t="n">
         <x:f>COUNTIF('Observations'!$A$6:$A$500,A24)</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E24" s="17" t="str">
         <x:f>IF(D24&lt;3,"",MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,A24,'Observations'!$F$6:$F$500,"&lt;"&amp;F24))</x:f>
       </x:c>
-      <x:c r="F24" s="17" t="n">
+      <x:c r="F24" s="17" t="str">
         <x:f>IF(D24&lt;2,"",MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,A24,'Observations'!$F$6:$F$500,"&lt;"&amp;G24))</x:f>
-        <x:v>3</x:v>
       </x:c>
       <x:c r="G24" s="17" t="n">
         <x:f>IF(D24=0,"",MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,A24))</x:f>
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H24" s="24" t="str">
         <x:f>IF(E24="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A24,'Observations'!$F$6:$F$500,E24))</x:f>
       </x:c>
-      <x:c r="I24" s="24" t="n">
+      <x:c r="I24" s="24" t="str">
         <x:f>IF(F24="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A24,'Observations'!$F$6:$F$500,F24))</x:f>
-        <x:v>0.252</x:v>
       </x:c>
       <x:c r="J24" s="24" t="n">
         <x:f>IF(G24="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A24,'Observations'!$F$6:$F$500,G24))</x:f>
-        <x:v>0.367</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="K24" s="25" t="str">
         <x:f>IF(H24="","",IF(H24&gt;=1,30,-LN(1-H24)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L24" s="25" t="n">
+      <x:c r="L24" s="25" t="str">
         <x:f>IF(I24="","",IF(I24&gt;=1,30,-LN(1-I24)/LN(2)))</x:f>
-        <x:v>0.41888982477445036</x:v>
       </x:c>
       <x:c r="M24" s="25" t="n">
         <x:f>IF(J24="","",IF(J24&gt;=1,30,-LN(1-J24)/LN(2)))</x:f>
-        <x:v>0.6597225952337457</x:v>
+        <x:v>0.7086321957146922</x:v>
       </x:c>
       <x:c r="N24" s="25" t="n">
         <x:f>IF(D24&lt;2,0,(M24-L24)/(G24-F24))</x:f>
-        <x:v>0.060208192614823824</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="O24" s="25" t="n">
         <x:f>IF(D24&lt;3,0,(L24-K24)/(F24-E24))</x:f>
@@ -11462,11 +11375,11 @@
       </x:c>
       <x:c r="Q24" s="17" t="str">
         <x:f>IF(D24=0,"Ungraded — no normalized observation",IF(D24=1,"Flat — one observation",IF(D24=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Constant velocity — two observations</x:v>
+        <x:v>Flat — one observation</x:v>
       </x:c>
       <x:c r="R24" s="24" t="n">
         <x:f>IF(D24=0,"",J24)</x:f>
-        <x:v>0.367</x:v>
+        <x:v>0.3881</x:v>
       </x:c>
       <x:c r="S24" s="17" t="str">
         <x:f>IF(R24="","N/A",IF(R24&gt;='Methodology'!$G$7,"A",IF(R24&gt;='Methodology'!$G$8,"B",IF(R24&gt;='Methodology'!$G$9,"C",IF(R24&gt;='Methodology'!$G$10,"D","F")))))</x:f>
@@ -11478,7 +11391,7 @@
       </x:c>
       <x:c r="U24" s="27" t="n">
         <x:f>MIN(D24,3)</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -11792,7 +11705,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0e49ec014fe4ca4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3940efb08a1b4cf0"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/data/reports/personal-ai-four-year-capability-report-card.xlsx
+++ b/data/reports/personal-ai-four-year-capability-report-card.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf406edfcae7447e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report Card" sheetId="2" r:id="Re0f20c91a52a4356"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="R63887f00eaca4d6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog" sheetId="4" r:id="R8a0855d5ac824b1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="5" r:id="R5ec971cd060b4aa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" r:id="R97928a25773440d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb476777359f446ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report Card" sheetId="2" r:id="R5556f148f8e84843"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="R01f1ad4543ab448c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog" sheetId="4" r:id="Rcb18794c03764b5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="5" r:id="Rbe2d11aea2f5487f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" r:id="Rd45443569aed4bac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -657,7 +657,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R531620a691b843e4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb88b64215b414f32"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1182,7 +1182,7 @@
       </x:c>
       <x:c r="G6" s="55" t="n">
         <x:f>F17</x:f>
-        <x:v>0.6045222756154646</x:v>
+        <x:v>0.9993730805998696</x:v>
       </x:c>
       <x:c r="J6" s="56" t="n">
         <x:f>H17</x:f>
@@ -1293,7 +1293,7 @@
       </x:c>
       <x:c r="F13" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A13,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.3879915646798451</x:v>
+        <x:v>0.9992876406259662</x:v>
       </x:c>
       <x:c r="G13" s="62" t="n">
         <x:f>IFERROR(AVERAGEIFS('Model'!$N$6:$N$28,'Model'!$C$6:$C$28,A13,'Model'!$D$6:$D$28,"&gt;=2"),"")</x:f>
@@ -1338,7 +1338,7 @@
       </x:c>
       <x:c r="F14" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A14,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.6964852462818304</x:v>
+        <x:v>0.9994304467495118</x:v>
       </x:c>
       <x:c r="G14" s="62" t="n">
         <x:f>IFERROR(AVERAGEIFS('Model'!$N$6:$N$28,'Model'!$C$6:$C$28,A14,'Model'!$D$6:$D$28,"&gt;=2"),"")</x:f>
@@ -1383,7 +1383,7 @@
       </x:c>
       <x:c r="F15" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A15,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.49477499999999996</x:v>
+        <x:v>0.9994171172882931</x:v>
       </x:c>
       <x:c r="G15" s="62" t="str">
         <x:f>IFERROR(AVERAGEIFS('Model'!$N$6:$N$28,'Model'!$C$6:$C$28,A15,'Model'!$D$6:$D$28,"&gt;=2"),"")</x:f>
@@ -1426,7 +1426,7 @@
       </x:c>
       <x:c r="F16" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A16,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.8511685682823786</x:v>
+        <x:v>0.9993435394864443</x:v>
       </x:c>
       <x:c r="G16" s="62" t="n">
         <x:f>IFERROR(AVERAGEIFS('Model'!$N$6:$N$28,'Model'!$C$6:$C$28,A16,'Model'!$D$6:$D$28,"&gt;=2"),"")</x:f>
@@ -1471,7 +1471,7 @@
       </x:c>
       <x:c r="F17" s="59" t="n">
         <x:f>IFERROR(SUMPRODUCT(F13:F16,K13:K16)/SUM(K13:K16),"")</x:f>
-        <x:v>0.6045222756154646</x:v>
+        <x:v>0.9993730805998696</x:v>
       </x:c>
       <x:c r="G17" s="63" t="n">
         <x:f>IFERROR(SUMPRODUCT(G13:G16,K13:K16)/SUM(K13:K16),"")</x:f>
@@ -1820,23 +1820,23 @@
       </x:c>
       <x:c r="B33" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AA$6:$AA$28),"")</x:f>
-        <x:v>0.38316394903962403</x:v>
+        <x:v>0.4424327894136026</x:v>
       </x:c>
       <x:c r="C33" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AA$6:$AA$28),"")</x:f>
-        <x:v>0.5516288014851415</x:v>
+        <x:v>0.5542078496744175</x:v>
       </x:c>
       <x:c r="D33" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AA$6:$AA$28),"")</x:f>
-        <x:v>0.49477499999999996</x:v>
+        <x:v>0.5437748143537641</x:v>
       </x:c>
       <x:c r="E33" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AA$6:$AA$28),"")</x:f>
-        <x:v>0.5045057474556296</x:v>
+        <x:v>0.4861851043936697</x:v>
       </x:c>
       <x:c r="F33" s="19" t="n">
         <x:f>IFERROR((IF(B33="",0,B33*$K$13)+IF(C33="",0,C33*$K$14)+IF(D33="",0,D33*$K$15)+IF(E33="",0,E33*$K$16))/(IF(B33="",0,$K$13)+IF(C33="",0,$K$14)+IF(D33="",0,$K$15)+IF(E33="",0,$K$16)),"")</x:f>
-        <x:v>0.48664599978661627</x:v>
+        <x:v>0.5093070801978395</x:v>
       </x:c>
       <x:c r="H33" s="41" t="str">
         <x:v>Carried</x:v>
@@ -1860,23 +1860,23 @@
       </x:c>
       <x:c r="B34" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AC$6:$AC$28),"")</x:f>
-        <x:v>0.38377665177872605</x:v>
+        <x:v>0.5201235754313581</x:v>
       </x:c>
       <x:c r="C34" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AC$6:$AC$28),"")</x:f>
-        <x:v>0.5936525123660638</x:v>
+        <x:v>0.6163240249116865</x:v>
       </x:c>
       <x:c r="D34" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AC$6:$AC$28),"")</x:f>
-        <x:v>0.49477499999999996</x:v>
+        <x:v>0.6073447169609767</x:v>
       </x:c>
       <x:c r="E34" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AC$6:$AC$28),"")</x:f>
-        <x:v>0.5988820122205774</x:v>
+        <x:v>0.5577794922080178</x:v>
       </x:c>
       <x:c r="F34" s="19" t="n">
         <x:f>IFERROR((IF(B34="",0,B34*$K$13)+IF(C34="",0,C34*$K$14)+IF(D34="",0,D34*$K$15)+IF(E34="",0,E34*$K$16))/(IF(B34="",0,$K$13)+IF(C34="",0,$K$14)+IF(D34="",0,$K$15)+IF(E34="",0,$K$16)),"")</x:f>
-        <x:v>0.5194627563134246</x:v>
+        <x:v>0.577679677992254</x:v>
       </x:c>
       <x:c r="H34" s="43" t="str">
         <x:v>Projected</x:v>
@@ -1900,23 +1900,23 @@
       </x:c>
       <x:c r="B35" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AE$6:$AE$28),"")</x:f>
-        <x:v>0.3843866883590058</x:v>
+        <x:v>0.6151637853497977</x:v>
       </x:c>
       <x:c r="C35" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AE$6:$AE$28),"")</x:f>
-        <x:v>0.6285892778775987</x:v>
+        <x:v>0.6923115986830656</x:v>
       </x:c>
       <x:c r="D35" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AE$6:$AE$28),"")</x:f>
-        <x:v>0.49477499999999996</x:v>
+        <x:v>0.6851106554714131</x:v>
       </x:c>
       <x:c r="E35" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AE$6:$AE$28),"")</x:f>
-        <x:v>0.6892922475171135</x:v>
+        <x:v>0.6453618941327806</x:v>
       </x:c>
       <x:c r="F35" s="19" t="n">
         <x:f>IFERROR((IF(B35="",0,B35*$K$13)+IF(C35="",0,C35*$K$14)+IF(D35="",0,D35*$K$15)+IF(E35="",0,E35*$K$16))/(IF(B35="",0,$K$13)+IF(C35="",0,$K$14)+IF(D35="",0,$K$15)+IF(E35="",0,$K$16)),"")</x:f>
-        <x:v>0.5490255054101908</x:v>
+        <x:v>0.6613208197560287</x:v>
       </x:c>
       <x:c r="H35" s="17" t="str">
         <x:v>Δ score</x:v>
@@ -1940,23 +1940,23 @@
       </x:c>
       <x:c r="B36" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AG$6:$AG$28),"")</x:f>
-        <x:v>0.384994070382179</x:v>
+        <x:v>0.7218444199987707</x:v>
       </x:c>
       <x:c r="C36" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AG$6:$AG$28),"")</x:f>
-        <x:v>0.6552135427322853</x:v>
+        <x:v>0.7776060503927473</x:v>
       </x:c>
       <x:c r="D36" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AG$6:$AG$28),"")</x:f>
-        <x:v>0.49477499999999996</x:v>
+        <x:v>0.7724012841588479</x:v>
       </x:c>
       <x:c r="E36" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AG$6:$AG$28),"")</x:f>
-        <x:v>0.7596996524545245</x:v>
+        <x:v>0.7436712963261605</x:v>
       </x:c>
       <x:c r="F36" s="19" t="n">
         <x:f>IFERROR((IF(B36="",0,B36*$K$13)+IF(C36="",0,C36*$K$14)+IF(D36="",0,D36*$K$15)+IF(E36="",0,E36*$K$16))/(IF(B36="",0,$K$13)+IF(C36="",0,$K$14)+IF(D36="",0,$K$15)+IF(E36="",0,$K$16)),"")</x:f>
-        <x:v>0.571877199174807</x:v>
+        <x:v>0.7552062403983184</x:v>
       </x:c>
       <x:c r="H36" s="17" t="str">
         <x:v>Gap velocity</x:v>
@@ -1980,23 +1980,23 @@
       </x:c>
       <x:c r="B37" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AI$6:$AI$28),"")</x:f>
-        <x:v>0.3855988093994764</x:v>
+        <x:v>0.8274510558805968</x:v>
       </x:c>
       <x:c r="C37" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AI$6:$AI$28),"")</x:f>
-        <x:v>0.6728198020609567</x:v>
+        <x:v>0.8620418070235887</x:v>
       </x:c>
       <x:c r="D37" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AI$6:$AI$28),"")</x:f>
-        <x:v>0.49477499999999996</x:v>
+        <x:v>0.8588131214151832</x:v>
       </x:c>
       <x:c r="E37" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AI$6:$AI$28),"")</x:f>
-        <x:v>0.8057929460443367</x:v>
+        <x:v>0.8409909764664045</x:v>
       </x:c>
       <x:c r="F37" s="19" t="n">
         <x:f>IFERROR((IF(B37="",0,B37*$K$13)+IF(C37="",0,C37*$K$14)+IF(D37="",0,D37*$K$15)+IF(E37="",0,E37*$K$16))/(IF(B37="",0,$K$13)+IF(C37="",0,$K$14)+IF(D37="",0,$K$15)+IF(E37="",0,$K$16)),"")</x:f>
-        <x:v>0.5869555183395334</x:v>
+        <x:v>0.8481464770683281</x:v>
       </x:c>
       <x:c r="H37" s="17" t="str">
         <x:v>Gap acceleration</x:v>
@@ -2020,23 +2020,23 @@
       </x:c>
       <x:c r="B38" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AK$6:$AK$28),"")</x:f>
-        <x:v>0.38620091691186426</x:v>
+        <x:v>0.9145150572651771</x:v>
       </x:c>
       <x:c r="C38" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AK$6:$AK$28),"")</x:f>
-        <x:v>0.6836043273990166</x:v>
+        <x:v>0.9316521565137644</x:v>
       </x:c>
       <x:c r="D38" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AK$6:$AK$28),"")</x:f>
-        <x:v>0.49477499999999996</x:v>
+        <x:v>0.9300525871524342</x:v>
       </x:c>
       <x:c r="E38" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AK$6:$AK$28),"")</x:f>
-        <x:v>0.8315862366021204</x:v>
+        <x:v>0.9212230631693503</x:v>
       </x:c>
       <x:c r="F38" s="19" t="n">
         <x:f>IFERROR((IF(B38="",0,B38*$K$13)+IF(C38="",0,C38*$K$14)+IF(D38="",0,D38*$K$15)+IF(E38="",0,E38*$K$16))/(IF(B38="",0,$K$13)+IF(C38="",0,$K$14)+IF(D38="",0,$K$15)+IF(E38="",0,$K$16)),"")</x:f>
-        <x:v>0.5957937945439886</x:v>
+        <x:v>0.9247680721655871</x:v>
       </x:c>
       <x:c r="H38" s="17" t="str">
         <x:v>Acceleration coverage</x:v>
@@ -2060,23 +2060,23 @@
       </x:c>
       <x:c r="B39" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AM$6:$AM$28),"")</x:f>
-        <x:v>0.3868004043702625</x:v>
+        <x:v>0.9695743097262906</x:v>
       </x:c>
       <x:c r="C39" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AM$6:$AM$28),"")</x:f>
-        <x:v>0.6900065362516443</x:v>
+        <x:v>0.9756737239300851</x:v>
       </x:c>
       <x:c r="D39" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AM$6:$AM$28),"")</x:f>
-        <x:v>0.49477499999999996</x:v>
+        <x:v>0.9751044072714762</x:v>
       </x:c>
       <x:c r="E39" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AM$6:$AM$28),"")</x:f>
-        <x:v>0.8440411975090854</x:v>
+        <x:v>0.9719618145132762</x:v>
       </x:c>
       <x:c r="F39" s="19" t="n">
         <x:f>IFERROR((IF(B39="",0,B39*$K$13)+IF(C39="",0,C39*$K$14)+IF(D39="",0,D39*$K$15)+IF(E39="",0,E39*$K$16))/(IF(B39="",0,$K$13)+IF(C39="",0,$K$14)+IF(D39="",0,$K$15)+IF(E39="",0,$K$16)),"")</x:f>
-        <x:v>0.6005670899547221</x:v>
+        <x:v>0.9732235495310044</x:v>
       </x:c>
       <x:c r="H39" s="17" t="str">
         <x:v>Confidence</x:v>
@@ -2100,23 +2100,23 @@
       </x:c>
       <x:c r="B40" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AO$6:$AO$28),"")</x:f>
-        <x:v>0.3873972831757628</x:v>
+        <x:v>0.9933421330022913</x:v>
       </x:c>
       <x:c r="C40" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AO$6:$AO$28),"")</x:f>
-        <x:v>0.6939103772836017</x:v>
+        <x:v>0.9946768303638789</x:v>
       </x:c>
       <x:c r="D40" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AO$6:$AO$28),"")</x:f>
-        <x:v>0.49477499999999996</x:v>
+        <x:v>0.9945522502949141</x:v>
       </x:c>
       <x:c r="E40" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AO$6:$AO$28),"")</x:f>
-        <x:v>0.8492616924053543</x:v>
+        <x:v>0.9938645760162426</x:v>
       </x:c>
       <x:c r="F40" s="19" t="n">
         <x:f>IFERROR((IF(B40="",0,B40*$K$13)+IF(C40="",0,C40*$K$14)+IF(D40="",0,D40*$K$15)+IF(E40="",0,E40*$K$16))/(IF(B40="",0,$K$13)+IF(C40="",0,$K$14)+IF(D40="",0,$K$15)+IF(E40="",0,$K$16)),"")</x:f>
-        <x:v>0.6030923469479429</x:v>
+        <x:v>0.994140673743486</x:v>
       </x:c>
       <x:c r="H40" s="17" t="str">
         <x:v>Direct stewardship</x:v>
@@ -2134,35 +2134,35 @@
       <x:c r="Q40" s="17"/>
       <x:c r="R40" s="17"/>
     </x:row>
-    <x:row r="41" ht="15" hidden="0" customHeight="1">
+    <x:row r="41" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A41" s="17" t="str">
         <x:v>2028-Q4</x:v>
       </x:c>
       <x:c r="B41" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.3879915646798451</x:v>
+        <x:v>0.9992876406259662</x:v>
       </x:c>
       <x:c r="C41" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.6964852462818304</x:v>
+        <x:v>0.9994304467495118</x:v>
       </x:c>
       <x:c r="D41" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.49477499999999996</x:v>
+        <x:v>0.9994171172882931</x:v>
       </x:c>
       <x:c r="E41" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.8511685682823786</x:v>
+        <x:v>0.9993435394864443</x:v>
       </x:c>
       <x:c r="F41" s="19" t="n">
         <x:f>IFERROR((IF(B41="",0,B41*$K$13)+IF(C41="",0,C41*$K$14)+IF(D41="",0,D41*$K$15)+IF(E41="",0,E41*$K$16))/(IF(B41="",0,$K$13)+IF(C41="",0,$K$14)+IF(D41="",0,$K$15)+IF(E41="",0,$K$16)),"")</x:f>
-        <x:v>0.6045222756154646</x:v>
+        <x:v>0.9993730805998696</x:v>
       </x:c>
       <x:c r="H41" s="17" t="str">
         <x:v>Caution</x:v>
       </x:c>
       <x:c r="I41" s="17" t="str">
-        <x:v>The composite uses continuous confidence weights. Sparse series project flat or constant velocity; projections are scenarios, not calibrated probabilities.</x:v>
+        <x:v>The composite uses continuous confidence weights. The forecast conjectures that progress raises future progress and transfers across benchmarks; confidence and acceleration coverage expose how weakly that causal feedback is presently measured.</x:v>
       </x:c>
       <x:c r="J41" s="17"/>
       <x:c r="K41" s="17"/>
@@ -2216,7 +2216,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6218106c435547f6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ea0620aef5144a1"/>
 </x:worksheet>
 </file>
 
@@ -3129,76 +3129,76 @@
         <x:v>0.0038906349206349333</x:v>
       </x:c>
       <x:c r="AA6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-MAX('Model'!$M6,'Model'!$M6+'Model'!$N6*(12-'Methodology'!$B$8)+0.5*'Model'!$P6*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.17749000000000004</x:v>
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.25726205661658574</x:v>
       </x:c>
       <x:c r="AB6" s="46" t="n">
         <x:f>IF(OR(AA6="",Y6=""),"",AA6-Y6)</x:f>
-        <x:v>2.7755575615628914e-17</x:v>
+        <x:v>0.07977205661658573</x:v>
       </x:c>
       <x:c r="AC6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-MAX('Model'!$M6,'Model'!$M6+'Model'!$N6*(13-'Methodology'!$B$8)+0.5*'Model'!$P6*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.17749000000000004</x:v>
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.3607543236133861</x:v>
       </x:c>
       <x:c r="AD6" s="46" t="n">
         <x:f>IF(OR(AC6="",AA6=""),"",AC6-AA6)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.10349226699680036</x:v>
       </x:c>
       <x:c r="AE6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-MAX('Model'!$M6,'Model'!$M6+'Model'!$N6*(14-'Methodology'!$B$8)+0.5*'Model'!$P6*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.17749000000000004</x:v>
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.4873578410248741</x:v>
       </x:c>
       <x:c r="AF6" s="46" t="n">
         <x:f>IF(OR(AE6="",AC6=""),"",AE6-AC6)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.126603517411488</x:v>
       </x:c>
       <x:c r="AG6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-MAX('Model'!$M6,'Model'!$M6+'Model'!$N6*(15-'Methodology'!$B$8)+0.5*'Model'!$P6*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.17749000000000004</x:v>
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6294676237982958</x:v>
       </x:c>
       <x:c r="AH6" s="46" t="n">
         <x:f>IF(OR(AG6="",AE6=""),"",AG6-AE6)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.14210978277342168</x:v>
       </x:c>
       <x:c r="AI6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-MAX('Model'!$M6,'Model'!$M6+'Model'!$N6*(16-'Methodology'!$B$8)+0.5*'Model'!$P6*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.17749000000000004</x:v>
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7701467276860849</x:v>
       </x:c>
       <x:c r="AJ6" s="46" t="n">
         <x:f>IF(OR(AI6="",AG6=""),"",AI6-AG6)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.14067910388778915</x:v>
       </x:c>
       <x:c r="AK6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-MAX('Model'!$M6,'Model'!$M6+'Model'!$N6*(17-'Methodology'!$B$8)+0.5*'Model'!$P6*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.17749000000000004</x:v>
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8861250996264014</x:v>
       </x:c>
       <x:c r="AL6" s="46" t="n">
         <x:f>IF(OR(AK6="",AI6=""),"",AK6-AI6)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.11597837194031646</x:v>
       </x:c>
       <x:c r="AM6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-MAX('Model'!$M6,'Model'!$M6+'Model'!$N6*(18-'Methodology'!$B$8)+0.5*'Model'!$P6*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.17749000000000004</x:v>
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9594697927158433</x:v>
       </x:c>
       <x:c r="AN6" s="46" t="n">
         <x:f>IF(OR(AM6="",AK6=""),"",AM6-AK6)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.07334469308944191</x:v>
       </x:c>
       <x:c r="AO6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-MAX('Model'!$M6,'Model'!$M6+'Model'!$N6*(19-'Methodology'!$B$8)+0.5*'Model'!$P6*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.17749000000000004</x:v>
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9911310235836901</x:v>
       </x:c>
       <x:c r="AP6" s="46" t="n">
         <x:f>IF(OR(AO6="",AM6=""),"",AO6-AM6)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.03166123086784678</x:v>
       </x:c>
       <x:c r="AQ6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-MAX('Model'!$M6,'Model'!$M6+'Model'!$N6*(20-'Methodology'!$B$8)+0.5*'Model'!$P6*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.17749000000000004</x:v>
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9990510626766174</x:v>
       </x:c>
       <x:c r="AR6" s="46" t="n">
         <x:f>IF(OR(AQ6="",AO6=""),"",AQ6-AO6)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.007920039092927267</x:v>
       </x:c>
       <x:c r="AS6" s="24" t="n">
         <x:f>IF('Model'!$D6=0,"",Y6)</x:f>
@@ -3226,7 +3226,7 @@
       </x:c>
       <x:c r="AY6" s="17" t="str">
         <x:f>'Model'!Q6</x:f>
-        <x:v>Velocity + acceleration — latest three observations</x:v>
+        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="46" hidden="0" customHeight="1">
@@ -3312,76 +3312,76 @@
         <x:v>0.004326490454545454</x:v>
       </x:c>
       <x:c r="AA7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-MAX('Model'!$M7,'Model'!$M7+'Model'!$N7*(12-'Methodology'!$B$8)+0.5*'Model'!$P7*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.014375098852413282</x:v>
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.10607715721830968</x:v>
       </x:c>
       <x:c r="AB7" s="46" t="n">
         <x:f>IF(OR(AA7="",Y7=""),"",AA7-Y7)</x:f>
-        <x:v>0.004307663852413282</x:v>
+        <x:v>0.09600972221830968</x:v>
       </x:c>
       <x:c r="AC7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-MAX('Model'!$M7,'Model'!$M7+'Model'!$N7*(13-'Methodology'!$B$8)+0.5*'Model'!$P7*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.018664018026126716</x:v>
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.23063535751472852</x:v>
       </x:c>
       <x:c r="AD7" s="46" t="n">
         <x:f>IF(OR(AC7="",AA7=""),"",AC7-AA7)</x:f>
-        <x:v>0.004288919173713435</x:v>
+        <x:v>0.12455820029641884</x:v>
       </x:c>
       <x:c r="AE7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-MAX('Model'!$M7,'Model'!$M7+'Model'!$N7*(14-'Methodology'!$B$8)+0.5*'Model'!$P7*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.022934274088085127</x:v>
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.3830091216381757</x:v>
       </x:c>
       <x:c r="AF7" s="46" t="n">
         <x:f>IF(OR(AE7="",AC7=""),"",AE7-AC7)</x:f>
-        <x:v>0.004270256061958411</x:v>
+        <x:v>0.15237376412344716</x:v>
       </x:c>
       <x:c r="AG7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-MAX('Model'!$M7,'Model'!$M7+'Model'!$N7*(15-'Methodology'!$B$8)+0.5*'Model'!$P7*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.027185948250297076</x:v>
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.5540454637768562</x:v>
       </x:c>
       <x:c r="AH7" s="46" t="n">
         <x:f>IF(OR(AG7="",AE7=""),"",AG7-AE7)</x:f>
-        <x:v>0.004251674162211949</x:v>
+        <x:v>0.17103634213868046</x:v>
       </x:c>
       <x:c r="AI7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-MAX('Model'!$M7,'Model'!$M7+'Model'!$N7*(16-'Methodology'!$B$8)+0.5*'Model'!$P7*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.031419121371379255</x:v>
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7233599112042924</x:v>
       </x:c>
       <x:c r="AJ7" s="46" t="n">
         <x:f>IF(OR(AI7="",AG7=""),"",AI7-AG7)</x:f>
-        <x:v>0.004233173121082179</x:v>
+        <x:v>0.1693144474274363</x:v>
       </x:c>
       <x:c r="AK7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-MAX('Model'!$M7,'Model'!$M7+'Model'!$N7*(17-'Methodology'!$B$8)+0.5*'Model'!$P7*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.03563387395809425</x:v>
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8629457730411109</x:v>
       </x:c>
       <x:c r="AL7" s="46" t="n">
         <x:f>IF(OR(AK7="",AI7=""),"",AK7-AI7)</x:f>
-        <x:v>0.004214752586714998</x:v>
+        <x:v>0.13958586183681843</x:v>
       </x:c>
       <x:c r="AM7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-MAX('Model'!$M7,'Model'!$M7+'Model'!$N7*(18-'Methodology'!$B$8)+0.5*'Model'!$P7*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.039830286166882</x:v>
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9512198367718484</x:v>
       </x:c>
       <x:c r="AN7" s="46" t="n">
         <x:f>IF(OR(AM7="",AK7=""),"",AM7-AK7)</x:f>
-        <x:v>0.004196412208787748</x:v>
+        <x:v>0.08827406373073754</x:v>
       </x:c>
       <x:c r="AO7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-MAX('Model'!$M7,'Model'!$M7+'Model'!$N7*(19-'Methodology'!$B$8)+0.5*'Model'!$P7*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.04400843780538366</x:v>
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9893257363767952</x:v>
       </x:c>
       <x:c r="AP7" s="46" t="n">
         <x:f>IF(OR(AO7="",AM7=""),"",AO7-AM7)</x:f>
-        <x:v>0.004178151638501659</x:v>
+        <x:v>0.038105899604946813</x:v>
       </x:c>
       <x:c r="AQ7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-MAX('Model'!$M7,'Model'!$M7+'Model'!$N7*(20-'Methodology'!$B$8)+0.5*'Model'!$P7*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.048168408333959856</x:v>
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9988579057293402</x:v>
       </x:c>
       <x:c r="AR7" s="46" t="n">
         <x:f>IF(OR(AQ7="",AO7=""),"",AQ7-AO7)</x:f>
-        <x:v>0.004159970528576196</x:v>
+        <x:v>0.009532169352544972</x:v>
       </x:c>
       <x:c r="AS7" s="24" t="n">
         <x:f>IF('Model'!$D7=0,"",Y7)</x:f>
@@ -3409,7 +3409,7 @@
       </x:c>
       <x:c r="AY7" s="17" t="str">
         <x:f>'Model'!Q7</x:f>
-        <x:v>Constant velocity — two observations</x:v>
+        <x:v>Shared frontier transfer — velocity contributor</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="46" hidden="0" customHeight="1">
@@ -3495,76 +3495,76 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-MAX('Model'!$M8,'Model'!$M8+'Model'!$N8*(12-'Methodology'!$B$8)+0.5*'Model'!$P8*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9999999990686774</x:v>
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9999999991590028</x:v>
       </x:c>
       <x:c r="AB8" s="46" t="n">
         <x:f>IF(OR(AA8="",Y8=""),"",AA8-Y8)</x:f>
-        <x:v>-9.313225746154785e-10</x:v>
+        <x:v>-8.409971608003275e-10</x:v>
       </x:c>
       <x:c r="AC8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-MAX('Model'!$M8,'Model'!$M8+'Model'!$N8*(13-'Methodology'!$B$8)+0.5*'Model'!$P8*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9999999990686774</x:v>
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9999999992761864</x:v>
       </x:c>
       <x:c r="AD8" s="46" t="n">
         <x:f>IF(OR(AC8="",AA8=""),"",AC8-AA8)</x:f>
-        <x:v>0</x:v>
+        <x:v>1.1718359615997542e-10</x:v>
       </x:c>
       <x:c r="AE8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-MAX('Model'!$M8,'Model'!$M8+'Model'!$N8*(14-'Methodology'!$B$8)+0.5*'Model'!$P8*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9999999990686774</x:v>
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9999999994195388</x:v>
       </x:c>
       <x:c r="AF8" s="46" t="n">
         <x:f>IF(OR(AE8="",AC8=""),"",AE8-AC8)</x:f>
-        <x:v>0</x:v>
+        <x:v>1.433523300065076e-10</x:v>
       </x:c>
       <x:c r="AG8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-MAX('Model'!$M8,'Model'!$M8+'Model'!$N8*(15-'Methodology'!$B$8)+0.5*'Model'!$P8*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9999999990686774</x:v>
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9999999995804487</x:v>
       </x:c>
       <x:c r="AH8" s="46" t="n">
         <x:f>IF(OR(AG8="",AE8=""),"",AG8-AE8)</x:f>
-        <x:v>0</x:v>
+        <x:v>1.6090995202944214e-10</x:v>
       </x:c>
       <x:c r="AI8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-MAX('Model'!$M8,'Model'!$M8+'Model'!$N8*(16-'Methodology'!$B$8)+0.5*'Model'!$P8*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9999999990686774</x:v>
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9999999997397386</x:v>
       </x:c>
       <x:c r="AJ8" s="46" t="n">
         <x:f>IF(OR(AI8="",AG8=""),"",AI8-AG8)</x:f>
-        <x:v>0</x:v>
+        <x:v>1.592899145919091e-10</x:v>
       </x:c>
       <x:c r="AK8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-MAX('Model'!$M8,'Model'!$M8+'Model'!$N8*(17-'Methodology'!$B$8)+0.5*'Model'!$P8*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9999999990686774</x:v>
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9999999998710603</x:v>
       </x:c>
       <x:c r="AL8" s="46" t="n">
         <x:f>IF(OR(AK8="",AI8=""),"",AK8-AI8)</x:f>
-        <x:v>0</x:v>
+        <x:v>1.3132162024476202e-10</x:v>
       </x:c>
       <x:c r="AM8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-MAX('Model'!$M8,'Model'!$M8+'Model'!$N8*(18-'Methodology'!$B$8)+0.5*'Model'!$P8*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9999999990686774</x:v>
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9999999999541079</x:v>
       </x:c>
       <x:c r="AN8" s="46" t="n">
         <x:f>IF(OR(AM8="",AK8=""),"",AM8-AK8)</x:f>
-        <x:v>0</x:v>
+        <x:v>8.30476798441282e-11</x:v>
       </x:c>
       <x:c r="AO8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-MAX('Model'!$M8,'Model'!$M8+'Model'!$N8*(19-'Methodology'!$B$8)+0.5*'Model'!$P8*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9999999990686774</x:v>
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9999999999899577</x:v>
       </x:c>
       <x:c r="AP8" s="46" t="n">
         <x:f>IF(OR(AO8="",AM8=""),"",AO8-AM8)</x:f>
-        <x:v>0</x:v>
+        <x:v>3.584976759896108e-11</x:v>
       </x:c>
       <x:c r="AQ8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-MAX('Model'!$M8,'Model'!$M8+'Model'!$N8*(20-'Methodology'!$B$8)+0.5*'Model'!$P8*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9999999990686774</x:v>
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9999999999989255</x:v>
       </x:c>
       <x:c r="AR8" s="46" t="n">
         <x:f>IF(OR(AQ8="",AO8=""),"",AQ8-AO8)</x:f>
-        <x:v>0</x:v>
+        <x:v>8.967826481409702e-12</x:v>
       </x:c>
       <x:c r="AS8" s="24" t="n">
         <x:f>IF('Model'!$D8=0,"",Y8)</x:f>
@@ -3592,7 +3592,7 @@
       </x:c>
       <x:c r="AY8" s="17" t="str">
         <x:f>'Model'!Q8</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="46" hidden="0" customHeight="1">
@@ -3676,76 +3676,76 @@
         <x:f>IF(OR(Y9="",W9=""),"",Y9-W9)</x:f>
       </x:c>
       <x:c r="AA9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-MAX('Model'!$M9,'Model'!$M9+'Model'!$N9*(12-'Methodology'!$B$8)+0.5*'Model'!$P9*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.43211866252478814</x:v>
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.48719527217643377</x:v>
       </x:c>
       <x:c r="AB9" s="46" t="n">
         <x:f>IF(OR(AA9="",Y9=""),"",AA9-Y9)</x:f>
-        <x:v>-5.551115123125783e-17</x:v>
+        <x:v>0.05507660965164557</x:v>
       </x:c>
       <x:c r="AC9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-MAX('Model'!$M9,'Model'!$M9+'Model'!$N9*(13-'Methodology'!$B$8)+0.5*'Model'!$P9*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.43211866252478814</x:v>
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.5586489043517079</x:v>
       </x:c>
       <x:c r="AD9" s="46" t="n">
         <x:f>IF(OR(AC9="",AA9=""),"",AC9-AA9)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.07145363217527412</x:v>
       </x:c>
       <x:c r="AE9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-MAX('Model'!$M9,'Model'!$M9+'Model'!$N9*(14-'Methodology'!$B$8)+0.5*'Model'!$P9*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.43211866252478814</x:v>
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6460591179621225</x:v>
       </x:c>
       <x:c r="AF9" s="46" t="n">
         <x:f>IF(OR(AE9="",AC9=""),"",AE9-AC9)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.08741021361041457</x:v>
       </x:c>
       <x:c r="AG9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-MAX('Model'!$M9,'Model'!$M9+'Model'!$N9*(15-'Methodology'!$B$8)+0.5*'Model'!$P9*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.43211866252478814</x:v>
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7441752423979136</x:v>
       </x:c>
       <x:c r="AH9" s="46" t="n">
         <x:f>IF(OR(AG9="",AE9=""),"",AG9-AE9)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.0981161244357911</x:v>
       </x:c>
       <x:c r="AI9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-MAX('Model'!$M9,'Model'!$M9+'Model'!$N9*(16-'Methodology'!$B$8)+0.5*'Model'!$P9*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.43211866252478814</x:v>
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8413035905889531</x:v>
       </x:c>
       <x:c r="AJ9" s="46" t="n">
         <x:f>IF(OR(AI9="",AG9=""),"",AI9-AG9)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.09712834819103955</x:v>
       </x:c>
       <x:c r="AK9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-MAX('Model'!$M9,'Model'!$M9+'Model'!$N9*(17-'Methodology'!$B$8)+0.5*'Model'!$P9*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.43211866252478814</x:v>
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9213779398073997</x:v>
       </x:c>
       <x:c r="AL9" s="46" t="n">
         <x:f>IF(OR(AK9="",AI9=""),"",AK9-AI9)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.08007434921844658</x:v>
       </x:c>
       <x:c r="AM9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-MAX('Model'!$M9,'Model'!$M9+'Model'!$N9*(18-'Methodology'!$B$8)+0.5*'Model'!$P9*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.43211866252478814</x:v>
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9720169380060126</x:v>
       </x:c>
       <x:c r="AN9" s="46" t="n">
         <x:f>IF(OR(AM9="",AK9=""),"",AM9-AK9)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05063899819861295</x:v>
       </x:c>
       <x:c r="AO9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-MAX('Model'!$M9,'Model'!$M9+'Model'!$N9*(19-'Methodology'!$B$8)+0.5*'Model'!$P9*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.43211866252478814</x:v>
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9938766383517159</x:v>
       </x:c>
       <x:c r="AP9" s="46" t="n">
         <x:f>IF(OR(AO9="",AM9=""),"",AO9-AM9)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.02185970034570328</x:v>
       </x:c>
       <x:c r="AQ9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-MAX('Model'!$M9,'Model'!$M9+'Model'!$N9*(20-'Methodology'!$B$8)+0.5*'Model'!$P9*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.43211866252478814</x:v>
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9993448300976491</x:v>
       </x:c>
       <x:c r="AR9" s="46" t="n">
         <x:f>IF(OR(AQ9="",AO9=""),"",AQ9-AO9)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.00546819174593316</x:v>
       </x:c>
       <x:c r="AS9" s="24" t="n">
         <x:f>IF('Model'!$D9=0,"",Y9)</x:f>
@@ -3773,7 +3773,7 @@
       </x:c>
       <x:c r="AY9" s="17" t="str">
         <x:f>'Model'!Q9</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="46" hidden="0" customHeight="1">
@@ -3861,76 +3861,76 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(12-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6</x:v>
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6387944494858837</x:v>
       </x:c>
       <x:c r="AB10" s="46" t="n">
         <x:f>IF(OR(AA10="",Y10=""),"",AA10-Y10)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.03879444948588373</x:v>
       </x:c>
       <x:c r="AC10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(13-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6</x:v>
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6891244233448279</x:v>
       </x:c>
       <x:c r="AD10" s="46" t="n">
         <x:f>IF(OR(AC10="",AA10=""),"",AC10-AA10)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05032997385894422</x:v>
       </x:c>
       <x:c r="AE10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(14-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6</x:v>
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7506937744342922</x:v>
       </x:c>
       <x:c r="AF10" s="46" t="n">
         <x:f>IF(OR(AE10="",AC10=""),"",AE10-AC10)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.061569351089464264</x:v>
       </x:c>
       <x:c r="AG10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(15-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6</x:v>
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8198040747459828</x:v>
       </x:c>
       <x:c r="AH10" s="46" t="n">
         <x:f>IF(OR(AG10="",AE10=""),"",AG10-AE10)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.06911030031169063</x:v>
       </x:c>
       <x:c r="AI10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(16-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6</x:v>
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8882186126301613</x:v>
       </x:c>
       <x:c r="AJ10" s="46" t="n">
         <x:f>IF(OR(AI10="",AG10=""),"",AI10-AG10)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.0684145378841785</x:v>
       </x:c>
       <x:c r="AK10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(17-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6</x:v>
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9446207825443588</x:v>
       </x:c>
       <x:c r="AL10" s="46" t="n">
         <x:f>IF(OR(AK10="",AI10=""),"",AK10-AI10)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05640216991419744</x:v>
       </x:c>
       <x:c r="AM10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(18-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6</x:v>
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9802895005365738</x:v>
       </x:c>
       <x:c r="AN10" s="46" t="n">
         <x:f>IF(OR(AM10="",AK10=""),"",AM10-AK10)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.03566871799221505</x:v>
       </x:c>
       <x:c r="AO10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(19-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6</x:v>
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9956868724191512</x:v>
       </x:c>
       <x:c r="AP10" s="46" t="n">
         <x:f>IF(OR(AO10="",AM10=""),"",AO10-AM10)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.015397371882577393</x:v>
       </x:c>
       <x:c r="AQ10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-MAX('Model'!$M10,'Model'!$M10+'Model'!$N10*(20-'Methodology'!$B$8)+0.5*'Model'!$P10*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6</x:v>
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9995385163349345</x:v>
       </x:c>
       <x:c r="AR10" s="46" t="n">
         <x:f>IF(OR(AQ10="",AO10=""),"",AQ10-AO10)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.0038516439157832982</x:v>
       </x:c>
       <x:c r="AS10" s="24" t="n">
         <x:f>IF('Model'!$D10=0,"",Y10)</x:f>
@@ -3958,7 +3958,7 @@
       </x:c>
       <x:c r="AY10" s="17" t="str">
         <x:f>'Model'!Q10</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="46" hidden="0" customHeight="1">
@@ -4042,76 +4042,76 @@
         <x:f>IF(OR(Y11="",W11=""),"",Y11-W11)</x:f>
       </x:c>
       <x:c r="AA11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-MAX('Model'!$M11,'Model'!$M11+'Model'!$N11*(12-'Methodology'!$B$8)+0.5*'Model'!$P11*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.18516388283148966</x:v>
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.26419167929840837</x:v>
       </x:c>
       <x:c r="AB11" s="46" t="n">
         <x:f>IF(OR(AA11="",Y11=""),"",AA11-Y11)</x:f>
-        <x:v>-2.7755575615628914e-17</x:v>
+        <x:v>0.07902779646691868</x:v>
       </x:c>
       <x:c r="AC11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-MAX('Model'!$M11,'Model'!$M11+'Model'!$N11*(13-'Methodology'!$B$8)+0.5*'Model'!$P11*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.18516388283148966</x:v>
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.36671838048944505</x:v>
       </x:c>
       <x:c r="AD11" s="46" t="n">
         <x:f>IF(OR(AC11="",AA11=""),"",AC11-AA11)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.10252670119103668</x:v>
       </x:c>
       <x:c r="AE11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-MAX('Model'!$M11,'Model'!$M11+'Model'!$N11*(14-'Methodology'!$B$8)+0.5*'Model'!$P11*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.18516388283148966</x:v>
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.49214070793525455</x:v>
       </x:c>
       <x:c r="AF11" s="46" t="n">
         <x:f>IF(OR(AE11="",AC11=""),"",AE11-AC11)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.1254223274458095</x:v>
       </x:c>
       <x:c r="AG11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-MAX('Model'!$M11,'Model'!$M11+'Model'!$N11*(15-'Methodology'!$B$8)+0.5*'Model'!$P11*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.18516388283148966</x:v>
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6329246298410738</x:v>
       </x:c>
       <x:c r="AH11" s="46" t="n">
         <x:f>IF(OR(AG11="",AE11=""),"",AG11-AE11)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.14078392190581923</x:v>
       </x:c>
       <x:c r="AI11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-MAX('Model'!$M11,'Model'!$M11+'Model'!$N11*(16-'Methodology'!$B$8)+0.5*'Model'!$P11*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.18516388283148966</x:v>
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7722912208596286</x:v>
       </x:c>
       <x:c r="AJ11" s="46" t="n">
         <x:f>IF(OR(AI11="",AG11=""),"",AI11-AG11)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.13936659101855486</x:v>
       </x:c>
       <x:c r="AK11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-MAX('Model'!$M11,'Model'!$M11+'Model'!$N11*(17-'Methodology'!$B$8)+0.5*'Model'!$P11*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.18516388283148966</x:v>
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8871875336915368</x:v>
       </x:c>
       <x:c r="AL11" s="46" t="n">
         <x:f>IF(OR(AK11="",AI11=""),"",AK11-AI11)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.11489631283190815</x:v>
       </x:c>
       <x:c r="AM11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-MAX('Model'!$M11,'Model'!$M11+'Model'!$N11*(18-'Methodology'!$B$8)+0.5*'Model'!$P11*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.18516388283148966</x:v>
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9598479328744245</x:v>
       </x:c>
       <x:c r="AN11" s="46" t="n">
         <x:f>IF(OR(AM11="",AK11=""),"",AM11-AK11)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.07266039918288769</x:v>
       </x:c>
       <x:c r="AO11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-MAX('Model'!$M11,'Model'!$M11+'Model'!$N11*(19-'Methodology'!$B$8)+0.5*'Model'!$P11*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.18516388283148966</x:v>
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9912137696729219</x:v>
       </x:c>
       <x:c r="AP11" s="46" t="n">
         <x:f>IF(OR(AO11="",AM11=""),"",AO11-AM11)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.03136583679849736</x:v>
       </x:c>
       <x:c r="AQ11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-MAX('Model'!$M11,'Model'!$M11+'Model'!$N11*(20-'Methodology'!$B$8)+0.5*'Model'!$P11*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.18516388283148966</x:v>
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9990599161055532</x:v>
       </x:c>
       <x:c r="AR11" s="46" t="n">
         <x:f>IF(OR(AQ11="",AO11=""),"",AQ11-AO11)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.007846146432631373</x:v>
       </x:c>
       <x:c r="AS11" s="24" t="n">
         <x:f>IF('Model'!$D11=0,"",Y11)</x:f>
@@ -4139,7 +4139,7 @@
       </x:c>
       <x:c r="AY11" s="17" t="str">
         <x:f>'Model'!Q11</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="46" hidden="0" customHeight="1">
@@ -4223,76 +4223,76 @@
         <x:f>IF(OR(Y12="",W12=""),"",Y12-W12)</x:f>
       </x:c>
       <x:c r="AA12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-MAX('Model'!$M12,'Model'!$M12+'Model'!$N12*(12-'Methodology'!$B$8)+0.5*'Model'!$P12*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.273</x:v>
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.34350891194059385</x:v>
       </x:c>
       <x:c r="AB12" s="46" t="n">
         <x:f>IF(OR(AA12="",Y12=""),"",AA12-Y12)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.07050891194059383</x:v>
       </x:c>
       <x:c r="AC12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-MAX('Model'!$M12,'Model'!$M12+'Model'!$N12*(13-'Methodology'!$B$8)+0.5*'Model'!$P12*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.273</x:v>
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.4349836394292248</x:v>
       </x:c>
       <x:c r="AD12" s="46" t="n">
         <x:f>IF(OR(AC12="",AA12=""),"",AC12-AA12)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.09147472748863095</x:v>
       </x:c>
       <x:c r="AE12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-MAX('Model'!$M12,'Model'!$M12+'Model'!$N12*(14-'Methodology'!$B$8)+0.5*'Model'!$P12*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.273</x:v>
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.546885935034326</x:v>
       </x:c>
       <x:c r="AF12" s="46" t="n">
         <x:f>IF(OR(AE12="",AC12=""),"",AE12-AC12)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.11190229560510123</x:v>
       </x:c>
       <x:c r="AG12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-MAX('Model'!$M12,'Model'!$M12+'Model'!$N12*(15-'Methodology'!$B$8)+0.5*'Model'!$P12*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.273</x:v>
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6724939058508238</x:v>
       </x:c>
       <x:c r="AH12" s="46" t="n">
         <x:f>IF(OR(AG12="",AE12=""),"",AG12-AE12)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.12560797081649777</x:v>
       </x:c>
       <x:c r="AI12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-MAX('Model'!$M12,'Model'!$M12+'Model'!$N12*(16-'Methodology'!$B$8)+0.5*'Model'!$P12*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.273</x:v>
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7968373284553182</x:v>
       </x:c>
       <x:c r="AJ12" s="46" t="n">
         <x:f>IF(OR(AI12="",AG12=""),"",AI12-AG12)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.12434342260449438</x:v>
       </x:c>
       <x:c r="AK12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-MAX('Model'!$M12,'Model'!$M12+'Model'!$N12*(17-'Methodology'!$B$8)+0.5*'Model'!$P12*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.273</x:v>
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8993482722743721</x:v>
       </x:c>
       <x:c r="AL12" s="46" t="n">
         <x:f>IF(OR(AK12="",AI12=""),"",AK12-AI12)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.1025109438190539</x:v>
       </x:c>
       <x:c r="AM12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-MAX('Model'!$M12,'Model'!$M12+'Model'!$N12*(18-'Methodology'!$B$8)+0.5*'Model'!$P12*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.273</x:v>
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9641761672252228</x:v>
       </x:c>
       <x:c r="AN12" s="46" t="n">
         <x:f>IF(OR(AM12="",AK12=""),"",AM12-AK12)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.06482789495085073</x:v>
       </x:c>
       <x:c r="AO12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-MAX('Model'!$M12,'Model'!$M12+'Model'!$N12*(19-'Methodology'!$B$8)+0.5*'Model'!$P12*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.273</x:v>
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9921608906218072</x:v>
       </x:c>
       <x:c r="AP12" s="46" t="n">
         <x:f>IF(OR(AO12="",AM12=""),"",AO12-AM12)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.02798472339658442</x:v>
       </x:c>
       <x:c r="AQ12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-MAX('Model'!$M12,'Model'!$M12+'Model'!$N12*(20-'Methodology'!$B$8)+0.5*'Model'!$P12*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.273</x:v>
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9991612534387434</x:v>
       </x:c>
       <x:c r="AR12" s="46" t="n">
         <x:f>IF(OR(AQ12="",AO12=""),"",AQ12-AO12)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.007000362816936168</x:v>
       </x:c>
       <x:c r="AS12" s="24" t="n">
         <x:f>IF('Model'!$D12=0,"",Y12)</x:f>
@@ -4320,7 +4320,7 @@
       </x:c>
       <x:c r="AY12" s="17" t="str">
         <x:f>'Model'!Q12</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="46" hidden="0" customHeight="1">
@@ -4406,76 +4406,76 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(12-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3033</x:v>
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.3708702323920382</x:v>
       </x:c>
       <x:c r="AB13" s="46" t="n">
         <x:f>IF(OR(AA13="",Y13=""),"",AA13-Y13)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.06757023239203819</x:v>
       </x:c>
       <x:c r="AC13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(13-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3033</x:v>
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.45853246436085415</x:v>
       </x:c>
       <x:c r="AD13" s="46" t="n">
         <x:f>IF(OR(AC13="",AA13=""),"",AC13-AA13)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.08766223196881595</x:v>
       </x:c>
       <x:c r="AE13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(14-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3033</x:v>
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.5657708816209285</x:v>
       </x:c>
       <x:c r="AF13" s="46" t="n">
         <x:f>IF(OR(AE13="",AC13=""),"",AE13-AC13)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.10723841726007433</x:v>
       </x:c>
       <x:c r="AG13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(15-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3033</x:v>
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6861437471888155</x:v>
       </x:c>
       <x:c r="AH13" s="46" t="n">
         <x:f>IF(OR(AG13="",AE13=""),"",AG13-AE13)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.12037286556788707</x:v>
       </x:c>
       <x:c r="AI13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(16-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3033</x:v>
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8053047685485835</x:v>
       </x:c>
       <x:c r="AJ13" s="46" t="n">
         <x:f>IF(OR(AI13="",AG13=""),"",AI13-AG13)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.11916102135976792</x:v>
       </x:c>
       <x:c r="AK13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(17-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3033</x:v>
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.903543247996637</x:v>
       </x:c>
       <x:c r="AL13" s="46" t="n">
         <x:f>IF(OR(AK13="",AI13=""),"",AK13-AI13)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.09823847944805353</x:v>
       </x:c>
       <x:c r="AM13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(18-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3033</x:v>
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9656692375595775</x:v>
       </x:c>
       <x:c r="AN13" s="46" t="n">
         <x:f>IF(OR(AM13="",AK13=""),"",AM13-AK13)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.062125989562940465</x:v>
       </x:c>
       <x:c r="AO13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(19-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3033</x:v>
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9924876100360566</x:v>
       </x:c>
       <x:c r="AP13" s="46" t="n">
         <x:f>IF(OR(AO13="",AM13=""),"",AO13-AM13)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.026818372476479113</x:v>
       </x:c>
       <x:c r="AQ13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-MAX('Model'!$M13,'Model'!$M13+'Model'!$N13*(20-'Methodology'!$B$8)+0.5*'Model'!$P13*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3033</x:v>
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9991962108263721</x:v>
       </x:c>
       <x:c r="AR13" s="46" t="n">
         <x:f>IF(OR(AQ13="",AO13=""),"",AQ13-AO13)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.006708600790315544</x:v>
       </x:c>
       <x:c r="AS13" s="24" t="n">
         <x:f>IF('Model'!$D13=0,"",Y13)</x:f>
@@ -4503,7 +4503,7 @@
       </x:c>
       <x:c r="AY13" s="17" t="str">
         <x:f>'Model'!Q13</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="46" hidden="0" customHeight="1">
@@ -4597,76 +4597,76 @@
         <x:v>0.05199999999999999</x:v>
       </x:c>
       <x:c r="AA14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-MAX('Model'!$M14,'Model'!$M14+'Model'!$N14*(12-'Methodology'!$B$8)+0.5*'Model'!$P14*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.5252389939287958</x:v>
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.558426214496493</x:v>
       </x:c>
       <x:c r="AB14" s="46" t="n">
         <x:f>IF(OR(AA14="",Y14=""),"",AA14-Y14)</x:f>
-        <x:v>0.014238993928795796</x:v>
+        <x:v>0.04742621449649298</x:v>
       </x:c>
       <x:c r="AC14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-MAX('Model'!$M14,'Model'!$M14+'Model'!$N14*(13-'Methodology'!$B$8)+0.5*'Model'!$P14*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.5193134232385967</x:v>
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6199546075390522</x:v>
       </x:c>
       <x:c r="AD14" s="46" t="n">
         <x:f>IF(OR(AC14="",AA14=""),"",AC14-AA14)</x:f>
-        <x:v>-0.005925570690199056</x:v>
+        <x:v>0.06152839304255919</x:v>
       </x:c>
       <x:c r="AE14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-MAX('Model'!$M14,'Model'!$M14+'Model'!$N14*(14-'Methodology'!$B$8)+0.5*'Model'!$P14*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.511</x:v>
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6952231392459222</x:v>
       </x:c>
       <x:c r="AF14" s="46" t="n">
         <x:f>IF(OR(AE14="",AC14=""),"",AE14-AC14)</x:f>
-        <x:v>-0.00831342323859674</x:v>
+        <x:v>0.07526853170686998</x:v>
       </x:c>
       <x:c r="AG14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-MAX('Model'!$M14,'Model'!$M14+'Model'!$N14*(15-'Methodology'!$B$8)+0.5*'Model'!$P14*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.511</x:v>
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.779710481376964</x:v>
       </x:c>
       <x:c r="AH14" s="46" t="n">
         <x:f>IF(OR(AG14="",AE14=""),"",AG14-AE14)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.08448734213104181</x:v>
       </x:c>
       <x:c r="AI14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-MAX('Model'!$M14,'Model'!$M14+'Model'!$N14*(16-'Methodology'!$B$8)+0.5*'Model'!$P14*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.511</x:v>
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8633472539403722</x:v>
       </x:c>
       <x:c r="AJ14" s="46" t="n">
         <x:f>IF(OR(AI14="",AG14=""),"",AI14-AG14)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.08363677256340818</x:v>
       </x:c>
       <x:c r="AK14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-MAX('Model'!$M14,'Model'!$M14+'Model'!$N14*(17-'Methodology'!$B$8)+0.5*'Model'!$P14*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.511</x:v>
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9322989066604787</x:v>
       </x:c>
       <x:c r="AL14" s="46" t="n">
         <x:f>IF(OR(AK14="",AI14=""),"",AK14-AI14)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.0689516527201065</x:v>
       </x:c>
       <x:c r="AM14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-MAX('Model'!$M14,'Model'!$M14+'Model'!$N14*(18-'Methodology'!$B$8)+0.5*'Model'!$P14*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.511</x:v>
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9759039144059615</x:v>
       </x:c>
       <x:c r="AN14" s="46" t="n">
         <x:f>IF(OR(AM14="",AK14=""),"",AM14-AK14)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.043605007745482816</x:v>
       </x:c>
       <x:c r="AO14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-MAX('Model'!$M14,'Model'!$M14+'Model'!$N14*(19-'Methodology'!$B$8)+0.5*'Model'!$P14*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.511</x:v>
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9947272015324123</x:v>
       </x:c>
       <x:c r="AP14" s="46" t="n">
         <x:f>IF(OR(AO14="",AM14=""),"",AO14-AM14)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.01882328712645087</x:v>
       </x:c>
       <x:c r="AQ14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-MAX('Model'!$M14,'Model'!$M14+'Model'!$N14*(20-'Methodology'!$B$8)+0.5*'Model'!$P14*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.511</x:v>
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9994358362194574</x:v>
       </x:c>
       <x:c r="AR14" s="46" t="n">
         <x:f>IF(OR(AQ14="",AO14=""),"",AQ14-AO14)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.004708634687045077</x:v>
       </x:c>
       <x:c r="AS14" s="24" t="n">
         <x:f>IF('Model'!$D14=0,"",Y14)</x:f>
@@ -4694,7 +4694,7 @@
       </x:c>
       <x:c r="AY14" s="17" t="str">
         <x:f>'Model'!Q14</x:f>
-        <x:v>Velocity + acceleration — latest three observations</x:v>
+        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="46" hidden="0" customHeight="1">
@@ -4784,76 +4784,76 @@
         <x:v>0.08399999999999996</x:v>
       </x:c>
       <x:c r="AA15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-MAX('Model'!$M15,'Model'!$M15+'Model'!$N15*(12-'Methodology'!$B$8)+0.5*'Model'!$P15*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6756493491231983</x:v>
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6451155466198808</x:v>
       </x:c>
       <x:c r="AB15" s="46" t="n">
         <x:f>IF(OR(AA15="",Y15=""),"",AA15-Y15)</x:f>
-        <x:v>0.06864934912319831</x:v>
+        <x:v>0.038115546619880813</x:v>
       </x:c>
       <x:c r="AC15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-MAX('Model'!$M15,'Model'!$M15+'Model'!$N15*(13-'Methodology'!$B$8)+0.5*'Model'!$P15*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.7313832431847436</x:v>
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6945647459362935</x:v>
       </x:c>
       <x:c r="AD15" s="46" t="n">
         <x:f>IF(OR(AC15="",AA15=""),"",AC15-AA15)</x:f>
-        <x:v>0.055733894061545275</x:v>
+        <x:v>0.04944919931641267</x:v>
       </x:c>
       <x:c r="AE15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-MAX('Model'!$M15,'Model'!$M15+'Model'!$N15*(14-'Methodology'!$B$8)+0.5*'Model'!$P15*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.7767725835602166</x:v>
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.755056633381692</x:v>
       </x:c>
       <x:c r="AF15" s="46" t="n">
         <x:f>IF(OR(AE15="",AC15=""),"",AE15-AC15)</x:f>
-        <x:v>0.04538934037547304</x:v>
+        <x:v>0.06049188744539857</x:v>
       </x:c>
       <x:c r="AG15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-MAX('Model'!$M15,'Model'!$M15+'Model'!$N15*(15-'Methodology'!$B$8)+0.5*'Model'!$P15*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.813852131076838</x:v>
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8229575034379281</x:v>
       </x:c>
       <x:c r="AH15" s="46" t="n">
         <x:f>IF(OR(AG15="",AE15=""),"",AG15-AE15)</x:f>
-        <x:v>0.03707954751662135</x:v>
+        <x:v>0.06790087005623602</x:v>
       </x:c>
       <x:c r="AI15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-MAX('Model'!$M15,'Model'!$M15+'Model'!$N15*(16-'Methodology'!$B$8)+0.5*'Model'!$P15*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8442368546032146</x:v>
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8901747869091334</x:v>
       </x:c>
       <x:c r="AJ15" s="46" t="n">
         <x:f>IF(OR(AI15="",AG15=""),"",AI15-AG15)</x:f>
-        <x:v>0.030384723526376667</x:v>
+        <x:v>0.06721728347120537</x:v>
       </x:c>
       <x:c r="AK15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-MAX('Model'!$M15,'Model'!$M15+'Model'!$N15*(17-'Methodology'!$B$8)+0.5*'Model'!$P15*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8692121343567735</x:v>
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9455899188498325</x:v>
       </x:c>
       <x:c r="AL15" s="46" t="n">
         <x:f>IF(OR(AK15="",AI15=""),"",AK15-AI15)</x:f>
-        <x:v>0.024975279753558843</x:v>
+        <x:v>0.055415131940699025</x:v>
       </x:c>
       <x:c r="AM15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-MAX('Model'!$M15,'Model'!$M15+'Model'!$N15*(18-'Methodology'!$B$8)+0.5*'Model'!$P15*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8898038806901376</x:v>
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9806344342771838</x:v>
       </x:c>
       <x:c r="AN15" s="46" t="n">
         <x:f>IF(OR(AM15="",AK15=""),"",AM15-AK15)</x:f>
-        <x:v>0.020591746333364136</x:v>
+        <x:v>0.03504451542735132</x:v>
       </x:c>
       <x:c r="AO15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-MAX('Model'!$M15,'Model'!$M15+'Model'!$N15*(19-'Methodology'!$B$8)+0.5*'Model'!$P15*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9068331841779688</x:v>
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9957623521518161</x:v>
       </x:c>
       <x:c r="AP15" s="46" t="n">
         <x:f>IF(OR(AO15="",AM15=""),"",AO15-AM15)</x:f>
-        <x:v>0.01702930348783116</x:v>
+        <x:v>0.015127917874632302</x:v>
       </x:c>
       <x:c r="AQ15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-MAX('Model'!$M15,'Model'!$M15+'Model'!$N15*(20-'Methodology'!$B$8)+0.5*'Model'!$P15*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9209590213026758</x:v>
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9995465922990731</x:v>
       </x:c>
       <x:c r="AR15" s="46" t="n">
         <x:f>IF(OR(AQ15="",AO15=""),"",AQ15-AO15)</x:f>
-        <x:v>0.014125837124707052</x:v>
+        <x:v>0.0037842401472569787</x:v>
       </x:c>
       <x:c r="AS15" s="24" t="n">
         <x:f>IF('Model'!$D15=0,"",Y15)</x:f>
@@ -4881,7 +4881,7 @@
       </x:c>
       <x:c r="AY15" s="17" t="str">
         <x:f>'Model'!Q15</x:f>
-        <x:v>Velocity + acceleration — latest three observations</x:v>
+        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="46" hidden="0" customHeight="1">
@@ -4969,76 +4969,76 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-MAX('Model'!$M16,'Model'!$M16+'Model'!$N16*(12-'Methodology'!$B$8)+0.5*'Model'!$P16*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.758</x:v>
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7814706419389598</x:v>
       </x:c>
       <x:c r="AB16" s="46" t="n">
         <x:f>IF(OR(AA16="",Y16=""),"",AA16-Y16)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.023470641938959758</x:v>
       </x:c>
       <x:c r="AC16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-MAX('Model'!$M16,'Model'!$M16+'Model'!$N16*(13-'Methodology'!$B$8)+0.5*'Model'!$P16*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.758</x:v>
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8119202761236209</x:v>
       </x:c>
       <x:c r="AD16" s="46" t="n">
         <x:f>IF(OR(AC16="",AA16=""),"",AC16-AA16)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.03044963418466118</x:v>
       </x:c>
       <x:c r="AE16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-MAX('Model'!$M16,'Model'!$M16+'Model'!$N16*(14-'Methodology'!$B$8)+0.5*'Model'!$P16*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.758</x:v>
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8491697335327468</x:v>
       </x:c>
       <x:c r="AF16" s="46" t="n">
         <x:f>IF(OR(AE16="",AC16=""),"",AE16-AC16)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.037249457409125886</x:v>
       </x:c>
       <x:c r="AG16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-MAX('Model'!$M16,'Model'!$M16+'Model'!$N16*(15-'Methodology'!$B$8)+0.5*'Model'!$P16*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.758</x:v>
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8909814652213196</x:v>
       </x:c>
       <x:c r="AH16" s="46" t="n">
         <x:f>IF(OR(AG16="",AE16=""),"",AG16-AE16)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.04181173168857277</x:v>
       </x:c>
       <x:c r="AI16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-MAX('Model'!$M16,'Model'!$M16+'Model'!$N16*(16-'Methodology'!$B$8)+0.5*'Model'!$P16*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.758</x:v>
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9323722606412477</x:v>
       </x:c>
       <x:c r="AJ16" s="46" t="n">
         <x:f>IF(OR(AI16="",AG16=""),"",AI16-AG16)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.04139079541992807</x:v>
       </x:c>
       <x:c r="AK16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-MAX('Model'!$M16,'Model'!$M16+'Model'!$N16*(17-'Methodology'!$B$8)+0.5*'Model'!$P16*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.758</x:v>
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9664955734393371</x:v>
       </x:c>
       <x:c r="AL16" s="46" t="n">
         <x:f>IF(OR(AK16="",AI16=""),"",AK16-AI16)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.034123312798089445</x:v>
       </x:c>
       <x:c r="AM16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-MAX('Model'!$M16,'Model'!$M16+'Model'!$N16*(18-'Methodology'!$B$8)+0.5*'Model'!$P16*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.758</x:v>
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9880751478246271</x:v>
       </x:c>
       <x:c r="AN16" s="46" t="n">
         <x:f>IF(OR(AM16="",AK16=""),"",AM16-AK16)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.021579574385290012</x:v>
       </x:c>
       <x:c r="AO16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-MAX('Model'!$M16,'Model'!$M16+'Model'!$N16*(19-'Methodology'!$B$8)+0.5*'Model'!$P16*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.758</x:v>
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9973905578135864</x:v>
       </x:c>
       <x:c r="AP16" s="46" t="n">
         <x:f>IF(OR(AO16="",AM16=""),"",AO16-AM16)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.0093154099889593</x:v>
       </x:c>
       <x:c r="AQ16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-MAX('Model'!$M16,'Model'!$M16+'Model'!$N16*(20-'Methodology'!$B$8)+0.5*'Model'!$P16*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.758</x:v>
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9997208023826354</x:v>
       </x:c>
       <x:c r="AR16" s="46" t="n">
         <x:f>IF(OR(AQ16="",AO16=""),"",AQ16-AO16)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.002330244569048956</x:v>
       </x:c>
       <x:c r="AS16" s="24" t="n">
         <x:f>IF('Model'!$D16=0,"",Y16)</x:f>
@@ -5066,7 +5066,7 @@
       </x:c>
       <x:c r="AY16" s="17" t="str">
         <x:f>'Model'!Q16</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="46" hidden="0" customHeight="1">
@@ -5164,76 +5164,76 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-MAX('Model'!$M17,'Model'!$M17+'Model'!$N17*(12-'Methodology'!$B$8)+0.5*'Model'!$P17*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.5559444005391392</x:v>
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.48437907664109925</x:v>
       </x:c>
       <x:c r="AB17" s="46" t="n">
         <x:f>IF(OR(AA17="",Y17=""),"",AA17-Y17)</x:f>
-        <x:v>0.1269444005391392</x:v>
+        <x:v>0.055379076641099256</x:v>
       </x:c>
       <x:c r="AC17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-MAX('Model'!$M17,'Model'!$M17+'Model'!$N17*(13-'Methodology'!$B$8)+0.5*'Model'!$P17*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.68880370470504</x:v>
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.5562251143247421</x:v>
       </x:c>
       <x:c r="AD17" s="46" t="n">
         <x:f>IF(OR(AC17="",AA17=""),"",AC17-AA17)</x:f>
-        <x:v>0.13285930416590086</x:v>
+        <x:v>0.07184603768364284</x:v>
       </x:c>
       <x:c r="AE17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-MAX('Model'!$M17,'Model'!$M17+'Model'!$N17*(14-'Methodology'!$B$8)+0.5*'Model'!$P17*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.803470698584923</x:v>
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6441153630049521</x:v>
       </x:c>
       <x:c r="AF17" s="46" t="n">
         <x:f>IF(OR(AE17="",AC17=""),"",AE17-AC17)</x:f>
-        <x:v>0.114666993879883</x:v>
+        <x:v>0.08789024868021</x:v>
       </x:c>
       <x:c r="AG17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-MAX('Model'!$M17,'Model'!$M17+'Model'!$N17*(15-'Methodology'!$B$8)+0.5*'Model'!$P17*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8881551407169437</x:v>
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7427703166998905</x:v>
       </x:c>
       <x:c r="AH17" s="46" t="n">
         <x:f>IF(OR(AG17="",AE17=""),"",AG17-AE17)</x:f>
-        <x:v>0.08468444213202064</x:v>
+        <x:v>0.09865495369493837</x:v>
       </x:c>
       <x:c r="AI17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-MAX('Model'!$M17,'Model'!$M17+'Model'!$N17*(16-'Methodology'!$B$8)+0.5*'Model'!$P17*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9426411323247148</x:v>
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8404320695295553</x:v>
       </x:c>
       <x:c r="AJ17" s="46" t="n">
         <x:f>IF(OR(AI17="",AG17=""),"",AI17-AG17)</x:f>
-        <x:v>0.05448599160777112</x:v>
+        <x:v>0.09766175282966483</x:v>
       </x:c>
       <x:c r="AK17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-MAX('Model'!$M17,'Model'!$M17+'Model'!$N17*(17-'Methodology'!$B$8)+0.5*'Model'!$P17*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9734917574329855</x:v>
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9209461670820722</x:v>
       </x:c>
       <x:c r="AL17" s="46" t="n">
         <x:f>IF(OR(AK17="",AI17=""),"",AK17-AI17)</x:f>
-        <x:v>0.030850625108270746</x:v>
+        <x:v>0.08051409755251693</x:v>
       </x:c>
       <x:c r="AM17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-MAX('Model'!$M17,'Model'!$M17+'Model'!$N17*(18-'Methodology'!$B$8)+0.5*'Model'!$P17*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9889603036663265</x:v>
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9718632620159591</x:v>
       </x:c>
       <x:c r="AN17" s="46" t="n">
         <x:f>IF(OR(AM17="",AK17=""),"",AM17-AK17)</x:f>
-        <x:v>0.01546854623334093</x:v>
+        <x:v>0.05091709493388685</x:v>
       </x:c>
       <x:c r="AO17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-MAX('Model'!$M17,'Model'!$M17+'Model'!$N17*(19-'Methodology'!$B$8)+0.5*'Model'!$P17*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9958568644345129</x:v>
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9938430103783383</x:v>
       </x:c>
       <x:c r="AP17" s="46" t="n">
         <x:f>IF(OR(AO17="",AM17=""),"",AO17-AM17)</x:f>
-        <x:v>0.006896560768186455</x:v>
+        <x:v>0.02197974836237926</x:v>
       </x:c>
       <x:c r="AQ17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-MAX('Model'!$M17,'Model'!$M17+'Model'!$N17*(20-'Methodology'!$B$8)+0.5*'Model'!$P17*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.998598810142451</x:v>
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.999341232068119</x:v>
       </x:c>
       <x:c r="AR17" s="46" t="n">
         <x:f>IF(OR(AQ17="",AO17=""),"",AQ17-AO17)</x:f>
-        <x:v>0.002741945707938065</x:v>
+        <x:v>0.005498221689780647</x:v>
       </x:c>
       <x:c r="AS17" s="24" t="n">
         <x:f>IF('Model'!$D17=0,"",Y17)</x:f>
@@ -5261,7 +5261,7 @@
       </x:c>
       <x:c r="AY17" s="17" t="str">
         <x:f>'Model'!Q17</x:f>
-        <x:v>Velocity + acceleration — latest three observations</x:v>
+        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="46" hidden="0" customHeight="1">
@@ -5344,55 +5344,55 @@
         <x:f>IF(OR(Y18="",W18=""),"",Y18-W18)</x:f>
       </x:c>
       <x:c r="AA18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-MAX('Model'!$M18,'Model'!$M18+'Model'!$N18*(12-'Methodology'!$B$8)+0.5*'Model'!$P18*POWER(12-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AB18" s="46" t="str">
         <x:f>IF(OR(AA18="",Y18=""),"",AA18-Y18)</x:f>
       </x:c>
       <x:c r="AC18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-MAX('Model'!$M18,'Model'!$M18+'Model'!$N18*(13-'Methodology'!$B$8)+0.5*'Model'!$P18*POWER(13-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AD18" s="46" t="str">
         <x:f>IF(OR(AC18="",AA18=""),"",AC18-AA18)</x:f>
       </x:c>
       <x:c r="AE18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-MAX('Model'!$M18,'Model'!$M18+'Model'!$N18*(14-'Methodology'!$B$8)+0.5*'Model'!$P18*POWER(14-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AF18" s="46" t="str">
         <x:f>IF(OR(AE18="",AC18=""),"",AE18-AC18)</x:f>
       </x:c>
       <x:c r="AG18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-MAX('Model'!$M18,'Model'!$M18+'Model'!$N18*(15-'Methodology'!$B$8)+0.5*'Model'!$P18*POWER(15-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AH18" s="46" t="str">
         <x:f>IF(OR(AG18="",AE18=""),"",AG18-AE18)</x:f>
       </x:c>
       <x:c r="AI18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-MAX('Model'!$M18,'Model'!$M18+'Model'!$N18*(16-'Methodology'!$B$8)+0.5*'Model'!$P18*POWER(16-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AJ18" s="46" t="str">
         <x:f>IF(OR(AI18="",AG18=""),"",AI18-AG18)</x:f>
       </x:c>
       <x:c r="AK18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-MAX('Model'!$M18,'Model'!$M18+'Model'!$N18*(17-'Methodology'!$B$8)+0.5*'Model'!$P18*POWER(17-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AL18" s="46" t="str">
         <x:f>IF(OR(AK18="",AI18=""),"",AK18-AI18)</x:f>
       </x:c>
       <x:c r="AM18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-MAX('Model'!$M18,'Model'!$M18+'Model'!$N18*(18-'Methodology'!$B$8)+0.5*'Model'!$P18*POWER(18-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AN18" s="46" t="str">
         <x:f>IF(OR(AM18="",AK18=""),"",AM18-AK18)</x:f>
       </x:c>
       <x:c r="AO18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-MAX('Model'!$M18,'Model'!$M18+'Model'!$N18*(19-'Methodology'!$B$8)+0.5*'Model'!$P18*POWER(19-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AP18" s="46" t="str">
         <x:f>IF(OR(AO18="",AM18=""),"",AO18-AM18)</x:f>
       </x:c>
       <x:c r="AQ18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-MAX('Model'!$M18,'Model'!$M18+'Model'!$N18*(20-'Methodology'!$B$8)+0.5*'Model'!$P18*POWER(20-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AR18" s="46" t="str">
         <x:f>IF(OR(AQ18="",AO18=""),"",AQ18-AO18)</x:f>
@@ -5511,76 +5511,76 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-MAX('Model'!$M19,'Model'!$M19+'Model'!$N19*(12-'Methodology'!$B$8)+0.5*'Model'!$P19*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.384</x:v>
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.44374345220826106</x:v>
       </x:c>
       <x:c r="AB19" s="46" t="n">
         <x:f>IF(OR(AA19="",Y19=""),"",AA19-Y19)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05974345220826105</x:v>
       </x:c>
       <x:c r="AC19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-MAX('Model'!$M19,'Model'!$M19+'Model'!$N19*(13-'Methodology'!$B$8)+0.5*'Model'!$P19*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.384</x:v>
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.5212516119510351</x:v>
       </x:c>
       <x:c r="AD19" s="46" t="n">
         <x:f>IF(OR(AC19="",AA19=""),"",AC19-AA19)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.07750815974277403</x:v>
       </x:c>
       <x:c r="AE19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-MAX('Model'!$M19,'Model'!$M19+'Model'!$N19*(14-'Methodology'!$B$8)+0.5*'Model'!$P19*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.384</x:v>
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.61606841262881</x:v>
       </x:c>
       <x:c r="AF19" s="46" t="n">
         <x:f>IF(OR(AE19="",AC19=""),"",AE19-AC19)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.09481680067777487</x:v>
       </x:c>
       <x:c r="AG19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-MAX('Model'!$M19,'Model'!$M19+'Model'!$N19*(15-'Methodology'!$B$8)+0.5*'Model'!$P19*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.384</x:v>
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7224982751088136</x:v>
       </x:c>
       <x:c r="AH19" s="46" t="n">
         <x:f>IF(OR(AG19="",AE19=""),"",AG19-AE19)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.10642986248000363</x:v>
       </x:c>
       <x:c r="AI19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-MAX('Model'!$M19,'Model'!$M19+'Model'!$N19*(16-'Methodology'!$B$8)+0.5*'Model'!$P19*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.384</x:v>
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8278566634504484</x:v>
       </x:c>
       <x:c r="AJ19" s="46" t="n">
         <x:f>IF(OR(AI19="",AG19=""),"",AI19-AG19)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.1053583883416348</x:v>
       </x:c>
       <x:c r="AK19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-MAX('Model'!$M19,'Model'!$M19+'Model'!$N19*(17-'Methodology'!$B$8)+0.5*'Model'!$P19*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.384</x:v>
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9147160051183125</x:v>
       </x:c>
       <x:c r="AL19" s="46" t="n">
         <x:f>IF(OR(AK19="",AI19=""),"",AK19-AI19)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.08685934166786413</x:v>
       </x:c>
       <x:c r="AM19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-MAX('Model'!$M19,'Model'!$M19+'Model'!$N19*(18-'Methodology'!$B$8)+0.5*'Model'!$P19*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.384</x:v>
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9696458308263236</x:v>
       </x:c>
       <x:c r="AN19" s="46" t="n">
         <x:f>IF(OR(AM19="",AK19=""),"",AM19-AK19)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05492982570801108</x:v>
       </x:c>
       <x:c r="AO19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-MAX('Model'!$M19,'Model'!$M19+'Model'!$N19*(19-'Methodology'!$B$8)+0.5*'Model'!$P19*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.384</x:v>
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9933577835254929</x:v>
       </x:c>
       <x:c r="AP19" s="46" t="n">
         <x:f>IF(OR(AO19="",AM19=""),"",AO19-AM19)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.02371195269916926</x:v>
       </x:c>
       <x:c r="AQ19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-MAX('Model'!$M19,'Model'!$M19+'Model'!$N19*(20-'Methodology'!$B$8)+0.5*'Model'!$P19*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.384</x:v>
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9992893151557991</x:v>
       </x:c>
       <x:c r="AR19" s="46" t="n">
         <x:f>IF(OR(AQ19="",AO19=""),"",AQ19-AO19)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.0059315316303062415</x:v>
       </x:c>
       <x:c r="AS19" s="24" t="n">
         <x:f>IF('Model'!$D19=0,"",Y19)</x:f>
@@ -5608,7 +5608,7 @@
       </x:c>
       <x:c r="AY19" s="17" t="str">
         <x:f>'Model'!Q19</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="46" hidden="0" customHeight="1">
@@ -5700,76 +5700,76 @@
         <x:v>0.10600000000000004</x:v>
       </x:c>
       <x:c r="AA20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-MAX('Model'!$M20,'Model'!$M20+'Model'!$N20*(12-'Methodology'!$B$8)+0.5*'Model'!$P20*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6592688668048576</x:v>
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.5954497834241899</x:v>
       </x:c>
       <x:c r="AB20" s="46" t="n">
         <x:f>IF(OR(AA20="",Y20=""),"",AA20-Y20)</x:f>
-        <x:v>0.10726886680485759</x:v>
+        <x:v>0.043449783424189814</x:v>
       </x:c>
       <x:c r="AC20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-MAX('Model'!$M20,'Model'!$M20+'Model'!$N20*(13-'Methodology'!$B$8)+0.5*'Model'!$P20*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.770767215434066</x:v>
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6518193541462074</x:v>
       </x:c>
       <x:c r="AD20" s="46" t="n">
         <x:f>IF(OR(AC20="",AA20=""),"",AC20-AA20)</x:f>
-        <x:v>0.11149834862920838</x:v>
+        <x:v>0.05636957072201754</x:v>
       </x:c>
       <x:c r="AE20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-MAX('Model'!$M20,'Model'!$M20+'Model'!$N20*(14-'Methodology'!$B$8)+0.5*'Model'!$P20*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.8635816629980508</x:v>
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7207770273664073</x:v>
       </x:c>
       <x:c r="AF20" s="46" t="n">
         <x:f>IF(OR(AE20="",AC20=""),"",AE20-AC20)</x:f>
-        <x:v>0.09281444756398483</x:v>
+        <x:v>0.06895767322019986</x:v>
       </x:c>
       <x:c r="AG20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-MAX('Model'!$M20,'Model'!$M20+'Model'!$N20*(15-'Methodology'!$B$8)+0.5*'Model'!$P20*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9281875273322151</x:v>
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7981805637155007</x:v>
       </x:c>
       <x:c r="AH20" s="46" t="n">
         <x:f>IF(OR(AG20="",AE20=""),"",AG20-AE20)</x:f>
-        <x:v>0.06460586433416426</x:v>
+        <x:v>0.07740353634909347</x:v>
       </x:c>
       <x:c r="AI20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-MAX('Model'!$M20,'Model'!$M20+'Model'!$N20*(16-'Methodology'!$B$8)+0.5*'Model'!$P20*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9665606274987677</x:v>
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8748048461457807</x:v>
       </x:c>
       <x:c r="AJ20" s="46" t="n">
         <x:f>IF(OR(AI20="",AG20=""),"",AI20-AG20)</x:f>
-        <x:v>0.0383731001665526</x:v>
+        <x:v>0.07662428243027997</x:v>
       </x:c>
       <x:c r="AK20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-MAX('Model'!$M20,'Model'!$M20+'Model'!$N20*(17-'Methodology'!$B$8)+0.5*'Model'!$P20*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9862264000033575</x:v>
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9379752764496818</x:v>
       </x:c>
       <x:c r="AL20" s="46" t="n">
         <x:f>IF(OR(AK20="",AI20=""),"",AK20-AI20)</x:f>
-        <x:v>0.019665772504589785</x:v>
+        <x:v>0.06317043030390113</x:v>
       </x:c>
       <x:c r="AM20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-MAX('Model'!$M20,'Model'!$M20+'Model'!$N20*(18-'Methodology'!$B$8)+0.5*'Model'!$P20*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9949815694050459</x:v>
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9779242406009626</x:v>
       </x:c>
       <x:c r="AN20" s="46" t="n">
         <x:f>IF(OR(AM20="",AK20=""),"",AM20-AK20)</x:f>
-        <x:v>0.008755169401688412</x:v>
+        <x:v>0.0399489641512808</x:v>
       </x:c>
       <x:c r="AO20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-MAX('Model'!$M20,'Model'!$M20+'Model'!$N20*(19-'Methodology'!$B$8)+0.5*'Model'!$P20*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9983825923727305</x:v>
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9951692971094493</x:v>
       </x:c>
       <x:c r="AP20" s="46" t="n">
         <x:f>IF(OR(AO20="",AM20=""),"",AO20-AM20)</x:f>
-        <x:v>0.0034010229676846304</x:v>
+        <x:v>0.017245056508486734</x:v>
       </x:c>
       <x:c r="AQ20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-MAX('Model'!$M20,'Model'!$M20+'Model'!$N20*(20-'Methodology'!$B$8)+0.5*'Model'!$P20*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9995388925276858</x:v>
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9994831382951266</x:v>
       </x:c>
       <x:c r="AR20" s="46" t="n">
         <x:f>IF(OR(AQ20="",AO20=""),"",AQ20-AO20)</x:f>
-        <x:v>0.0011563001549552698</x:v>
+        <x:v>0.004313841185677236</x:v>
       </x:c>
       <x:c r="AS20" s="24" t="n">
         <x:f>IF('Model'!$D20=0,"",Y20)</x:f>
@@ -5797,7 +5797,7 @@
       </x:c>
       <x:c r="AY20" s="17" t="str">
         <x:f>'Model'!Q20</x:f>
-        <x:v>Velocity + acceleration — latest three observations</x:v>
+        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="46" hidden="0" customHeight="1">
@@ -5885,76 +5885,76 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-MAX('Model'!$M21,'Model'!$M21+'Model'!$N21*(12-'Methodology'!$B$8)+0.5*'Model'!$P21*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.582</x:v>
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6225401997127485</x:v>
       </x:c>
       <x:c r="AB21" s="46" t="n">
         <x:f>IF(OR(AA21="",Y21=""),"",AA21-Y21)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.04054019971274858</x:v>
       </x:c>
       <x:c r="AC21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-MAX('Model'!$M21,'Model'!$M21+'Model'!$N21*(13-'Methodology'!$B$8)+0.5*'Model'!$P21*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.582</x:v>
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6751350223953452</x:v>
       </x:c>
       <x:c r="AD21" s="46" t="n">
         <x:f>IF(OR(AC21="",AA21=""),"",AC21-AA21)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05259482268259663</x:v>
       </x:c>
       <x:c r="AE21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-MAX('Model'!$M21,'Model'!$M21+'Model'!$N21*(14-'Methodology'!$B$8)+0.5*'Model'!$P21*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.582</x:v>
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7394749942838353</x:v>
       </x:c>
       <x:c r="AF21" s="46" t="n">
         <x:f>IF(OR(AE21="",AC21=""),"",AE21-AC21)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.06433997188849017</x:v>
       </x:c>
       <x:c r="AG21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-MAX('Model'!$M21,'Model'!$M21+'Model'!$N21*(15-'Methodology'!$B$8)+0.5*'Model'!$P21*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.582</x:v>
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.811695258109552</x:v>
       </x:c>
       <x:c r="AH21" s="46" t="n">
         <x:f>IF(OR(AG21="",AE21=""),"",AG21-AE21)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.07222026382571667</x:v>
       </x:c>
       <x:c r="AI21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-MAX('Model'!$M21,'Model'!$M21+'Model'!$N21*(16-'Methodology'!$B$8)+0.5*'Model'!$P21*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.582</x:v>
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8831884501985185</x:v>
       </x:c>
       <x:c r="AJ21" s="46" t="n">
         <x:f>IF(OR(AI21="",AG21=""),"",AI21-AG21)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.07149319208896654</x:v>
       </x:c>
       <x:c r="AK21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-MAX('Model'!$M21,'Model'!$M21+'Model'!$N21*(17-'Methodology'!$B$8)+0.5*'Model'!$P21*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.582</x:v>
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.942128717758855</x:v>
       </x:c>
       <x:c r="AL21" s="46" t="n">
         <x:f>IF(OR(AK21="",AI21=""),"",AK21-AI21)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.058940267560336435</x:v>
       </x:c>
       <x:c r="AM21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-MAX('Model'!$M21,'Model'!$M21+'Model'!$N21*(18-'Methodology'!$B$8)+0.5*'Model'!$P21*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.582</x:v>
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9794025280607196</x:v>
       </x:c>
       <x:c r="AN21" s="46" t="n">
         <x:f>IF(OR(AM21="",AK21=""),"",AM21-AK21)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.03727381030186461</x:v>
       </x:c>
       <x:c r="AO21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-MAX('Model'!$M21,'Model'!$M21+'Model'!$N21*(19-'Methodology'!$B$8)+0.5*'Model'!$P21*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.582</x:v>
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.995492781678013</x:v>
       </x:c>
       <x:c r="AP21" s="46" t="n">
         <x:f>IF(OR(AO21="",AM21=""),"",AO21-AM21)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.016090253617293437</x:v>
       </x:c>
       <x:c r="AQ21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-MAX('Model'!$M21,'Model'!$M21+'Model'!$N21*(20-'Methodology'!$B$8)+0.5*'Model'!$P21*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.582</x:v>
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9995177495700065</x:v>
       </x:c>
       <x:c r="AR21" s="46" t="n">
         <x:f>IF(OR(AQ21="",AO21=""),"",AQ21-AO21)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.0040249678919934695</x:v>
       </x:c>
       <x:c r="AS21" s="24" t="n">
         <x:f>IF('Model'!$D21=0,"",Y21)</x:f>
@@ -5982,7 +5982,7 @@
       </x:c>
       <x:c r="AY21" s="17" t="str">
         <x:f>'Model'!Q21</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="46" hidden="0" customHeight="1">
@@ -6070,76 +6070,76 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-MAX('Model'!$M22,'Model'!$M22+'Model'!$N22*(12-'Methodology'!$B$8)+0.5*'Model'!$P22*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.676</x:v>
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7074235040835659</x:v>
       </x:c>
       <x:c r="AB22" s="46" t="n">
         <x:f>IF(OR(AA22="",Y22=""),"",AA22-Y22)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.03142350408356587</x:v>
       </x:c>
       <x:c r="AC22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-MAX('Model'!$M22,'Model'!$M22+'Model'!$N22*(13-'Methodology'!$B$8)+0.5*'Model'!$P22*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.676</x:v>
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7481907829093106</x:v>
       </x:c>
       <x:c r="AD22" s="46" t="n">
         <x:f>IF(OR(AC22="",AA22=""),"",AC22-AA22)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.04076727882574471</x:v>
       </x:c>
       <x:c r="AE22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-MAX('Model'!$M22,'Model'!$M22+'Model'!$N22*(14-'Methodology'!$B$8)+0.5*'Model'!$P22*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.676</x:v>
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7980619572917766</x:v>
       </x:c>
       <x:c r="AF22" s="46" t="n">
         <x:f>IF(OR(AE22="",AC22=""),"",AE22-AC22)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.04987117438246602</x:v>
       </x:c>
       <x:c r="AG22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-MAX('Model'!$M22,'Model'!$M22+'Model'!$N22*(15-'Methodology'!$B$8)+0.5*'Model'!$P22*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.676</x:v>
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8540413005442461</x:v>
       </x:c>
       <x:c r="AH22" s="46" t="n">
         <x:f>IF(OR(AG22="",AE22=""),"",AG22-AE22)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05597934325246945</x:v>
       </x:c>
       <x:c r="AI22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-MAX('Model'!$M22,'Model'!$M22+'Model'!$N22*(16-'Methodology'!$B$8)+0.5*'Model'!$P22*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.676</x:v>
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9094570762304307</x:v>
       </x:c>
       <x:c r="AJ22" s="46" t="n">
         <x:f>IF(OR(AI22="",AG22=""),"",AI22-AG22)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05541577568618461</x:v>
       </x:c>
       <x:c r="AK22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-MAX('Model'!$M22,'Model'!$M22+'Model'!$N22*(17-'Methodology'!$B$8)+0.5*'Model'!$P22*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.676</x:v>
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9551428338609307</x:v>
       </x:c>
       <x:c r="AL22" s="46" t="n">
         <x:f>IF(OR(AK22="",AI22=""),"",AK22-AI22)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.04568575763049998</x:v>
       </x:c>
       <x:c r="AM22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-MAX('Model'!$M22,'Model'!$M22+'Model'!$N22*(18-'Methodology'!$B$8)+0.5*'Model'!$P22*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.676</x:v>
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9840344954346247</x:v>
       </x:c>
       <x:c r="AN22" s="46" t="n">
         <x:f>IF(OR(AM22="",AK22=""),"",AM22-AK22)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.02889166157369405</x:v>
       </x:c>
       <x:c r="AO22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-MAX('Model'!$M22,'Model'!$M22+'Model'!$N22*(19-'Methodology'!$B$8)+0.5*'Model'!$P22*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.676</x:v>
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9965063666595124</x:v>
       </x:c>
       <x:c r="AP22" s="46" t="n">
         <x:f>IF(OR(AO22="",AM22=""),"",AO22-AM22)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.012471871224887687</x:v>
       </x:c>
       <x:c r="AQ22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-MAX('Model'!$M22,'Model'!$M22+'Model'!$N22*(20-'Methodology'!$B$8)+0.5*'Model'!$P22*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.676</x:v>
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.999626198231297</x:v>
       </x:c>
       <x:c r="AR22" s="46" t="n">
         <x:f>IF(OR(AQ22="",AO22=""),"",AQ22-AO22)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.003119831571784526</x:v>
       </x:c>
       <x:c r="AS22" s="24" t="n">
         <x:f>IF('Model'!$D22=0,"",Y22)</x:f>
@@ -6167,7 +6167,7 @@
       </x:c>
       <x:c r="AY22" s="17" t="str">
         <x:f>'Model'!Q22</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="46" hidden="0" customHeight="1">
@@ -6253,76 +6253,76 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-MAX('Model'!$M23,'Model'!$M23+'Model'!$N23*(12-'Methodology'!$B$8)+0.5*'Model'!$P23*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.33299999999999996</x:v>
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.3976897445177112</x:v>
       </x:c>
       <x:c r="AB23" s="46" t="n">
         <x:f>IF(OR(AA23="",Y23=""),"",AA23-Y23)</x:f>
-        <x:v>-5.551115123125783e-17</x:v>
+        <x:v>0.0646897445177112</x:v>
       </x:c>
       <x:c r="AC23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-MAX('Model'!$M23,'Model'!$M23+'Model'!$N23*(13-'Methodology'!$B$8)+0.5*'Model'!$P23*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.33299999999999996</x:v>
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.4816149759275006</x:v>
       </x:c>
       <x:c r="AD23" s="46" t="n">
         <x:f>IF(OR(AC23="",AA23=""),"",AC23-AA23)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.08392523140978936</x:v>
       </x:c>
       <x:c r="AE23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-MAX('Model'!$M23,'Model'!$M23+'Model'!$N23*(14-'Methodology'!$B$8)+0.5*'Model'!$P23*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.33299999999999996</x:v>
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.5842818688691822</x:v>
       </x:c>
       <x:c r="AF23" s="46" t="n">
         <x:f>IF(OR(AE23="",AC23=""),"",AE23-AC23)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.10266689294168163</x:v>
       </x:c>
       <x:c r="AG23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-MAX('Model'!$M23,'Model'!$M23+'Model'!$N23*(15-'Methodology'!$B$8)+0.5*'Model'!$P23*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.33299999999999996</x:v>
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6995232946389263</x:v>
       </x:c>
       <x:c r="AH23" s="46" t="n">
         <x:f>IF(OR(AG23="",AE23=""),"",AG23-AE23)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.11524142576974405</x:v>
       </x:c>
       <x:c r="AI23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-MAX('Model'!$M23,'Model'!$M23+'Model'!$N23*(16-'Methodology'!$B$8)+0.5*'Model'!$P23*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.33299999999999996</x:v>
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.813604536560794</x:v>
       </x:c>
       <x:c r="AJ23" s="46" t="n">
         <x:f>IF(OR(AI23="",AG23=""),"",AI23-AG23)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.11408124192186775</x:v>
       </x:c>
       <x:c r="AK23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-MAX('Model'!$M23,'Model'!$M23+'Model'!$N23*(17-'Methodology'!$B$8)+0.5*'Model'!$P23*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.33299999999999996</x:v>
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9076551548927183</x:v>
       </x:c>
       <x:c r="AL23" s="46" t="n">
         <x:f>IF(OR(AK23="",AI23=""),"",AK23-AI23)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.0940506183319243</x:v>
       </x:c>
       <x:c r="AM23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-MAX('Model'!$M23,'Model'!$M23+'Model'!$N23*(18-'Methodology'!$B$8)+0.5*'Model'!$P23*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.33299999999999996</x:v>
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9671327421447368</x:v>
       </x:c>
       <x:c r="AN23" s="46" t="n">
         <x:f>IF(OR(AM23="",AK23=""),"",AM23-AK23)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05947758725201846</x:v>
       </x:c>
       <x:c r="AO23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-MAX('Model'!$M23,'Model'!$M23+'Model'!$N23*(19-'Methodology'!$B$8)+0.5*'Model'!$P23*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.33299999999999996</x:v>
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9928078597589346</x:v>
       </x:c>
       <x:c r="AP23" s="46" t="n">
         <x:f>IF(OR(AO23="",AM23=""),"",AO23-AM23)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.02567511761419783</x:v>
       </x:c>
       <x:c r="AQ23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-MAX('Model'!$M23,'Model'!$M23+'Model'!$N23*(20-'Methodology'!$B$8)+0.5*'Model'!$P23*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.33299999999999996</x:v>
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9992304759885032</x:v>
       </x:c>
       <x:c r="AR23" s="46" t="n">
         <x:f>IF(OR(AQ23="",AO23=""),"",AQ23-AO23)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.006422616229568634</x:v>
       </x:c>
       <x:c r="AS23" s="24" t="n">
         <x:f>IF('Model'!$D23=0,"",Y23)</x:f>
@@ -6350,7 +6350,7 @@
       </x:c>
       <x:c r="AY23" s="17" t="str">
         <x:f>'Model'!Q23</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="46" hidden="0" customHeight="1">
@@ -6444,76 +6444,76 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(12-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3881</x:v>
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.4474458091010307</x:v>
       </x:c>
       <x:c r="AB24" s="46" t="n">
         <x:f>IF(OR(AA24="",Y24=""),"",AA24-Y24)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05934580910103071</x:v>
       </x:c>
       <x:c r="AC24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(13-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3881</x:v>
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.5244380866117506</x:v>
       </x:c>
       <x:c r="AD24" s="46" t="n">
         <x:f>IF(OR(AC24="",AA24=""),"",AC24-AA24)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.07699227751071991</x:v>
       </x:c>
       <x:c r="AE24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(14-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3881</x:v>
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6186238014408585</x:v>
       </x:c>
       <x:c r="AF24" s="46" t="n">
         <x:f>IF(OR(AE24="",AC24=""),"",AE24-AC24)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.09418571482910787</x:v>
       </x:c>
       <x:c r="AG24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(15-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3881</x:v>
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7243452833426672</x:v>
       </x:c>
       <x:c r="AH24" s="46" t="n">
         <x:f>IF(OR(AG24="",AE24=""),"",AG24-AE24)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.10572148190180874</x:v>
       </x:c>
       <x:c r="AI24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(16-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3881</x:v>
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8290024226709892</x:v>
       </x:c>
       <x:c r="AJ24" s="46" t="n">
         <x:f>IF(OR(AI24="",AG24=""),"",AI24-AG24)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.10465713932832199</x:v>
       </x:c>
       <x:c r="AK24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(17-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3881</x:v>
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9152836420972329</x:v>
       </x:c>
       <x:c r="AL24" s="46" t="n">
         <x:f>IF(OR(AK24="",AI24=""),"",AK24-AI24)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.08628121942624367</x:v>
       </x:c>
       <x:c r="AM24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(18-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3881</x:v>
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9698478634458237</x:v>
       </x:c>
       <x:c r="AN24" s="46" t="n">
         <x:f>IF(OR(AM24="",AK24=""),"",AM24-AK24)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05456422134859085</x:v>
       </x:c>
       <x:c r="AO24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(19-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3881</x:v>
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9934019930831965</x:v>
       </x:c>
       <x:c r="AP24" s="46" t="n">
         <x:f>IF(OR(AO24="",AM24=""),"",AO24-AM24)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.0235541296373728</x:v>
       </x:c>
       <x:c r="AQ24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-MAX('Model'!$M24,'Model'!$M24+'Model'!$N24*(20-'Methodology'!$B$8)+0.5*'Model'!$P24*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.3881</x:v>
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.999294045363366</x:v>
       </x:c>
       <x:c r="AR24" s="46" t="n">
         <x:f>IF(OR(AQ24="",AO24=""),"",AQ24-AO24)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.005892052280169424</x:v>
       </x:c>
       <x:c r="AS24" s="24" t="n">
         <x:f>IF('Model'!$D24=0,"",Y24)</x:f>
@@ -6541,7 +6541,7 @@
       </x:c>
       <x:c r="AY24" s="17" t="str">
         <x:f>'Model'!Q24</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="46" hidden="0" customHeight="1">
@@ -6624,55 +6624,55 @@
         <x:f>IF(OR(Y25="",W25=""),"",Y25-W25)</x:f>
       </x:c>
       <x:c r="AA25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-MAX('Model'!$M25,'Model'!$M25+'Model'!$N25*(12-'Methodology'!$B$8)+0.5*'Model'!$P25*POWER(12-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AB25" s="46" t="str">
         <x:f>IF(OR(AA25="",Y25=""),"",AA25-Y25)</x:f>
       </x:c>
       <x:c r="AC25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-MAX('Model'!$M25,'Model'!$M25+'Model'!$N25*(13-'Methodology'!$B$8)+0.5*'Model'!$P25*POWER(13-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AD25" s="46" t="str">
         <x:f>IF(OR(AC25="",AA25=""),"",AC25-AA25)</x:f>
       </x:c>
       <x:c r="AE25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-MAX('Model'!$M25,'Model'!$M25+'Model'!$N25*(14-'Methodology'!$B$8)+0.5*'Model'!$P25*POWER(14-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AF25" s="46" t="str">
         <x:f>IF(OR(AE25="",AC25=""),"",AE25-AC25)</x:f>
       </x:c>
       <x:c r="AG25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-MAX('Model'!$M25,'Model'!$M25+'Model'!$N25*(15-'Methodology'!$B$8)+0.5*'Model'!$P25*POWER(15-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AH25" s="46" t="str">
         <x:f>IF(OR(AG25="",AE25=""),"",AG25-AE25)</x:f>
       </x:c>
       <x:c r="AI25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-MAX('Model'!$M25,'Model'!$M25+'Model'!$N25*(16-'Methodology'!$B$8)+0.5*'Model'!$P25*POWER(16-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AJ25" s="46" t="str">
         <x:f>IF(OR(AI25="",AG25=""),"",AI25-AG25)</x:f>
       </x:c>
       <x:c r="AK25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-MAX('Model'!$M25,'Model'!$M25+'Model'!$N25*(17-'Methodology'!$B$8)+0.5*'Model'!$P25*POWER(17-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AL25" s="46" t="str">
         <x:f>IF(OR(AK25="",AI25=""),"",AK25-AI25)</x:f>
       </x:c>
       <x:c r="AM25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-MAX('Model'!$M25,'Model'!$M25+'Model'!$N25*(18-'Methodology'!$B$8)+0.5*'Model'!$P25*POWER(18-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AN25" s="46" t="str">
         <x:f>IF(OR(AM25="",AK25=""),"",AM25-AK25)</x:f>
       </x:c>
       <x:c r="AO25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-MAX('Model'!$M25,'Model'!$M25+'Model'!$N25*(19-'Methodology'!$B$8)+0.5*'Model'!$P25*POWER(19-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AP25" s="46" t="str">
         <x:f>IF(OR(AO25="",AM25=""),"",AO25-AM25)</x:f>
       </x:c>
       <x:c r="AQ25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-MAX('Model'!$M25,'Model'!$M25+'Model'!$N25*(20-'Methodology'!$B$8)+0.5*'Model'!$P25*POWER(20-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AR25" s="46" t="str">
         <x:f>IF(OR(AQ25="",AO25=""),"",AQ25-AO25)</x:f>
@@ -6793,76 +6793,76 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-MAX('Model'!$M26,'Model'!$M26+'Model'!$N26*(12-'Methodology'!$B$8)+0.5*'Model'!$P26*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.30501149491125934</x:v>
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.23966231616778544</x:v>
       </x:c>
       <x:c r="AB26" s="46" t="n">
         <x:f>IF(OR(AA26="",Y26=""),"",AA26-Y26)</x:f>
-        <x:v>0.14701149491125934</x:v>
+        <x:v>0.08166231616778544</x:v>
       </x:c>
       <x:c r="AC26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-MAX('Model'!$M26,'Model'!$M26+'Model'!$N26*(13-'Methodology'!$B$8)+0.5*'Model'!$P26*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.49376402444115486</x:v>
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.34560691114086295</x:v>
       </x:c>
       <x:c r="AD26" s="46" t="n">
         <x:f>IF(OR(AC26="",AA26=""),"",AC26-AA26)</x:f>
-        <x:v>0.18875252952989552</x:v>
+        <x:v>0.10594459497307751</x:v>
       </x:c>
       <x:c r="AE26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-MAX('Model'!$M26,'Model'!$M26+'Model'!$N26*(14-'Methodology'!$B$8)+0.5*'Model'!$P26*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.6745844950342269</x:v>
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.47521039518418506</x:v>
       </x:c>
       <x:c r="AF26" s="46" t="n">
         <x:f>IF(OR(AE26="",AC26=""),"",AE26-AC26)</x:f>
-        <x:v>0.18082047059307205</x:v>
+        <x:v>0.12960348404332211</x:v>
       </x:c>
       <x:c r="AG26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-MAX('Model'!$M26,'Model'!$M26+'Model'!$N26*(15-'Methodology'!$B$8)+0.5*'Model'!$P26*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.815399304909049</x:v>
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.6206875773402938</x:v>
       </x:c>
       <x:c r="AH26" s="46" t="n">
         <x:f>IF(OR(AG26="",AE26=""),"",AG26-AE26)</x:f>
-        <x:v>0.1408148098748221</x:v>
+        <x:v>0.14547718215610872</x:v>
       </x:c>
       <x:c r="AI26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-MAX('Model'!$M26,'Model'!$M26+'Model'!$N26*(16-'Methodology'!$B$8)+0.5*'Model'!$P26*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9075858920886734</x:v>
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7647001795864896</x:v>
       </x:c>
       <x:c r="AJ26" s="46" t="n">
         <x:f>IF(OR(AI26="",AG26=""),"",AI26-AG26)</x:f>
-        <x:v>0.09218658717962436</x:v>
+        <x:v>0.14401260224619583</x:v>
       </x:c>
       <x:c r="AK26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-MAX('Model'!$M26,'Model'!$M26+'Model'!$N26*(17-'Methodology'!$B$8)+0.5*'Model'!$P26*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9591724732042408</x:v>
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8834267472558752</x:v>
       </x:c>
       <x:c r="AL26" s="46" t="n">
         <x:f>IF(OR(AK26="",AI26=""),"",AK26-AI26)</x:f>
-        <x:v>0.051586581115567465</x:v>
+        <x:v>0.11872656766938561</x:v>
       </x:c>
       <x:c r="AM26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-MAX('Model'!$M26,'Model'!$M26+'Model'!$N26*(18-'Methodology'!$B$8)+0.5*'Model'!$P26*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9840823950181709</x:v>
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9585093986294878</x:v>
       </x:c>
       <x:c r="AN26" s="46" t="n">
         <x:f>IF(OR(AM26="",AK26=""),"",AM26-AK26)</x:f>
-        <x:v>0.024909921813930036</x:v>
+        <x:v>0.07508265137361259</x:v>
       </x:c>
       <x:c r="AO26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-MAX('Model'!$M26,'Model'!$M26+'Model'!$N26*(19-'Methodology'!$B$8)+0.5*'Model'!$P26*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9945233848107087</x:v>
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9909208664423133</x:v>
       </x:c>
       <x:c r="AP26" s="46" t="n">
         <x:f>IF(OR(AO26="",AM26=""),"",AO26-AM26)</x:f>
-        <x:v>0.010440989792537825</x:v>
+        <x:v>0.032411467812825445</x:v>
       </x:c>
       <x:c r="AQ26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-MAX('Model'!$M26,'Model'!$M26+'Model'!$N26*(20-'Methodology'!$B$8)+0.5*'Model'!$P26*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.9983371365647572</x:v>
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.999028576885037</x:v>
       </x:c>
       <x:c r="AR26" s="46" t="n">
         <x:f>IF(OR(AQ26="",AO26=""),"",AQ26-AO26)</x:f>
-        <x:v>0.003813751754048522</x:v>
+        <x:v>0.008107710442723737</x:v>
       </x:c>
       <x:c r="AS26" s="24" t="n">
         <x:f>IF('Model'!$D26=0,"",Y26)</x:f>
@@ -6890,7 +6890,7 @@
       </x:c>
       <x:c r="AY26" s="17" t="str">
         <x:f>'Model'!Q26</x:f>
-        <x:v>Velocity + acceleration — latest three observations</x:v>
+        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="46" hidden="0" customHeight="1">
@@ -6973,55 +6973,55 @@
         <x:f>IF(OR(Y27="",W27=""),"",Y27-W27)</x:f>
       </x:c>
       <x:c r="AA27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-MAX('Model'!$M27,'Model'!$M27+'Model'!$N27*(12-'Methodology'!$B$8)+0.5*'Model'!$P27*POWER(12-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AB27" s="46" t="str">
         <x:f>IF(OR(AA27="",Y27=""),"",AA27-Y27)</x:f>
       </x:c>
       <x:c r="AC27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-MAX('Model'!$M27,'Model'!$M27+'Model'!$N27*(13-'Methodology'!$B$8)+0.5*'Model'!$P27*POWER(13-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AD27" s="46" t="str">
         <x:f>IF(OR(AC27="",AA27=""),"",AC27-AA27)</x:f>
       </x:c>
       <x:c r="AE27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-MAX('Model'!$M27,'Model'!$M27+'Model'!$N27*(14-'Methodology'!$B$8)+0.5*'Model'!$P27*POWER(14-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AF27" s="46" t="str">
         <x:f>IF(OR(AE27="",AC27=""),"",AE27-AC27)</x:f>
       </x:c>
       <x:c r="AG27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-MAX('Model'!$M27,'Model'!$M27+'Model'!$N27*(15-'Methodology'!$B$8)+0.5*'Model'!$P27*POWER(15-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AH27" s="46" t="str">
         <x:f>IF(OR(AG27="",AE27=""),"",AG27-AE27)</x:f>
       </x:c>
       <x:c r="AI27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-MAX('Model'!$M27,'Model'!$M27+'Model'!$N27*(16-'Methodology'!$B$8)+0.5*'Model'!$P27*POWER(16-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AJ27" s="46" t="str">
         <x:f>IF(OR(AI27="",AG27=""),"",AI27-AG27)</x:f>
       </x:c>
       <x:c r="AK27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-MAX('Model'!$M27,'Model'!$M27+'Model'!$N27*(17-'Methodology'!$B$8)+0.5*'Model'!$P27*POWER(17-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AL27" s="46" t="str">
         <x:f>IF(OR(AK27="",AI27=""),"",AK27-AI27)</x:f>
       </x:c>
       <x:c r="AM27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-MAX('Model'!$M27,'Model'!$M27+'Model'!$N27*(18-'Methodology'!$B$8)+0.5*'Model'!$P27*POWER(18-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AN27" s="46" t="str">
         <x:f>IF(OR(AM27="",AK27=""),"",AM27-AK27)</x:f>
       </x:c>
       <x:c r="AO27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-MAX('Model'!$M27,'Model'!$M27+'Model'!$N27*(19-'Methodology'!$B$8)+0.5*'Model'!$P27*POWER(19-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AP27" s="46" t="str">
         <x:f>IF(OR(AO27="",AM27=""),"",AO27-AM27)</x:f>
       </x:c>
       <x:c r="AQ27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-MAX('Model'!$M27,'Model'!$M27+'Model'!$N27*(20-'Methodology'!$B$8)+0.5*'Model'!$P27*POWER(20-'Methodology'!$B$8,2))))</x:f>
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
       </x:c>
       <x:c r="AR27" s="46" t="str">
         <x:f>IF(OR(AQ27="",AO27=""),"",AQ27-AO27)</x:f>
@@ -7138,76 +7138,76 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-MAX('Model'!$M28,'Model'!$M28+'Model'!$N28*(12-'Methodology'!$B$8)+0.5*'Model'!$P28*POWER(12-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.704</x:v>
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7327078926195539</x:v>
       </x:c>
       <x:c r="AB28" s="46" t="n">
         <x:f>IF(OR(AA28="",Y28=""),"",AA28-Y28)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.028707892619553976</x:v>
       </x:c>
       <x:c r="AC28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-MAX('Model'!$M28,'Model'!$M28+'Model'!$N28*(13-'Methodology'!$B$8)+0.5*'Model'!$P28*POWER(13-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.704</x:v>
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.7699520732751727</x:v>
       </x:c>
       <x:c r="AD28" s="46" t="n">
         <x:f>IF(OR(AC28="",AA28=""),"",AC28-AA28)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.03724418065561874</x:v>
       </x:c>
       <x:c r="AE28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-MAX('Model'!$M28,'Model'!$M28+'Model'!$N28*(14-'Methodology'!$B$8)+0.5*'Model'!$P28*POWER(14-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.704</x:v>
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8155133930813762</x:v>
       </x:c>
       <x:c r="AF28" s="46" t="n">
         <x:f>IF(OR(AE28="",AC28=""),"",AE28-AC28)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.04556131980620348</x:v>
       </x:c>
       <x:c r="AG28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-MAX('Model'!$M28,'Model'!$M28+'Model'!$N28*(15-'Methodology'!$B$8)+0.5*'Model'!$P28*POWER(15-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.704</x:v>
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.8666550153120273</x:v>
       </x:c>
       <x:c r="AH28" s="46" t="n">
         <x:f>IF(OR(AG28="",AE28=""),"",AG28-AE28)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05114162223065111</x:v>
       </x:c>
       <x:c r="AI28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-MAX('Model'!$M28,'Model'!$M28+'Model'!$N28*(16-'Methodology'!$B$8)+0.5*'Model'!$P28*POWER(16-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.704</x:v>
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9172817733463193</x:v>
       </x:c>
       <x:c r="AJ28" s="46" t="n">
         <x:f>IF(OR(AI28="",AG28=""),"",AI28-AG28)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.05062675803429206</x:v>
       </x:c>
       <x:c r="AK28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-MAX('Model'!$M28,'Model'!$M28+'Model'!$N28*(17-'Methodology'!$B$8)+0.5*'Model'!$P28*POWER(17-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.704</x:v>
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9590193790828255</x:v>
       </x:c>
       <x:c r="AL28" s="46" t="n">
         <x:f>IF(OR(AK28="",AI28=""),"",AK28-AI28)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.0417376057365062</x:v>
       </x:c>
       <x:c r="AM28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-MAX('Model'!$M28,'Model'!$M28+'Model'!$N28*(18-'Methodology'!$B$8)+0.5*'Model'!$P28*POWER(18-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.704</x:v>
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9854142303970646</x:v>
       </x:c>
       <x:c r="AN28" s="46" t="n">
         <x:f>IF(OR(AM28="",AK28=""),"",AM28-AK28)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.02639485131423902</x:v>
       </x:c>
       <x:c r="AO28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-MAX('Model'!$M28,'Model'!$M28+'Model'!$N28*(19-'Methodology'!$B$8)+0.5*'Model'!$P28*POWER(19-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.704</x:v>
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9968082855901719</x:v>
       </x:c>
       <x:c r="AP28" s="46" t="n">
         <x:f>IF(OR(AO28="",AM28=""),"",AO28-AM28)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.011394055193107322</x:v>
       </x:c>
       <x:c r="AQ28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-MAX('Model'!$M28,'Model'!$M28+'Model'!$N28*(20-'Methodology'!$B$8)+0.5*'Model'!$P28*POWER(20-'Methodology'!$B$8,2))))</x:f>
-        <x:v>0.704</x:v>
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
+        <x:v>0.9996585020878515</x:v>
       </x:c>
       <x:c r="AR28" s="46" t="n">
         <x:f>IF(OR(AQ28="",AO28=""),"",AQ28-AO28)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.0028502164976795807</x:v>
       </x:c>
       <x:c r="AS28" s="24" t="n">
         <x:f>IF('Model'!$D28=0,"",Y28)</x:f>
@@ -7235,7 +7235,7 @@
       </x:c>
       <x:c r="AY28" s="17" t="str">
         <x:f>'Model'!Q28</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8794,7 +8794,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f0c1b5e2b4d484e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re173a23f1dac45fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9610,7 +9610,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c7b77da95ff4712"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R304642bdcb484e1e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9774,67 +9774,67 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="B3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="C3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="H3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="I3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="J3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="K3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="L3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="M3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="N3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="O3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="P3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="Q3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="R3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="S3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="T3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
       <x:c r="U3" s="6" t="str">
-        <x:v>Helper sheet. Latest three comparable quarter frontiers determine velocity and acceleration; sparse histories fall back to constant velocity, flat, or blank. Evidence credits feed category confidence.</x:v>
+        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
       </x:c>
     </x:row>
     <x:row r="4"/>
@@ -9966,8 +9966,8 @@
         <x:v>-0.0718969048742778</x:v>
       </x:c>
       <x:c r="Q6" s="17" t="str">
-        <x:f>IF(D6=0,"Ungraded — no normalized observation",IF(D6=1,"Flat — one observation",IF(D6=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Velocity + acceleration — latest three observations</x:v>
+        <x:f>IF(D6=0,"Ungraded — no normalized observation",IF(D6=1,"Shared frontier transfer — one observation",IF(D6=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
       </x:c>
       <x:c r="R6" s="24" t="n">
         <x:f>IF(D6=0,"",J6)</x:f>
@@ -10046,8 +10046,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q7" s="17" t="str">
-        <x:f>IF(D7=0,"Ungraded — no normalized observation",IF(D7=1,"Flat — one observation",IF(D7=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Constant velocity — two observations</x:v>
+        <x:f>IF(D7=0,"Ungraded — no normalized observation",IF(D7=1,"Shared frontier transfer — one observation",IF(D7=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — velocity contributor</x:v>
       </x:c>
       <x:c r="R7" s="24" t="n">
         <x:f>IF(D7=0,"",J7)</x:f>
@@ -10123,8 +10123,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q8" s="17" t="str">
-        <x:f>IF(D8=0,"Ungraded — no normalized observation",IF(D8=1,"Flat — one observation",IF(D8=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:f>IF(D8=0,"Ungraded — no normalized observation",IF(D8=1,"Shared frontier transfer — one observation",IF(D8=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
       <x:c r="R8" s="24" t="n">
         <x:f>IF(D8=0,"",J8)</x:f>
@@ -10200,8 +10200,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q9" s="17" t="str">
-        <x:f>IF(D9=0,"Ungraded — no normalized observation",IF(D9=1,"Flat — one observation",IF(D9=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:f>IF(D9=0,"Ungraded — no normalized observation",IF(D9=1,"Shared frontier transfer — one observation",IF(D9=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
       <x:c r="R9" s="24" t="n">
         <x:f>IF(D9=0,"",J9)</x:f>
@@ -10277,8 +10277,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q10" s="17" t="str">
-        <x:f>IF(D10=0,"Ungraded — no normalized observation",IF(D10=1,"Flat — one observation",IF(D10=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:f>IF(D10=0,"Ungraded — no normalized observation",IF(D10=1,"Shared frontier transfer — one observation",IF(D10=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
       <x:c r="R10" s="24" t="n">
         <x:f>IF(D10=0,"",J10)</x:f>
@@ -10354,8 +10354,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q11" s="17" t="str">
-        <x:f>IF(D11=0,"Ungraded — no normalized observation",IF(D11=1,"Flat — one observation",IF(D11=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:f>IF(D11=0,"Ungraded — no normalized observation",IF(D11=1,"Shared frontier transfer — one observation",IF(D11=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
       <x:c r="R11" s="24" t="n">
         <x:f>IF(D11=0,"",J11)</x:f>
@@ -10431,8 +10431,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q12" s="17" t="str">
-        <x:f>IF(D12=0,"Ungraded — no normalized observation",IF(D12=1,"Flat — one observation",IF(D12=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:f>IF(D12=0,"Ungraded — no normalized observation",IF(D12=1,"Shared frontier transfer — one observation",IF(D12=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
       <x:c r="R12" s="24" t="n">
         <x:f>IF(D12=0,"",J12)</x:f>
@@ -10508,8 +10508,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q13" s="17" t="str">
-        <x:f>IF(D13=0,"Ungraded — no normalized observation",IF(D13=1,"Flat — one observation",IF(D13=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:f>IF(D13=0,"Ungraded — no normalized observation",IF(D13=1,"Shared frontier transfer — one observation",IF(D13=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
       <x:c r="R13" s="24" t="n">
         <x:f>IF(D13=0,"",J13)</x:f>
@@ -10591,8 +10591,8 @@
         <x:v>-0.06052809013923022</x:v>
       </x:c>
       <x:c r="Q14" s="17" t="str">
-        <x:f>IF(D14=0,"Ungraded — no normalized observation",IF(D14=1,"Flat — one observation",IF(D14=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Velocity + acceleration — latest three observations</x:v>
+        <x:f>IF(D14=0,"Ungraded — no normalized observation",IF(D14=1,"Shared frontier transfer — one observation",IF(D14=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
       </x:c>
       <x:c r="R14" s="24" t="n">
         <x:f>IF(D14=0,"",J14)</x:f>
@@ -10674,8 +10674,8 @@
         <x:v>-0.004969950297574337</x:v>
       </x:c>
       <x:c r="Q15" s="17" t="str">
-        <x:f>IF(D15=0,"Ungraded — no normalized observation",IF(D15=1,"Flat — one observation",IF(D15=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Velocity + acceleration — latest three observations</x:v>
+        <x:f>IF(D15=0,"Ungraded — no normalized observation",IF(D15=1,"Shared frontier transfer — one observation",IF(D15=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
       </x:c>
       <x:c r="R15" s="24" t="n">
         <x:f>IF(D15=0,"",J15)</x:f>
@@ -10751,8 +10751,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q16" s="17" t="str">
-        <x:f>IF(D16=0,"Ungraded — no normalized observation",IF(D16=1,"Flat — one observation",IF(D16=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:f>IF(D16=0,"Ungraded — no normalized observation",IF(D16=1,"Shared frontier transfer — one observation",IF(D16=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
       <x:c r="R16" s="24" t="n">
         <x:f>IF(D16=0,"",J16)</x:f>
@@ -10834,8 +10834,8 @@
         <x:v>0.15016501951621217</x:v>
       </x:c>
       <x:c r="Q17" s="17" t="str">
-        <x:f>IF(D17=0,"Ungraded — no normalized observation",IF(D17=1,"Flat — one observation",IF(D17=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Velocity + acceleration — latest three observations</x:v>
+        <x:f>IF(D17=0,"Ungraded — no normalized observation",IF(D17=1,"Shared frontier transfer — one observation",IF(D17=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
       </x:c>
       <x:c r="R17" s="24" t="n">
         <x:f>IF(D17=0,"",J17)</x:f>
@@ -10908,7 +10908,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q18" s="17" t="str">
-        <x:f>IF(D18=0,"Ungraded — no normalized observation",IF(D18=1,"Flat — one observation",IF(D18=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
+        <x:f>IF(D18=0,"Ungraded — no normalized observation",IF(D18=1,"Shared frontier transfer — one observation",IF(D18=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
         <x:v>Ungraded — no normalized observation</x:v>
       </x:c>
       <x:c r="R18" s="24" t="str">
@@ -10983,8 +10983,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q19" s="17" t="str">
-        <x:f>IF(D19=0,"Ungraded — no normalized observation",IF(D19=1,"Flat — one observation",IF(D19=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:f>IF(D19=0,"Ungraded — no normalized observation",IF(D19=1,"Shared frontier transfer — one observation",IF(D19=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
       <x:c r="R19" s="24" t="n">
         <x:f>IF(D19=0,"",J19)</x:f>
@@ -11066,8 +11066,8 @@
         <x:v>0.17695542656782204</x:v>
       </x:c>
       <x:c r="Q20" s="17" t="str">
-        <x:f>IF(D20=0,"Ungraded — no normalized observation",IF(D20=1,"Flat — one observation",IF(D20=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Velocity + acceleration — latest three observations</x:v>
+        <x:f>IF(D20=0,"Ungraded — no normalized observation",IF(D20=1,"Shared frontier transfer — one observation",IF(D20=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
       </x:c>
       <x:c r="R20" s="24" t="n">
         <x:f>IF(D20=0,"",J20)</x:f>
@@ -11143,8 +11143,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q21" s="17" t="str">
-        <x:f>IF(D21=0,"Ungraded — no normalized observation",IF(D21=1,"Flat — one observation",IF(D21=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:f>IF(D21=0,"Ungraded — no normalized observation",IF(D21=1,"Shared frontier transfer — one observation",IF(D21=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
       <x:c r="R21" s="24" t="n">
         <x:f>IF(D21=0,"",J21)</x:f>
@@ -11220,8 +11220,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q22" s="17" t="str">
-        <x:f>IF(D22=0,"Ungraded — no normalized observation",IF(D22=1,"Flat — one observation",IF(D22=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:f>IF(D22=0,"Ungraded — no normalized observation",IF(D22=1,"Shared frontier transfer — one observation",IF(D22=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
       <x:c r="R22" s="24" t="n">
         <x:f>IF(D22=0,"",J22)</x:f>
@@ -11297,8 +11297,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q23" s="17" t="str">
-        <x:f>IF(D23=0,"Ungraded — no normalized observation",IF(D23=1,"Flat — one observation",IF(D23=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:f>IF(D23=0,"Ungraded — no normalized observation",IF(D23=1,"Shared frontier transfer — one observation",IF(D23=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
       <x:c r="R23" s="24" t="n">
         <x:f>IF(D23=0,"",J23)</x:f>
@@ -11374,8 +11374,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q24" s="17" t="str">
-        <x:f>IF(D24=0,"Ungraded — no normalized observation",IF(D24=1,"Flat — one observation",IF(D24=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:f>IF(D24=0,"Ungraded — no normalized observation",IF(D24=1,"Shared frontier transfer — one observation",IF(D24=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
       <x:c r="R24" s="24" t="n">
         <x:f>IF(D24=0,"",J24)</x:f>
@@ -11448,7 +11448,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q25" s="17" t="str">
-        <x:f>IF(D25=0,"Ungraded — no normalized observation",IF(D25=1,"Flat — one observation",IF(D25=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
+        <x:f>IF(D25=0,"Ungraded — no normalized observation",IF(D25=1,"Shared frontier transfer — one observation",IF(D25=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
         <x:v>Ungraded — no normalized observation</x:v>
       </x:c>
       <x:c r="R25" s="24" t="str">
@@ -11529,8 +11529,8 @@
         <x:v>0.18034796332026068</x:v>
       </x:c>
       <x:c r="Q26" s="17" t="str">
-        <x:f>IF(D26=0,"Ungraded — no normalized observation",IF(D26=1,"Flat — one observation",IF(D26=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Velocity + acceleration — latest three observations</x:v>
+        <x:f>IF(D26=0,"Ungraded — no normalized observation",IF(D26=1,"Shared frontier transfer — one observation",IF(D26=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
       </x:c>
       <x:c r="R26" s="24" t="n">
         <x:f>IF(D26=0,"",J26)</x:f>
@@ -11603,7 +11603,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q27" s="17" t="str">
-        <x:f>IF(D27=0,"Ungraded — no normalized observation",IF(D27=1,"Flat — one observation",IF(D27=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
+        <x:f>IF(D27=0,"Ungraded — no normalized observation",IF(D27=1,"Shared frontier transfer — one observation",IF(D27=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
         <x:v>Ungraded — no normalized observation</x:v>
       </x:c>
       <x:c r="R27" s="24" t="str">
@@ -11678,8 +11678,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q28" s="17" t="str">
-        <x:f>IF(D28=0,"Ungraded — no normalized observation",IF(D28=1,"Flat — one observation",IF(D28=2,"Constant velocity — two observations","Velocity + acceleration — latest three observations")))</x:f>
-        <x:v>Flat — one observation</x:v>
+        <x:f>IF(D28=0,"Ungraded — no normalized observation",IF(D28=1,"Shared frontier transfer — one observation",IF(D28=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:v>Shared frontier transfer — one observation</x:v>
       </x:c>
       <x:c r="R28" s="24" t="n">
         <x:f>IF(D28=0,"",J28)</x:f>
@@ -11705,7 +11705,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3940efb08a1b4cf0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec132fc97b6a466b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12000,16 +12000,16 @@
     </x:row>
     <x:row r="13" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A13" s="17" t="str">
-        <x:v>Missing-history rule</x:v>
+        <x:v>Sparse-history rule</x:v>
       </x:c>
       <x:c r="B13" s="17" t="str">
-        <x:v>Blank</x:v>
+        <x:v>Shared frontier</x:v>
       </x:c>
       <x:c r="C13" s="17" t="str">
         <x:v>rule</x:v>
       </x:c>
       <x:c r="D13" s="17" t="str">
-        <x:v>No score is fabricated before release or without a normalized observation</x:v>
+        <x:v>Every graded benchmark receives the pooled frontier depth gain; sparse evidence widens uncertainty instead of forcing zero progress</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -12132,13 +12132,13 @@
     </x:row>
     <x:row r="20" ht="38" hidden="0" customHeight="1">
       <x:c r="A20" s="17" t="str">
-        <x:v>Projection</x:v>
+        <x:v>Feedback</x:v>
       </x:c>
       <x:c r="B20" s="17" t="str">
-        <x:v>d(h) = MAX(d_now, d_now + v·h + 0.5·a·h²)</x:v>
+        <x:v>k = a / v; dv/dh = k·v; v(h) = v·EXP(k·h)</x:v>
       </x:c>
       <x:c r="C20" s="17" t="str">
-        <x:v>A monotonic frontier forecast; negative acceleration can flatten but not reverse capability.</x:v>
+        <x:v>The conjectured causal loop: progress raises the next quarter's rate of progress. At h = 0, dv/dh equals the measured initial acceleration a.</x:v>
       </x:c>
       <x:c r="D20" s="17"/>
       <x:c r="E20" s="17"/>
@@ -12150,13 +12150,13 @@
     </x:row>
     <x:row r="21" ht="38" hidden="0" customHeight="1">
       <x:c r="A21" s="17" t="str">
-        <x:v>Back-transform</x:v>
+        <x:v>Projection</x:v>
       </x:c>
       <x:c r="B21" s="17" t="str">
-        <x:v>score(h) = 1 - 2^(-d(h))</x:v>
+        <x:v>Δd(h) = v·(EXP(k·h) - 1) / k</x:v>
       </x:c>
       <x:c r="C21" s="17" t="str">
-        <x:v>Approaches 100% asymptotically rather than overshooting it.</x:v>
+        <x:v>Continuous shared-frontier depth gain; when k = 0, Δd = v·h. Each graded benchmark receives the same gain from its current depth.</x:v>
       </x:c>
       <x:c r="D21" s="17"/>
       <x:c r="E21" s="17"/>
@@ -12168,13 +12168,13 @@
     </x:row>
     <x:row r="22" ht="38" hidden="0" customHeight="1">
       <x:c r="A22" s="17" t="str">
-        <x:v>Evidence count</x:v>
+        <x:v>Back-transform</x:v>
       </x:c>
       <x:c r="B22" s="17" t="str">
-        <x:v>3+ points: v + a; 2 points: v only; 1 point: flat; 0 points: blank</x:v>
+        <x:v>score_b(h) = 1 - 2^(-(d_b,now + MAX(0,Δd(h))))</x:v>
       </x:c>
       <x:c r="C22" s="17" t="str">
-        <x:v>Forecast strength is visible instead of disguised by a single smooth curve.</x:v>
+        <x:v>Approaches 100% asymptotically. Evidence confidence reports uncertainty; it does not convert missing history into permanent zero progress.</x:v>
       </x:c>
       <x:c r="D22" s="17"/>
       <x:c r="E22" s="17"/>

--- a/data/reports/personal-ai-four-year-capability-report-card.xlsx
+++ b/data/reports/personal-ai-four-year-capability-report-card.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb476777359f446ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report Card" sheetId="2" r:id="R5556f148f8e84843"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="R01f1ad4543ab448c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog" sheetId="4" r:id="Rcb18794c03764b5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="5" r:id="Rbe2d11aea2f5487f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" r:id="Rd45443569aed4bac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb0da1c4f666e49f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report Card" sheetId="2" r:id="Ra62135cd9bf94e69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="R821f2d6423dc4f54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog" sheetId="4" r:id="R4b382c85d5394d2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="5" r:id="Reacb70d7a7f647f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METR Horizon" sheetId="6" r:id="Rda69219fd7784c9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="7" r:id="Re3486c2007df45ca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,15 +19,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="8">
+  <x:numFmts count="9">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0%"/>
     <x:numFmt numFmtId="202" formatCode="0.0%"/>
-    <x:numFmt numFmtId="203" formatCode="0.000"/>
-    <x:numFmt numFmtId="204" formatCode="0.0"/>
-    <x:numFmt numFmtId="205" formatCode="0"/>
-    <x:numFmt numFmtId="206" formatCode="+0.000;-0.000;0.000"/>
-    <x:numFmt numFmtId="207" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.0"/>
+    <x:numFmt numFmtId="204" formatCode="0.000"/>
+    <x:numFmt numFmtId="205" formatCode="+0.000;-0.000;0.000"/>
+    <x:numFmt numFmtId="206" formatCode="0.00x"/>
+    <x:numFmt numFmtId="207" formatCode="0"/>
+    <x:numFmt numFmtId="208" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="8">
     <x:font>
@@ -209,6 +211,12 @@
     <x:xf numFmtId="205" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="206" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
@@ -265,10 +273,7 @@
     <x:xf numFmtId="202" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="206" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="205" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -277,16 +282,13 @@
     <x:xf numFmtId="202" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="207" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="208" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="207" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="208" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="206" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="206" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="205" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -657,7 +659,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb88b64215b414f32"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Refc11a42d41a4166"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -703,7 +705,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ProjectionModelTable" displayName="ProjectionModelTable" ref="A5:U28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ProjectionModelTable" displayName="ProjectionModelTable" ref="A5:U28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="21">
     <x:tableColumn id="1" name="Benchmark ID"/>
     <x:tableColumn id="2" name="Benchmark Name"/>
@@ -720,12 +722,52 @@
     <x:tableColumn id="13" name="Latest depth"/>
     <x:tableColumn id="14" name="Recent gap velocity"/>
     <x:tableColumn id="15" name="Prior gap velocity"/>
-    <x:tableColumn id="16" name="Gap acceleration"/>
+    <x:tableColumn id="16" name="Benchmark-local acceleration (diagnostic)"/>
     <x:tableColumn id="17" name="Projection basis"/>
     <x:tableColumn id="18" name="Current score"/>
     <x:tableColumn id="19" name="Letter"/>
     <x:tableColumn id="20" name="GPA"/>
     <x:tableColumn id="21" name="Evidence credits"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="MetrHorizonObservationsTable" displayName="MetrHorizonObservationsTable" ref="A5:L15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
+    <x:tableColumn id="1" name="Metric"/>
+    <x:tableColumn id="2" name="Model / system"/>
+    <x:tableColumn id="3" name="Release date"/>
+    <x:tableColumn id="4" name="Horizon (minutes)"/>
+    <x:tableColumn id="5" name="log₂ minutes"/>
+    <x:tableColumn id="6" name="Elapsed quarters to latest"/>
+    <x:tableColumn id="7" name="Fitted log₂ minutes"/>
+    <x:tableColumn id="8" name="Residual"/>
+    <x:tableColumn id="9" name="Harness"/>
+    <x:tableColumn id="10" name="Source URL"/>
+    <x:tableColumn id="11" name="Comparability note"/>
+    <x:tableColumn id="12" name="Observation role"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="MetrHorizonFitTable" displayName="MetrHorizonFitTable" ref="N5:Y7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
+    <x:tableColumn id="1" name="Metric"/>
+    <x:tableColumn id="2" name="Observations"/>
+    <x:tableColumn id="3" name="Source velocity (doublings/qtr)"/>
+    <x:tableColumn id="4" name="Quadratic current velocity"/>
+    <x:tableColumn id="5" name="Quadratic acceleration"/>
+    <x:tableColumn id="6" name="Relative acceleration k"/>
+    <x:tableColumn id="7" name="Velocity growth / qtr"/>
+    <x:tableColumn id="8" name="Fit R²"/>
+    <x:tableColumn id="9" name="Evidence role"/>
+    <x:tableColumn id="10" name="β₀"/>
+    <x:tableColumn id="11" name="β₁"/>
+    <x:tableColumn id="12" name="β₂"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1134,67 +1176,67 @@
       <x:c r="F5" s="9" t="str">
         <x:v>CURRENT LETTER</x:v>
       </x:c>
-      <x:c r="G5" s="49" t="str">
+      <x:c r="G5" s="51" t="str">
         <x:v>2028-Q4 SCORE</x:v>
       </x:c>
-      <x:c r="H5" s="49" t="str">
+      <x:c r="H5" s="51" t="str">
         <x:v>2028-Q4 SCORE</x:v>
       </x:c>
-      <x:c r="I5" s="49" t="str">
+      <x:c r="I5" s="51" t="str">
         <x:v>2028-Q4 SCORE</x:v>
       </x:c>
       <x:c r="J5" s="9" t="str">
-        <x:v>GAP ACCELERATION / QTR²</x:v>
+        <x:v>METR H50 ACCELERATION / QTR²</x:v>
       </x:c>
       <x:c r="K5" s="9" t="str">
-        <x:v>GAP ACCELERATION / QTR²</x:v>
+        <x:v>METR H50 ACCELERATION / QTR²</x:v>
       </x:c>
       <x:c r="L5" s="9" t="str">
-        <x:v>GAP ACCELERATION / QTR²</x:v>
+        <x:v>METR H50 ACCELERATION / QTR²</x:v>
       </x:c>
       <x:c r="M5" s="9" t="str">
+        <x:v>METR H80 GUARDRAIL / QTR²</x:v>
+      </x:c>
+      <x:c r="N5" s="9" t="str">
+        <x:v>METR H80 GUARDRAIL / QTR²</x:v>
+      </x:c>
+      <x:c r="O5" s="9" t="str">
+        <x:v>METR H80 GUARDRAIL / QTR²</x:v>
+      </x:c>
+      <x:c r="P5" s="9" t="str">
         <x:v>OVERALL CONFIDENCE</x:v>
       </x:c>
-      <x:c r="N5" s="9" t="str">
+      <x:c r="Q5" s="9" t="str">
         <x:v>OVERALL CONFIDENCE</x:v>
       </x:c>
-      <x:c r="O5" s="9" t="str">
+      <x:c r="R5" s="9" t="str">
         <x:v>OVERALL CONFIDENCE</x:v>
       </x:c>
-      <x:c r="P5" s="9" t="str">
-        <x:v>ACCELERATION COVERAGE</x:v>
-      </x:c>
-      <x:c r="Q5" s="9" t="str">
-        <x:v>ACCELERATION COVERAGE</x:v>
-      </x:c>
-      <x:c r="R5" s="9" t="str">
-        <x:v>ACCELERATION COVERAGE</x:v>
-      </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="55" t="n">
+      <x:c r="A6" s="57" t="n">
         <x:f>D17</x:f>
         <x:v>0.45660533834944794</x:v>
       </x:c>
-      <x:c r="D6" s="54" t="str">
+      <x:c r="D6" s="56" t="str">
         <x:f>IF(A6&gt;='Methodology'!$G$7,"A",IF(A6&gt;='Methodology'!$G$8,"B",IF(A6&gt;='Methodology'!$G$9,"C",IF(A6&gt;='Methodology'!$G$10,"D","F"))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="G6" s="55" t="n">
+      <x:c r="G6" s="57" t="n">
         <x:f>F17</x:f>
-        <x:v>0.9993730805998696</x:v>
-      </x:c>
-      <x:c r="J6" s="56" t="n">
+        <x:v>0.9871465644823302</x:v>
+      </x:c>
+      <x:c r="J6" s="58" t="n">
         <x:f>H17</x:f>
-        <x:v>0.046536604581876154</x:v>
-      </x:c>
-      <x:c r="M6" s="54" t="str">
+        <x:v>0.209120615134694</x:v>
+      </x:c>
+      <x:c r="M6" s="58" t="n">
+        <x:f>I17</x:f>
+        <x:v>0.3429173634620018</x:v>
+      </x:c>
+      <x:c r="P6" s="56" t="str">
         <x:f>J17</x:f>
         <x:v>Low</x:v>
-      </x:c>
-      <x:c r="P6" s="57" t="n">
-        <x:f>I17</x:f>
-        <x:v>0.3</x:v>
       </x:c>
     </x:row>
     <x:row r="7"/>
@@ -1236,7 +1278,7 @@
         <x:v>CATEGORY REPORT CARD</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A12" s="13" t="str">
         <x:v>Category</x:v>
       </x:c>
@@ -1256,13 +1298,13 @@
         <x:v>2028-Q4 score</x:v>
       </x:c>
       <x:c r="G12" s="13" t="str">
-        <x:v>Gap velocity / qtr</x:v>
+        <x:v>Economic gap velocity / qtr</x:v>
       </x:c>
       <x:c r="H12" s="13" t="str">
-        <x:v>Gap acceleration / qtr²</x:v>
+        <x:v>METR H50 accel. / qtr²</x:v>
       </x:c>
       <x:c r="I12" s="13" t="str">
-        <x:v>Accel. coverage</x:v>
+        <x:v>METR H80 guardrail / qtr²</x:v>
       </x:c>
       <x:c r="J12" s="13" t="str">
         <x:v>Confidence</x:v>
@@ -1287,26 +1329,20 @@
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A13,'Report Card'!$AS$6:$AS$28),"")</x:f>
         <x:v>0.38254856862232545</x:v>
       </x:c>
-      <x:c r="E13" s="60" t="n">
+      <x:c r="E13" s="61" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A13,'Report Card'!$AU$6:$AU$28),"")</x:f>
         <x:v>0.7142857142857143</x:v>
       </x:c>
       <x:c r="F13" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A13,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.9992876406259662</x:v>
-      </x:c>
-      <x:c r="G13" s="62" t="n">
+        <x:v>0.9853948286212714</x:v>
+      </x:c>
+      <x:c r="G13" s="27" t="n">
         <x:f>IFERROR(AVERAGEIFS('Model'!$N$6:$N$28,'Model'!$C$6:$C$28,A13,'Model'!$D$6:$D$28,"&gt;=2"),"")</x:f>
         <x:v>0.006549844650824333</x:v>
       </x:c>
-      <x:c r="H13" s="62" t="n">
-        <x:f>IFERROR(AVERAGEIFS('Model'!$P$6:$P$28,'Model'!$C$6:$C$28,A13,'Model'!$D$6:$D$28,"&gt;=3"),"")</x:f>
-        <x:v>-0.0718969048742778</x:v>
-      </x:c>
-      <x:c r="I13" s="19" t="n">
-        <x:f>IFERROR(COUNTIFS('Model'!$C$6:$C$28,A13,'Model'!$D$6:$D$28,"&gt;=3")/COUNTIFS('Model'!$C$6:$C$28,A13,'Model'!$D$6:$D$28,"&gt;0"),"")</x:f>
-        <x:v>0.14285714285714285</x:v>
-      </x:c>
+      <x:c r="H13" s="27"/>
+      <x:c r="I13" s="27"/>
       <x:c r="J13" s="17" t="str">
         <x:f>IF(K13&gt;=0.8,"High",IF(K13&gt;=0.5,"Medium","Low"))</x:f>
         <x:v>Low</x:v>
@@ -1332,26 +1368,20 @@
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A14,'Report Card'!$AS$6:$AS$28),"")</x:f>
         <x:v>0.5063285714285714</x:v>
       </x:c>
-      <x:c r="E14" s="60" t="n">
+      <x:c r="E14" s="61" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A14,'Report Card'!$AU$6:$AU$28),"")</x:f>
         <x:v>0.42857142857142855</x:v>
       </x:c>
       <x:c r="F14" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A14,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.9994304467495118</x:v>
-      </x:c>
-      <x:c r="G14" s="62" t="n">
+        <x:v>0.988322715842724</x:v>
+      </x:c>
+      <x:c r="G14" s="27" t="n">
         <x:f>IFERROR(AVERAGEIFS('Model'!$N$6:$N$28,'Model'!$C$6:$C$28,A14,'Model'!$D$6:$D$28,"&gt;=2"),"")</x:f>
         <x:v>0.23660304317034014</x:v>
       </x:c>
-      <x:c r="H14" s="62" t="n">
-        <x:f>IFERROR(AVERAGEIFS('Model'!$P$6:$P$28,'Model'!$C$6:$C$28,A14,'Model'!$D$6:$D$28,"&gt;=3"),"")</x:f>
-        <x:v>0.06540560141180742</x:v>
-      </x:c>
-      <x:c r="I14" s="19" t="n">
-        <x:f>IFERROR(COUNTIFS('Model'!$C$6:$C$28,A14,'Model'!$D$6:$D$28,"&gt;=3")/COUNTIFS('Model'!$C$6:$C$28,A14,'Model'!$D$6:$D$28,"&gt;0"),"")</x:f>
-        <x:v>0.5714285714285714</x:v>
-      </x:c>
+      <x:c r="H14" s="27"/>
+      <x:c r="I14" s="27"/>
       <x:c r="J14" s="17" t="str">
         <x:f>IF(K14&gt;=0.8,"High",IF(K14&gt;=0.5,"Medium","Low"))</x:f>
         <x:v>Medium</x:v>
@@ -1377,24 +1407,19 @@
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A15,'Report Card'!$AS$6:$AS$28),"")</x:f>
         <x:v>0.49477499999999996</x:v>
       </x:c>
-      <x:c r="E15" s="60" t="n">
+      <x:c r="E15" s="61" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A15,'Report Card'!$AU$6:$AU$28),"")</x:f>
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="F15" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A15,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.9994171172882931</x:v>
-      </x:c>
-      <x:c r="G15" s="62" t="str">
+        <x:v>0.9880494281278704</x:v>
+      </x:c>
+      <x:c r="G15" s="27" t="str">
         <x:f>IFERROR(AVERAGEIFS('Model'!$N$6:$N$28,'Model'!$C$6:$C$28,A15,'Model'!$D$6:$D$28,"&gt;=2"),"")</x:f>
       </x:c>
-      <x:c r="H15" s="62" t="str">
-        <x:f>IFERROR(AVERAGEIFS('Model'!$P$6:$P$28,'Model'!$C$6:$C$28,A15,'Model'!$D$6:$D$28,"&gt;=3"),"")</x:f>
-      </x:c>
-      <x:c r="I15" s="19" t="n">
-        <x:f>IFERROR(COUNTIFS('Model'!$C$6:$C$28,A15,'Model'!$D$6:$D$28,"&gt;=3")/COUNTIFS('Model'!$C$6:$C$28,A15,'Model'!$D$6:$D$28,"&gt;0"),"")</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="H15" s="27"/>
+      <x:c r="I15" s="27"/>
       <x:c r="J15" s="17" t="str">
         <x:f>IF(K15&gt;=0.8,"High",IF(K15&gt;=0.5,"Medium","Low"))</x:f>
         <x:v>Low</x:v>
@@ -1420,26 +1445,20 @@
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A16,'Report Card'!$AS$6:$AS$28),"")</x:f>
         <x:v>0.431</x:v>
       </x:c>
-      <x:c r="E16" s="60" t="n">
+      <x:c r="E16" s="61" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A16,'Report Card'!$AU$6:$AU$28),"")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="F16" s="24" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,A16,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.9993435394864443</x:v>
-      </x:c>
-      <x:c r="G16" s="62" t="n">
+        <x:v>0.986540896837564</x:v>
+      </x:c>
+      <x:c r="G16" s="27" t="n">
         <x:f>IFERROR(AVERAGEIFS('Model'!$N$6:$N$28,'Model'!$C$6:$C$28,A16,'Model'!$D$6:$D$28,"&gt;=2"),"")</x:f>
         <x:v>0.18665713536174539</x:v>
       </x:c>
-      <x:c r="H16" s="62" t="n">
-        <x:f>IFERROR(AVERAGEIFS('Model'!$P$6:$P$28,'Model'!$C$6:$C$28,A16,'Model'!$D$6:$D$28,"&gt;=3"),"")</x:f>
-        <x:v>0.18034796332026068</x:v>
-      </x:c>
-      <x:c r="I16" s="19" t="n">
-        <x:f>IFERROR(COUNTIFS('Model'!$C$6:$C$28,A16,'Model'!$D$6:$D$28,"&gt;=3")/COUNTIFS('Model'!$C$6:$C$28,A16,'Model'!$D$6:$D$28,"&gt;0"),"")</x:f>
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="H16" s="27"/>
+      <x:c r="I16" s="27"/>
       <x:c r="J16" s="17" t="str">
         <x:f>IF(K16&gt;=0.8,"High",IF(K16&gt;=0.5,"Medium","Low"))</x:f>
         <x:v>Low</x:v>
@@ -1450,42 +1469,42 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="58" t="str">
+      <x:c r="A17" s="59" t="str">
         <x:v>Overall (confidence-weighted)</x:v>
       </x:c>
-      <x:c r="B17" s="58" t="n">
+      <x:c r="B17" s="59" t="n">
         <x:f>SUM(B13:B16)</x:f>
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C17" s="58" t="n">
+      <x:c r="C17" s="59" t="n">
         <x:f>SUM(C13:C16)</x:f>
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D17" s="59" t="n">
+      <x:c r="D17" s="60" t="n">
         <x:f>IFERROR(SUMPRODUCT(D13:D16,K13:K16)/SUM(K13:K16),"")</x:f>
         <x:v>0.45660533834944794</x:v>
       </x:c>
-      <x:c r="E17" s="61" t="n">
+      <x:c r="E17" s="62" t="n">
         <x:f>IFERROR(SUMPRODUCT(E13:E16,K13:K16)/SUM(K13:K16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="F17" s="59" t="n">
+      <x:c r="F17" s="60" t="n">
         <x:f>IFERROR(SUMPRODUCT(F13:F16,K13:K16)/SUM(K13:K16),"")</x:f>
-        <x:v>0.9993730805998696</x:v>
+        <x:v>0.9871465644823302</x:v>
       </x:c>
       <x:c r="G17" s="63" t="n">
         <x:f>IFERROR(SUMPRODUCT(G13:G16,K13:K16)/SUM(K13:K16),"")</x:f>
         <x:v>0.12060641981551987</x:v>
       </x:c>
       <x:c r="H17" s="63" t="n">
-        <x:f>IFERROR((IF(H13="",0,H13*K13)+IF(H14="",0,H14*K14)+IF(H15="",0,H15*K15)+IF(H16="",0,H16*K16))/(IF(H13="",0,K13)+IF(H14="",0,K14)+IF(H15="",0,K15)+IF(H16="",0,K16)),"")</x:f>
-        <x:v>0.046536604581876154</x:v>
-      </x:c>
-      <x:c r="I17" s="64" t="n">
-        <x:f>COUNTIF('Model'!$D$6:$D$28,"&gt;=3")/COUNTIF('Model'!$D$6:$D$28,"&gt;0")</x:f>
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="J17" s="58" t="str">
+        <x:f>'METR Horizon'!$O$15</x:f>
+        <x:v>0.209120615134694</x:v>
+      </x:c>
+      <x:c r="I17" s="63" t="n">
+        <x:f>'METR Horizon'!$O$18</x:f>
+        <x:v>0.3429173634620018</x:v>
+      </x:c>
+      <x:c r="J17" s="59" t="str">
         <x:f>IF(K17&gt;=0.8,"High",IF(K17&gt;=0.5,"Medium","Low"))</x:f>
         <x:v>Low</x:v>
       </x:c>
@@ -1798,7 +1817,7 @@
         <x:f>IFERROR((IF(B32="",0,B32*$K$13)+IF(C32="",0,C32*$K$14)+IF(D32="",0,D32*$K$15)+IF(E32="",0,E32*$K$16))/(IF(B32="",0,$K$13)+IF(C32="",0,$K$14)+IF(D32="",0,$K$15)+IF(E32="",0,$K$16)),"")</x:f>
         <x:v>0.45660533834944794</x:v>
       </x:c>
-      <x:c r="H32" s="42" t="str">
+      <x:c r="H32" s="44" t="str">
         <x:v>Observed</x:v>
       </x:c>
       <x:c r="I32" s="17" t="str">
@@ -1820,25 +1839,25 @@
       </x:c>
       <x:c r="B33" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AA$6:$AA$28),"")</x:f>
-        <x:v>0.4424327894136026</x:v>
+        <x:v>0.439756326830644</x:v>
       </x:c>
       <x:c r="C33" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AA$6:$AA$28),"")</x:f>
-        <x:v>0.5542078496744175</x:v>
+        <x:v>0.5520679354408163</x:v>
       </x:c>
       <x:c r="D33" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AA$6:$AA$28),"")</x:f>
-        <x:v>0.5437748143537641</x:v>
+        <x:v>0.5415848189315059</x:v>
       </x:c>
       <x:c r="E33" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AA$6:$AA$28),"")</x:f>
-        <x:v>0.4861851043936697</x:v>
+        <x:v>0.4837186639062336</x:v>
       </x:c>
       <x:c r="F33" s="19" t="n">
         <x:f>IFERROR((IF(B33="",0,B33*$K$13)+IF(C33="",0,C33*$K$14)+IF(D33="",0,D33*$K$15)+IF(E33="",0,E33*$K$16))/(IF(B33="",0,$K$13)+IF(C33="",0,$K$14)+IF(D33="",0,$K$15)+IF(E33="",0,$K$16)),"")</x:f>
-        <x:v>0.5093070801978395</x:v>
-      </x:c>
-      <x:c r="H33" s="41" t="str">
+        <x:v>0.5069516309988237</x:v>
+      </x:c>
+      <x:c r="H33" s="43" t="str">
         <x:v>Carried</x:v>
       </x:c>
       <x:c r="I33" s="17" t="str">
@@ -1860,29 +1879,29 @@
       </x:c>
       <x:c r="B34" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AC$6:$AC$28),"")</x:f>
-        <x:v>0.5201235754313581</x:v>
+        <x:v>0.5083333246341348</x:v>
       </x:c>
       <x:c r="C34" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AC$6:$AC$28),"")</x:f>
-        <x:v>0.6163240249116865</x:v>
+        <x:v>0.6068973564204667</x:v>
       </x:c>
       <x:c r="D34" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AC$6:$AC$28),"")</x:f>
-        <x:v>0.6073447169609767</x:v>
+        <x:v>0.5976974327293203</x:v>
       </x:c>
       <x:c r="E34" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AC$6:$AC$28),"")</x:f>
-        <x:v>0.5577794922080178</x:v>
+        <x:v>0.5469144227284541</x:v>
       </x:c>
       <x:c r="F34" s="19" t="n">
         <x:f>IFERROR((IF(B34="",0,B34*$K$13)+IF(C34="",0,C34*$K$14)+IF(D34="",0,D34*$K$15)+IF(E34="",0,E34*$K$16))/(IF(B34="",0,$K$13)+IF(C34="",0,$K$14)+IF(D34="",0,$K$15)+IF(E34="",0,$K$16)),"")</x:f>
-        <x:v>0.577679677992254</x:v>
-      </x:c>
-      <x:c r="H34" s="43" t="str">
+        <x:v>0.5673035430993775</x:v>
+      </x:c>
+      <x:c r="H34" s="45" t="str">
         <x:v>Projected</x:v>
       </x:c>
       <x:c r="I34" s="17" t="str">
-        <x:v>Gold cells extrapolate failure-gap velocity/acceleration.</x:v>
+        <x:v>Gold cells extrapolate economic failure-gap velocity under METR-derived acceleration feedback.</x:v>
       </x:c>
       <x:c r="J34" s="17"/>
       <x:c r="K34" s="17"/>
@@ -1900,23 +1919,23 @@
       </x:c>
       <x:c r="B35" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AE$6:$AE$28),"")</x:f>
-        <x:v>0.6151637853497977</x:v>
+        <x:v>0.587410140740915</x:v>
       </x:c>
       <x:c r="C35" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AE$6:$AE$28),"")</x:f>
-        <x:v>0.6923115986830656</x:v>
+        <x:v>0.6701217053847245</x:v>
       </x:c>
       <x:c r="D35" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AE$6:$AE$28),"")</x:f>
-        <x:v>0.6851106554714131</x:v>
+        <x:v>0.6624014440550343</x:v>
       </x:c>
       <x:c r="E35" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AE$6:$AE$28),"")</x:f>
-        <x:v>0.6453618941327806</x:v>
+        <x:v>0.6197860788110534</x:v>
       </x:c>
       <x:c r="F35" s="19" t="n">
         <x:f>IFERROR((IF(B35="",0,B35*$K$13)+IF(C35="",0,C35*$K$14)+IF(D35="",0,D35*$K$15)+IF(E35="",0,E35*$K$16))/(IF(B35="",0,$K$13)+IF(C35="",0,$K$14)+IF(D35="",0,$K$15)+IF(E35="",0,$K$16)),"")</x:f>
-        <x:v>0.6613208197560287</x:v>
+        <x:v>0.6368959313305393</x:v>
       </x:c>
       <x:c r="H35" s="17" t="str">
         <x:v>Δ score</x:v>
@@ -1940,29 +1959,29 @@
       </x:c>
       <x:c r="B36" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AG$6:$AG$28),"")</x:f>
-        <x:v>0.7218444199987707</x:v>
+        <x:v>0.6739743760895377</x:v>
       </x:c>
       <x:c r="C36" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AG$6:$AG$28),"")</x:f>
-        <x:v>0.7776060503927473</x:v>
+        <x:v>0.7393324765431778</x:v>
       </x:c>
       <x:c r="D36" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AG$6:$AG$28),"")</x:f>
-        <x:v>0.7724012841588479</x:v>
+        <x:v>0.7332319799839944</x:v>
       </x:c>
       <x:c r="E36" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AG$6:$AG$28),"")</x:f>
-        <x:v>0.7436712963261605</x:v>
+        <x:v>0.6995576161331938</x:v>
       </x:c>
       <x:c r="F36" s="19" t="n">
         <x:f>IFERROR((IF(B36="",0,B36*$K$13)+IF(C36="",0,C36*$K$14)+IF(D36="",0,D36*$K$15)+IF(E36="",0,E36*$K$16))/(IF(B36="",0,$K$13)+IF(C36="",0,$K$14)+IF(D36="",0,$K$15)+IF(E36="",0,$K$16)),"")</x:f>
-        <x:v>0.7552062403983184</x:v>
+        <x:v>0.7130777020429603</x:v>
       </x:c>
       <x:c r="H36" s="17" t="str">
-        <x:v>Gap velocity</x:v>
+        <x:v>Economic gap velocity</x:v>
       </x:c>
       <x:c r="I36" s="17" t="str">
-        <x:v>Failure-gap halvings per quarter, estimated only from benchmarks with at least two observations.</x:v>
+        <x:v>Failure-gap halvings per quarter from economic-work benchmarks with at least two observations. This anchors the initial economic progress rate.</x:v>
       </x:c>
       <x:c r="J36" s="17"/>
       <x:c r="K36" s="17"/>
@@ -1980,29 +1999,29 @@
       </x:c>
       <x:c r="B37" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AI$6:$AI$28),"")</x:f>
-        <x:v>0.8274510558805968</x:v>
+        <x:v>0.7623625126941986</x:v>
       </x:c>
       <x:c r="C37" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AI$6:$AI$28),"")</x:f>
-        <x:v>0.8620418070235887</x:v>
+        <x:v>0.8100015129071042</x:v>
       </x:c>
       <x:c r="D37" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AI$6:$AI$28),"")</x:f>
-        <x:v>0.8588131214151832</x:v>
+        <x:v>0.8055549094277401</x:v>
       </x:c>
       <x:c r="E37" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AI$6:$AI$28),"")</x:f>
-        <x:v>0.8409909764664045</x:v>
+        <x:v>0.781009933127585</x:v>
       </x:c>
       <x:c r="F37" s="19" t="n">
         <x:f>IFERROR((IF(B37="",0,B37*$K$13)+IF(C37="",0,C37*$K$14)+IF(D37="",0,D37*$K$15)+IF(E37="",0,E37*$K$16))/(IF(B37="",0,$K$13)+IF(C37="",0,$K$14)+IF(D37="",0,$K$15)+IF(E37="",0,$K$16)),"")</x:f>
-        <x:v>0.8481464770683281</x:v>
+        <x:v>0.7908646163430304</x:v>
       </x:c>
       <x:c r="H37" s="17" t="str">
-        <x:v>Gap acceleration</x:v>
+        <x:v>METR H50 acceleration</x:v>
       </x:c>
       <x:c r="I37" s="17" t="str">
-        <x:v>Change in failure-gap velocity per quarter², estimated only from benchmarks with at least three observations. Positive means progress is speeding up.</x:v>
+        <x:v>Task-horizon doublings per quarter². This real rate, not a multiplier, determines how quickly capability velocity compounds.</x:v>
       </x:c>
       <x:c r="J37" s="17"/>
       <x:c r="K37" s="17"/>
@@ -2020,29 +2039,29 @@
       </x:c>
       <x:c r="B38" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AK$6:$AK$28),"")</x:f>
-        <x:v>0.9145150572651771</x:v>
+        <x:v>0.8445889873614946</x:v>
       </x:c>
       <x:c r="C38" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AK$6:$AK$28),"")</x:f>
-        <x:v>0.9316521565137644</x:v>
+        <x:v>0.8757441108569992</x:v>
       </x:c>
       <x:c r="D38" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AK$6:$AK$28),"")</x:f>
-        <x:v>0.9300525871524342</x:v>
+        <x:v>0.8728361052331197</x:v>
       </x:c>
       <x:c r="E38" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AK$6:$AK$28),"")</x:f>
-        <x:v>0.9212230631693503</x:v>
+        <x:v>0.8567840939732696</x:v>
       </x:c>
       <x:c r="F38" s="19" t="n">
         <x:f>IFERROR((IF(B38="",0,B38*$K$13)+IF(C38="",0,C38*$K$14)+IF(D38="",0,D38*$K$15)+IF(E38="",0,E38*$K$16))/(IF(B38="",0,$K$13)+IF(C38="",0,$K$14)+IF(D38="",0,$K$15)+IF(E38="",0,$K$16)),"")</x:f>
-        <x:v>0.9247680721655871</x:v>
+        <x:v>0.8632288948971795</x:v>
       </x:c>
       <x:c r="H38" s="17" t="str">
-        <x:v>Acceleration coverage</x:v>
+        <x:v>METR H80 guardrail</x:v>
       </x:c>
       <x:c r="I38" s="17" t="str">
-        <x:v>Benchmarks with a 3+ point acceleration estimate divided by graded benchmarks. Coverage prevents a sparse estimate from looking universal.</x:v>
+        <x:v>Higher-reliability task-horizon acceleration. The slower positive relative acceleration controls; H80 currently confirms rather than constrains H50.</x:v>
       </x:c>
       <x:c r="J38" s="17"/>
       <x:c r="K38" s="17"/>
@@ -2060,29 +2079,29 @@
       </x:c>
       <x:c r="B39" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AM$6:$AM$28),"")</x:f>
-        <x:v>0.9695743097262906</x:v>
+        <x:v>0.9121378817463913</x:v>
       </x:c>
       <x:c r="C39" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AM$6:$AM$28),"")</x:f>
-        <x:v>0.9756737239300851</x:v>
+        <x:v>0.9297515315019272</x:v>
       </x:c>
       <x:c r="D39" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AM$6:$AM$28),"")</x:f>
-        <x:v>0.9751044072714762</x:v>
+        <x:v>0.9281074811243535</x:v>
       </x:c>
       <x:c r="E39" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AM$6:$AM$28),"")</x:f>
-        <x:v>0.9719618145132762</x:v>
+        <x:v>0.9190324246815915</x:v>
       </x:c>
       <x:c r="F39" s="19" t="n">
         <x:f>IFERROR((IF(B39="",0,B39*$K$13)+IF(C39="",0,C39*$K$14)+IF(D39="",0,D39*$K$15)+IF(E39="",0,E39*$K$16))/(IF(B39="",0,$K$13)+IF(C39="",0,$K$14)+IF(D39="",0,$K$15)+IF(E39="",0,$K$16)),"")</x:f>
-        <x:v>0.9732235495310044</x:v>
+        <x:v>0.922676013712278</x:v>
       </x:c>
       <x:c r="H39" s="17" t="str">
-        <x:v>Confidence</x:v>
+        <x:v>Transfer coefficient</x:v>
       </x:c>
       <x:c r="I39" s="17" t="str">
-        <x:v>Evidence coverage and longitudinal depth: one credit per distinct quarterly observation, capped at three per benchmark. Category weight = credits ÷ maximum credits. High ≥80%; Medium ≥50%; Low &lt;50%.</x:v>
+        <x:v>Economic gap velocity divided by H50 horizon velocity. It preserves the economic data's current rate while importing METR's relative acceleration.</x:v>
       </x:c>
       <x:c r="J39" s="17"/>
       <x:c r="K39" s="17"/>
@@ -2100,29 +2119,29 @@
       </x:c>
       <x:c r="B40" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AO$6:$AO$28),"")</x:f>
-        <x:v>0.9933421330022913</x:v>
+        <x:v>0.9591506123323177</x:v>
       </x:c>
       <x:c r="C40" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AO$6:$AO$28),"")</x:f>
-        <x:v>0.9946768303638789</x:v>
+        <x:v>0.9673396569559615</x:v>
       </x:c>
       <x:c r="D40" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AO$6:$AO$28),"")</x:f>
-        <x:v>0.9945522502949141</x:v>
+        <x:v>0.9665752951063545</x:v>
       </x:c>
       <x:c r="E40" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AO$6:$AO$28),"")</x:f>
-        <x:v>0.9938645760162426</x:v>
+        <x:v>0.9623560649522802</x:v>
       </x:c>
       <x:c r="F40" s="19" t="n">
         <x:f>IFERROR((IF(B40="",0,B40*$K$13)+IF(C40="",0,C40*$K$14)+IF(D40="",0,D40*$K$15)+IF(E40="",0,E40*$K$16))/(IF(B40="",0,$K$13)+IF(C40="",0,$K$14)+IF(D40="",0,$K$15)+IF(E40="",0,$K$16)),"")</x:f>
-        <x:v>0.994140673743486</x:v>
+        <x:v>0.964050064411599</x:v>
       </x:c>
       <x:c r="H40" s="17" t="str">
-        <x:v>Direct stewardship</x:v>
+        <x:v>Confidence</x:v>
       </x:c>
       <x:c r="I40" s="17" t="str">
-        <x:v>Low confidence: all 7 sources are graded, but 4 newly normalized series and EnterpriseArena each have one observation. Only Vending-Bench has a 3-point acceleration estimate.</x:v>
+        <x:v>Evidence coverage and longitudinal depth: one credit per distinct quarterly observation, capped at three per benchmark. Category weight = credits ÷ maximum credits. High ≥80%; Medium ≥50%; Low &lt;50%.</x:v>
       </x:c>
       <x:c r="J40" s="17"/>
       <x:c r="K40" s="17"/>
@@ -2134,35 +2153,35 @@
       <x:c r="Q40" s="17"/>
       <x:c r="R40" s="17"/>
     </x:row>
-    <x:row r="41" ht="21.600000381469727" hidden="0" customHeight="1">
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
       <x:c r="A41" s="17" t="str">
         <x:v>2028-Q4</x:v>
       </x:c>
       <x:c r="B41" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,B$21,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.9992876406259662</x:v>
+        <x:v>0.9853948286212714</x:v>
       </x:c>
       <x:c r="C41" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,C$21,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.9994304467495118</x:v>
+        <x:v>0.988322715842724</x:v>
       </x:c>
       <x:c r="D41" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,D$21,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.9994171172882931</x:v>
+        <x:v>0.9880494281278704</x:v>
       </x:c>
       <x:c r="E41" s="19" t="n">
         <x:f>IFERROR(AVERAGEIF('Report Card'!$A$6:$A$28,E$21,'Report Card'!$AQ$6:$AQ$28),"")</x:f>
-        <x:v>0.9993435394864443</x:v>
+        <x:v>0.986540896837564</x:v>
       </x:c>
       <x:c r="F41" s="19" t="n">
         <x:f>IFERROR((IF(B41="",0,B41*$K$13)+IF(C41="",0,C41*$K$14)+IF(D41="",0,D41*$K$15)+IF(E41="",0,E41*$K$16))/(IF(B41="",0,$K$13)+IF(C41="",0,$K$14)+IF(D41="",0,$K$15)+IF(E41="",0,$K$16)),"")</x:f>
-        <x:v>0.9993730805998696</x:v>
+        <x:v>0.9871465644823302</x:v>
       </x:c>
       <x:c r="H41" s="17" t="str">
-        <x:v>Caution</x:v>
+        <x:v>Direct stewardship</x:v>
       </x:c>
       <x:c r="I41" s="17" t="str">
-        <x:v>The composite uses continuous confidence weights. The forecast conjectures that progress raises future progress and transfers across benchmarks; confidence and acceleration coverage expose how weakly that causal feedback is presently measured.</x:v>
+        <x:v>Low confidence: all 7 sources are graded, but 4 newly normalized series and EnterpriseArena each have one observation. Only Vending-Bench has three release-quarter observations.</x:v>
       </x:c>
       <x:c r="J41" s="17"/>
       <x:c r="K41" s="17"/>
@@ -2173,6 +2192,23 @@
       <x:c r="P41" s="17"/>
       <x:c r="Q41" s="17"/>
       <x:c r="R41" s="17"/>
+    </x:row>
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
+      <x:c r="H42" s="17" t="str">
+        <x:v>Caution</x:v>
+      </x:c>
+      <x:c r="I42" s="17" t="str">
+        <x:v>The composite uses continuous confidence weights. The METR-to-economic transfer and quadratic acceleration fit are conjectural and low-confidence; the workbook exposes both as refutation targets.</x:v>
+      </x:c>
+      <x:c r="J42" s="17"/>
+      <x:c r="K42" s="17"/>
+      <x:c r="L42" s="17"/>
+      <x:c r="M42" s="17"/>
+      <x:c r="N42" s="17"/>
+      <x:c r="O42" s="17"/>
+      <x:c r="P42" s="17"/>
+      <x:c r="Q42" s="17"/>
+      <x:c r="R42" s="17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2203,6 +2239,7 @@
     <x:mergeCell ref="I39:R39"/>
     <x:mergeCell ref="I40:R40"/>
     <x:mergeCell ref="I41:R41"/>
+    <x:mergeCell ref="I42:R42"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="J13:J17">
     <x:cfRule type="expression" dxfId="5" priority="1">
@@ -2216,7 +2253,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ea0620aef5144a1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97793d73ec7f4592"/>
 </x:worksheet>
 </file>
 
@@ -2589,157 +2626,157 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="B3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="C3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="H3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="I3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="J3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="K3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="L3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="M3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="N3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="O3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="P3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="Q3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="R3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="S3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="T3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="U3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="V3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="W3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="X3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="Y3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="Z3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AA3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AB3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AC3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AD3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AE3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AF3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AG3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AH3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AI3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AJ3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AK3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AL3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AM3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AN3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AO3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AP3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AQ3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AR3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AS3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AT3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AU3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AV3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AW3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AX3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
       <x:c r="AY3" s="6" t="str">
-        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Δ score is quarter-over-quarter percentage-point change; acceleration is failure-gap acceleration per quarter². As of 2026-08-26.</x:v>
+        <x:v>Blue = observed release-quarter frontier; gray = carried frontier; gold = projected. Economic benchmarks set level and velocity; METR H50/H80 supplies the shared acceleration feedback. As of 2026-08-26.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="32" hidden="0" customHeight="1">
@@ -2821,58 +2858,58 @@
       <x:c r="Z4" s="13" t="str">
         <x:v>2026-Q3</x:v>
       </x:c>
-      <x:c r="AA4" s="28" t="str">
+      <x:c r="AA4" s="30" t="str">
         <x:v>2026-Q4</x:v>
       </x:c>
-      <x:c r="AB4" s="28" t="str">
+      <x:c r="AB4" s="30" t="str">
         <x:v>2026-Q4</x:v>
       </x:c>
-      <x:c r="AC4" s="28" t="str">
+      <x:c r="AC4" s="30" t="str">
         <x:v>2027-Q1</x:v>
       </x:c>
-      <x:c r="AD4" s="28" t="str">
+      <x:c r="AD4" s="30" t="str">
         <x:v>2027-Q1</x:v>
       </x:c>
-      <x:c r="AE4" s="28" t="str">
+      <x:c r="AE4" s="30" t="str">
         <x:v>2027-Q2</x:v>
       </x:c>
-      <x:c r="AF4" s="28" t="str">
+      <x:c r="AF4" s="30" t="str">
         <x:v>2027-Q2</x:v>
       </x:c>
-      <x:c r="AG4" s="28" t="str">
+      <x:c r="AG4" s="30" t="str">
         <x:v>2027-Q3</x:v>
       </x:c>
-      <x:c r="AH4" s="28" t="str">
+      <x:c r="AH4" s="30" t="str">
         <x:v>2027-Q3</x:v>
       </x:c>
-      <x:c r="AI4" s="28" t="str">
+      <x:c r="AI4" s="30" t="str">
         <x:v>2027-Q4</x:v>
       </x:c>
-      <x:c r="AJ4" s="28" t="str">
+      <x:c r="AJ4" s="30" t="str">
         <x:v>2027-Q4</x:v>
       </x:c>
-      <x:c r="AK4" s="28" t="str">
+      <x:c r="AK4" s="30" t="str">
         <x:v>2028-Q1</x:v>
       </x:c>
-      <x:c r="AL4" s="28" t="str">
+      <x:c r="AL4" s="30" t="str">
         <x:v>2028-Q1</x:v>
       </x:c>
-      <x:c r="AM4" s="28" t="str">
+      <x:c r="AM4" s="30" t="str">
         <x:v>2028-Q2</x:v>
       </x:c>
-      <x:c r="AN4" s="28" t="str">
+      <x:c r="AN4" s="30" t="str">
         <x:v>2028-Q2</x:v>
       </x:c>
-      <x:c r="AO4" s="28" t="str">
+      <x:c r="AO4" s="30" t="str">
         <x:v>2028-Q3</x:v>
       </x:c>
-      <x:c r="AP4" s="28" t="str">
+      <x:c r="AP4" s="30" t="str">
         <x:v>2028-Q3</x:v>
       </x:c>
-      <x:c r="AQ4" s="28" t="str">
+      <x:c r="AQ4" s="30" t="str">
         <x:v>2028-Q4</x:v>
       </x:c>
-      <x:c r="AR4" s="28" t="str">
+      <x:c r="AR4" s="30" t="str">
         <x:v>2028-Q4</x:v>
       </x:c>
       <x:c r="AS4" s="13" t="str">
@@ -2968,58 +3005,58 @@
       <x:c r="Z5" s="13" t="str">
         <x:v>Δ score</x:v>
       </x:c>
-      <x:c r="AA5" s="28" t="str">
+      <x:c r="AA5" s="30" t="str">
         <x:v>Score</x:v>
       </x:c>
-      <x:c r="AB5" s="28" t="str">
+      <x:c r="AB5" s="30" t="str">
         <x:v>Δ score</x:v>
       </x:c>
-      <x:c r="AC5" s="28" t="str">
+      <x:c r="AC5" s="30" t="str">
         <x:v>Score</x:v>
       </x:c>
-      <x:c r="AD5" s="28" t="str">
+      <x:c r="AD5" s="30" t="str">
         <x:v>Δ score</x:v>
       </x:c>
-      <x:c r="AE5" s="28" t="str">
+      <x:c r="AE5" s="30" t="str">
         <x:v>Score</x:v>
       </x:c>
-      <x:c r="AF5" s="28" t="str">
+      <x:c r="AF5" s="30" t="str">
         <x:v>Δ score</x:v>
       </x:c>
-      <x:c r="AG5" s="28" t="str">
+      <x:c r="AG5" s="30" t="str">
         <x:v>Score</x:v>
       </x:c>
-      <x:c r="AH5" s="28" t="str">
+      <x:c r="AH5" s="30" t="str">
         <x:v>Δ score</x:v>
       </x:c>
-      <x:c r="AI5" s="28" t="str">
+      <x:c r="AI5" s="30" t="str">
         <x:v>Score</x:v>
       </x:c>
-      <x:c r="AJ5" s="28" t="str">
+      <x:c r="AJ5" s="30" t="str">
         <x:v>Δ score</x:v>
       </x:c>
-      <x:c r="AK5" s="28" t="str">
+      <x:c r="AK5" s="30" t="str">
         <x:v>Score</x:v>
       </x:c>
-      <x:c r="AL5" s="28" t="str">
+      <x:c r="AL5" s="30" t="str">
         <x:v>Δ score</x:v>
       </x:c>
-      <x:c r="AM5" s="28" t="str">
+      <x:c r="AM5" s="30" t="str">
         <x:v>Score</x:v>
       </x:c>
-      <x:c r="AN5" s="28" t="str">
+      <x:c r="AN5" s="30" t="str">
         <x:v>Δ score</x:v>
       </x:c>
-      <x:c r="AO5" s="28" t="str">
+      <x:c r="AO5" s="30" t="str">
         <x:v>Score</x:v>
       </x:c>
-      <x:c r="AP5" s="28" t="str">
+      <x:c r="AP5" s="30" t="str">
         <x:v>Δ score</x:v>
       </x:c>
-      <x:c r="AQ5" s="28" t="str">
+      <x:c r="AQ5" s="30" t="str">
         <x:v>Score</x:v>
       </x:c>
-      <x:c r="AR5" s="28" t="str">
+      <x:c r="AR5" s="30" t="str">
         <x:v>Δ score</x:v>
       </x:c>
       <x:c r="AS5" s="13" t="str">
@@ -3035,10 +3072,10 @@
         <x:v>Overall GPA</x:v>
       </x:c>
       <x:c r="AW5" s="13" t="str">
-        <x:v>Gap velocity (halvings/qtr)</x:v>
+        <x:v>Economic gap velocity (halvings/qtr)</x:v>
       </x:c>
       <x:c r="AX5" s="13" t="str">
-        <x:v>Gap acceleration (halvings/qtr²)</x:v>
+        <x:v>Local acceleration (diagnostic)</x:v>
       </x:c>
       <x:c r="AY5" s="13" t="str">
         <x:v>Projection basis</x:v>
@@ -3057,148 +3094,148 @@
       <x:c r="D6" s="17" t="str">
         <x:v>Frontier ending balance / $63,000 published good-strategy target</x:v>
       </x:c>
-      <x:c r="E6" s="44" t="str">
+      <x:c r="E6" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F6" s="44" t="str">
+      <x:c r="F6" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G6" s="44" t="str">
+      <x:c r="G6" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H6" s="44" t="str">
+      <x:c r="H6" s="46" t="str">
         <x:f>IF(OR(G6="",E6=""),"",G6-E6)</x:f>
       </x:c>
-      <x:c r="I6" s="44" t="str">
+      <x:c r="I6" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J6" s="44" t="str">
+      <x:c r="J6" s="46" t="str">
         <x:f>IF(OR(I6="",G6=""),"",I6-G6)</x:f>
       </x:c>
-      <x:c r="K6" s="44" t="str">
+      <x:c r="K6" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L6" s="44" t="str">
+      <x:c r="L6" s="46" t="str">
         <x:f>IF(OR(K6="",I6=""),"",K6-I6)</x:f>
       </x:c>
-      <x:c r="M6" s="44" t="str">
+      <x:c r="M6" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N6" s="44" t="str">
+      <x:c r="N6" s="46" t="str">
         <x:f>IF(OR(M6="",K6=""),"",M6-K6)</x:f>
       </x:c>
-      <x:c r="O6" s="44" t="str">
+      <x:c r="O6" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P6" s="44" t="str">
+      <x:c r="P6" s="46" t="str">
         <x:f>IF(OR(O6="",M6=""),"",O6-M6)</x:f>
       </x:c>
-      <x:c r="Q6" s="44" t="str">
+      <x:c r="Q6" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R6" s="44" t="str">
+      <x:c r="R6" s="46" t="str">
         <x:f>IF(OR(Q6="",O6=""),"",Q6-O6)</x:f>
       </x:c>
-      <x:c r="S6" s="44" t="str">
+      <x:c r="S6" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T6" s="44" t="str">
+      <x:c r="T6" s="46" t="str">
         <x:f>IF(OR(S6="",Q6=""),"",S6-Q6)</x:f>
       </x:c>
-      <x:c r="U6" s="45" t="n">
+      <x:c r="U6" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
         <x:v>0.12726333333333334</x:v>
       </x:c>
-      <x:c r="V6" s="45" t="str">
+      <x:c r="V6" s="47" t="str">
         <x:f>IF(OR(U6="",S6=""),"",U6-S6)</x:f>
       </x:c>
-      <x:c r="W6" s="45" t="n">
+      <x:c r="W6" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.17359936507936508</x:v>
       </x:c>
-      <x:c r="X6" s="45" t="n">
+      <x:c r="X6" s="47" t="n">
         <x:f>IF(OR(W6="",U6=""),"",W6-U6)</x:f>
         <x:v>0.046336031746031736</x:v>
       </x:c>
-      <x:c r="Y6" s="45" t="n">
+      <x:c r="Y6" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B6,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.17749</x:v>
       </x:c>
-      <x:c r="Z6" s="45" t="n">
+      <x:c r="Z6" s="47" t="n">
         <x:f>IF(OR(Y6="",W6=""),"",Y6-W6)</x:f>
         <x:v>0.0038906349206349333</x:v>
       </x:c>
-      <x:c r="AA6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.25726205661658574</x:v>
-      </x:c>
-      <x:c r="AB6" s="46" t="n">
+      <x:c r="AA6" s="48" t="n">
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.25369672803078414</x:v>
+      </x:c>
+      <x:c r="AB6" s="48" t="n">
         <x:f>IF(OR(AA6="",Y6=""),"",AA6-Y6)</x:f>
-        <x:v>0.07977205661658573</x:v>
-      </x:c>
-      <x:c r="AC6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.3607543236133861</x:v>
-      </x:c>
-      <x:c r="AD6" s="46" t="n">
+        <x:v>0.07620672803078413</x:v>
+      </x:c>
+      <x:c r="AC6" s="48" t="n">
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.34504847423265517</x:v>
+      </x:c>
+      <x:c r="AD6" s="48" t="n">
         <x:f>IF(OR(AC6="",AA6=""),"",AC6-AA6)</x:f>
-        <x:v>0.10349226699680036</x:v>
-      </x:c>
-      <x:c r="AE6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.4873578410248741</x:v>
-      </x:c>
-      <x:c r="AF6" s="46" t="n">
+        <x:v>0.09135174620187103</x:v>
+      </x:c>
+      <x:c r="AE6" s="48" t="n">
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.45038707852878657</x:v>
+      </x:c>
+      <x:c r="AF6" s="48" t="n">
         <x:f>IF(OR(AE6="",AC6=""),"",AE6-AC6)</x:f>
-        <x:v>0.126603517411488</x:v>
-      </x:c>
-      <x:c r="AG6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6294676237982958</x:v>
-      </x:c>
-      <x:c r="AH6" s="46" t="n">
+        <x:v>0.1053386042961314</x:v>
+      </x:c>
+      <x:c r="AG6" s="48" t="n">
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.5656997097464205</x:v>
+      </x:c>
+      <x:c r="AH6" s="48" t="n">
         <x:f>IF(OR(AG6="",AE6=""),"",AG6-AE6)</x:f>
-        <x:v>0.14210978277342168</x:v>
-      </x:c>
-      <x:c r="AI6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7701467276860849</x:v>
-      </x:c>
-      <x:c r="AJ6" s="46" t="n">
+        <x:v>0.11531263121763391</x:v>
+      </x:c>
+      <x:c r="AI6" s="48" t="n">
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.683441968535624</x:v>
+      </x:c>
+      <x:c r="AJ6" s="48" t="n">
         <x:f>IF(OR(AI6="",AG6=""),"",AI6-AG6)</x:f>
-        <x:v>0.14067910388778915</x:v>
-      </x:c>
-      <x:c r="AK6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8861250996264014</x:v>
-      </x:c>
-      <x:c r="AL6" s="46" t="n">
+        <x:v>0.11774225878920352</x:v>
+      </x:c>
+      <x:c r="AK6" s="48" t="n">
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7929762480385834</x:v>
+      </x:c>
+      <x:c r="AL6" s="48" t="n">
         <x:f>IF(OR(AK6="",AI6=""),"",AK6-AI6)</x:f>
-        <x:v>0.11597837194031646</x:v>
-      </x:c>
-      <x:c r="AM6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9594697927158433</x:v>
-      </x:c>
-      <x:c r="AN6" s="46" t="n">
+        <x:v>0.10953427950295935</x:v>
+      </x:c>
+      <x:c r="AM6" s="48" t="n">
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8829584527677609</x:v>
+      </x:c>
+      <x:c r="AN6" s="48" t="n">
         <x:f>IF(OR(AM6="",AK6=""),"",AM6-AK6)</x:f>
-        <x:v>0.07334469308944191</x:v>
-      </x:c>
-      <x:c r="AO6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9911310235836901</x:v>
-      </x:c>
-      <x:c r="AP6" s="46" t="n">
+        <x:v>0.0899822047291775</x:v>
+      </x:c>
+      <x:c r="AO6" s="48" t="n">
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9455843356483303</x:v>
+      </x:c>
+      <x:c r="AP6" s="48" t="n">
         <x:f>IF(OR(AO6="",AM6=""),"",AO6-AM6)</x:f>
-        <x:v>0.03166123086784678</x:v>
-      </x:c>
-      <x:c r="AQ6" s="46" t="n">
-        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9990510626766174</x:v>
-      </x:c>
-      <x:c r="AR6" s="46" t="n">
+        <x:v>0.06262588288056947</x:v>
+      </x:c>
+      <x:c r="AQ6" s="48" t="n">
+        <x:f>IF('Model'!$D6=0,"",1-POWER(2,-('Model'!$M6+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9805443814725214</x:v>
+      </x:c>
+      <x:c r="AR6" s="48" t="n">
         <x:f>IF(OR(AQ6="",AO6=""),"",AQ6-AO6)</x:f>
-        <x:v>0.007920039092927267</x:v>
+        <x:v>0.0349600458241911</x:v>
       </x:c>
       <x:c r="AS6" s="24" t="n">
         <x:f>IF('Model'!$D6=0,"",Y6)</x:f>
@@ -3208,25 +3245,25 @@
         <x:f>'Model'!S6</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU6" s="26" t="n">
+      <x:c r="AU6" s="25" t="n">
         <x:f>IF('Model'!$D6=0,"",'Model'!T6)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV6" s="26" t="n">
+      <x:c r="AV6" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW6" s="25" t="n">
+      <x:c r="AW6" s="26" t="n">
         <x:f>'Model'!N6</x:f>
         <x:v>0.00680814351431791</x:v>
       </x:c>
-      <x:c r="AX6" s="25" t="n">
+      <x:c r="AX6" s="26" t="n">
         <x:f>'Model'!P6</x:f>
         <x:v>-0.0718969048742778</x:v>
       </x:c>
       <x:c r="AY6" s="17" t="str">
         <x:f>'Model'!Q6</x:f>
-        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
+        <x:v>METR feedback transfer — local acceleration retained as diagnostic</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="46" hidden="0" customHeight="1">
@@ -3242,146 +3279,146 @@
       <x:c r="D7" s="17" t="str">
         <x:v>Frontier best-run final cash / $2.2B estimated upper bound</x:v>
       </x:c>
-      <x:c r="E7" s="44" t="str">
+      <x:c r="E7" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F7" s="44" t="str">
+      <x:c r="F7" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G7" s="44" t="str">
+      <x:c r="G7" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H7" s="44" t="str">
+      <x:c r="H7" s="46" t="str">
         <x:f>IF(OR(G7="",E7=""),"",G7-E7)</x:f>
       </x:c>
-      <x:c r="I7" s="44" t="str">
+      <x:c r="I7" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J7" s="44" t="str">
+      <x:c r="J7" s="46" t="str">
         <x:f>IF(OR(I7="",G7=""),"",I7-G7)</x:f>
       </x:c>
-      <x:c r="K7" s="44" t="str">
+      <x:c r="K7" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L7" s="44" t="str">
+      <x:c r="L7" s="46" t="str">
         <x:f>IF(OR(K7="",I7=""),"",K7-I7)</x:f>
       </x:c>
-      <x:c r="M7" s="44" t="str">
+      <x:c r="M7" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N7" s="44" t="str">
+      <x:c r="N7" s="46" t="str">
         <x:f>IF(OR(M7="",K7=""),"",M7-K7)</x:f>
       </x:c>
-      <x:c r="O7" s="44" t="str">
+      <x:c r="O7" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P7" s="44" t="str">
+      <x:c r="P7" s="46" t="str">
         <x:f>IF(OR(O7="",M7=""),"",O7-M7)</x:f>
       </x:c>
-      <x:c r="Q7" s="44" t="str">
+      <x:c r="Q7" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R7" s="44" t="str">
+      <x:c r="R7" s="46" t="str">
         <x:f>IF(OR(Q7="",O7=""),"",Q7-O7)</x:f>
       </x:c>
-      <x:c r="S7" s="44" t="str">
+      <x:c r="S7" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T7" s="44" t="str">
+      <x:c r="T7" s="46" t="str">
         <x:f>IF(OR(S7="",Q7=""),"",S7-Q7)</x:f>
       </x:c>
-      <x:c r="U7" s="44" t="str">
+      <x:c r="U7" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
       </x:c>
-      <x:c r="V7" s="44" t="str">
+      <x:c r="V7" s="46" t="str">
         <x:f>IF(OR(U7="",S7=""),"",U7-S7)</x:f>
       </x:c>
-      <x:c r="W7" s="45" t="n">
+      <x:c r="W7" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.005740944545454546</x:v>
       </x:c>
-      <x:c r="X7" s="45" t="str">
+      <x:c r="X7" s="47" t="str">
         <x:f>IF(OR(W7="",U7=""),"",W7-U7)</x:f>
       </x:c>
-      <x:c r="Y7" s="45" t="n">
+      <x:c r="Y7" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B7,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.010067435</x:v>
       </x:c>
-      <x:c r="Z7" s="45" t="n">
+      <x:c r="Z7" s="47" t="n">
         <x:f>IF(OR(Y7="",W7=""),"",Y7-W7)</x:f>
         <x:v>0.004326490454545454</x:v>
       </x:c>
-      <x:c r="AA7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.10607715721830968</x:v>
-      </x:c>
-      <x:c r="AB7" s="46" t="n">
+      <x:c r="AA7" s="48" t="n">
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.10178610316181147</x:v>
+      </x:c>
+      <x:c r="AB7" s="48" t="n">
         <x:f>IF(OR(AA7="",Y7=""),"",AA7-Y7)</x:f>
-        <x:v>0.09600972221830968</x:v>
-      </x:c>
-      <x:c r="AC7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.23063535751472852</x:v>
-      </x:c>
-      <x:c r="AD7" s="46" t="n">
+        <x:v>0.09171866816181147</x:v>
+      </x:c>
+      <x:c r="AC7" s="48" t="n">
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.21173256999485568</x:v>
+      </x:c>
+      <x:c r="AD7" s="48" t="n">
         <x:f>IF(OR(AC7="",AA7=""),"",AC7-AA7)</x:f>
-        <x:v>0.12455820029641884</x:v>
-      </x:c>
-      <x:c r="AE7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.3830091216381757</x:v>
-      </x:c>
-      <x:c r="AF7" s="46" t="n">
+        <x:v>0.10994646683304421</x:v>
+      </x:c>
+      <x:c r="AE7" s="48" t="n">
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.3385129310170796</x:v>
+      </x:c>
+      <x:c r="AF7" s="48" t="n">
         <x:f>IF(OR(AE7="",AC7=""),"",AE7-AC7)</x:f>
-        <x:v>0.15237376412344716</x:v>
-      </x:c>
-      <x:c r="AG7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.5540454637768562</x:v>
-      </x:c>
-      <x:c r="AH7" s="46" t="n">
+        <x:v>0.1267803610222239</x:v>
+      </x:c>
+      <x:c r="AG7" s="48" t="n">
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.47729754007736</x:v>
+      </x:c>
+      <x:c r="AH7" s="48" t="n">
         <x:f>IF(OR(AG7="",AE7=""),"",AG7-AE7)</x:f>
-        <x:v>0.17103634213868046</x:v>
-      </x:c>
-      <x:c r="AI7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7233599112042924</x:v>
-      </x:c>
-      <x:c r="AJ7" s="46" t="n">
+        <x:v>0.13878460906028045</x:v>
+      </x:c>
+      <x:c r="AI7" s="48" t="n">
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6190063293347431</x:v>
+      </x:c>
+      <x:c r="AJ7" s="48" t="n">
         <x:f>IF(OR(AI7="",AG7=""),"",AI7-AG7)</x:f>
-        <x:v>0.1693144474274363</x:v>
-      </x:c>
-      <x:c r="AK7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8629457730411109</x:v>
-      </x:c>
-      <x:c r="AL7" s="46" t="n">
+        <x:v>0.14170878925738306</x:v>
+      </x:c>
+      <x:c r="AK7" s="48" t="n">
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7508363985907904</x:v>
+      </x:c>
+      <x:c r="AL7" s="48" t="n">
         <x:f>IF(OR(AK7="",AI7=""),"",AK7-AI7)</x:f>
-        <x:v>0.13958586183681843</x:v>
-      </x:c>
-      <x:c r="AM7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9512198367718484</x:v>
-      </x:c>
-      <x:c r="AN7" s="46" t="n">
+        <x:v>0.13183006925604734</x:v>
+      </x:c>
+      <x:c r="AM7" s="48" t="n">
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8591345526945822</x:v>
+      </x:c>
+      <x:c r="AN7" s="48" t="n">
         <x:f>IF(OR(AM7="",AK7=""),"",AM7-AK7)</x:f>
-        <x:v>0.08827406373073754</x:v>
-      </x:c>
-      <x:c r="AO7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9893257363767952</x:v>
-      </x:c>
-      <x:c r="AP7" s="46" t="n">
+        <x:v>0.10829815410379173</x:v>
+      </x:c>
+      <x:c r="AO7" s="48" t="n">
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.934507983869099</x:v>
+      </x:c>
+      <x:c r="AP7" s="48" t="n">
         <x:f>IF(OR(AO7="",AM7=""),"",AO7-AM7)</x:f>
-        <x:v>0.038105899604946813</x:v>
-      </x:c>
-      <x:c r="AQ7" s="46" t="n">
-        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9988579057293402</x:v>
-      </x:c>
-      <x:c r="AR7" s="46" t="n">
+        <x:v>0.07537343117451678</x:v>
+      </x:c>
+      <x:c r="AQ7" s="48" t="n">
+        <x:f>IF('Model'!$D7=0,"",1-POWER(2,-('Model'!$M7+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9765841748397365</x:v>
+      </x:c>
+      <x:c r="AR7" s="48" t="n">
         <x:f>IF(OR(AQ7="",AO7=""),"",AQ7-AO7)</x:f>
-        <x:v>0.009532169352544972</x:v>
+        <x:v>0.04207619097063753</x:v>
       </x:c>
       <x:c r="AS7" s="24" t="n">
         <x:f>IF('Model'!$D7=0,"",Y7)</x:f>
@@ -3391,25 +3428,25 @@
         <x:f>'Model'!S7</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU7" s="26" t="n">
+      <x:c r="AU7" s="25" t="n">
         <x:f>IF('Model'!$D7=0,"",'Model'!T7)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV7" s="26" t="n">
+      <x:c r="AV7" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW7" s="25" t="n">
+      <x:c r="AW7" s="26" t="n">
         <x:f>'Model'!N7</x:f>
         <x:v>0.006291545787330755</x:v>
       </x:c>
-      <x:c r="AX7" s="25" t="n">
+      <x:c r="AX7" s="26" t="n">
         <x:f>'Model'!P7</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY7" s="17" t="str">
         <x:f>'Model'!Q7</x:f>
-        <x:v>Shared frontier transfer — velocity contributor</x:v>
+        <x:v>METR feedback transfer — economic velocity contributor</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="46" hidden="0" customHeight="1">
@@ -3425,146 +3462,146 @@
       <x:c r="D8" s="17" t="str">
         <x:v>Frontier mean final funds / $1M published substantial-profit threshold</x:v>
       </x:c>
-      <x:c r="E8" s="44" t="str">
+      <x:c r="E8" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F8" s="44" t="str">
+      <x:c r="F8" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G8" s="44" t="str">
+      <x:c r="G8" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H8" s="44" t="str">
+      <x:c r="H8" s="46" t="str">
         <x:f>IF(OR(G8="",E8=""),"",G8-E8)</x:f>
       </x:c>
-      <x:c r="I8" s="44" t="str">
+      <x:c r="I8" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J8" s="44" t="str">
+      <x:c r="J8" s="46" t="str">
         <x:f>IF(OR(I8="",G8=""),"",I8-G8)</x:f>
       </x:c>
-      <x:c r="K8" s="44" t="str">
+      <x:c r="K8" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L8" s="44" t="str">
+      <x:c r="L8" s="46" t="str">
         <x:f>IF(OR(K8="",I8=""),"",K8-I8)</x:f>
       </x:c>
-      <x:c r="M8" s="44" t="str">
+      <x:c r="M8" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N8" s="44" t="str">
+      <x:c r="N8" s="46" t="str">
         <x:f>IF(OR(M8="",K8=""),"",M8-K8)</x:f>
       </x:c>
-      <x:c r="O8" s="44" t="str">
+      <x:c r="O8" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P8" s="44" t="str">
+      <x:c r="P8" s="46" t="str">
         <x:f>IF(OR(O8="",M8=""),"",O8-M8)</x:f>
       </x:c>
-      <x:c r="Q8" s="44" t="str">
+      <x:c r="Q8" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R8" s="44" t="str">
+      <x:c r="R8" s="46" t="str">
         <x:f>IF(OR(Q8="",O8=""),"",Q8-O8)</x:f>
       </x:c>
-      <x:c r="S8" s="44" t="str">
+      <x:c r="S8" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T8" s="44" t="str">
+      <x:c r="T8" s="46" t="str">
         <x:f>IF(OR(S8="",Q8=""),"",S8-Q8)</x:f>
       </x:c>
-      <x:c r="U8" s="44" t="str">
+      <x:c r="U8" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
       </x:c>
-      <x:c r="V8" s="44" t="str">
+      <x:c r="V8" s="46" t="str">
         <x:f>IF(OR(U8="",S8=""),"",U8-S8)</x:f>
       </x:c>
-      <x:c r="W8" s="45" t="n">
+      <x:c r="W8" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X8" s="45" t="str">
+      <x:c r="X8" s="47" t="str">
         <x:f>IF(OR(W8="",U8=""),"",W8-U8)</x:f>
       </x:c>
-      <x:c r="Y8" s="44" t="n">
+      <x:c r="Y8" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B8,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z8" s="44" t="n">
+      <x:c r="Z8" s="46" t="n">
         <x:f>IF(OR(Y8="",W8=""),"",Y8-W8)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9999999991590028</x:v>
-      </x:c>
-      <x:c r="AB8" s="46" t="n">
+      <x:c r="AA8" s="48" t="n">
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9999999991549658</x:v>
+      </x:c>
+      <x:c r="AB8" s="48" t="n">
         <x:f>IF(OR(AA8="",Y8=""),"",AA8-Y8)</x:f>
-        <x:v>-8.409971608003275e-10</x:v>
-      </x:c>
-      <x:c r="AC8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9999999992761864</x:v>
-      </x:c>
-      <x:c r="AD8" s="46" t="n">
+        <x:v>-8.450341537624695e-10</x:v>
+      </x:c>
+      <x:c r="AC8" s="48" t="n">
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9999999992584028</x:v>
+      </x:c>
+      <x:c r="AD8" s="48" t="n">
         <x:f>IF(OR(AC8="",AA8=""),"",AC8-AA8)</x:f>
-        <x:v>1.1718359615997542e-10</x:v>
-      </x:c>
-      <x:c r="AE8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9999999994195388</x:v>
-      </x:c>
-      <x:c r="AF8" s="46" t="n">
+        <x:v>1.034369256913692e-10</x:v>
+      </x:c>
+      <x:c r="AE8" s="48" t="n">
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9999999993776769</x:v>
+      </x:c>
+      <x:c r="AF8" s="48" t="n">
         <x:f>IF(OR(AE8="",AC8=""),"",AE8-AC8)</x:f>
-        <x:v>1.433523300065076e-10</x:v>
-      </x:c>
-      <x:c r="AG8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9999999995804487</x:v>
-      </x:c>
-      <x:c r="AH8" s="46" t="n">
+        <x:v>1.192741461153446e-10</x:v>
+      </x:c>
+      <x:c r="AG8" s="48" t="n">
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9999999995082447</x:v>
+      </x:c>
+      <x:c r="AH8" s="48" t="n">
         <x:f>IF(OR(AG8="",AE8=""),"",AG8-AE8)</x:f>
-        <x:v>1.6090995202944214e-10</x:v>
-      </x:c>
-      <x:c r="AI8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9999999997397386</x:v>
-      </x:c>
-      <x:c r="AJ8" s="46" t="n">
+        <x:v>1.3056777881104153e-10</x:v>
+      </x:c>
+      <x:c r="AI8" s="48" t="n">
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9999999996415635</x:v>
+      </x:c>
+      <x:c r="AJ8" s="48" t="n">
         <x:f>IF(OR(AI8="",AG8=""),"",AI8-AG8)</x:f>
-        <x:v>1.592899145919091e-10</x:v>
-      </x:c>
-      <x:c r="AK8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9999999998710603</x:v>
-      </x:c>
-      <x:c r="AL8" s="46" t="n">
+        <x:v>1.333188004437602e-10</x:v>
+      </x:c>
+      <x:c r="AK8" s="48" t="n">
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9999999997655884</x:v>
+      </x:c>
+      <x:c r="AL8" s="48" t="n">
         <x:f>IF(OR(AK8="",AI8=""),"",AK8-AI8)</x:f>
-        <x:v>1.3132162024476202e-10</x:v>
-      </x:c>
-      <x:c r="AM8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9999999999541079</x:v>
-      </x:c>
-      <x:c r="AN8" s="46" t="n">
+        <x:v>1.240249014600181e-10</x:v>
+      </x:c>
+      <x:c r="AM8" s="48" t="n">
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9999999998674747</x:v>
+      </x:c>
+      <x:c r="AN8" s="48" t="n">
         <x:f>IF(OR(AM8="",AK8=""),"",AM8-AK8)</x:f>
-        <x:v>8.30476798441282e-11</x:v>
-      </x:c>
-      <x:c r="AO8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9999999999899577</x:v>
-      </x:c>
-      <x:c r="AP8" s="46" t="n">
+        <x:v>1.0188627719287524e-10</x:v>
+      </x:c>
+      <x:c r="AO8" s="48" t="n">
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9999999999383855</x:v>
+      </x:c>
+      <x:c r="AP8" s="48" t="n">
         <x:f>IF(OR(AO8="",AM8=""),"",AO8-AM8)</x:f>
-        <x:v>3.584976759896108e-11</x:v>
-      </x:c>
-      <x:c r="AQ8" s="46" t="n">
-        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9999999999989255</x:v>
-      </x:c>
-      <x:c r="AR8" s="46" t="n">
+        <x:v>7.091083276122845e-11</x:v>
+      </x:c>
+      <x:c r="AQ8" s="48" t="n">
+        <x:f>IF('Model'!$D8=0,"",1-POWER(2,-('Model'!$M8+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9999999999779705</x:v>
+      </x:c>
+      <x:c r="AR8" s="48" t="n">
         <x:f>IF(OR(AQ8="",AO8=""),"",AQ8-AO8)</x:f>
-        <x:v>8.967826481409702e-12</x:v>
+        <x:v>3.9585001943009956e-11</x:v>
       </x:c>
       <x:c r="AS8" s="24" t="n">
         <x:f>IF('Model'!$D8=0,"",Y8)</x:f>
@@ -3574,25 +3611,25 @@
         <x:f>'Model'!S8</x:f>
         <x:v>A</x:v>
       </x:c>
-      <x:c r="AU8" s="26" t="n">
+      <x:c r="AU8" s="25" t="n">
         <x:f>IF('Model'!$D8=0,"",'Model'!T8)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AV8" s="26" t="n">
+      <x:c r="AV8" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW8" s="25" t="n">
+      <x:c r="AW8" s="26" t="n">
         <x:f>'Model'!N8</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX8" s="25" t="n">
+      <x:c r="AX8" s="26" t="n">
         <x:f>'Model'!P8</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY8" s="17" t="str">
         <x:f>'Model'!Q8</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="46" hidden="0" customHeight="1">
@@ -3608,144 +3645,144 @@
       <x:c r="D9" s="17" t="str">
         <x:v>Best-model mean final worth / $436,195 expert-strategy final worth</x:v>
       </x:c>
-      <x:c r="E9" s="44" t="str">
+      <x:c r="E9" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F9" s="44" t="str">
+      <x:c r="F9" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G9" s="44" t="str">
+      <x:c r="G9" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H9" s="44" t="str">
+      <x:c r="H9" s="46" t="str">
         <x:f>IF(OR(G9="",E9=""),"",G9-E9)</x:f>
       </x:c>
-      <x:c r="I9" s="44" t="str">
+      <x:c r="I9" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J9" s="44" t="str">
+      <x:c r="J9" s="46" t="str">
         <x:f>IF(OR(I9="",G9=""),"",I9-G9)</x:f>
       </x:c>
-      <x:c r="K9" s="44" t="str">
+      <x:c r="K9" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L9" s="44" t="str">
+      <x:c r="L9" s="46" t="str">
         <x:f>IF(OR(K9="",I9=""),"",K9-I9)</x:f>
       </x:c>
-      <x:c r="M9" s="44" t="str">
+      <x:c r="M9" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N9" s="44" t="str">
+      <x:c r="N9" s="46" t="str">
         <x:f>IF(OR(M9="",K9=""),"",M9-K9)</x:f>
       </x:c>
-      <x:c r="O9" s="44" t="str">
+      <x:c r="O9" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P9" s="44" t="str">
+      <x:c r="P9" s="46" t="str">
         <x:f>IF(OR(O9="",M9=""),"",O9-M9)</x:f>
       </x:c>
-      <x:c r="Q9" s="44" t="str">
+      <x:c r="Q9" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R9" s="44" t="str">
+      <x:c r="R9" s="46" t="str">
         <x:f>IF(OR(Q9="",O9=""),"",Q9-O9)</x:f>
       </x:c>
-      <x:c r="S9" s="44" t="str">
+      <x:c r="S9" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T9" s="44" t="str">
+      <x:c r="T9" s="46" t="str">
         <x:f>IF(OR(S9="",Q9=""),"",S9-Q9)</x:f>
       </x:c>
-      <x:c r="U9" s="44" t="str">
+      <x:c r="U9" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
       </x:c>
-      <x:c r="V9" s="44" t="str">
+      <x:c r="V9" s="46" t="str">
         <x:f>IF(OR(U9="",S9=""),"",U9-S9)</x:f>
       </x:c>
-      <x:c r="W9" s="44" t="str">
+      <x:c r="W9" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
       </x:c>
-      <x:c r="X9" s="44" t="str">
+      <x:c r="X9" s="46" t="str">
         <x:f>IF(OR(W9="",U9=""),"",W9-U9)</x:f>
       </x:c>
-      <x:c r="Y9" s="45" t="n">
+      <x:c r="Y9" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B9,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.4321186625247882</x:v>
       </x:c>
-      <x:c r="Z9" s="45" t="str">
+      <x:c r="Z9" s="47" t="str">
         <x:f>IF(OR(Y9="",W9=""),"",Y9-W9)</x:f>
       </x:c>
-      <x:c r="AA9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.48719527217643377</x:v>
-      </x:c>
-      <x:c r="AB9" s="46" t="n">
+      <x:c r="AA9" s="48" t="n">
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.4847336807479482</x:v>
+      </x:c>
+      <x:c r="AB9" s="48" t="n">
         <x:f>IF(OR(AA9="",Y9=""),"",AA9-Y9)</x:f>
-        <x:v>0.05507660965164557</x:v>
-      </x:c>
-      <x:c r="AC9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.5586489043517079</x:v>
-      </x:c>
-      <x:c r="AD9" s="46" t="n">
+        <x:v>0.052615018223160004</x:v>
+      </x:c>
+      <x:c r="AC9" s="48" t="n">
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.5478051957615221</x:v>
+      </x:c>
+      <x:c r="AD9" s="48" t="n">
         <x:f>IF(OR(AC9="",AA9=""),"",AC9-AA9)</x:f>
-        <x:v>0.07145363217527412</x:v>
-      </x:c>
-      <x:c r="AE9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6460591179621225</x:v>
-      </x:c>
-      <x:c r="AF9" s="46" t="n">
+        <x:v>0.06307151501357389</x:v>
+      </x:c>
+      <x:c r="AE9" s="48" t="n">
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.620533585076496</x:v>
+      </x:c>
+      <x:c r="AF9" s="48" t="n">
         <x:f>IF(OR(AE9="",AC9=""),"",AE9-AC9)</x:f>
-        <x:v>0.08741021361041457</x:v>
-      </x:c>
-      <x:c r="AG9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7441752423979136</x:v>
-      </x:c>
-      <x:c r="AH9" s="46" t="n">
+        <x:v>0.07272838931497394</x:v>
+      </x:c>
+      <x:c r="AG9" s="48" t="n">
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7001482903611196</x:v>
+      </x:c>
+      <x:c r="AH9" s="48" t="n">
         <x:f>IF(OR(AG9="",AE9=""),"",AG9-AE9)</x:f>
-        <x:v>0.0981161244357911</x:v>
-      </x:c>
-      <x:c r="AI9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8413035905889531</x:v>
-      </x:c>
-      <x:c r="AJ9" s="46" t="n">
+        <x:v>0.07961470528462355</x:v>
+      </x:c>
+      <x:c r="AI9" s="48" t="n">
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7814404708799771</x:v>
+      </x:c>
+      <x:c r="AJ9" s="48" t="n">
         <x:f>IF(OR(AI9="",AG9=""),"",AI9-AG9)</x:f>
-        <x:v>0.09712834819103955</x:v>
-      </x:c>
-      <x:c r="AK9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9213779398073997</x:v>
-      </x:c>
-      <x:c r="AL9" s="46" t="n">
+        <x:v>0.08129218051885756</x:v>
+      </x:c>
+      <x:c r="AK9" s="48" t="n">
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8570656585901864</x:v>
+      </x:c>
+      <x:c r="AL9" s="48" t="n">
         <x:f>IF(OR(AK9="",AI9=""),"",AK9-AI9)</x:f>
-        <x:v>0.08007434921844658</x:v>
-      </x:c>
-      <x:c r="AM9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9720169380060126</x:v>
-      </x:c>
-      <x:c r="AN9" s="46" t="n">
+        <x:v>0.07562518771020921</x:v>
+      </x:c>
+      <x:c r="AM9" s="48" t="n">
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.919191608147728</x:v>
+      </x:c>
+      <x:c r="AN9" s="48" t="n">
         <x:f>IF(OR(AM9="",AK9=""),"",AM9-AK9)</x:f>
-        <x:v>0.05063899819861295</x:v>
-      </x:c>
-      <x:c r="AO9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9938766383517159</x:v>
-      </x:c>
-      <x:c r="AP9" s="46" t="n">
+        <x:v>0.06212594955754169</x:v>
+      </x:c>
+      <x:c r="AO9" s="48" t="n">
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9624300734925674</x:v>
+      </x:c>
+      <x:c r="AP9" s="48" t="n">
         <x:f>IF(OR(AO9="",AM9=""),"",AO9-AM9)</x:f>
-        <x:v>0.02185970034570328</x:v>
-      </x:c>
-      <x:c r="AQ9" s="46" t="n">
-        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9993448300976491</x:v>
-      </x:c>
-      <x:c r="AR9" s="46" t="n">
+        <x:v>0.04323846534483933</x:v>
+      </x:c>
+      <x:c r="AQ9" s="48" t="n">
+        <x:f>IF('Model'!$D9=0,"",1-POWER(2,-('Model'!$M9+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9865673576360263</x:v>
+      </x:c>
+      <x:c r="AR9" s="48" t="n">
         <x:f>IF(OR(AQ9="",AO9=""),"",AQ9-AO9)</x:f>
-        <x:v>0.00546819174593316</x:v>
+        <x:v>0.024137284143458948</x:v>
       </x:c>
       <x:c r="AS9" s="24" t="n">
         <x:f>IF('Model'!$D9=0,"",Y9)</x:f>
@@ -3755,25 +3792,25 @@
         <x:f>'Model'!S9</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU9" s="26" t="n">
+      <x:c r="AU9" s="25" t="n">
         <x:f>IF('Model'!$D9=0,"",'Model'!T9)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV9" s="26" t="n">
+      <x:c r="AV9" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW9" s="25" t="n">
+      <x:c r="AW9" s="26" t="n">
         <x:f>'Model'!N9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX9" s="25" t="n">
+      <x:c r="AX9" s="26" t="n">
         <x:f>'Model'!P9</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY9" s="17" t="str">
         <x:f>'Model'!Q9</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="46" hidden="0" customHeight="1">
@@ -3789,148 +3826,148 @@
       <x:c r="D10" s="17" t="str">
         <x:v>Best-system full-horizon survival rate</x:v>
       </x:c>
-      <x:c r="E10" s="44" t="str">
+      <x:c r="E10" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F10" s="44" t="str">
+      <x:c r="F10" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G10" s="44" t="str">
+      <x:c r="G10" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H10" s="44" t="str">
+      <x:c r="H10" s="46" t="str">
         <x:f>IF(OR(G10="",E10=""),"",G10-E10)</x:f>
       </x:c>
-      <x:c r="I10" s="44" t="str">
+      <x:c r="I10" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J10" s="44" t="str">
+      <x:c r="J10" s="46" t="str">
         <x:f>IF(OR(I10="",G10=""),"",I10-G10)</x:f>
       </x:c>
-      <x:c r="K10" s="44" t="str">
+      <x:c r="K10" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L10" s="44" t="str">
+      <x:c r="L10" s="46" t="str">
         <x:f>IF(OR(K10="",I10=""),"",K10-I10)</x:f>
       </x:c>
-      <x:c r="M10" s="44" t="str">
+      <x:c r="M10" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N10" s="44" t="str">
+      <x:c r="N10" s="46" t="str">
         <x:f>IF(OR(M10="",K10=""),"",M10-K10)</x:f>
       </x:c>
-      <x:c r="O10" s="44" t="str">
+      <x:c r="O10" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P10" s="44" t="str">
+      <x:c r="P10" s="46" t="str">
         <x:f>IF(OR(O10="",M10=""),"",O10-M10)</x:f>
       </x:c>
-      <x:c r="Q10" s="44" t="str">
+      <x:c r="Q10" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R10" s="44" t="str">
+      <x:c r="R10" s="46" t="str">
         <x:f>IF(OR(Q10="",O10=""),"",Q10-O10)</x:f>
       </x:c>
-      <x:c r="S10" s="44" t="str">
+      <x:c r="S10" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T10" s="44" t="str">
+      <x:c r="T10" s="46" t="str">
         <x:f>IF(OR(S10="",Q10=""),"",S10-Q10)</x:f>
       </x:c>
-      <x:c r="U10" s="45" t="n">
+      <x:c r="U10" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="V10" s="45" t="str">
+      <x:c r="V10" s="47" t="str">
         <x:f>IF(OR(U10="",S10=""),"",U10-S10)</x:f>
       </x:c>
-      <x:c r="W10" s="44" t="n">
+      <x:c r="W10" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="X10" s="44" t="n">
+      <x:c r="X10" s="46" t="n">
         <x:f>IF(OR(W10="",U10=""),"",W10-U10)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y10" s="44" t="n">
+      <x:c r="Y10" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B10,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="Z10" s="44" t="n">
+      <x:c r="Z10" s="46" t="n">
         <x:f>IF(OR(Y10="",W10=""),"",Y10-W10)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6387944494858837</x:v>
-      </x:c>
-      <x:c r="AB10" s="46" t="n">
+      <x:c r="AA10" s="48" t="n">
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6370605721660693</x:v>
+      </x:c>
+      <x:c r="AB10" s="48" t="n">
         <x:f>IF(OR(AA10="",Y10=""),"",AA10-Y10)</x:f>
-        <x:v>0.03879444948588373</x:v>
-      </x:c>
-      <x:c r="AC10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6891244233448279</x:v>
-      </x:c>
-      <x:c r="AD10" s="46" t="n">
+        <x:v>0.03706057216606928</x:v>
+      </x:c>
+      <x:c r="AC10" s="48" t="n">
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6814864131658729</x:v>
+      </x:c>
+      <x:c r="AD10" s="48" t="n">
         <x:f>IF(OR(AC10="",AA10=""),"",AC10-AA10)</x:f>
-        <x:v>0.05032997385894422</x:v>
-      </x:c>
-      <x:c r="AE10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7506937744342922</x:v>
-      </x:c>
-      <x:c r="AF10" s="46" t="n">
+        <x:v>0.04442584099980362</x:v>
+      </x:c>
+      <x:c r="AE10" s="48" t="n">
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7327142909040798</x:v>
+      </x:c>
+      <x:c r="AF10" s="48" t="n">
         <x:f>IF(OR(AE10="",AC10=""),"",AE10-AC10)</x:f>
-        <x:v>0.061569351089464264</x:v>
-      </x:c>
-      <x:c r="AG10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8198040747459828</x:v>
-      </x:c>
-      <x:c r="AH10" s="46" t="n">
+        <x:v>0.05122787773820692</x:v>
+      </x:c>
+      <x:c r="AG10" s="48" t="n">
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7887927002693804</x:v>
+      </x:c>
+      <x:c r="AH10" s="48" t="n">
         <x:f>IF(OR(AG10="",AE10=""),"",AG10-AE10)</x:f>
-        <x:v>0.06911030031169063</x:v>
-      </x:c>
-      <x:c r="AI10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8882186126301613</x:v>
-      </x:c>
-      <x:c r="AJ10" s="46" t="n">
+        <x:v>0.05607840936530062</x:v>
+      </x:c>
+      <x:c r="AI10" s="48" t="n">
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8460526770668437</x:v>
+      </x:c>
+      <x:c r="AJ10" s="48" t="n">
         <x:f>IF(OR(AI10="",AG10=""),"",AI10-AG10)</x:f>
-        <x:v>0.0684145378841785</x:v>
-      </x:c>
-      <x:c r="AK10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9446207825443588</x:v>
-      </x:c>
-      <x:c r="AL10" s="46" t="n">
+        <x:v>0.05725997679746331</x:v>
+      </x:c>
+      <x:c r="AK10" s="48" t="n">
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8993209799460594</x:v>
+      </x:c>
+      <x:c r="AL10" s="48" t="n">
         <x:f>IF(OR(AK10="",AI10=""),"",AK10-AI10)</x:f>
-        <x:v>0.05640216991419744</x:v>
-      </x:c>
-      <x:c r="AM10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9802895005365738</x:v>
-      </x:c>
-      <x:c r="AN10" s="46" t="n">
+        <x:v>0.05326830287921569</x:v>
+      </x:c>
+      <x:c r="AM10" s="48" t="n">
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9430807906373228</x:v>
+      </x:c>
+      <x:c r="AN10" s="48" t="n">
         <x:f>IF(OR(AM10="",AK10=""),"",AM10-AK10)</x:f>
-        <x:v>0.03566871799221505</x:v>
-      </x:c>
-      <x:c r="AO10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9956868724191512</x:v>
-      </x:c>
-      <x:c r="AP10" s="46" t="n">
+        <x:v>0.043759810691263334</x:v>
+      </x:c>
+      <x:c r="AO10" s="48" t="n">
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9735367767678595</x:v>
+      </x:c>
+      <x:c r="AP10" s="48" t="n">
         <x:f>IF(OR(AO10="",AM10=""),"",AO10-AM10)</x:f>
-        <x:v>0.015397371882577393</x:v>
-      </x:c>
-      <x:c r="AQ10" s="46" t="n">
-        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9995385163349345</x:v>
-      </x:c>
-      <x:c r="AR10" s="46" t="n">
+        <x:v>0.030455986130536794</x:v>
+      </x:c>
+      <x:c r="AQ10" s="48" t="n">
+        <x:f>IF('Model'!$D10=0,"",1-POWER(2,-('Model'!$M10+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9905384160545265</x:v>
+      </x:c>
+      <x:c r="AR10" s="48" t="n">
         <x:f>IF(OR(AQ10="",AO10=""),"",AQ10-AO10)</x:f>
-        <x:v>0.0038516439157832982</x:v>
+        <x:v>0.01700163928666698</x:v>
       </x:c>
       <x:c r="AS10" s="24" t="n">
         <x:f>IF('Model'!$D10=0,"",Y10)</x:f>
@@ -3940,25 +3977,25 @@
         <x:f>'Model'!S10</x:f>
         <x:v>D</x:v>
       </x:c>
-      <x:c r="AU10" s="26" t="n">
+      <x:c r="AU10" s="25" t="n">
         <x:f>IF('Model'!$D10=0,"",'Model'!T10)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AV10" s="26" t="n">
+      <x:c r="AV10" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW10" s="25" t="n">
+      <x:c r="AW10" s="26" t="n">
         <x:f>'Model'!N10</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX10" s="25" t="n">
+      <x:c r="AX10" s="26" t="n">
         <x:f>'Model'!P10</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY10" s="17" t="str">
         <x:f>'Model'!Q10</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="46" hidden="0" customHeight="1">
@@ -3974,144 +4011,144 @@
       <x:c r="D11" s="17" t="str">
         <x:v>Best LLM final net worth / $131,510.42 oracle final net worth</x:v>
       </x:c>
-      <x:c r="E11" s="44" t="str">
+      <x:c r="E11" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F11" s="44" t="str">
+      <x:c r="F11" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G11" s="44" t="str">
+      <x:c r="G11" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H11" s="44" t="str">
+      <x:c r="H11" s="46" t="str">
         <x:f>IF(OR(G11="",E11=""),"",G11-E11)</x:f>
       </x:c>
-      <x:c r="I11" s="44" t="str">
+      <x:c r="I11" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J11" s="44" t="str">
+      <x:c r="J11" s="46" t="str">
         <x:f>IF(OR(I11="",G11=""),"",I11-G11)</x:f>
       </x:c>
-      <x:c r="K11" s="44" t="str">
+      <x:c r="K11" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L11" s="44" t="str">
+      <x:c r="L11" s="46" t="str">
         <x:f>IF(OR(K11="",I11=""),"",K11-I11)</x:f>
       </x:c>
-      <x:c r="M11" s="44" t="str">
+      <x:c r="M11" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N11" s="44" t="str">
+      <x:c r="N11" s="46" t="str">
         <x:f>IF(OR(M11="",K11=""),"",M11-K11)</x:f>
       </x:c>
-      <x:c r="O11" s="44" t="str">
+      <x:c r="O11" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P11" s="44" t="str">
+      <x:c r="P11" s="46" t="str">
         <x:f>IF(OR(O11="",M11=""),"",O11-M11)</x:f>
       </x:c>
-      <x:c r="Q11" s="44" t="str">
+      <x:c r="Q11" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R11" s="44" t="str">
+      <x:c r="R11" s="46" t="str">
         <x:f>IF(OR(Q11="",O11=""),"",Q11-O11)</x:f>
       </x:c>
-      <x:c r="S11" s="44" t="str">
+      <x:c r="S11" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T11" s="44" t="str">
+      <x:c r="T11" s="46" t="str">
         <x:f>IF(OR(S11="",Q11=""),"",S11-Q11)</x:f>
       </x:c>
-      <x:c r="U11" s="44" t="str">
+      <x:c r="U11" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
       </x:c>
-      <x:c r="V11" s="44" t="str">
+      <x:c r="V11" s="46" t="str">
         <x:f>IF(OR(U11="",S11=""),"",U11-S11)</x:f>
       </x:c>
-      <x:c r="W11" s="44" t="str">
+      <x:c r="W11" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
       </x:c>
-      <x:c r="X11" s="44" t="str">
+      <x:c r="X11" s="46" t="str">
         <x:f>IF(OR(W11="",U11=""),"",W11-U11)</x:f>
       </x:c>
-      <x:c r="Y11" s="45" t="n">
+      <x:c r="Y11" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B11,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.18516388283148968</x:v>
       </x:c>
-      <x:c r="Z11" s="45" t="str">
+      <x:c r="Z11" s="47" t="str">
         <x:f>IF(OR(Y11="",W11=""),"",Y11-W11)</x:f>
       </x:c>
-      <x:c r="AA11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.26419167929840837</x:v>
-      </x:c>
-      <x:c r="AB11" s="46" t="n">
+      <x:c r="AA11" s="48" t="n">
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.2606596146410979</x:v>
+      </x:c>
+      <x:c r="AB11" s="48" t="n">
         <x:f>IF(OR(AA11="",Y11=""),"",AA11-Y11)</x:f>
-        <x:v>0.07902779646691868</x:v>
-      </x:c>
-      <x:c r="AC11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.36671838048944505</x:v>
-      </x:c>
-      <x:c r="AD11" s="46" t="n">
+        <x:v>0.0754957318096082</x:v>
+      </x:c>
+      <x:c r="AC11" s="48" t="n">
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.35115906409666175</x:v>
+      </x:c>
+      <x:c r="AD11" s="48" t="n">
         <x:f>IF(OR(AC11="",AA11=""),"",AC11-AA11)</x:f>
-        <x:v>0.10252670119103668</x:v>
-      </x:c>
-      <x:c r="AE11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.49214070793525455</x:v>
-      </x:c>
-      <x:c r="AF11" s="46" t="n">
+        <x:v>0.09049944945556387</x:v>
+      </x:c>
+      <x:c r="AE11" s="48" t="n">
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.45551487656412093</x:v>
+      </x:c>
+      <x:c r="AF11" s="48" t="n">
         <x:f>IF(OR(AE11="",AC11=""),"",AE11-AC11)</x:f>
-        <x:v>0.1254223274458095</x:v>
-      </x:c>
-      <x:c r="AG11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6329246298410738</x:v>
-      </x:c>
-      <x:c r="AH11" s="46" t="n">
+        <x:v>0.10435581246745917</x:v>
+      </x:c>
+      <x:c r="AG11" s="48" t="n">
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.5697516599246406</x:v>
+      </x:c>
+      <x:c r="AH11" s="48" t="n">
         <x:f>IF(OR(AG11="",AE11=""),"",AG11-AE11)</x:f>
-        <x:v>0.14078392190581923</x:v>
-      </x:c>
-      <x:c r="AI11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7722912208596286</x:v>
-      </x:c>
-      <x:c r="AJ11" s="46" t="n">
+        <x:v>0.11423678336051968</x:v>
+      </x:c>
+      <x:c r="AI11" s="48" t="n">
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6863954028316503</x:v>
+      </x:c>
+      <x:c r="AJ11" s="48" t="n">
         <x:f>IF(OR(AI11="",AG11=""),"",AI11-AG11)</x:f>
-        <x:v>0.13936659101855486</x:v>
-      </x:c>
-      <x:c r="AK11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8871875336915368</x:v>
-      </x:c>
-      <x:c r="AL11" s="46" t="n">
+        <x:v>0.11664374290700974</x:v>
+      </x:c>
+      <x:c r="AK11" s="48" t="n">
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7949077455472912</x:v>
+      </x:c>
+      <x:c r="AL11" s="48" t="n">
         <x:f>IF(OR(AK11="",AI11=""),"",AK11-AI11)</x:f>
-        <x:v>0.11489631283190815</x:v>
-      </x:c>
-      <x:c r="AM11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9598479328744245</x:v>
-      </x:c>
-      <x:c r="AN11" s="46" t="n">
+        <x:v>0.10851234271564081</x:v>
+      </x:c>
+      <x:c r="AM11" s="48" t="n">
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8840504311265364</x:v>
+      </x:c>
+      <x:c r="AN11" s="48" t="n">
         <x:f>IF(OR(AM11="",AK11=""),"",AM11-AK11)</x:f>
-        <x:v>0.07266039918288769</x:v>
-      </x:c>
-      <x:c r="AO11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9912137696729219</x:v>
-      </x:c>
-      <x:c r="AP11" s="46" t="n">
+        <x:v>0.0891426855792452</x:v>
+      </x:c>
+      <x:c r="AO11" s="48" t="n">
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9460920248343978</x:v>
+      </x:c>
+      <x:c r="AP11" s="48" t="n">
         <x:f>IF(OR(AO11="",AM11=""),"",AO11-AM11)</x:f>
-        <x:v>0.03136583679849736</x:v>
-      </x:c>
-      <x:c r="AQ11" s="46" t="n">
-        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9990599161055532</x:v>
-      </x:c>
-      <x:c r="AR11" s="46" t="n">
+        <x:v>0.06204159370786144</x:v>
+      </x:c>
+      <x:c r="AQ11" s="48" t="n">
+        <x:f>IF('Model'!$D11=0,"",1-POWER(2,-('Model'!$M11+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9807258991890161</x:v>
+      </x:c>
+      <x:c r="AR11" s="48" t="n">
         <x:f>IF(OR(AQ11="",AO11=""),"",AQ11-AO11)</x:f>
-        <x:v>0.007846146432631373</x:v>
+        <x:v>0.03463387435461829</x:v>
       </x:c>
       <x:c r="AS11" s="24" t="n">
         <x:f>IF('Model'!$D11=0,"",Y11)</x:f>
@@ -4121,25 +4158,25 @@
         <x:f>'Model'!S11</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU11" s="26" t="n">
+      <x:c r="AU11" s="25" t="n">
         <x:f>IF('Model'!$D11=0,"",'Model'!T11)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV11" s="26" t="n">
+      <x:c r="AV11" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW11" s="25" t="n">
+      <x:c r="AW11" s="26" t="n">
         <x:f>'Model'!N11</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX11" s="25" t="n">
+      <x:c r="AX11" s="26" t="n">
         <x:f>'Model'!P11</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY11" s="17" t="str">
         <x:f>'Model'!Q11</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="46" hidden="0" customHeight="1">
@@ -4155,144 +4192,144 @@
       <x:c r="D12" s="17" t="str">
         <x:v>Best LLM mean final net assets / human-participant mean</x:v>
       </x:c>
-      <x:c r="E12" s="44" t="str">
+      <x:c r="E12" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F12" s="44" t="str">
+      <x:c r="F12" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G12" s="44" t="str">
+      <x:c r="G12" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H12" s="44" t="str">
+      <x:c r="H12" s="46" t="str">
         <x:f>IF(OR(G12="",E12=""),"",G12-E12)</x:f>
       </x:c>
-      <x:c r="I12" s="44" t="str">
+      <x:c r="I12" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J12" s="44" t="str">
+      <x:c r="J12" s="46" t="str">
         <x:f>IF(OR(I12="",G12=""),"",I12-G12)</x:f>
       </x:c>
-      <x:c r="K12" s="44" t="str">
+      <x:c r="K12" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L12" s="44" t="str">
+      <x:c r="L12" s="46" t="str">
         <x:f>IF(OR(K12="",I12=""),"",K12-I12)</x:f>
       </x:c>
-      <x:c r="M12" s="44" t="str">
+      <x:c r="M12" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N12" s="44" t="str">
+      <x:c r="N12" s="46" t="str">
         <x:f>IF(OR(M12="",K12=""),"",M12-K12)</x:f>
       </x:c>
-      <x:c r="O12" s="44" t="str">
+      <x:c r="O12" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P12" s="44" t="str">
+      <x:c r="P12" s="46" t="str">
         <x:f>IF(OR(O12="",M12=""),"",O12-M12)</x:f>
       </x:c>
-      <x:c r="Q12" s="44" t="str">
+      <x:c r="Q12" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R12" s="44" t="str">
+      <x:c r="R12" s="46" t="str">
         <x:f>IF(OR(Q12="",O12=""),"",Q12-O12)</x:f>
       </x:c>
-      <x:c r="S12" s="44" t="str">
+      <x:c r="S12" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T12" s="44" t="str">
+      <x:c r="T12" s="46" t="str">
         <x:f>IF(OR(S12="",Q12=""),"",S12-Q12)</x:f>
       </x:c>
-      <x:c r="U12" s="44" t="str">
+      <x:c r="U12" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
       </x:c>
-      <x:c r="V12" s="44" t="str">
+      <x:c r="V12" s="46" t="str">
         <x:f>IF(OR(U12="",S12=""),"",U12-S12)</x:f>
       </x:c>
-      <x:c r="W12" s="44" t="str">
+      <x:c r="W12" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
       </x:c>
-      <x:c r="X12" s="44" t="str">
+      <x:c r="X12" s="46" t="str">
         <x:f>IF(OR(W12="",U12=""),"",W12-U12)</x:f>
       </x:c>
-      <x:c r="Y12" s="45" t="n">
+      <x:c r="Y12" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B12,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.273</x:v>
       </x:c>
-      <x:c r="Z12" s="45" t="str">
+      <x:c r="Z12" s="47" t="str">
         <x:f>IF(OR(Y12="",W12=""),"",Y12-W12)</x:f>
       </x:c>
-      <x:c r="AA12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.34350891194059385</x:v>
-      </x:c>
-      <x:c r="AB12" s="46" t="n">
+      <x:c r="AA12" s="48" t="n">
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.34035758991183096</x:v>
+      </x:c>
+      <x:c r="AB12" s="48" t="n">
         <x:f>IF(OR(AA12="",Y12=""),"",AA12-Y12)</x:f>
-        <x:v>0.07050891194059383</x:v>
-      </x:c>
-      <x:c r="AC12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.4349836394292248</x:v>
-      </x:c>
-      <x:c r="AD12" s="46" t="n">
+        <x:v>0.06735758991183094</x:v>
+      </x:c>
+      <x:c r="AC12" s="48" t="n">
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.4211015559289739</x:v>
+      </x:c>
+      <x:c r="AD12" s="48" t="n">
         <x:f>IF(OR(AC12="",AA12=""),"",AC12-AA12)</x:f>
-        <x:v>0.09147472748863095</x:v>
-      </x:c>
-      <x:c r="AE12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.546885935034326</x:v>
-      </x:c>
-      <x:c r="AF12" s="46" t="n">
+        <x:v>0.08074396601714295</x:v>
+      </x:c>
+      <x:c r="AE12" s="48" t="n">
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.514208223718165</x:v>
+      </x:c>
+      <x:c r="AF12" s="48" t="n">
         <x:f>IF(OR(AE12="",AC12=""),"",AE12-AC12)</x:f>
-        <x:v>0.11190229560510123</x:v>
-      </x:c>
-      <x:c r="AG12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6724939058508238</x:v>
-      </x:c>
-      <x:c r="AH12" s="46" t="n">
+        <x:v>0.09310666778919108</x:v>
+      </x:c>
+      <x:c r="AG12" s="48" t="n">
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6161307327395991</x:v>
+      </x:c>
+      <x:c r="AH12" s="48" t="n">
         <x:f>IF(OR(AG12="",AE12=""),"",AG12-AE12)</x:f>
-        <x:v>0.12560797081649777</x:v>
-      </x:c>
-      <x:c r="AI12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7968373284553182</x:v>
-      </x:c>
-      <x:c r="AJ12" s="46" t="n">
+        <x:v>0.10192250902143407</x:v>
+      </x:c>
+      <x:c r="AI12" s="48" t="n">
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7202007405689884</x:v>
+      </x:c>
+      <x:c r="AJ12" s="48" t="n">
         <x:f>IF(OR(AI12="",AG12=""),"",AI12-AG12)</x:f>
-        <x:v>0.12434342260449438</x:v>
-      </x:c>
-      <x:c r="AK12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8993482722743721</x:v>
-      </x:c>
-      <x:c r="AL12" s="46" t="n">
+        <x:v>0.10407000782938935</x:v>
+      </x:c>
+      <x:c r="AK12" s="48" t="n">
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.817015881051963</x:v>
+      </x:c>
+      <x:c r="AL12" s="48" t="n">
         <x:f>IF(OR(AK12="",AI12=""),"",AK12-AI12)</x:f>
-        <x:v>0.1025109438190539</x:v>
-      </x:c>
-      <x:c r="AM12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9641761672252228</x:v>
-      </x:c>
-      <x:c r="AN12" s="46" t="n">
+        <x:v>0.09681514048297457</x:v>
+      </x:c>
+      <x:c r="AM12" s="48" t="n">
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.896549336983334</x:v>
+      </x:c>
+      <x:c r="AN12" s="48" t="n">
         <x:f>IF(OR(AM12="",AK12=""),"",AM12-AK12)</x:f>
-        <x:v>0.06482789495085073</x:v>
-      </x:c>
-      <x:c r="AO12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9921608906218072</x:v>
-      </x:c>
-      <x:c r="AP12" s="46" t="n">
+        <x:v>0.07953345593137107</x:v>
+      </x:c>
+      <x:c r="AO12" s="48" t="n">
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9519030917755846</x:v>
+      </x:c>
+      <x:c r="AP12" s="48" t="n">
         <x:f>IF(OR(AO12="",AM12=""),"",AO12-AM12)</x:f>
-        <x:v>0.02798472339658442</x:v>
-      </x:c>
-      <x:c r="AQ12" s="46" t="n">
-        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9991612534387434</x:v>
-      </x:c>
-      <x:c r="AR12" s="46" t="n">
+        <x:v>0.055353754792250576</x:v>
+      </x:c>
+      <x:c r="AQ12" s="48" t="n">
+        <x:f>IF('Model'!$D12=0,"",1-POWER(2,-('Model'!$M12+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9828035711791019</x:v>
+      </x:c>
+      <x:c r="AR12" s="48" t="n">
         <x:f>IF(OR(AQ12="",AO12=""),"",AQ12-AO12)</x:f>
-        <x:v>0.007000362816936168</x:v>
+        <x:v>0.030900479403517256</x:v>
       </x:c>
       <x:c r="AS12" s="24" t="n">
         <x:f>IF('Model'!$D12=0,"",Y12)</x:f>
@@ -4302,25 +4339,25 @@
         <x:f>'Model'!S12</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU12" s="26" t="n">
+      <x:c r="AU12" s="25" t="n">
         <x:f>IF('Model'!$D12=0,"",'Model'!T12)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV12" s="26" t="n">
+      <x:c r="AV12" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW12" s="25" t="n">
+      <x:c r="AW12" s="26" t="n">
         <x:f>'Model'!N12</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX12" s="25" t="n">
+      <x:c r="AX12" s="26" t="n">
         <x:f>'Model'!P12</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY12" s="17" t="str">
         <x:f>'Model'!Q12</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="46" hidden="0" customHeight="1">
@@ -4336,146 +4373,146 @@
       <x:c r="D13" s="17" t="str">
         <x:v>Public 600-task pass rate, max reasoning</x:v>
       </x:c>
-      <x:c r="E13" s="44" t="str">
+      <x:c r="E13" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F13" s="44" t="str">
+      <x:c r="F13" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G13" s="44" t="str">
+      <x:c r="G13" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H13" s="44" t="str">
+      <x:c r="H13" s="46" t="str">
         <x:f>IF(OR(G13="",E13=""),"",G13-E13)</x:f>
       </x:c>
-      <x:c r="I13" s="44" t="str">
+      <x:c r="I13" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J13" s="44" t="str">
+      <x:c r="J13" s="46" t="str">
         <x:f>IF(OR(I13="",G13=""),"",I13-G13)</x:f>
       </x:c>
-      <x:c r="K13" s="44" t="str">
+      <x:c r="K13" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L13" s="44" t="str">
+      <x:c r="L13" s="46" t="str">
         <x:f>IF(OR(K13="",I13=""),"",K13-I13)</x:f>
       </x:c>
-      <x:c r="M13" s="44" t="str">
+      <x:c r="M13" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N13" s="44" t="str">
+      <x:c r="N13" s="46" t="str">
         <x:f>IF(OR(M13="",K13=""),"",M13-K13)</x:f>
       </x:c>
-      <x:c r="O13" s="44" t="str">
+      <x:c r="O13" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P13" s="44" t="str">
+      <x:c r="P13" s="46" t="str">
         <x:f>IF(OR(O13="",M13=""),"",O13-M13)</x:f>
       </x:c>
-      <x:c r="Q13" s="44" t="str">
+      <x:c r="Q13" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R13" s="44" t="str">
+      <x:c r="R13" s="46" t="str">
         <x:f>IF(OR(Q13="",O13=""),"",Q13-O13)</x:f>
       </x:c>
-      <x:c r="S13" s="44" t="str">
+      <x:c r="S13" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T13" s="44" t="str">
+      <x:c r="T13" s="46" t="str">
         <x:f>IF(OR(S13="",Q13=""),"",S13-Q13)</x:f>
       </x:c>
-      <x:c r="U13" s="44" t="str">
+      <x:c r="U13" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
       </x:c>
-      <x:c r="V13" s="44" t="str">
+      <x:c r="V13" s="46" t="str">
         <x:f>IF(OR(U13="",S13=""),"",U13-S13)</x:f>
       </x:c>
-      <x:c r="W13" s="45" t="n">
+      <x:c r="W13" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.3033</x:v>
       </x:c>
-      <x:c r="X13" s="45" t="str">
+      <x:c r="X13" s="47" t="str">
         <x:f>IF(OR(W13="",U13=""),"",W13-U13)</x:f>
       </x:c>
-      <x:c r="Y13" s="44" t="n">
+      <x:c r="Y13" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B13,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.3033</x:v>
       </x:c>
-      <x:c r="Z13" s="44" t="n">
+      <x:c r="Z13" s="46" t="n">
         <x:f>IF(OR(Y13="",W13=""),"",Y13-W13)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.3708702323920382</x:v>
-      </x:c>
-      <x:c r="AB13" s="46" t="n">
+      <x:c r="AA13" s="48" t="n">
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.3678502515702513</x:v>
+      </x:c>
+      <x:c r="AB13" s="48" t="n">
         <x:f>IF(OR(AA13="",Y13=""),"",AA13-Y13)</x:f>
-        <x:v>0.06757023239203819</x:v>
-      </x:c>
-      <x:c r="AC13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.45853246436085415</x:v>
-      </x:c>
-      <x:c r="AD13" s="46" t="n">
+        <x:v>0.0645502515702513</x:v>
+      </x:c>
+      <x:c r="AC13" s="48" t="n">
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.445228960131659</x:v>
+      </x:c>
+      <x:c r="AD13" s="48" t="n">
         <x:f>IF(OR(AC13="",AA13=""),"",AC13-AA13)</x:f>
-        <x:v>0.08766223196881595</x:v>
-      </x:c>
-      <x:c r="AE13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.5657708816209285</x:v>
-      </x:c>
-      <x:c r="AF13" s="46" t="n">
+        <x:v>0.07737870856140772</x:v>
+      </x:c>
+      <x:c r="AE13" s="48" t="n">
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.5344551161821809</x:v>
+      </x:c>
+      <x:c r="AF13" s="48" t="n">
         <x:f>IF(OR(AE13="",AC13=""),"",AE13-AC13)</x:f>
-        <x:v>0.10723841726007433</x:v>
-      </x:c>
-      <x:c r="AG13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6861437471888155</x:v>
-      </x:c>
-      <x:c r="AH13" s="46" t="n">
+        <x:v>0.08922615605052187</x:v>
+      </x:c>
+      <x:c r="AG13" s="48" t="n">
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6321296856941935</x:v>
+      </x:c>
+      <x:c r="AH13" s="48" t="n">
         <x:f>IF(OR(AG13="",AE13=""),"",AG13-AE13)</x:f>
-        <x:v>0.12037286556788707</x:v>
-      </x:c>
-      <x:c r="AI13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8053047685485835</x:v>
-      </x:c>
-      <x:c r="AJ13" s="46" t="n">
+        <x:v>0.09767456951201259</x:v>
+      </x:c>
+      <x:c r="AI13" s="48" t="n">
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.731862250281175</x:v>
+      </x:c>
+      <x:c r="AJ13" s="48" t="n">
         <x:f>IF(OR(AI13="",AG13=""),"",AI13-AG13)</x:f>
-        <x:v>0.11916102135976792</x:v>
-      </x:c>
-      <x:c r="AK13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.903543247996637</x:v>
-      </x:c>
-      <x:c r="AL13" s="46" t="n">
+        <x:v>0.09973256458698154</x:v>
+      </x:c>
+      <x:c r="AK13" s="48" t="n">
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.824642316821049</x:v>
+      </x:c>
+      <x:c r="AL13" s="48" t="n">
         <x:f>IF(OR(AK13="",AI13=""),"",AK13-AI13)</x:f>
-        <x:v>0.09823847944805353</x:v>
-      </x:c>
-      <x:c r="AM13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9656692375595775</x:v>
-      </x:c>
-      <x:c r="AN13" s="46" t="n">
+        <x:v>0.09278006653987403</x:v>
+      </x:c>
+      <x:c r="AM13" s="48" t="n">
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9008609670925569</x:v>
+      </x:c>
+      <x:c r="AN13" s="48" t="n">
         <x:f>IF(OR(AM13="",AK13=""),"",AM13-AK13)</x:f>
-        <x:v>0.062125989562940465</x:v>
-      </x:c>
-      <x:c r="AO13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9924876100360566</x:v>
-      </x:c>
-      <x:c r="AP13" s="46" t="n">
+        <x:v>0.07621865027150787</x:v>
+      </x:c>
+      <x:c r="AO13" s="48" t="n">
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9539076809354193</x:v>
+      </x:c>
+      <x:c r="AP13" s="48" t="n">
         <x:f>IF(OR(AO13="",AM13=""),"",AO13-AM13)</x:f>
-        <x:v>0.026818372476479113</x:v>
-      </x:c>
-      <x:c r="AQ13" s="46" t="n">
-        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9991962108263721</x:v>
-      </x:c>
-      <x:c r="AR13" s="46" t="n">
+        <x:v>0.053046713842862414</x:v>
+      </x:c>
+      <x:c r="AQ13" s="48" t="n">
+        <x:f>IF('Model'!$D13=0,"",1-POWER(2,-('Model'!$M13+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9835202861629715</x:v>
+      </x:c>
+      <x:c r="AR13" s="48" t="n">
         <x:f>IF(OR(AQ13="",AO13=""),"",AQ13-AO13)</x:f>
-        <x:v>0.006708600790315544</x:v>
+        <x:v>0.029612605227552158</x:v>
       </x:c>
       <x:c r="AS13" s="24" t="n">
         <x:f>IF('Model'!$D13=0,"",Y13)</x:f>
@@ -4485,25 +4522,25 @@
         <x:f>'Model'!S13</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU13" s="26" t="n">
+      <x:c r="AU13" s="25" t="n">
         <x:f>IF('Model'!$D13=0,"",'Model'!T13)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV13" s="26" t="n">
+      <x:c r="AV13" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW13" s="25" t="n">
+      <x:c r="AW13" s="26" t="n">
         <x:f>'Model'!N13</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX13" s="25" t="n">
+      <x:c r="AX13" s="26" t="n">
         <x:f>'Model'!P13</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY13" s="17" t="str">
         <x:f>'Model'!Q13</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="46" hidden="0" customHeight="1">
@@ -4519,154 +4556,154 @@
       <x:c r="D14" s="17" t="str">
         <x:v>Strict task success across enterprise workflows</x:v>
       </x:c>
-      <x:c r="E14" s="44" t="str">
+      <x:c r="E14" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F14" s="44" t="str">
+      <x:c r="F14" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G14" s="44" t="str">
+      <x:c r="G14" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H14" s="44" t="str">
+      <x:c r="H14" s="46" t="str">
         <x:f>IF(OR(G14="",E14=""),"",G14-E14)</x:f>
       </x:c>
-      <x:c r="I14" s="44" t="str">
+      <x:c r="I14" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J14" s="44" t="str">
+      <x:c r="J14" s="46" t="str">
         <x:f>IF(OR(I14="",G14=""),"",I14-G14)</x:f>
       </x:c>
-      <x:c r="K14" s="44" t="str">
+      <x:c r="K14" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L14" s="44" t="str">
+      <x:c r="L14" s="46" t="str">
         <x:f>IF(OR(K14="",I14=""),"",K14-I14)</x:f>
       </x:c>
-      <x:c r="M14" s="44" t="str">
+      <x:c r="M14" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N14" s="44" t="str">
+      <x:c r="N14" s="46" t="str">
         <x:f>IF(OR(M14="",K14=""),"",M14-K14)</x:f>
       </x:c>
-      <x:c r="O14" s="45" t="n">
+      <x:c r="O14" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P14" s="45" t="str">
+      <x:c r="P14" s="47" t="str">
         <x:f>IF(OR(O14="",M14=""),"",O14-M14)</x:f>
       </x:c>
-      <x:c r="Q14" s="45" t="n">
+      <x:c r="Q14" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
         <x:v>0.341</x:v>
       </x:c>
-      <x:c r="R14" s="45" t="n">
+      <x:c r="R14" s="47" t="n">
         <x:f>IF(OR(Q14="",O14=""),"",Q14-O14)</x:f>
         <x:v>0.14100000000000001</x:v>
       </x:c>
-      <x:c r="S14" s="45" t="n">
+      <x:c r="S14" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
         <x:v>0.394</x:v>
       </x:c>
-      <x:c r="T14" s="45" t="n">
+      <x:c r="T14" s="47" t="n">
         <x:f>IF(OR(S14="",Q14=""),"",S14-Q14)</x:f>
         <x:v>0.05299999999999999</x:v>
       </x:c>
-      <x:c r="U14" s="45" t="n">
+      <x:c r="U14" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
         <x:v>0.459</x:v>
       </x:c>
-      <x:c r="V14" s="45" t="n">
+      <x:c r="V14" s="47" t="n">
         <x:f>IF(OR(U14="",S14=""),"",U14-S14)</x:f>
         <x:v>0.065</x:v>
       </x:c>
-      <x:c r="W14" s="44" t="n">
+      <x:c r="W14" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.459</x:v>
       </x:c>
-      <x:c r="X14" s="44" t="n">
+      <x:c r="X14" s="46" t="n">
         <x:f>IF(OR(W14="",U14=""),"",W14-U14)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y14" s="45" t="n">
+      <x:c r="Y14" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B14,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.511</x:v>
       </x:c>
-      <x:c r="Z14" s="45" t="n">
+      <x:c r="Z14" s="47" t="n">
         <x:f>IF(OR(Y14="",W14=""),"",Y14-W14)</x:f>
         <x:v>0.05199999999999999</x:v>
       </x:c>
-      <x:c r="AA14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.558426214496493</x:v>
-      </x:c>
-      <x:c r="AB14" s="46" t="n">
+      <x:c r="AA14" s="48" t="n">
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.5563065494730197</x:v>
+      </x:c>
+      <x:c r="AB14" s="48" t="n">
         <x:f>IF(OR(AA14="",Y14=""),"",AA14-Y14)</x:f>
-        <x:v>0.04742621449649298</x:v>
-      </x:c>
-      <x:c r="AC14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6199546075390522</x:v>
-      </x:c>
-      <x:c r="AD14" s="46" t="n">
+        <x:v>0.04530654947301971</x:v>
+      </x:c>
+      <x:c r="AC14" s="48" t="n">
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6106171400952796</x:v>
+      </x:c>
+      <x:c r="AD14" s="48" t="n">
         <x:f>IF(OR(AC14="",AA14=""),"",AC14-AA14)</x:f>
-        <x:v>0.06152839304255919</x:v>
-      </x:c>
-      <x:c r="AE14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6952231392459222</x:v>
-      </x:c>
-      <x:c r="AF14" s="46" t="n">
+        <x:v>0.05431059062225985</x:v>
+      </x:c>
+      <x:c r="AE14" s="48" t="n">
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6732432206302374</x:v>
+      </x:c>
+      <x:c r="AF14" s="48" t="n">
         <x:f>IF(OR(AE14="",AC14=""),"",AE14-AC14)</x:f>
-        <x:v>0.07526853170686998</x:v>
-      </x:c>
-      <x:c r="AG14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.779710481376964</x:v>
-      </x:c>
-      <x:c r="AH14" s="46" t="n">
+        <x:v>0.06262608053495788</x:v>
+      </x:c>
+      <x:c r="AG14" s="48" t="n">
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7417990760793176</x:v>
+      </x:c>
+      <x:c r="AH14" s="48" t="n">
         <x:f>IF(OR(AG14="",AE14=""),"",AG14-AE14)</x:f>
-        <x:v>0.08448734213104181</x:v>
-      </x:c>
-      <x:c r="AI14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8633472539403722</x:v>
-      </x:c>
-      <x:c r="AJ14" s="46" t="n">
+        <x:v>0.06855585544908016</x:v>
+      </x:c>
+      <x:c r="AI14" s="48" t="n">
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8117993977142164</x:v>
+      </x:c>
+      <x:c r="AJ14" s="48" t="n">
         <x:f>IF(OR(AI14="",AG14=""),"",AI14-AG14)</x:f>
-        <x:v>0.08363677256340818</x:v>
-      </x:c>
-      <x:c r="AK14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9322989066604787</x:v>
-      </x:c>
-      <x:c r="AL14" s="46" t="n">
+        <x:v>0.07000032163489878</x:v>
+      </x:c>
+      <x:c r="AK14" s="48" t="n">
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8769198979840576</x:v>
+      </x:c>
+      <x:c r="AL14" s="48" t="n">
         <x:f>IF(OR(AK14="",AI14=""),"",AK14-AI14)</x:f>
-        <x:v>0.0689516527201065</x:v>
-      </x:c>
-      <x:c r="AM14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9759039144059615</x:v>
-      </x:c>
-      <x:c r="AN14" s="46" t="n">
+        <x:v>0.06512050026984118</x:v>
+      </x:c>
+      <x:c r="AM14" s="48" t="n">
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.930416266554127</x:v>
+      </x:c>
+      <x:c r="AN14" s="48" t="n">
         <x:f>IF(OR(AM14="",AK14=""),"",AM14-AK14)</x:f>
-        <x:v>0.043605007745482816</x:v>
-      </x:c>
-      <x:c r="AO14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9947272015324123</x:v>
-      </x:c>
-      <x:c r="AP14" s="46" t="n">
+        <x:v>0.05349636857006945</x:v>
+      </x:c>
+      <x:c r="AO14" s="48" t="n">
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9676487095987083</x:v>
+      </x:c>
+      <x:c r="AP14" s="48" t="n">
         <x:f>IF(OR(AO14="",AM14=""),"",AO14-AM14)</x:f>
-        <x:v>0.01882328712645087</x:v>
-      </x:c>
-      <x:c r="AQ14" s="46" t="n">
-        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9994358362194574</x:v>
-      </x:c>
-      <x:c r="AR14" s="46" t="n">
+        <x:v>0.03723244304458129</x:v>
+      </x:c>
+      <x:c r="AQ14" s="48" t="n">
+        <x:f>IF('Model'!$D14=0,"",1-POWER(2,-('Model'!$M14+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9884332136266587</x:v>
+      </x:c>
+      <x:c r="AR14" s="48" t="n">
         <x:f>IF(OR(AQ14="",AO14=""),"",AQ14-AO14)</x:f>
-        <x:v>0.004708634687045077</x:v>
+        <x:v>0.0207845040279504</x:v>
       </x:c>
       <x:c r="AS14" s="24" t="n">
         <x:f>IF('Model'!$D14=0,"",Y14)</x:f>
@@ -4676,25 +4713,25 @@
         <x:f>'Model'!S14</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU14" s="26" t="n">
+      <x:c r="AU14" s="25" t="n">
         <x:f>IF('Model'!$D14=0,"",'Model'!T14)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV14" s="26" t="n">
+      <x:c r="AV14" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW14" s="25" t="n">
+      <x:c r="AW14" s="26" t="n">
         <x:f>'Model'!N14</x:f>
         <x:v>0.0728970644372906</x:v>
       </x:c>
-      <x:c r="AX14" s="25" t="n">
+      <x:c r="AX14" s="26" t="n">
         <x:f>'Model'!P14</x:f>
         <x:v>-0.06052809013923022</x:v>
       </x:c>
       <x:c r="AY14" s="17" t="str">
         <x:f>'Model'!Q14</x:f>
-        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
+        <x:v>METR feedback transfer — local acceleration retained as diagnostic</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="46" hidden="0" customHeight="1">
@@ -4710,150 +4747,150 @@
       <x:c r="D15" s="17" t="str">
         <x:v>Pi-harness full-suite pass rate</x:v>
       </x:c>
-      <x:c r="E15" s="44" t="str">
+      <x:c r="E15" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F15" s="44" t="str">
+      <x:c r="F15" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G15" s="44" t="str">
+      <x:c r="G15" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H15" s="44" t="str">
+      <x:c r="H15" s="46" t="str">
         <x:f>IF(OR(G15="",E15=""),"",G15-E15)</x:f>
       </x:c>
-      <x:c r="I15" s="44" t="str">
+      <x:c r="I15" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J15" s="44" t="str">
+      <x:c r="J15" s="46" t="str">
         <x:f>IF(OR(I15="",G15=""),"",I15-G15)</x:f>
       </x:c>
-      <x:c r="K15" s="44" t="str">
+      <x:c r="K15" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L15" s="44" t="str">
+      <x:c r="L15" s="46" t="str">
         <x:f>IF(OR(K15="",I15=""),"",K15-I15)</x:f>
       </x:c>
-      <x:c r="M15" s="44" t="str">
+      <x:c r="M15" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N15" s="44" t="str">
+      <x:c r="N15" s="46" t="str">
         <x:f>IF(OR(M15="",K15=""),"",M15-K15)</x:f>
       </x:c>
-      <x:c r="O15" s="44" t="str">
+      <x:c r="O15" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P15" s="44" t="str">
+      <x:c r="P15" s="46" t="str">
         <x:f>IF(OR(O15="",M15=""),"",O15-M15)</x:f>
       </x:c>
-      <x:c r="Q15" s="44" t="str">
+      <x:c r="Q15" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R15" s="44" t="str">
+      <x:c r="R15" s="46" t="str">
         <x:f>IF(OR(Q15="",O15=""),"",Q15-O15)</x:f>
       </x:c>
-      <x:c r="S15" s="45" t="n">
+      <x:c r="S15" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
         <x:v>0.29</x:v>
       </x:c>
-      <x:c r="T15" s="45" t="str">
+      <x:c r="T15" s="47" t="str">
         <x:f>IF(OR(S15="",Q15=""),"",S15-Q15)</x:f>
       </x:c>
-      <x:c r="U15" s="44" t="n">
+      <x:c r="U15" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
         <x:v>0.29</x:v>
       </x:c>
-      <x:c r="V15" s="44" t="n">
+      <x:c r="V15" s="46" t="n">
         <x:f>IF(OR(U15="",S15=""),"",U15-S15)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="W15" s="45" t="n">
+      <x:c r="W15" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.523</x:v>
       </x:c>
-      <x:c r="X15" s="45" t="n">
+      <x:c r="X15" s="47" t="n">
         <x:f>IF(OR(W15="",U15=""),"",W15-U15)</x:f>
         <x:v>0.23300000000000004</x:v>
       </x:c>
-      <x:c r="Y15" s="45" t="n">
+      <x:c r="Y15" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B15,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.607</x:v>
       </x:c>
-      <x:c r="Z15" s="45" t="n">
+      <x:c r="Z15" s="47" t="n">
         <x:f>IF(OR(Y15="",W15=""),"",Y15-W15)</x:f>
         <x:v>0.08399999999999996</x:v>
       </x:c>
-      <x:c r="AA15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6451155466198808</x:v>
-      </x:c>
-      <x:c r="AB15" s="46" t="n">
+      <x:c r="AA15" s="48" t="n">
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.643412012153163</x:v>
+      </x:c>
+      <x:c r="AB15" s="48" t="n">
         <x:f>IF(OR(AA15="",Y15=""),"",AA15-Y15)</x:f>
-        <x:v>0.038115546619880813</x:v>
-      </x:c>
-      <x:c r="AC15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6945647459362935</x:v>
-      </x:c>
-      <x:c r="AD15" s="46" t="n">
+        <x:v>0.03641201215316303</x:v>
+      </x:c>
+      <x:c r="AC15" s="48" t="n">
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.68706040093547</x:v>
+      </x:c>
+      <x:c r="AD15" s="48" t="n">
         <x:f>IF(OR(AC15="",AA15=""),"",AC15-AA15)</x:f>
-        <x:v>0.04944919931641267</x:v>
-      </x:c>
-      <x:c r="AE15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.755056633381692</x:v>
-      </x:c>
-      <x:c r="AF15" s="46" t="n">
+        <x:v>0.043648388782307035</x:v>
+      </x:c>
+      <x:c r="AE15" s="48" t="n">
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7373917908132583</x:v>
+      </x:c>
+      <x:c r="AF15" s="48" t="n">
         <x:f>IF(OR(AE15="",AC15=""),"",AE15-AC15)</x:f>
-        <x:v>0.06049188744539857</x:v>
-      </x:c>
-      <x:c r="AG15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8229575034379281</x:v>
-      </x:c>
-      <x:c r="AH15" s="46" t="n">
+        <x:v>0.05033138987778829</x:v>
+      </x:c>
+      <x:c r="AG15" s="48" t="n">
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7924888280146662</x:v>
+      </x:c>
+      <x:c r="AH15" s="48" t="n">
         <x:f>IF(OR(AG15="",AE15=""),"",AG15-AE15)</x:f>
-        <x:v>0.06790087005623602</x:v>
-      </x:c>
-      <x:c r="AI15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8901747869091334</x:v>
-      </x:c>
-      <x:c r="AJ15" s="46" t="n">
+        <x:v>0.055097037201407906</x:v>
+      </x:c>
+      <x:c r="AI15" s="48" t="n">
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8487467552181739</x:v>
+      </x:c>
+      <x:c r="AJ15" s="48" t="n">
         <x:f>IF(OR(AI15="",AG15=""),"",AI15-AG15)</x:f>
-        <x:v>0.06721728347120537</x:v>
-      </x:c>
-      <x:c r="AK15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9455899188498325</x:v>
-      </x:c>
-      <x:c r="AL15" s="46" t="n">
+        <x:v>0.05625792720350764</x:v>
+      </x:c>
+      <x:c r="AK15" s="48" t="n">
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9010828627970033</x:v>
+      </x:c>
+      <x:c r="AL15" s="48" t="n">
         <x:f>IF(OR(AK15="",AI15=""),"",AK15-AI15)</x:f>
-        <x:v>0.055415131940699025</x:v>
-      </x:c>
-      <x:c r="AM15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9806344342771838</x:v>
-      </x:c>
-      <x:c r="AN15" s="46" t="n">
+        <x:v>0.05233610757882945</x:v>
+      </x:c>
+      <x:c r="AM15" s="48" t="n">
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9440768768011696</x:v>
+      </x:c>
+      <x:c r="AN15" s="48" t="n">
         <x:f>IF(OR(AM15="",AK15=""),"",AM15-AK15)</x:f>
-        <x:v>0.03504451542735132</x:v>
-      </x:c>
-      <x:c r="AO15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9957623521518161</x:v>
-      </x:c>
-      <x:c r="AP15" s="46" t="n">
+        <x:v>0.04299401400416625</x:v>
+      </x:c>
+      <x:c r="AO15" s="48" t="n">
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.973999883174422</x:v>
+      </x:c>
+      <x:c r="AP15" s="48" t="n">
         <x:f>IF(OR(AO15="",AM15=""),"",AO15-AM15)</x:f>
-        <x:v>0.015127917874632302</x:v>
-      </x:c>
-      <x:c r="AQ15" s="46" t="n">
-        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9995465922990731</x:v>
-      </x:c>
-      <x:c r="AR15" s="46" t="n">
+        <x:v>0.029923006373252403</x:v>
+      </x:c>
+      <x:c r="AQ15" s="48" t="n">
+        <x:f>IF('Model'!$D15=0,"",1-POWER(2,-('Model'!$M15+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9907039937735723</x:v>
+      </x:c>
+      <x:c r="AR15" s="48" t="n">
         <x:f>IF(OR(AQ15="",AO15=""),"",AQ15-AO15)</x:f>
-        <x:v>0.0037842401472569787</x:v>
+        <x:v>0.016704110599150335</x:v>
       </x:c>
       <x:c r="AS15" s="24" t="n">
         <x:f>IF('Model'!$D15=0,"",Y15)</x:f>
@@ -4863,25 +4900,25 @@
         <x:f>'Model'!S15</x:f>
         <x:v>D</x:v>
       </x:c>
-      <x:c r="AU15" s="26" t="n">
+      <x:c r="AU15" s="25" t="n">
         <x:f>IF('Model'!$D15=0,"",'Model'!T15)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AV15" s="26" t="n">
+      <x:c r="AV15" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW15" s="25" t="n">
+      <x:c r="AW15" s="26" t="n">
         <x:f>'Model'!N15</x:f>
         <x:v>0.2794599537469049</x:v>
       </x:c>
-      <x:c r="AX15" s="25" t="n">
+      <x:c r="AX15" s="26" t="n">
         <x:f>'Model'!P15</x:f>
         <x:v>-0.004969950297574337</x:v>
       </x:c>
       <x:c r="AY15" s="17" t="str">
         <x:f>'Model'!Q15</x:f>
-        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
+        <x:v>METR feedback transfer — local acceleration retained as diagnostic</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="46" hidden="0" customHeight="1">
@@ -4897,148 +4934,148 @@
       <x:c r="D16" s="17" t="str">
         <x:v>Avg@3 weighted deterministic-checker score</x:v>
       </x:c>
-      <x:c r="E16" s="44" t="str">
+      <x:c r="E16" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F16" s="44" t="str">
+      <x:c r="F16" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G16" s="44" t="str">
+      <x:c r="G16" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H16" s="44" t="str">
+      <x:c r="H16" s="46" t="str">
         <x:f>IF(OR(G16="",E16=""),"",G16-E16)</x:f>
       </x:c>
-      <x:c r="I16" s="44" t="str">
+      <x:c r="I16" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J16" s="44" t="str">
+      <x:c r="J16" s="46" t="str">
         <x:f>IF(OR(I16="",G16=""),"",I16-G16)</x:f>
       </x:c>
-      <x:c r="K16" s="44" t="str">
+      <x:c r="K16" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L16" s="44" t="str">
+      <x:c r="L16" s="46" t="str">
         <x:f>IF(OR(K16="",I16=""),"",K16-I16)</x:f>
       </x:c>
-      <x:c r="M16" s="44" t="str">
+      <x:c r="M16" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N16" s="44" t="str">
+      <x:c r="N16" s="46" t="str">
         <x:f>IF(OR(M16="",K16=""),"",M16-K16)</x:f>
       </x:c>
-      <x:c r="O16" s="44" t="str">
+      <x:c r="O16" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P16" s="44" t="str">
+      <x:c r="P16" s="46" t="str">
         <x:f>IF(OR(O16="",M16=""),"",O16-M16)</x:f>
       </x:c>
-      <x:c r="Q16" s="44" t="str">
+      <x:c r="Q16" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R16" s="44" t="str">
+      <x:c r="R16" s="46" t="str">
         <x:f>IF(OR(Q16="",O16=""),"",Q16-O16)</x:f>
       </x:c>
-      <x:c r="S16" s="44" t="str">
+      <x:c r="S16" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T16" s="44" t="str">
+      <x:c r="T16" s="46" t="str">
         <x:f>IF(OR(S16="",Q16=""),"",S16-Q16)</x:f>
       </x:c>
-      <x:c r="U16" s="45" t="n">
+      <x:c r="U16" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
         <x:v>0.758</x:v>
       </x:c>
-      <x:c r="V16" s="45" t="str">
+      <x:c r="V16" s="47" t="str">
         <x:f>IF(OR(U16="",S16=""),"",U16-S16)</x:f>
       </x:c>
-      <x:c r="W16" s="44" t="n">
+      <x:c r="W16" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.758</x:v>
       </x:c>
-      <x:c r="X16" s="44" t="n">
+      <x:c r="X16" s="46" t="n">
         <x:f>IF(OR(W16="",U16=""),"",W16-U16)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y16" s="44" t="n">
+      <x:c r="Y16" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B16,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.758</x:v>
       </x:c>
-      <x:c r="Z16" s="44" t="n">
+      <x:c r="Z16" s="46" t="n">
         <x:f>IF(OR(Y16="",W16=""),"",Y16-W16)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7814706419389598</x:v>
-      </x:c>
-      <x:c r="AB16" s="46" t="n">
+      <x:c r="AA16" s="48" t="n">
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7804216461604719</x:v>
+      </x:c>
+      <x:c r="AB16" s="48" t="n">
         <x:f>IF(OR(AA16="",Y16=""),"",AA16-Y16)</x:f>
-        <x:v>0.023470641938959758</x:v>
-      </x:c>
-      <x:c r="AC16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8119202761236209</x:v>
-      </x:c>
-      <x:c r="AD16" s="46" t="n">
+        <x:v>0.02242164616047193</x:v>
+      </x:c>
+      <x:c r="AC16" s="48" t="n">
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8072992799653531</x:v>
+      </x:c>
+      <x:c r="AD16" s="48" t="n">
         <x:f>IF(OR(AC16="",AA16=""),"",AC16-AA16)</x:f>
-        <x:v>0.03044963418466118</x:v>
-      </x:c>
-      <x:c r="AE16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8491697335327468</x:v>
-      </x:c>
-      <x:c r="AF16" s="46" t="n">
+        <x:v>0.026877633804881174</x:v>
+      </x:c>
+      <x:c r="AE16" s="48" t="n">
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8382921459969683</x:v>
+      </x:c>
+      <x:c r="AF16" s="48" t="n">
         <x:f>IF(OR(AE16="",AC16=""),"",AE16-AC16)</x:f>
-        <x:v>0.037249457409125886</x:v>
-      </x:c>
-      <x:c r="AG16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8909814652213196</x:v>
-      </x:c>
-      <x:c r="AH16" s="46" t="n">
+        <x:v>0.030992866031615218</x:v>
+      </x:c>
+      <x:c r="AG16" s="48" t="n">
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8722195836629753</x:v>
+      </x:c>
+      <x:c r="AH16" s="48" t="n">
         <x:f>IF(OR(AG16="",AE16=""),"",AG16-AE16)</x:f>
-        <x:v>0.04181173168857277</x:v>
-      </x:c>
-      <x:c r="AI16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9323722606412477</x:v>
-      </x:c>
-      <x:c r="AJ16" s="46" t="n">
+        <x:v>0.03392743766600692</x:v>
+      </x:c>
+      <x:c r="AI16" s="48" t="n">
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9068618696254405</x:v>
+      </x:c>
+      <x:c r="AJ16" s="48" t="n">
         <x:f>IF(OR(AI16="",AG16=""),"",AI16-AG16)</x:f>
-        <x:v>0.04139079541992807</x:v>
-      </x:c>
-      <x:c r="AK16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9664955734393371</x:v>
-      </x:c>
-      <x:c r="AL16" s="46" t="n">
+        <x:v>0.034642285962465214</x:v>
+      </x:c>
+      <x:c r="AK16" s="48" t="n">
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9390891928673659</x:v>
+      </x:c>
+      <x:c r="AL16" s="48" t="n">
         <x:f>IF(OR(AK16="",AI16=""),"",AK16-AI16)</x:f>
-        <x:v>0.034123312798089445</x:v>
-      </x:c>
-      <x:c r="AM16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9880751478246271</x:v>
-      </x:c>
-      <x:c r="AN16" s="46" t="n">
+        <x:v>0.032227323241925454</x:v>
+      </x:c>
+      <x:c r="AM16" s="48" t="n">
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9655638783355802</x:v>
+      </x:c>
+      <x:c r="AN16" s="48" t="n">
         <x:f>IF(OR(AM16="",AK16=""),"",AM16-AK16)</x:f>
-        <x:v>0.021579574385290012</x:v>
-      </x:c>
-      <x:c r="AO16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9973905578135864</x:v>
-      </x:c>
-      <x:c r="AP16" s="46" t="n">
+        <x:v>0.0264746854682143</x:v>
+      </x:c>
+      <x:c r="AO16" s="48" t="n">
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.983989749944555</x:v>
+      </x:c>
+      <x:c r="AP16" s="48" t="n">
         <x:f>IF(OR(AO16="",AM16=""),"",AO16-AM16)</x:f>
-        <x:v>0.0093154099889593</x:v>
-      </x:c>
-      <x:c r="AQ16" s="46" t="n">
-        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9997208023826354</x:v>
-      </x:c>
-      <x:c r="AR16" s="46" t="n">
+        <x:v>0.018425871608974798</x:v>
+      </x:c>
+      <x:c r="AQ16" s="48" t="n">
+        <x:f>IF('Model'!$D16=0,"",1-POWER(2,-('Model'!$M16+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9942757417129885</x:v>
+      </x:c>
+      <x:c r="AR16" s="48" t="n">
         <x:f>IF(OR(AQ16="",AO16=""),"",AQ16-AO16)</x:f>
-        <x:v>0.002330244569048956</x:v>
+        <x:v>0.010285991768433478</x:v>
       </x:c>
       <x:c r="AS16" s="24" t="n">
         <x:f>IF('Model'!$D16=0,"",Y16)</x:f>
@@ -5048,25 +5085,25 @@
         <x:f>'Model'!S16</x:f>
         <x:v>C</x:v>
       </x:c>
-      <x:c r="AU16" s="26" t="n">
+      <x:c r="AU16" s="25" t="n">
         <x:f>IF('Model'!$D16=0,"",'Model'!T16)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AV16" s="26" t="n">
+      <x:c r="AV16" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW16" s="25" t="n">
+      <x:c r="AW16" s="26" t="n">
         <x:f>'Model'!N16</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX16" s="25" t="n">
+      <x:c r="AX16" s="26" t="n">
         <x:f>'Model'!P16</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY16" s="17" t="str">
         <x:f>'Model'!Q16</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="46" hidden="0" customHeight="1">
@@ -5082,158 +5119,158 @@
       <x:c r="D17" s="17" t="str">
         <x:v>Fraction of workplace tasks completed</x:v>
       </x:c>
-      <x:c r="E17" s="44" t="str">
+      <x:c r="E17" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F17" s="44" t="str">
+      <x:c r="F17" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G17" s="44" t="str">
+      <x:c r="G17" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H17" s="44" t="str">
+      <x:c r="H17" s="46" t="str">
         <x:f>IF(OR(G17="",E17=""),"",G17-E17)</x:f>
       </x:c>
-      <x:c r="I17" s="44" t="str">
+      <x:c r="I17" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J17" s="44" t="str">
+      <x:c r="J17" s="46" t="str">
         <x:f>IF(OR(I17="",G17=""),"",I17-G17)</x:f>
       </x:c>
-      <x:c r="K17" s="45" t="n">
+      <x:c r="K17" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
         <x:v>0.24</x:v>
       </x:c>
-      <x:c r="L17" s="45" t="str">
+      <x:c r="L17" s="47" t="str">
         <x:f>IF(OR(K17="",I17=""),"",K17-I17)</x:f>
       </x:c>
-      <x:c r="M17" s="44" t="n">
+      <x:c r="M17" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
         <x:v>0.24</x:v>
       </x:c>
-      <x:c r="N17" s="44" t="n">
+      <x:c r="N17" s="46" t="n">
         <x:f>IF(OR(M17="",K17=""),"",M17-K17)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O17" s="45" t="n">
+      <x:c r="O17" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
         <x:v>0.303</x:v>
       </x:c>
-      <x:c r="P17" s="45" t="n">
+      <x:c r="P17" s="47" t="n">
         <x:f>IF(OR(O17="",M17=""),"",O17-M17)</x:f>
         <x:v>0.063</x:v>
       </x:c>
-      <x:c r="Q17" s="45" t="n">
+      <x:c r="Q17" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
         <x:v>0.429</x:v>
       </x:c>
-      <x:c r="R17" s="45" t="n">
+      <x:c r="R17" s="47" t="n">
         <x:f>IF(OR(Q17="",O17=""),"",Q17-O17)</x:f>
         <x:v>0.126</x:v>
       </x:c>
-      <x:c r="S17" s="44" t="n">
+      <x:c r="S17" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
         <x:v>0.429</x:v>
       </x:c>
-      <x:c r="T17" s="44" t="n">
+      <x:c r="T17" s="46" t="n">
         <x:f>IF(OR(S17="",Q17=""),"",S17-Q17)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U17" s="44" t="n">
+      <x:c r="U17" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
         <x:v>0.429</x:v>
       </x:c>
-      <x:c r="V17" s="44" t="n">
+      <x:c r="V17" s="46" t="n">
         <x:f>IF(OR(U17="",S17=""),"",U17-S17)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="W17" s="44" t="n">
+      <x:c r="W17" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.429</x:v>
       </x:c>
-      <x:c r="X17" s="44" t="n">
+      <x:c r="X17" s="46" t="n">
         <x:f>IF(OR(W17="",U17=""),"",W17-U17)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y17" s="44" t="n">
+      <x:c r="Y17" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B17,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.429</x:v>
       </x:c>
-      <x:c r="Z17" s="44" t="n">
+      <x:c r="Z17" s="46" t="n">
         <x:f>IF(OR(Y17="",W17=""),"",Y17-W17)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.48437907664109925</x:v>
-      </x:c>
-      <x:c r="AB17" s="46" t="n">
+      <x:c r="AA17" s="48" t="n">
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.48190396676706404</x:v>
+      </x:c>
+      <x:c r="AB17" s="48" t="n">
         <x:f>IF(OR(AA17="",Y17=""),"",AA17-Y17)</x:f>
-        <x:v>0.055379076641099256</x:v>
-      </x:c>
-      <x:c r="AC17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.5562251143247421</x:v>
-      </x:c>
-      <x:c r="AD17" s="46" t="n">
+        <x:v>0.05290396676706405</x:v>
+      </x:c>
+      <x:c r="AC17" s="48" t="n">
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.5453218547942835</x:v>
+      </x:c>
+      <x:c r="AD17" s="48" t="n">
         <x:f>IF(OR(AC17="",AA17=""),"",AC17-AA17)</x:f>
-        <x:v>0.07184603768364284</x:v>
-      </x:c>
-      <x:c r="AE17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6441153630049521</x:v>
-      </x:c>
-      <x:c r="AF17" s="46" t="n">
+        <x:v>0.06341788802721948</x:v>
+      </x:c>
+      <x:c r="AE17" s="48" t="n">
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6184496502655739</x:v>
+      </x:c>
+      <x:c r="AF17" s="48" t="n">
         <x:f>IF(OR(AE17="",AC17=""),"",AE17-AC17)</x:f>
-        <x:v>0.08789024868021</x:v>
-      </x:c>
-      <x:c r="AG17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7427703166998905</x:v>
-      </x:c>
-      <x:c r="AH17" s="46" t="n">
+        <x:v>0.07312779547129034</x:v>
+      </x:c>
+      <x:c r="AG17" s="48" t="n">
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6985015796345406</x:v>
+      </x:c>
+      <x:c r="AH17" s="48" t="n">
         <x:f>IF(OR(AG17="",AE17=""),"",AG17-AE17)</x:f>
-        <x:v>0.09865495369493837</x:v>
-      </x:c>
-      <x:c r="AI17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8404320695295553</x:v>
-      </x:c>
-      <x:c r="AJ17" s="46" t="n">
+        <x:v>0.08005192936896677</x:v>
+      </x:c>
+      <x:c r="AI17" s="48" t="n">
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7802401965129194</x:v>
+      </x:c>
+      <x:c r="AJ17" s="48" t="n">
         <x:f>IF(OR(AI17="",AG17=""),"",AI17-AG17)</x:f>
-        <x:v>0.09766175282966483</x:v>
-      </x:c>
-      <x:c r="AK17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9209461670820722</x:v>
-      </x:c>
-      <x:c r="AL17" s="46" t="n">
+        <x:v>0.0817386168783788</x:v>
+      </x:c>
+      <x:c r="AK17" s="48" t="n">
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8562806988729998</x:v>
+      </x:c>
+      <x:c r="AL17" s="48" t="n">
         <x:f>IF(OR(AK17="",AI17=""),"",AK17-AI17)</x:f>
-        <x:v>0.08051409755251693</x:v>
-      </x:c>
-      <x:c r="AM17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9718632620159591</x:v>
-      </x:c>
-      <x:c r="AN17" s="46" t="n">
+        <x:v>0.07604050236008042</x:v>
+      </x:c>
+      <x:c r="AM17" s="48" t="n">
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9187478286347782</x:v>
+      </x:c>
+      <x:c r="AN17" s="48" t="n">
         <x:f>IF(OR(AM17="",AK17=""),"",AM17-AK17)</x:f>
-        <x:v>0.05091709493388685</x:v>
-      </x:c>
-      <x:c r="AO17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9938430103783383</x:v>
-      </x:c>
-      <x:c r="AP17" s="46" t="n">
+        <x:v>0.06246712976177837</x:v>
+      </x:c>
+      <x:c r="AO17" s="48" t="n">
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9622237488361195</x:v>
+      </x:c>
+      <x:c r="AP17" s="48" t="n">
         <x:f>IF(OR(AO17="",AM17=""),"",AO17-AM17)</x:f>
-        <x:v>0.02197974836237926</x:v>
-      </x:c>
-      <x:c r="AQ17" s="46" t="n">
-        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.999341232068119</x:v>
-      </x:c>
-      <x:c r="AR17" s="46" t="n">
+        <x:v>0.04347592020134128</x:v>
+      </x:c>
+      <x:c r="AQ17" s="48" t="n">
+        <x:f>IF('Model'!$D17=0,"",1-POWER(2,-('Model'!$M17+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9864935889178366</x:v>
+      </x:c>
+      <x:c r="AR17" s="48" t="n">
         <x:f>IF(OR(AQ17="",AO17=""),"",AQ17-AO17)</x:f>
-        <x:v>0.005498221689780647</x:v>
+        <x:v>0.024269840081717065</x:v>
       </x:c>
       <x:c r="AS17" s="24" t="n">
         <x:f>IF('Model'!$D17=0,"",Y17)</x:f>
@@ -5243,25 +5280,25 @@
         <x:f>'Model'!S17</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU17" s="26" t="n">
+      <x:c r="AU17" s="25" t="n">
         <x:f>IF('Model'!$D17=0,"",'Model'!T17)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV17" s="26" t="n">
+      <x:c r="AV17" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW17" s="25" t="n">
+      <x:c r="AW17" s="26" t="n">
         <x:f>'Model'!N17</x:f>
         <x:v>0.2876679105055806</x:v>
       </x:c>
-      <x:c r="AX17" s="25" t="n">
+      <x:c r="AX17" s="26" t="n">
         <x:f>'Model'!P17</x:f>
         <x:v>0.15016501951621217</x:v>
       </x:c>
       <x:c r="AY17" s="17" t="str">
         <x:f>'Model'!Q17</x:f>
-        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
+        <x:v>METR feedback transfer — local acceleration retained as diagnostic</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="46" hidden="0" customHeight="1">
@@ -5277,124 +5314,124 @@
       <x:c r="D18" s="17" t="str">
         <x:v>Browser workplace task success</x:v>
       </x:c>
-      <x:c r="E18" s="44" t="str">
+      <x:c r="E18" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F18" s="44" t="str">
+      <x:c r="F18" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G18" s="44" t="str">
+      <x:c r="G18" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H18" s="44" t="str">
+      <x:c r="H18" s="46" t="str">
         <x:f>IF(OR(G18="",E18=""),"",G18-E18)</x:f>
       </x:c>
-      <x:c r="I18" s="44" t="str">
+      <x:c r="I18" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J18" s="44" t="str">
+      <x:c r="J18" s="46" t="str">
         <x:f>IF(OR(I18="",G18=""),"",I18-G18)</x:f>
       </x:c>
-      <x:c r="K18" s="44" t="str">
+      <x:c r="K18" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L18" s="44" t="str">
+      <x:c r="L18" s="46" t="str">
         <x:f>IF(OR(K18="",I18=""),"",K18-I18)</x:f>
       </x:c>
-      <x:c r="M18" s="44" t="str">
+      <x:c r="M18" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N18" s="44" t="str">
+      <x:c r="N18" s="46" t="str">
         <x:f>IF(OR(M18="",K18=""),"",M18-K18)</x:f>
       </x:c>
-      <x:c r="O18" s="44" t="str">
+      <x:c r="O18" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P18" s="44" t="str">
+      <x:c r="P18" s="46" t="str">
         <x:f>IF(OR(O18="",M18=""),"",O18-M18)</x:f>
       </x:c>
-      <x:c r="Q18" s="44" t="str">
+      <x:c r="Q18" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R18" s="44" t="str">
+      <x:c r="R18" s="46" t="str">
         <x:f>IF(OR(Q18="",O18=""),"",Q18-O18)</x:f>
       </x:c>
-      <x:c r="S18" s="44" t="str">
+      <x:c r="S18" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T18" s="44" t="str">
+      <x:c r="T18" s="46" t="str">
         <x:f>IF(OR(S18="",Q18=""),"",S18-Q18)</x:f>
       </x:c>
-      <x:c r="U18" s="44" t="str">
+      <x:c r="U18" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
       </x:c>
-      <x:c r="V18" s="44" t="str">
+      <x:c r="V18" s="46" t="str">
         <x:f>IF(OR(U18="",S18=""),"",U18-S18)</x:f>
       </x:c>
-      <x:c r="W18" s="44" t="str">
+      <x:c r="W18" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
       </x:c>
-      <x:c r="X18" s="44" t="str">
+      <x:c r="X18" s="46" t="str">
         <x:f>IF(OR(W18="",U18=""),"",W18-U18)</x:f>
       </x:c>
-      <x:c r="Y18" s="44" t="str">
+      <x:c r="Y18" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B18,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
       </x:c>
-      <x:c r="Z18" s="44" t="str">
+      <x:c r="Z18" s="46" t="str">
         <x:f>IF(OR(Y18="",W18=""),"",Y18-W18)</x:f>
       </x:c>
-      <x:c r="AA18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AB18" s="46" t="str">
+      <x:c r="AA18" s="48" t="str">
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AB18" s="48" t="str">
         <x:f>IF(OR(AA18="",Y18=""),"",AA18-Y18)</x:f>
       </x:c>
-      <x:c r="AC18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AD18" s="46" t="str">
+      <x:c r="AC18" s="48" t="str">
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AD18" s="48" t="str">
         <x:f>IF(OR(AC18="",AA18=""),"",AC18-AA18)</x:f>
       </x:c>
-      <x:c r="AE18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AF18" s="46" t="str">
+      <x:c r="AE18" s="48" t="str">
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AF18" s="48" t="str">
         <x:f>IF(OR(AE18="",AC18=""),"",AE18-AC18)</x:f>
       </x:c>
-      <x:c r="AG18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AH18" s="46" t="str">
+      <x:c r="AG18" s="48" t="str">
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AH18" s="48" t="str">
         <x:f>IF(OR(AG18="",AE18=""),"",AG18-AE18)</x:f>
       </x:c>
-      <x:c r="AI18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AJ18" s="46" t="str">
+      <x:c r="AI18" s="48" t="str">
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AJ18" s="48" t="str">
         <x:f>IF(OR(AI18="",AG18=""),"",AI18-AG18)</x:f>
       </x:c>
-      <x:c r="AK18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AL18" s="46" t="str">
+      <x:c r="AK18" s="48" t="str">
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AL18" s="48" t="str">
         <x:f>IF(OR(AK18="",AI18=""),"",AK18-AI18)</x:f>
       </x:c>
-      <x:c r="AM18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AN18" s="46" t="str">
+      <x:c r="AM18" s="48" t="str">
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AN18" s="48" t="str">
         <x:f>IF(OR(AM18="",AK18=""),"",AM18-AK18)</x:f>
       </x:c>
-      <x:c r="AO18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AP18" s="46" t="str">
+      <x:c r="AO18" s="48" t="str">
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AP18" s="48" t="str">
         <x:f>IF(OR(AO18="",AM18=""),"",AO18-AM18)</x:f>
       </x:c>
-      <x:c r="AQ18" s="46" t="str">
-        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AR18" s="46" t="str">
+      <x:c r="AQ18" s="48" t="str">
+        <x:f>IF('Model'!$D18=0,"",1-POWER(2,-('Model'!$M18+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AR18" s="48" t="str">
         <x:f>IF(OR(AQ18="",AO18=""),"",AQ18-AO18)</x:f>
       </x:c>
       <x:c r="AS18" s="24" t="str">
@@ -5404,18 +5441,18 @@
         <x:f>'Model'!S18</x:f>
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="AU18" s="26" t="str">
+      <x:c r="AU18" s="25" t="str">
         <x:f>IF('Model'!$D18=0,"",'Model'!T18)</x:f>
       </x:c>
-      <x:c r="AV18" s="26" t="n">
+      <x:c r="AV18" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW18" s="25" t="n">
+      <x:c r="AW18" s="26" t="n">
         <x:f>'Model'!N18</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX18" s="25" t="n">
+      <x:c r="AX18" s="26" t="n">
         <x:f>'Model'!P18</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5437,150 +5474,150 @@
       <x:c r="D19" s="17" t="str">
         <x:v>Strict finance-work task pass rate</x:v>
       </x:c>
-      <x:c r="E19" s="44" t="str">
+      <x:c r="E19" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F19" s="44" t="str">
+      <x:c r="F19" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G19" s="44" t="str">
+      <x:c r="G19" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H19" s="44" t="str">
+      <x:c r="H19" s="46" t="str">
         <x:f>IF(OR(G19="",E19=""),"",G19-E19)</x:f>
       </x:c>
-      <x:c r="I19" s="44" t="str">
+      <x:c r="I19" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J19" s="44" t="str">
+      <x:c r="J19" s="46" t="str">
         <x:f>IF(OR(I19="",G19=""),"",I19-G19)</x:f>
       </x:c>
-      <x:c r="K19" s="44" t="str">
+      <x:c r="K19" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L19" s="44" t="str">
+      <x:c r="L19" s="46" t="str">
         <x:f>IF(OR(K19="",I19=""),"",K19-I19)</x:f>
       </x:c>
-      <x:c r="M19" s="44" t="str">
+      <x:c r="M19" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N19" s="44" t="str">
+      <x:c r="N19" s="46" t="str">
         <x:f>IF(OR(M19="",K19=""),"",M19-K19)</x:f>
       </x:c>
-      <x:c r="O19" s="44" t="str">
+      <x:c r="O19" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P19" s="44" t="str">
+      <x:c r="P19" s="46" t="str">
         <x:f>IF(OR(O19="",M19=""),"",O19-M19)</x:f>
       </x:c>
-      <x:c r="Q19" s="44" t="str">
+      <x:c r="Q19" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R19" s="44" t="str">
+      <x:c r="R19" s="46" t="str">
         <x:f>IF(OR(Q19="",O19=""),"",Q19-O19)</x:f>
       </x:c>
-      <x:c r="S19" s="45" t="n">
+      <x:c r="S19" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
         <x:v>0.384</x:v>
       </x:c>
-      <x:c r="T19" s="45" t="str">
+      <x:c r="T19" s="47" t="str">
         <x:f>IF(OR(S19="",Q19=""),"",S19-Q19)</x:f>
       </x:c>
-      <x:c r="U19" s="44" t="n">
+      <x:c r="U19" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
         <x:v>0.384</x:v>
       </x:c>
-      <x:c r="V19" s="44" t="n">
+      <x:c r="V19" s="46" t="n">
         <x:f>IF(OR(U19="",S19=""),"",U19-S19)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="W19" s="44" t="n">
+      <x:c r="W19" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.384</x:v>
       </x:c>
-      <x:c r="X19" s="44" t="n">
+      <x:c r="X19" s="46" t="n">
         <x:f>IF(OR(W19="",U19=""),"",W19-U19)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y19" s="44" t="n">
+      <x:c r="Y19" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B19,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.384</x:v>
       </x:c>
-      <x:c r="Z19" s="44" t="n">
+      <x:c r="Z19" s="46" t="n">
         <x:f>IF(OR(Y19="",W19=""),"",Y19-W19)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.44374345220826106</x:v>
-      </x:c>
-      <x:c r="AB19" s="46" t="n">
+      <x:c r="AA19" s="48" t="n">
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.44107328113574673</x:v>
+      </x:c>
+      <x:c r="AB19" s="48" t="n">
         <x:f>IF(OR(AA19="",Y19=""),"",AA19-Y19)</x:f>
-        <x:v>0.05974345220826105</x:v>
-      </x:c>
-      <x:c r="AC19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.5212516119510351</x:v>
-      </x:c>
-      <x:c r="AD19" s="46" t="n">
+        <x:v>0.05707328113574672</x:v>
+      </x:c>
+      <x:c r="AC19" s="48" t="n">
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.5094890762754443</x:v>
+      </x:c>
+      <x:c r="AD19" s="48" t="n">
         <x:f>IF(OR(AC19="",AA19=""),"",AC19-AA19)</x:f>
-        <x:v>0.07750815974277403</x:v>
-      </x:c>
-      <x:c r="AE19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.61606841262881</x:v>
-      </x:c>
-      <x:c r="AF19" s="46" t="n">
+        <x:v>0.06841579513969753</x:v>
+      </x:c>
+      <x:c r="AE19" s="48" t="n">
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.5883800079922828</x:v>
+      </x:c>
+      <x:c r="AF19" s="48" t="n">
         <x:f>IF(OR(AE19="",AC19=""),"",AE19-AC19)</x:f>
-        <x:v>0.09481680067777487</x:v>
-      </x:c>
-      <x:c r="AG19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7224982751088136</x:v>
-      </x:c>
-      <x:c r="AH19" s="46" t="n">
+        <x:v>0.07889093171683859</x:v>
+      </x:c>
+      <x:c r="AG19" s="48" t="n">
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6747407584148459</x:v>
+      </x:c>
+      <x:c r="AH19" s="48" t="n">
         <x:f>IF(OR(AG19="",AE19=""),"",AG19-AE19)</x:f>
-        <x:v>0.10642986248000363</x:v>
-      </x:c>
-      <x:c r="AI19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8278566634504484</x:v>
-      </x:c>
-      <x:c r="AJ19" s="46" t="n">
+        <x:v>0.08636075042256308</x:v>
+      </x:c>
+      <x:c r="AI19" s="48" t="n">
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7629211226829393</x:v>
+      </x:c>
+      <x:c r="AJ19" s="48" t="n">
         <x:f>IF(OR(AI19="",AG19=""),"",AI19-AG19)</x:f>
-        <x:v>0.1053583883416348</x:v>
-      </x:c>
-      <x:c r="AK19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9147160051183125</x:v>
-      </x:c>
-      <x:c r="AL19" s="46" t="n">
+        <x:v>0.08818036426809339</x:v>
+      </x:c>
+      <x:c r="AK19" s="48" t="n">
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8449543091169315</x:v>
+      </x:c>
+      <x:c r="AL19" s="48" t="n">
         <x:f>IF(OR(AK19="",AI19=""),"",AK19-AI19)</x:f>
-        <x:v>0.08685934166786413</x:v>
-      </x:c>
-      <x:c r="AM19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9696458308263236</x:v>
-      </x:c>
-      <x:c r="AN19" s="46" t="n">
+        <x:v>0.08203318643399216</x:v>
+      </x:c>
+      <x:c r="AM19" s="48" t="n">
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.912344417581477</x:v>
+      </x:c>
+      <x:c r="AN19" s="48" t="n">
         <x:f>IF(OR(AM19="",AK19=""),"",AM19-AK19)</x:f>
-        <x:v>0.05492982570801108</x:v>
-      </x:c>
-      <x:c r="AO19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9933577835254929</x:v>
-      </x:c>
-      <x:c r="AP19" s="46" t="n">
+        <x:v>0.06739010846454552</x:v>
+      </x:c>
+      <x:c r="AO19" s="48" t="n">
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9592466362225037</x:v>
+      </x:c>
+      <x:c r="AP19" s="48" t="n">
         <x:f>IF(OR(AO19="",AM19=""),"",AO19-AM19)</x:f>
-        <x:v>0.02371195269916926</x:v>
-      </x:c>
-      <x:c r="AQ19" s="46" t="n">
-        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9992893151557991</x:v>
-      </x:c>
-      <x:c r="AR19" s="46" t="n">
+        <x:v>0.04690221864102673</x:v>
+      </x:c>
+      <x:c r="AQ19" s="48" t="n">
+        <x:f>IF('Model'!$D19=0,"",1-POWER(2,-('Model'!$M19+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9854291607239708</x:v>
+      </x:c>
+      <x:c r="AR19" s="48" t="n">
         <x:f>IF(OR(AQ19="",AO19=""),"",AQ19-AO19)</x:f>
-        <x:v>0.0059315316303062415</x:v>
+        <x:v>0.026182524501467075</x:v>
       </x:c>
       <x:c r="AS19" s="24" t="n">
         <x:f>IF('Model'!$D19=0,"",Y19)</x:f>
@@ -5590,25 +5627,25 @@
         <x:f>'Model'!S19</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU19" s="26" t="n">
+      <x:c r="AU19" s="25" t="n">
         <x:f>IF('Model'!$D19=0,"",'Model'!T19)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV19" s="26" t="n">
+      <x:c r="AV19" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW19" s="25" t="n">
+      <x:c r="AW19" s="26" t="n">
         <x:f>'Model'!N19</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX19" s="25" t="n">
+      <x:c r="AX19" s="26" t="n">
         <x:f>'Model'!P19</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY19" s="17" t="str">
         <x:f>'Model'!Q19</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="46" hidden="0" customHeight="1">
@@ -5624,152 +5661,152 @@
       <x:c r="D20" s="17" t="str">
         <x:v>Pass^k / strict banking-agent success</x:v>
       </x:c>
-      <x:c r="E20" s="44" t="str">
+      <x:c r="E20" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F20" s="44" t="str">
+      <x:c r="F20" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G20" s="44" t="str">
+      <x:c r="G20" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H20" s="44" t="str">
+      <x:c r="H20" s="46" t="str">
         <x:f>IF(OR(G20="",E20=""),"",G20-E20)</x:f>
       </x:c>
-      <x:c r="I20" s="44" t="str">
+      <x:c r="I20" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J20" s="44" t="str">
+      <x:c r="J20" s="46" t="str">
         <x:f>IF(OR(I20="",G20=""),"",I20-G20)</x:f>
       </x:c>
-      <x:c r="K20" s="44" t="str">
+      <x:c r="K20" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L20" s="44" t="str">
+      <x:c r="L20" s="46" t="str">
         <x:f>IF(OR(K20="",I20=""),"",K20-I20)</x:f>
       </x:c>
-      <x:c r="M20" s="44" t="str">
+      <x:c r="M20" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N20" s="44" t="str">
+      <x:c r="N20" s="46" t="str">
         <x:f>IF(OR(M20="",K20=""),"",M20-K20)</x:f>
       </x:c>
-      <x:c r="O20" s="44" t="str">
+      <x:c r="O20" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P20" s="44" t="str">
+      <x:c r="P20" s="46" t="str">
         <x:f>IF(OR(O20="",M20=""),"",O20-M20)</x:f>
       </x:c>
-      <x:c r="Q20" s="45" t="n">
+      <x:c r="Q20" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
         <x:v>0.253</x:v>
       </x:c>
-      <x:c r="R20" s="45" t="str">
+      <x:c r="R20" s="47" t="str">
         <x:f>IF(OR(Q20="",O20=""),"",Q20-O20)</x:f>
       </x:c>
-      <x:c r="S20" s="45" t="n">
+      <x:c r="S20" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
         <x:v>0.322</x:v>
       </x:c>
-      <x:c r="T20" s="45" t="n">
+      <x:c r="T20" s="47" t="n">
         <x:f>IF(OR(S20="",Q20=""),"",S20-Q20)</x:f>
         <x:v>0.069</x:v>
       </x:c>
-      <x:c r="U20" s="45" t="n">
+      <x:c r="U20" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
         <x:v>0.394</x:v>
       </x:c>
-      <x:c r="V20" s="45" t="n">
+      <x:c r="V20" s="47" t="n">
         <x:f>IF(OR(U20="",S20=""),"",U20-S20)</x:f>
         <x:v>0.07200000000000001</x:v>
       </x:c>
-      <x:c r="W20" s="45" t="n">
+      <x:c r="W20" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.446</x:v>
       </x:c>
-      <x:c r="X20" s="45" t="n">
+      <x:c r="X20" s="47" t="n">
         <x:f>IF(OR(W20="",U20=""),"",W20-U20)</x:f>
         <x:v>0.05199999999999999</x:v>
       </x:c>
-      <x:c r="Y20" s="45" t="n">
+      <x:c r="Y20" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B20,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.552</x:v>
       </x:c>
-      <x:c r="Z20" s="45" t="n">
+      <x:c r="Z20" s="47" t="n">
         <x:f>IF(OR(Y20="",W20=""),"",Y20-W20)</x:f>
         <x:v>0.10600000000000004</x:v>
       </x:c>
-      <x:c r="AA20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.5954497834241899</x:v>
-      </x:c>
-      <x:c r="AB20" s="46" t="n">
+      <x:c r="AA20" s="48" t="n">
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.5935078408259976</x:v>
+      </x:c>
+      <x:c r="AB20" s="48" t="n">
         <x:f>IF(OR(AA20="",Y20=""),"",AA20-Y20)</x:f>
-        <x:v>0.043449783424189814</x:v>
-      </x:c>
-      <x:c r="AC20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6518193541462074</x:v>
-      </x:c>
-      <x:c r="AD20" s="46" t="n">
+        <x:v>0.041507840825997566</x:v>
+      </x:c>
+      <x:c r="AC20" s="48" t="n">
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6432647827457776</x:v>
+      </x:c>
+      <x:c r="AD20" s="48" t="n">
         <x:f>IF(OR(AC20="",AA20=""),"",AC20-AA20)</x:f>
-        <x:v>0.05636957072201754</x:v>
-      </x:c>
-      <x:c r="AE20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7207770273664073</x:v>
-      </x:c>
-      <x:c r="AF20" s="46" t="n">
+        <x:v>0.04975694191977997</x:v>
+      </x:c>
+      <x:c r="AE20" s="48" t="n">
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7006400058125694</x:v>
+      </x:c>
+      <x:c r="AF20" s="48" t="n">
         <x:f>IF(OR(AE20="",AC20=""),"",AE20-AC20)</x:f>
-        <x:v>0.06895767322019986</x:v>
-      </x:c>
-      <x:c r="AG20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7981805637155007</x:v>
-      </x:c>
-      <x:c r="AH20" s="46" t="n">
+        <x:v>0.05737522306679177</x:v>
+      </x:c>
+      <x:c r="AG20" s="48" t="n">
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7634478243017062</x:v>
+      </x:c>
+      <x:c r="AH20" s="48" t="n">
         <x:f>IF(OR(AG20="",AE20=""),"",AG20-AE20)</x:f>
-        <x:v>0.07740353634909347</x:v>
-      </x:c>
-      <x:c r="AI20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8748048461457807</x:v>
-      </x:c>
-      <x:c r="AJ20" s="46" t="n">
+        <x:v>0.06280781848913686</x:v>
+      </x:c>
+      <x:c r="AI20" s="48" t="n">
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8275789983148649</x:v>
+      </x:c>
+      <x:c r="AJ20" s="48" t="n">
         <x:f>IF(OR(AI20="",AG20=""),"",AI20-AG20)</x:f>
-        <x:v>0.07662428243027997</x:v>
-      </x:c>
-      <x:c r="AK20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9379752764496818</x:v>
-      </x:c>
-      <x:c r="AL20" s="46" t="n">
+        <x:v>0.06413117401315871</x:v>
+      </x:c>
+      <x:c r="AK20" s="48" t="n">
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8872394975395865</x:v>
+      </x:c>
+      <x:c r="AL20" s="48" t="n">
         <x:f>IF(OR(AK20="",AI20=""),"",AK20-AI20)</x:f>
-        <x:v>0.06317043030390113</x:v>
-      </x:c>
-      <x:c r="AM20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9779242406009626</x:v>
-      </x:c>
-      <x:c r="AN20" s="46" t="n">
+        <x:v>0.05966049922472161</x:v>
+      </x:c>
+      <x:c r="AM20" s="48" t="n">
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9362504855138014</x:v>
+      </x:c>
+      <x:c r="AN20" s="48" t="n">
         <x:f>IF(OR(AM20="",AK20=""),"",AM20-AK20)</x:f>
-        <x:v>0.0399489641512808</x:v>
-      </x:c>
-      <x:c r="AO20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9951692971094493</x:v>
-      </x:c>
-      <x:c r="AP20" s="46" t="n">
+        <x:v>0.04901098797421488</x:v>
+      </x:c>
+      <x:c r="AO20" s="48" t="n">
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9703611899800026</x:v>
+      </x:c>
+      <x:c r="AP20" s="48" t="n">
         <x:f>IF(OR(AO20="",AM20=""),"",AO20-AM20)</x:f>
-        <x:v>0.017245056508486734</x:v>
-      </x:c>
-      <x:c r="AQ20" s="46" t="n">
-        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9994831382951266</x:v>
-      </x:c>
-      <x:c r="AR20" s="46" t="n">
+        <x:v>0.034110704466201236</x:v>
+      </x:c>
+      <x:c r="AQ20" s="48" t="n">
+        <x:f>IF('Model'!$D20=0,"",1-POWER(2,-('Model'!$M20+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9894030259810697</x:v>
+      </x:c>
+      <x:c r="AR20" s="48" t="n">
         <x:f>IF(OR(AQ20="",AO20=""),"",AQ20-AO20)</x:f>
-        <x:v>0.004313841185677236</x:v>
+        <x:v>0.019041836001067014</x:v>
       </x:c>
       <x:c r="AS20" s="24" t="n">
         <x:f>IF('Model'!$D20=0,"",Y20)</x:f>
@@ -5779,25 +5816,25 @@
         <x:f>'Model'!S20</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU20" s="26" t="n">
+      <x:c r="AU20" s="25" t="n">
         <x:f>IF('Model'!$D20=0,"",'Model'!T20)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV20" s="26" t="n">
+      <x:c r="AV20" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW20" s="25" t="n">
+      <x:c r="AW20" s="26" t="n">
         <x:f>'Model'!N20</x:f>
         <x:v>0.30638724399158446</x:v>
       </x:c>
-      <x:c r="AX20" s="25" t="n">
+      <x:c r="AX20" s="26" t="n">
         <x:f>'Model'!P20</x:f>
         <x:v>0.17695542656782204</x:v>
       </x:c>
       <x:c r="AY20" s="17" t="str">
         <x:f>'Model'!Q20</x:f>
-        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
+        <x:v>METR feedback transfer — local acceleration retained as diagnostic</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="46" hidden="0" customHeight="1">
@@ -5813,148 +5850,148 @@
       <x:c r="D21" s="17" t="str">
         <x:v>Perfect task success rate</x:v>
       </x:c>
-      <x:c r="E21" s="44" t="str">
+      <x:c r="E21" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F21" s="44" t="str">
+      <x:c r="F21" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G21" s="44" t="str">
+      <x:c r="G21" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H21" s="44" t="str">
+      <x:c r="H21" s="46" t="str">
         <x:f>IF(OR(G21="",E21=""),"",G21-E21)</x:f>
       </x:c>
-      <x:c r="I21" s="44" t="str">
+      <x:c r="I21" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J21" s="44" t="str">
+      <x:c r="J21" s="46" t="str">
         <x:f>IF(OR(I21="",G21=""),"",I21-G21)</x:f>
       </x:c>
-      <x:c r="K21" s="44" t="str">
+      <x:c r="K21" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L21" s="44" t="str">
+      <x:c r="L21" s="46" t="str">
         <x:f>IF(OR(K21="",I21=""),"",K21-I21)</x:f>
       </x:c>
-      <x:c r="M21" s="44" t="str">
+      <x:c r="M21" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N21" s="44" t="str">
+      <x:c r="N21" s="46" t="str">
         <x:f>IF(OR(M21="",K21=""),"",M21-K21)</x:f>
       </x:c>
-      <x:c r="O21" s="44" t="str">
+      <x:c r="O21" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P21" s="44" t="str">
+      <x:c r="P21" s="46" t="str">
         <x:f>IF(OR(O21="",M21=""),"",O21-M21)</x:f>
       </x:c>
-      <x:c r="Q21" s="44" t="str">
+      <x:c r="Q21" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R21" s="44" t="str">
+      <x:c r="R21" s="46" t="str">
         <x:f>IF(OR(Q21="",O21=""),"",Q21-O21)</x:f>
       </x:c>
-      <x:c r="S21" s="44" t="str">
+      <x:c r="S21" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T21" s="44" t="str">
+      <x:c r="T21" s="46" t="str">
         <x:f>IF(OR(S21="",Q21=""),"",S21-Q21)</x:f>
       </x:c>
-      <x:c r="U21" s="45" t="n">
+      <x:c r="U21" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
         <x:v>0.582</x:v>
       </x:c>
-      <x:c r="V21" s="45" t="str">
+      <x:c r="V21" s="47" t="str">
         <x:f>IF(OR(U21="",S21=""),"",U21-S21)</x:f>
       </x:c>
-      <x:c r="W21" s="44" t="n">
+      <x:c r="W21" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.582</x:v>
       </x:c>
-      <x:c r="X21" s="44" t="n">
+      <x:c r="X21" s="46" t="n">
         <x:f>IF(OR(W21="",U21=""),"",W21-U21)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y21" s="44" t="n">
+      <x:c r="Y21" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B21,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.582</x:v>
       </x:c>
-      <x:c r="Z21" s="44" t="n">
+      <x:c r="Z21" s="46" t="n">
         <x:f>IF(OR(Y21="",W21=""),"",Y21-W21)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6225401997127485</x:v>
-      </x:c>
-      <x:c r="AB21" s="46" t="n">
+      <x:c r="AA21" s="48" t="n">
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6207282979135424</x:v>
+      </x:c>
+      <x:c r="AB21" s="48" t="n">
         <x:f>IF(OR(AA21="",Y21=""),"",AA21-Y21)</x:f>
-        <x:v>0.04054019971274858</x:v>
-      </x:c>
-      <x:c r="AC21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6751350223953452</x:v>
-      </x:c>
-      <x:c r="AD21" s="46" t="n">
+        <x:v>0.038728297913542487</x:v>
+      </x:c>
+      <x:c r="AC21" s="48" t="n">
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6671533017583371</x:v>
+      </x:c>
+      <x:c r="AD21" s="48" t="n">
         <x:f>IF(OR(AC21="",AA21=""),"",AC21-AA21)</x:f>
-        <x:v>0.05259482268259663</x:v>
-      </x:c>
-      <x:c r="AE21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7394749942838353</x:v>
-      </x:c>
-      <x:c r="AF21" s="46" t="n">
+        <x:v>0.04642500384479464</x:v>
+      </x:c>
+      <x:c r="AE21" s="48" t="n">
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7206864339947634</x:v>
+      </x:c>
+      <x:c r="AF21" s="48" t="n">
         <x:f>IF(OR(AE21="",AC21=""),"",AE21-AC21)</x:f>
-        <x:v>0.06433997188849017</x:v>
-      </x:c>
-      <x:c r="AG21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.811695258109552</x:v>
-      </x:c>
-      <x:c r="AH21" s="46" t="n">
+        <x:v>0.053533132236426306</x:v>
+      </x:c>
+      <x:c r="AG21" s="48" t="n">
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7792883717815026</x:v>
+      </x:c>
+      <x:c r="AH21" s="48" t="n">
         <x:f>IF(OR(AG21="",AE21=""),"",AG21-AE21)</x:f>
-        <x:v>0.07222026382571667</x:v>
-      </x:c>
-      <x:c r="AI21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8831884501985185</x:v>
-      </x:c>
-      <x:c r="AJ21" s="46" t="n">
+        <x:v>0.05860193778673917</x:v>
+      </x:c>
+      <x:c r="AI21" s="48" t="n">
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8391250475348516</x:v>
+      </x:c>
+      <x:c r="AJ21" s="48" t="n">
         <x:f>IF(OR(AI21="",AG21=""),"",AI21-AG21)</x:f>
-        <x:v>0.07149319208896654</x:v>
-      </x:c>
-      <x:c r="AK21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.942128717758855</x:v>
-      </x:c>
-      <x:c r="AL21" s="46" t="n">
+        <x:v>0.059836675753349056</x:v>
+      </x:c>
+      <x:c r="AK21" s="48" t="n">
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8947904240436321</x:v>
+      </x:c>
+      <x:c r="AL21" s="48" t="n">
         <x:f>IF(OR(AK21="",AI21=""),"",AK21-AI21)</x:f>
-        <x:v>0.058940267560336435</x:v>
-      </x:c>
-      <x:c r="AM21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9794025280607196</x:v>
-      </x:c>
-      <x:c r="AN21" s="46" t="n">
+        <x:v>0.05566537650878045</x:v>
+      </x:c>
+      <x:c r="AM21" s="48" t="n">
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9405194262160023</x:v>
+      </x:c>
+      <x:c r="AN21" s="48" t="n">
         <x:f>IF(OR(AM21="",AK21=""),"",AM21-AK21)</x:f>
-        <x:v>0.03727381030186461</x:v>
-      </x:c>
-      <x:c r="AO21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.995492781678013</x:v>
-      </x:c>
-      <x:c r="AP21" s="46" t="n">
+        <x:v>0.04572900217237019</x:v>
+      </x:c>
+      <x:c r="AO21" s="48" t="n">
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9723459317224132</x:v>
+      </x:c>
+      <x:c r="AP21" s="48" t="n">
         <x:f>IF(OR(AO21="",AM21=""),"",AO21-AM21)</x:f>
-        <x:v>0.016090253617293437</x:v>
-      </x:c>
-      <x:c r="AQ21" s="46" t="n">
-        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9995177495700065</x:v>
-      </x:c>
-      <x:c r="AR21" s="46" t="n">
+        <x:v>0.031826505506410974</x:v>
+      </x:c>
+      <x:c r="AQ21" s="48" t="n">
+        <x:f>IF('Model'!$D21=0,"",1-POWER(2,-('Model'!$M21+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9901126447769802</x:v>
+      </x:c>
+      <x:c r="AR21" s="48" t="n">
         <x:f>IF(OR(AQ21="",AO21=""),"",AQ21-AO21)</x:f>
-        <x:v>0.0040249678919934695</x:v>
+        <x:v>0.017766713054567007</x:v>
       </x:c>
       <x:c r="AS21" s="24" t="n">
         <x:f>IF('Model'!$D21=0,"",Y21)</x:f>
@@ -5964,25 +6001,25 @@
         <x:f>'Model'!S21</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU21" s="26" t="n">
+      <x:c r="AU21" s="25" t="n">
         <x:f>IF('Model'!$D21=0,"",'Model'!T21)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV21" s="26" t="n">
+      <x:c r="AV21" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW21" s="25" t="n">
+      <x:c r="AW21" s="26" t="n">
         <x:f>'Model'!N21</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX21" s="25" t="n">
+      <x:c r="AX21" s="26" t="n">
         <x:f>'Model'!P21</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY21" s="17" t="str">
         <x:f>'Model'!Q21</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="46" hidden="0" customHeight="1">
@@ -5998,148 +6035,148 @@
       <x:c r="D22" s="17" t="str">
         <x:v>Completeness checklist score</x:v>
       </x:c>
-      <x:c r="E22" s="44" t="str">
+      <x:c r="E22" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F22" s="44" t="str">
+      <x:c r="F22" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G22" s="44" t="str">
+      <x:c r="G22" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H22" s="44" t="str">
+      <x:c r="H22" s="46" t="str">
         <x:f>IF(OR(G22="",E22=""),"",G22-E22)</x:f>
       </x:c>
-      <x:c r="I22" s="44" t="str">
+      <x:c r="I22" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J22" s="44" t="str">
+      <x:c r="J22" s="46" t="str">
         <x:f>IF(OR(I22="",G22=""),"",I22-G22)</x:f>
       </x:c>
-      <x:c r="K22" s="44" t="str">
+      <x:c r="K22" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L22" s="44" t="str">
+      <x:c r="L22" s="46" t="str">
         <x:f>IF(OR(K22="",I22=""),"",K22-I22)</x:f>
       </x:c>
-      <x:c r="M22" s="44" t="str">
+      <x:c r="M22" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N22" s="44" t="str">
+      <x:c r="N22" s="46" t="str">
         <x:f>IF(OR(M22="",K22=""),"",M22-K22)</x:f>
       </x:c>
-      <x:c r="O22" s="44" t="str">
+      <x:c r="O22" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P22" s="44" t="str">
+      <x:c r="P22" s="46" t="str">
         <x:f>IF(OR(O22="",M22=""),"",O22-M22)</x:f>
       </x:c>
-      <x:c r="Q22" s="44" t="str">
+      <x:c r="Q22" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R22" s="44" t="str">
+      <x:c r="R22" s="46" t="str">
         <x:f>IF(OR(Q22="",O22=""),"",Q22-O22)</x:f>
       </x:c>
-      <x:c r="S22" s="44" t="str">
+      <x:c r="S22" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T22" s="44" t="str">
+      <x:c r="T22" s="46" t="str">
         <x:f>IF(OR(S22="",Q22=""),"",S22-Q22)</x:f>
       </x:c>
-      <x:c r="U22" s="45" t="n">
+      <x:c r="U22" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
         <x:v>0.676</x:v>
       </x:c>
-      <x:c r="V22" s="45" t="str">
+      <x:c r="V22" s="47" t="str">
         <x:f>IF(OR(U22="",S22=""),"",U22-S22)</x:f>
       </x:c>
-      <x:c r="W22" s="44" t="n">
+      <x:c r="W22" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.676</x:v>
       </x:c>
-      <x:c r="X22" s="44" t="n">
+      <x:c r="X22" s="46" t="n">
         <x:f>IF(OR(W22="",U22=""),"",W22-U22)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y22" s="44" t="n">
+      <x:c r="Y22" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B22,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.676</x:v>
       </x:c>
-      <x:c r="Z22" s="44" t="n">
+      <x:c r="Z22" s="46" t="n">
         <x:f>IF(OR(Y22="",W22=""),"",Y22-W22)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7074235040835659</x:v>
-      </x:c>
-      <x:c r="AB22" s="46" t="n">
+      <x:c r="AA22" s="48" t="n">
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7060190634545161</x:v>
+      </x:c>
+      <x:c r="AB22" s="48" t="n">
         <x:f>IF(OR(AA22="",Y22=""),"",AA22-Y22)</x:f>
-        <x:v>0.03142350408356587</x:v>
-      </x:c>
-      <x:c r="AC22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7481907829093106</x:v>
-      </x:c>
-      <x:c r="AD22" s="46" t="n">
+        <x:v>0.030019063454516104</x:v>
+      </x:c>
+      <x:c r="AC22" s="48" t="n">
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7420039946643571</x:v>
+      </x:c>
+      <x:c r="AD22" s="48" t="n">
         <x:f>IF(OR(AC22="",AA22=""),"",AC22-AA22)</x:f>
-        <x:v>0.04076727882574471</x:v>
-      </x:c>
-      <x:c r="AE22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7980619572917766</x:v>
-      </x:c>
-      <x:c r="AF22" s="46" t="n">
+        <x:v>0.03598493120984092</x:v>
+      </x:c>
+      <x:c r="AE22" s="48" t="n">
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7834985756323046</x:v>
+      </x:c>
+      <x:c r="AF22" s="48" t="n">
         <x:f>IF(OR(AE22="",AC22=""),"",AE22-AC22)</x:f>
-        <x:v>0.04987117438246602</x:v>
-      </x:c>
-      <x:c r="AG22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8540413005442461</x:v>
-      </x:c>
-      <x:c r="AH22" s="46" t="n">
+        <x:v>0.04149458096794756</x:v>
+      </x:c>
+      <x:c r="AG22" s="48" t="n">
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8289220872181982</x:v>
+      </x:c>
+      <x:c r="AH22" s="48" t="n">
         <x:f>IF(OR(AG22="",AE22=""),"",AG22-AE22)</x:f>
-        <x:v>0.05597934325246945</x:v>
-      </x:c>
-      <x:c r="AI22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9094570762304307</x:v>
-      </x:c>
-      <x:c r="AJ22" s="46" t="n">
+        <x:v>0.04542351158589353</x:v>
+      </x:c>
+      <x:c r="AI22" s="48" t="n">
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8753026684241434</x:v>
+      </x:c>
+      <x:c r="AJ22" s="48" t="n">
         <x:f>IF(OR(AI22="",AG22=""),"",AI22-AG22)</x:f>
-        <x:v>0.05541577568618461</x:v>
-      </x:c>
-      <x:c r="AK22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9551428338609307</x:v>
-      </x:c>
-      <x:c r="AL22" s="46" t="n">
+        <x:v>0.04638058120594524</x:v>
+      </x:c>
+      <x:c r="AK22" s="48" t="n">
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9184499937563081</x:v>
+      </x:c>
+      <x:c r="AL22" s="48" t="n">
         <x:f>IF(OR(AK22="",AI22=""),"",AK22-AI22)</x:f>
-        <x:v>0.04568575763049998</x:v>
-      </x:c>
-      <x:c r="AM22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9840344954346247</x:v>
-      </x:c>
-      <x:c r="AN22" s="46" t="n">
+        <x:v>0.0431473253321647</x:v>
+      </x:c>
+      <x:c r="AM22" s="48" t="n">
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9538954404162314</x:v>
+      </x:c>
+      <x:c r="AN22" s="48" t="n">
         <x:f>IF(OR(AM22="",AK22=""),"",AM22-AK22)</x:f>
-        <x:v>0.02889166157369405</x:v>
-      </x:c>
-      <x:c r="AO22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9965063666595124</x:v>
-      </x:c>
-      <x:c r="AP22" s="46" t="n">
+        <x:v>0.03544544665992333</x:v>
+      </x:c>
+      <x:c r="AO22" s="48" t="n">
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9785647891819662</x:v>
+      </x:c>
+      <x:c r="AP22" s="48" t="n">
         <x:f>IF(OR(AO22="",AM22=""),"",AO22-AM22)</x:f>
-        <x:v>0.012471871224887687</x:v>
-      </x:c>
-      <x:c r="AQ22" s="46" t="n">
-        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.999626198231297</x:v>
-      </x:c>
-      <x:c r="AR22" s="46" t="n">
+        <x:v>0.02466934876573479</x:v>
+      </x:c>
+      <x:c r="AQ22" s="48" t="n">
+        <x:f>IF('Model'!$D22=0,"",1-POWER(2,-('Model'!$M22+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9923361170041665</x:v>
+      </x:c>
+      <x:c r="AR22" s="48" t="n">
         <x:f>IF(OR(AQ22="",AO22=""),"",AQ22-AO22)</x:f>
-        <x:v>0.003119831571784526</x:v>
+        <x:v>0.013771327822200252</x:v>
       </x:c>
       <x:c r="AS22" s="24" t="n">
         <x:f>IF('Model'!$D22=0,"",Y22)</x:f>
@@ -6149,25 +6186,25 @@
         <x:f>'Model'!S22</x:f>
         <x:v>D</x:v>
       </x:c>
-      <x:c r="AU22" s="26" t="n">
+      <x:c r="AU22" s="25" t="n">
         <x:f>IF('Model'!$D22=0,"",'Model'!T22)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AV22" s="26" t="n">
+      <x:c r="AV22" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW22" s="25" t="n">
+      <x:c r="AW22" s="26" t="n">
         <x:f>'Model'!N22</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX22" s="25" t="n">
+      <x:c r="AX22" s="26" t="n">
         <x:f>'Model'!P22</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY22" s="17" t="str">
         <x:f>'Model'!Q22</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="46" hidden="0" customHeight="1">
@@ -6183,146 +6220,146 @@
       <x:c r="D23" s="17" t="str">
         <x:v>V1 six-model comparison score</x:v>
       </x:c>
-      <x:c r="E23" s="44" t="str">
+      <x:c r="E23" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F23" s="44" t="str">
+      <x:c r="F23" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G23" s="44" t="str">
+      <x:c r="G23" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H23" s="44" t="str">
+      <x:c r="H23" s="46" t="str">
         <x:f>IF(OR(G23="",E23=""),"",G23-E23)</x:f>
       </x:c>
-      <x:c r="I23" s="44" t="str">
+      <x:c r="I23" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J23" s="44" t="str">
+      <x:c r="J23" s="46" t="str">
         <x:f>IF(OR(I23="",G23=""),"",I23-G23)</x:f>
       </x:c>
-      <x:c r="K23" s="44" t="str">
+      <x:c r="K23" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L23" s="44" t="str">
+      <x:c r="L23" s="46" t="str">
         <x:f>IF(OR(K23="",I23=""),"",K23-I23)</x:f>
       </x:c>
-      <x:c r="M23" s="44" t="str">
+      <x:c r="M23" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N23" s="44" t="str">
+      <x:c r="N23" s="46" t="str">
         <x:f>IF(OR(M23="",K23=""),"",M23-K23)</x:f>
       </x:c>
-      <x:c r="O23" s="44" t="str">
+      <x:c r="O23" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P23" s="44" t="str">
+      <x:c r="P23" s="46" t="str">
         <x:f>IF(OR(O23="",M23=""),"",O23-M23)</x:f>
       </x:c>
-      <x:c r="Q23" s="44" t="str">
+      <x:c r="Q23" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R23" s="44" t="str">
+      <x:c r="R23" s="46" t="str">
         <x:f>IF(OR(Q23="",O23=""),"",Q23-O23)</x:f>
       </x:c>
-      <x:c r="S23" s="44" t="str">
+      <x:c r="S23" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T23" s="44" t="str">
+      <x:c r="T23" s="46" t="str">
         <x:f>IF(OR(S23="",Q23=""),"",S23-Q23)</x:f>
       </x:c>
-      <x:c r="U23" s="44" t="str">
+      <x:c r="U23" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
       </x:c>
-      <x:c r="V23" s="44" t="str">
+      <x:c r="V23" s="46" t="str">
         <x:f>IF(OR(U23="",S23=""),"",U23-S23)</x:f>
       </x:c>
-      <x:c r="W23" s="45" t="n">
+      <x:c r="W23" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.333</x:v>
       </x:c>
-      <x:c r="X23" s="45" t="str">
+      <x:c r="X23" s="47" t="str">
         <x:f>IF(OR(W23="",U23=""),"",W23-U23)</x:f>
       </x:c>
-      <x:c r="Y23" s="44" t="n">
+      <x:c r="Y23" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B23,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.333</x:v>
       </x:c>
-      <x:c r="Z23" s="44" t="n">
+      <x:c r="Z23" s="46" t="n">
         <x:f>IF(OR(Y23="",W23=""),"",Y23-W23)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.3976897445177112</x:v>
-      </x:c>
-      <x:c r="AB23" s="46" t="n">
+      <x:c r="AA23" s="48" t="n">
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.3947985040869205</x:v>
+      </x:c>
+      <x:c r="AB23" s="48" t="n">
         <x:f>IF(OR(AA23="",Y23=""),"",AA23-Y23)</x:f>
-        <x:v>0.0646897445177112</x:v>
-      </x:c>
-      <x:c r="AC23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.4816149759275006</x:v>
-      </x:c>
-      <x:c r="AD23" s="46" t="n">
+        <x:v>0.0617985040869205</x:v>
+      </x:c>
+      <x:c r="AC23" s="48" t="n">
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.4688785939540929</x:v>
+      </x:c>
+      <x:c r="AD23" s="48" t="n">
         <x:f>IF(OR(AC23="",AA23=""),"",AC23-AA23)</x:f>
-        <x:v>0.08392523140978936</x:v>
-      </x:c>
-      <x:c r="AE23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.5842818688691822</x:v>
-      </x:c>
-      <x:c r="AF23" s="46" t="n">
+        <x:v>0.0740800898671724</x:v>
+      </x:c>
+      <x:c r="AE23" s="48" t="n">
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.554301080082553</x:v>
+      </x:c>
+      <x:c r="AF23" s="48" t="n">
         <x:f>IF(OR(AE23="",AC23=""),"",AE23-AC23)</x:f>
-        <x:v>0.10266689294168163</x:v>
-      </x:c>
-      <x:c r="AG23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6995232946389263</x:v>
-      </x:c>
-      <x:c r="AH23" s="46" t="n">
+        <x:v>0.08542248612846004</x:v>
+      </x:c>
+      <x:c r="AG23" s="48" t="n">
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.647811827699192</x:v>
+      </x:c>
+      <x:c r="AH23" s="48" t="n">
         <x:f>IF(OR(AG23="",AE23=""),"",AG23-AE23)</x:f>
-        <x:v>0.11524142576974405</x:v>
-      </x:c>
-      <x:c r="AI23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.813604536560794</x:v>
-      </x:c>
-      <x:c r="AJ23" s="46" t="n">
+        <x:v>0.09351074761663902</x:v>
+      </x:c>
+      <x:c r="AI23" s="48" t="n">
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7432928390089618</x:v>
+      </x:c>
+      <x:c r="AJ23" s="48" t="n">
         <x:f>IF(OR(AI23="",AG23=""),"",AI23-AG23)</x:f>
-        <x:v>0.11408124192186775</x:v>
-      </x:c>
-      <x:c r="AK23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9076551548927183</x:v>
-      </x:c>
-      <x:c r="AL23" s="46" t="n">
+        <x:v>0.09548101130976983</x:v>
+      </x:c>
+      <x:c r="AK23" s="48" t="n">
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8321177340600541</x:v>
+      </x:c>
+      <x:c r="AL23" s="48" t="n">
         <x:f>IF(OR(AK23="",AI23=""),"",AK23-AI23)</x:f>
-        <x:v>0.0940506183319243</x:v>
-      </x:c>
-      <x:c r="AM23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9671327421447368</x:v>
-      </x:c>
-      <x:c r="AN23" s="46" t="n">
+        <x:v>0.08882489505109226</x:v>
+      </x:c>
+      <x:c r="AM23" s="48" t="n">
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9050872183877356</x:v>
+      </x:c>
+      <x:c r="AN23" s="48" t="n">
         <x:f>IF(OR(AM23="",AK23=""),"",AM23-AK23)</x:f>
-        <x:v>0.05947758725201846</x:v>
-      </x:c>
-      <x:c r="AO23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9928078597589346</x:v>
-      </x:c>
-      <x:c r="AP23" s="46" t="n">
+        <x:v>0.07296948432768158</x:v>
+      </x:c>
+      <x:c r="AO23" s="48" t="n">
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9558725752604058</x:v>
+      </x:c>
+      <x:c r="AP23" s="48" t="n">
         <x:f>IF(OR(AO23="",AM23=""),"",AO23-AM23)</x:f>
-        <x:v>0.02567511761419783</x:v>
-      </x:c>
-      <x:c r="AQ23" s="46" t="n">
-        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9992304759885032</x:v>
-      </x:c>
-      <x:c r="AR23" s="46" t="n">
+        <x:v>0.05078535687267016</x:v>
+      </x:c>
+      <x:c r="AQ23" s="48" t="n">
+        <x:f>IF('Model'!$D23=0,"",1-POWER(2,-('Model'!$M23+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9842228087709229</x:v>
+      </x:c>
+      <x:c r="AR23" s="48" t="n">
         <x:f>IF(OR(AQ23="",AO23=""),"",AQ23-AO23)</x:f>
-        <x:v>0.006422616229568634</x:v>
+        <x:v>0.02835023351051713</x:v>
       </x:c>
       <x:c r="AS23" s="24" t="n">
         <x:f>IF('Model'!$D23=0,"",Y23)</x:f>
@@ -6332,25 +6369,25 @@
         <x:f>'Model'!S23</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU23" s="26" t="n">
+      <x:c r="AU23" s="25" t="n">
         <x:f>IF('Model'!$D23=0,"",'Model'!T23)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV23" s="26" t="n">
+      <x:c r="AV23" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW23" s="25" t="n">
+      <x:c r="AW23" s="26" t="n">
         <x:f>'Model'!N23</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX23" s="25" t="n">
+      <x:c r="AX23" s="26" t="n">
         <x:f>'Model'!P23</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY23" s="17" t="str">
         <x:f>'Model'!Q23</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="46" hidden="0" customHeight="1">
@@ -6366,154 +6403,154 @@
       <x:c r="D24" s="17" t="str">
         <x:v>Assistant task accuracy on the current HAL configuration</x:v>
       </x:c>
-      <x:c r="E24" s="44" t="str">
+      <x:c r="E24" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F24" s="44" t="str">
+      <x:c r="F24" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G24" s="44" t="str">
+      <x:c r="G24" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H24" s="44" t="str">
+      <x:c r="H24" s="46" t="str">
         <x:f>IF(OR(G24="",E24=""),"",G24-E24)</x:f>
       </x:c>
-      <x:c r="I24" s="44" t="str">
+      <x:c r="I24" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J24" s="44" t="str">
+      <x:c r="J24" s="46" t="str">
         <x:f>IF(OR(I24="",G24=""),"",I24-G24)</x:f>
       </x:c>
-      <x:c r="K24" s="44" t="str">
+      <x:c r="K24" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L24" s="44" t="str">
+      <x:c r="L24" s="46" t="str">
         <x:f>IF(OR(K24="",I24=""),"",K24-I24)</x:f>
       </x:c>
-      <x:c r="M24" s="44" t="str">
+      <x:c r="M24" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N24" s="44" t="str">
+      <x:c r="N24" s="46" t="str">
         <x:f>IF(OR(M24="",K24=""),"",M24-K24)</x:f>
       </x:c>
-      <x:c r="O24" s="45" t="n">
+      <x:c r="O24" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
         <x:v>0.3881</x:v>
       </x:c>
-      <x:c r="P24" s="45" t="str">
+      <x:c r="P24" s="47" t="str">
         <x:f>IF(OR(O24="",M24=""),"",O24-M24)</x:f>
       </x:c>
-      <x:c r="Q24" s="44" t="n">
+      <x:c r="Q24" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
         <x:v>0.3881</x:v>
       </x:c>
-      <x:c r="R24" s="44" t="n">
+      <x:c r="R24" s="46" t="n">
         <x:f>IF(OR(Q24="",O24=""),"",Q24-O24)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S24" s="44" t="n">
+      <x:c r="S24" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
         <x:v>0.3881</x:v>
       </x:c>
-      <x:c r="T24" s="44" t="n">
+      <x:c r="T24" s="46" t="n">
         <x:f>IF(OR(S24="",Q24=""),"",S24-Q24)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U24" s="44" t="n">
+      <x:c r="U24" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
         <x:v>0.3881</x:v>
       </x:c>
-      <x:c r="V24" s="44" t="n">
+      <x:c r="V24" s="46" t="n">
         <x:f>IF(OR(U24="",S24=""),"",U24-S24)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="W24" s="44" t="n">
+      <x:c r="W24" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.3881</x:v>
       </x:c>
-      <x:c r="X24" s="44" t="n">
+      <x:c r="X24" s="46" t="n">
         <x:f>IF(OR(W24="",U24=""),"",W24-U24)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y24" s="44" t="n">
+      <x:c r="Y24" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B24,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.3881</x:v>
       </x:c>
-      <x:c r="Z24" s="44" t="n">
+      <x:c r="Z24" s="46" t="n">
         <x:f>IF(OR(Y24="",W24=""),"",Y24-W24)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.4474458091010307</x:v>
-      </x:c>
-      <x:c r="AB24" s="46" t="n">
+      <x:c r="AA24" s="48" t="n">
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.44479341027104446</x:v>
+      </x:c>
+      <x:c r="AB24" s="48" t="n">
         <x:f>IF(OR(AA24="",Y24=""),"",AA24-Y24)</x:f>
-        <x:v>0.05934580910103071</x:v>
-      </x:c>
-      <x:c r="AC24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.5244380866117506</x:v>
-      </x:c>
-      <x:c r="AD24" s="46" t="n">
+        <x:v>0.056693410271044464</x:v>
+      </x:c>
+      <x:c r="AC24" s="48" t="n">
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.512753840540494</x:v>
+      </x:c>
+      <x:c r="AD24" s="48" t="n">
         <x:f>IF(OR(AC24="",AA24=""),"",AC24-AA24)</x:f>
-        <x:v>0.07699227751071991</x:v>
-      </x:c>
-      <x:c r="AE24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6186238014408585</x:v>
-      </x:c>
-      <x:c r="AF24" s="46" t="n">
+        <x:v>0.06796043026944953</x:v>
+      </x:c>
+      <x:c r="AE24" s="48" t="n">
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.5911196865105159</x:v>
+      </x:c>
+      <x:c r="AF24" s="48" t="n">
         <x:f>IF(OR(AE24="",AC24=""),"",AE24-AC24)</x:f>
-        <x:v>0.09418571482910787</x:v>
-      </x:c>
-      <x:c r="AG24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7243452833426672</x:v>
-      </x:c>
-      <x:c r="AH24" s="46" t="n">
+        <x:v>0.07836584597002194</x:v>
+      </x:c>
+      <x:c r="AG24" s="48" t="n">
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.6769056332370849</x:v>
+      </x:c>
+      <x:c r="AH24" s="48" t="n">
         <x:f>IF(OR(AG24="",AE24=""),"",AG24-AE24)</x:f>
-        <x:v>0.10572148190180874</x:v>
-      </x:c>
-      <x:c r="AI24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8290024226709892</x:v>
-      </x:c>
-      <x:c r="AJ24" s="46" t="n">
+        <x:v>0.08578594672656892</x:v>
+      </x:c>
+      <x:c r="AI24" s="48" t="n">
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.764499082743004</x:v>
+      </x:c>
+      <x:c r="AJ24" s="48" t="n">
         <x:f>IF(OR(AI24="",AG24=""),"",AI24-AG24)</x:f>
-        <x:v>0.10465713932832199</x:v>
-      </x:c>
-      <x:c r="AK24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9152836420972329</x:v>
-      </x:c>
-      <x:c r="AL24" s="46" t="n">
+        <x:v>0.08759344950591919</x:v>
+      </x:c>
+      <x:c r="AK24" s="48" t="n">
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8459862690724844</x:v>
+      </x:c>
+      <x:c r="AL24" s="48" t="n">
         <x:f>IF(OR(AK24="",AI24=""),"",AK24-AI24)</x:f>
-        <x:v>0.08628121942624367</x:v>
-      </x:c>
-      <x:c r="AM24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9698478634458237</x:v>
-      </x:c>
-      <x:c r="AN24" s="46" t="n">
+        <x:v>0.08148718632948038</x:v>
+      </x:c>
+      <x:c r="AM24" s="48" t="n">
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9129278394774445</x:v>
+      </x:c>
+      <x:c r="AN24" s="48" t="n">
         <x:f>IF(OR(AM24="",AK24=""),"",AM24-AK24)</x:f>
-        <x:v>0.05456422134859085</x:v>
-      </x:c>
-      <x:c r="AO24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9934019930831965</x:v>
-      </x:c>
-      <x:c r="AP24" s="46" t="n">
+        <x:v>0.06694157040496007</x:v>
+      </x:c>
+      <x:c r="AO24" s="48" t="n">
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9595178842606331</x:v>
+      </x:c>
+      <x:c r="AP24" s="48" t="n">
         <x:f>IF(OR(AO24="",AM24=""),"",AO24-AM24)</x:f>
-        <x:v>0.0235541296373728</x:v>
-      </x:c>
-      <x:c r="AQ24" s="46" t="n">
-        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.999294045363366</x:v>
-      </x:c>
-      <x:c r="AR24" s="46" t="n">
+        <x:v>0.04659004478318862</x:v>
+      </x:c>
+      <x:c r="AQ24" s="48" t="n">
+        <x:f>IF('Model'!$D24=0,"",1-POWER(2,-('Model'!$M24+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9855261419594119</x:v>
+      </x:c>
+      <x:c r="AR24" s="48" t="n">
         <x:f>IF(OR(AQ24="",AO24=""),"",AQ24-AO24)</x:f>
-        <x:v>0.005892052280169424</x:v>
+        <x:v>0.02600825769877879</x:v>
       </x:c>
       <x:c r="AS24" s="24" t="n">
         <x:f>IF('Model'!$D24=0,"",Y24)</x:f>
@@ -6523,25 +6560,25 @@
         <x:f>'Model'!S24</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU24" s="26" t="n">
+      <x:c r="AU24" s="25" t="n">
         <x:f>IF('Model'!$D24=0,"",'Model'!T24)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV24" s="26" t="n">
+      <x:c r="AV24" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW24" s="25" t="n">
+      <x:c r="AW24" s="26" t="n">
         <x:f>'Model'!N24</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX24" s="25" t="n">
+      <x:c r="AX24" s="26" t="n">
         <x:f>'Model'!P24</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY24" s="17" t="str">
         <x:f>'Model'!Q24</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="46" hidden="0" customHeight="1">
@@ -6557,124 +6594,124 @@
       <x:c r="D25" s="17" t="str">
         <x:v>Expert preference / economic task quality</x:v>
       </x:c>
-      <x:c r="E25" s="44" t="str">
+      <x:c r="E25" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F25" s="44" t="str">
+      <x:c r="F25" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G25" s="44" t="str">
+      <x:c r="G25" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H25" s="44" t="str">
+      <x:c r="H25" s="46" t="str">
         <x:f>IF(OR(G25="",E25=""),"",G25-E25)</x:f>
       </x:c>
-      <x:c r="I25" s="44" t="str">
+      <x:c r="I25" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J25" s="44" t="str">
+      <x:c r="J25" s="46" t="str">
         <x:f>IF(OR(I25="",G25=""),"",I25-G25)</x:f>
       </x:c>
-      <x:c r="K25" s="44" t="str">
+      <x:c r="K25" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L25" s="44" t="str">
+      <x:c r="L25" s="46" t="str">
         <x:f>IF(OR(K25="",I25=""),"",K25-I25)</x:f>
       </x:c>
-      <x:c r="M25" s="44" t="str">
+      <x:c r="M25" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N25" s="44" t="str">
+      <x:c r="N25" s="46" t="str">
         <x:f>IF(OR(M25="",K25=""),"",M25-K25)</x:f>
       </x:c>
-      <x:c r="O25" s="44" t="str">
+      <x:c r="O25" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P25" s="44" t="str">
+      <x:c r="P25" s="46" t="str">
         <x:f>IF(OR(O25="",M25=""),"",O25-M25)</x:f>
       </x:c>
-      <x:c r="Q25" s="44" t="str">
+      <x:c r="Q25" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R25" s="44" t="str">
+      <x:c r="R25" s="46" t="str">
         <x:f>IF(OR(Q25="",O25=""),"",Q25-O25)</x:f>
       </x:c>
-      <x:c r="S25" s="44" t="str">
+      <x:c r="S25" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T25" s="44" t="str">
+      <x:c r="T25" s="46" t="str">
         <x:f>IF(OR(S25="",Q25=""),"",S25-Q25)</x:f>
       </x:c>
-      <x:c r="U25" s="44" t="str">
+      <x:c r="U25" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
       </x:c>
-      <x:c r="V25" s="44" t="str">
+      <x:c r="V25" s="46" t="str">
         <x:f>IF(OR(U25="",S25=""),"",U25-S25)</x:f>
       </x:c>
-      <x:c r="W25" s="44" t="str">
+      <x:c r="W25" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
       </x:c>
-      <x:c r="X25" s="44" t="str">
+      <x:c r="X25" s="46" t="str">
         <x:f>IF(OR(W25="",U25=""),"",W25-U25)</x:f>
       </x:c>
-      <x:c r="Y25" s="44" t="str">
+      <x:c r="Y25" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B25,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
       </x:c>
-      <x:c r="Z25" s="44" t="str">
+      <x:c r="Z25" s="46" t="str">
         <x:f>IF(OR(Y25="",W25=""),"",Y25-W25)</x:f>
       </x:c>
-      <x:c r="AA25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AB25" s="46" t="str">
+      <x:c r="AA25" s="48" t="str">
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AB25" s="48" t="str">
         <x:f>IF(OR(AA25="",Y25=""),"",AA25-Y25)</x:f>
       </x:c>
-      <x:c r="AC25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AD25" s="46" t="str">
+      <x:c r="AC25" s="48" t="str">
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AD25" s="48" t="str">
         <x:f>IF(OR(AC25="",AA25=""),"",AC25-AA25)</x:f>
       </x:c>
-      <x:c r="AE25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AF25" s="46" t="str">
+      <x:c r="AE25" s="48" t="str">
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AF25" s="48" t="str">
         <x:f>IF(OR(AE25="",AC25=""),"",AE25-AC25)</x:f>
       </x:c>
-      <x:c r="AG25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AH25" s="46" t="str">
+      <x:c r="AG25" s="48" t="str">
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AH25" s="48" t="str">
         <x:f>IF(OR(AG25="",AE25=""),"",AG25-AE25)</x:f>
       </x:c>
-      <x:c r="AI25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AJ25" s="46" t="str">
+      <x:c r="AI25" s="48" t="str">
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AJ25" s="48" t="str">
         <x:f>IF(OR(AI25="",AG25=""),"",AI25-AG25)</x:f>
       </x:c>
-      <x:c r="AK25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AL25" s="46" t="str">
+      <x:c r="AK25" s="48" t="str">
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AL25" s="48" t="str">
         <x:f>IF(OR(AK25="",AI25=""),"",AK25-AI25)</x:f>
       </x:c>
-      <x:c r="AM25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AN25" s="46" t="str">
+      <x:c r="AM25" s="48" t="str">
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AN25" s="48" t="str">
         <x:f>IF(OR(AM25="",AK25=""),"",AM25-AK25)</x:f>
       </x:c>
-      <x:c r="AO25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AP25" s="46" t="str">
+      <x:c r="AO25" s="48" t="str">
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AP25" s="48" t="str">
         <x:f>IF(OR(AO25="",AM25=""),"",AO25-AM25)</x:f>
       </x:c>
-      <x:c r="AQ25" s="46" t="str">
-        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AR25" s="46" t="str">
+      <x:c r="AQ25" s="48" t="str">
+        <x:f>IF('Model'!$D25=0,"",1-POWER(2,-('Model'!$M25+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AR25" s="48" t="str">
         <x:f>IF(OR(AQ25="",AO25=""),"",AQ25-AO25)</x:f>
       </x:c>
       <x:c r="AS25" s="24" t="str">
@@ -6684,18 +6721,18 @@
         <x:f>'Model'!S25</x:f>
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="AU25" s="26" t="str">
+      <x:c r="AU25" s="25" t="str">
         <x:f>IF('Model'!$D25=0,"",'Model'!T25)</x:f>
       </x:c>
-      <x:c r="AV25" s="26" t="n">
+      <x:c r="AV25" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW25" s="25" t="n">
+      <x:c r="AW25" s="26" t="n">
         <x:f>'Model'!N25</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX25" s="25" t="n">
+      <x:c r="AX25" s="26" t="n">
         <x:f>'Model'!P25</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -6717,152 +6754,152 @@
       <x:c r="D26" s="17" t="str">
         <x:v>Strict end-to-end job automation rate</x:v>
       </x:c>
-      <x:c r="E26" s="44" t="str">
+      <x:c r="E26" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F26" s="44" t="str">
+      <x:c r="F26" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G26" s="44" t="str">
+      <x:c r="G26" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H26" s="44" t="str">
+      <x:c r="H26" s="46" t="str">
         <x:f>IF(OR(G26="",E26=""),"",G26-E26)</x:f>
       </x:c>
-      <x:c r="I26" s="44" t="str">
+      <x:c r="I26" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J26" s="44" t="str">
+      <x:c r="J26" s="46" t="str">
         <x:f>IF(OR(I26="",G26=""),"",I26-G26)</x:f>
       </x:c>
-      <x:c r="K26" s="44" t="str">
+      <x:c r="K26" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L26" s="44" t="str">
+      <x:c r="L26" s="46" t="str">
         <x:f>IF(OR(K26="",I26=""),"",K26-I26)</x:f>
       </x:c>
-      <x:c r="M26" s="44" t="str">
+      <x:c r="M26" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N26" s="44" t="str">
+      <x:c r="N26" s="46" t="str">
         <x:f>IF(OR(M26="",K26=""),"",M26-K26)</x:f>
       </x:c>
-      <x:c r="O26" s="44" t="str">
+      <x:c r="O26" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P26" s="44" t="str">
+      <x:c r="P26" s="46" t="str">
         <x:f>IF(OR(O26="",M26=""),"",O26-M26)</x:f>
       </x:c>
-      <x:c r="Q26" s="45" t="n">
+      <x:c r="Q26" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
         <x:v>0.0208</x:v>
       </x:c>
-      <x:c r="R26" s="45" t="str">
+      <x:c r="R26" s="47" t="str">
         <x:f>IF(OR(Q26="",O26=""),"",Q26-O26)</x:f>
       </x:c>
-      <x:c r="S26" s="45" t="n">
+      <x:c r="S26" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
         <x:v>0.0375</x:v>
       </x:c>
-      <x:c r="T26" s="45" t="n">
+      <x:c r="T26" s="47" t="n">
         <x:f>IF(OR(S26="",Q26=""),"",S26-Q26)</x:f>
         <x:v>0.0167</x:v>
       </x:c>
-      <x:c r="U26" s="45" t="n">
+      <x:c r="U26" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
         <x:v>0.0417</x:v>
       </x:c>
-      <x:c r="V26" s="45" t="n">
+      <x:c r="V26" s="47" t="n">
         <x:f>IF(OR(U26="",S26=""),"",U26-S26)</x:f>
         <x:v>0.004200000000000002</x:v>
       </x:c>
-      <x:c r="W26" s="45" t="n">
+      <x:c r="W26" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.158</x:v>
       </x:c>
-      <x:c r="X26" s="45" t="n">
+      <x:c r="X26" s="47" t="n">
         <x:f>IF(OR(W26="",U26=""),"",W26-U26)</x:f>
         <x:v>0.1163</x:v>
       </x:c>
-      <x:c r="Y26" s="44" t="n">
+      <x:c r="Y26" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B26,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.158</x:v>
       </x:c>
-      <x:c r="Z26" s="44" t="n">
+      <x:c r="Z26" s="46" t="n">
         <x:f>IF(OR(Y26="",W26=""),"",Y26-W26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.23966231616778544</x:v>
-      </x:c>
-      <x:c r="AB26" s="46" t="n">
+      <x:c r="AA26" s="48" t="n">
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.23601250440957589</x:v>
+      </x:c>
+      <x:c r="AB26" s="48" t="n">
         <x:f>IF(OR(AA26="",Y26=""),"",AA26-Y26)</x:f>
-        <x:v>0.08166231616778544</x:v>
-      </x:c>
-      <x:c r="AC26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.34560691114086295</x:v>
-      </x:c>
-      <x:c r="AD26" s="46" t="n">
+        <x:v>0.07801250440957588</x:v>
+      </x:c>
+      <x:c r="AC26" s="48" t="n">
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.32952889971416244</x:v>
+      </x:c>
+      <x:c r="AD26" s="48" t="n">
         <x:f>IF(OR(AC26="",AA26=""),"",AC26-AA26)</x:f>
-        <x:v>0.10594459497307751</x:v>
-      </x:c>
-      <x:c r="AE26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.47521039518418506</x:v>
-      </x:c>
-      <x:c r="AF26" s="46" t="n">
+        <x:v>0.09351639530458655</x:v>
+      </x:c>
+      <x:c r="AE26" s="48" t="n">
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.4373635823530879</x:v>
+      </x:c>
+      <x:c r="AF26" s="48" t="n">
         <x:f>IF(OR(AE26="",AC26=""),"",AE26-AC26)</x:f>
-        <x:v>0.12960348404332211</x:v>
-      </x:c>
-      <x:c r="AG26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.6206875773402938</x:v>
-      </x:c>
-      <x:c r="AH26" s="46" t="n">
+        <x:v>0.10783468263892548</x:v>
+      </x:c>
+      <x:c r="AG26" s="48" t="n">
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.5554086340670459</x:v>
+      </x:c>
+      <x:c r="AH26" s="48" t="n">
         <x:f>IF(OR(AG26="",AE26=""),"",AG26-AE26)</x:f>
-        <x:v>0.14547718215610872</x:v>
-      </x:c>
-      <x:c r="AI26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7647001795864896</x:v>
-      </x:c>
-      <x:c r="AJ26" s="46" t="n">
+        <x:v>0.11804505171395796</x:v>
+      </x:c>
+      <x:c r="AI26" s="48" t="n">
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.675940885225706</x:v>
+      </x:c>
+      <x:c r="AJ26" s="48" t="n">
         <x:f>IF(OR(AI26="",AG26=""),"",AI26-AG26)</x:f>
-        <x:v>0.14401260224619583</x:v>
-      </x:c>
-      <x:c r="AK26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8834267472558752</x:v>
-      </x:c>
-      <x:c r="AL26" s="46" t="n">
+        <x:v>0.12053225115866006</x:v>
+      </x:c>
+      <x:c r="AK26" s="48" t="n">
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7880706627864551</x:v>
+      </x:c>
+      <x:c r="AL26" s="48" t="n">
         <x:f>IF(OR(AK26="",AI26=""),"",AK26-AI26)</x:f>
-        <x:v>0.11872656766938561</x:v>
-      </x:c>
-      <x:c r="AM26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9585093986294878</x:v>
-      </x:c>
-      <x:c r="AN26" s="46" t="n">
+        <x:v>0.11212977756074916</x:v>
+      </x:c>
+      <x:c r="AM26" s="48" t="n">
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8801850642915643</x:v>
+      </x:c>
+      <x:c r="AN26" s="48" t="n">
         <x:f>IF(OR(AM26="",AK26=""),"",AM26-AK26)</x:f>
-        <x:v>0.07508265137361259</x:v>
-      </x:c>
-      <x:c r="AO26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9909208664423133</x:v>
-      </x:c>
-      <x:c r="AP26" s="46" t="n">
+        <x:v>0.09211440150510919</x:v>
+      </x:c>
+      <x:c r="AO26" s="48" t="n">
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9442949150963443</x:v>
+      </x:c>
+      <x:c r="AP26" s="48" t="n">
         <x:f>IF(OR(AO26="",AM26=""),"",AO26-AM26)</x:f>
-        <x:v>0.032411467812825445</x:v>
-      </x:c>
-      <x:c r="AQ26" s="46" t="n">
-        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.999028576885037</x:v>
-      </x:c>
-      <x:c r="AR26" s="46" t="n">
+        <x:v>0.06410985080478004</x:v>
+      </x:c>
+      <x:c r="AQ26" s="48" t="n">
+        <x:f>IF('Model'!$D26=0,"",1-POWER(2,-('Model'!$M26+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9800833657947783</x:v>
+      </x:c>
+      <x:c r="AR26" s="48" t="n">
         <x:f>IF(OR(AQ26="",AO26=""),"",AQ26-AO26)</x:f>
-        <x:v>0.008107710442723737</x:v>
+        <x:v>0.03578845069843395</x:v>
       </x:c>
       <x:c r="AS26" s="24" t="n">
         <x:f>IF('Model'!$D26=0,"",Y26)</x:f>
@@ -6872,25 +6909,25 @@
         <x:f>'Model'!S26</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="AU26" s="26" t="n">
+      <x:c r="AU26" s="25" t="n">
         <x:f>IF('Model'!$D26=0,"",'Model'!T26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV26" s="26" t="n">
+      <x:c r="AV26" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW26" s="25" t="n">
+      <x:c r="AW26" s="26" t="n">
         <x:f>'Model'!N26</x:f>
         <x:v>0.18665713536174539</x:v>
       </x:c>
-      <x:c r="AX26" s="25" t="n">
+      <x:c r="AX26" s="26" t="n">
         <x:f>'Model'!P26</x:f>
         <x:v>0.18034796332026068</x:v>
       </x:c>
       <x:c r="AY26" s="17" t="str">
         <x:f>'Model'!Q26</x:f>
-        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
+        <x:v>METR feedback transfer — local acceleration retained as diagnostic</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="46" hidden="0" customHeight="1">
@@ -6906,124 +6943,124 @@
       <x:c r="D27" s="17" t="str">
         <x:v>Economic value of office-computer work</x:v>
       </x:c>
-      <x:c r="E27" s="44" t="str">
+      <x:c r="E27" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F27" s="44" t="str">
+      <x:c r="F27" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G27" s="44" t="str">
+      <x:c r="G27" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H27" s="44" t="str">
+      <x:c r="H27" s="46" t="str">
         <x:f>IF(OR(G27="",E27=""),"",G27-E27)</x:f>
       </x:c>
-      <x:c r="I27" s="44" t="str">
+      <x:c r="I27" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J27" s="44" t="str">
+      <x:c r="J27" s="46" t="str">
         <x:f>IF(OR(I27="",G27=""),"",I27-G27)</x:f>
       </x:c>
-      <x:c r="K27" s="44" t="str">
+      <x:c r="K27" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L27" s="44" t="str">
+      <x:c r="L27" s="46" t="str">
         <x:f>IF(OR(K27="",I27=""),"",K27-I27)</x:f>
       </x:c>
-      <x:c r="M27" s="44" t="str">
+      <x:c r="M27" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N27" s="44" t="str">
+      <x:c r="N27" s="46" t="str">
         <x:f>IF(OR(M27="",K27=""),"",M27-K27)</x:f>
       </x:c>
-      <x:c r="O27" s="44" t="str">
+      <x:c r="O27" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P27" s="44" t="str">
+      <x:c r="P27" s="46" t="str">
         <x:f>IF(OR(O27="",M27=""),"",O27-M27)</x:f>
       </x:c>
-      <x:c r="Q27" s="44" t="str">
+      <x:c r="Q27" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R27" s="44" t="str">
+      <x:c r="R27" s="46" t="str">
         <x:f>IF(OR(Q27="",O27=""),"",Q27-O27)</x:f>
       </x:c>
-      <x:c r="S27" s="44" t="str">
+      <x:c r="S27" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T27" s="44" t="str">
+      <x:c r="T27" s="46" t="str">
         <x:f>IF(OR(S27="",Q27=""),"",S27-Q27)</x:f>
       </x:c>
-      <x:c r="U27" s="44" t="str">
+      <x:c r="U27" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
       </x:c>
-      <x:c r="V27" s="44" t="str">
+      <x:c r="V27" s="46" t="str">
         <x:f>IF(OR(U27="",S27=""),"",U27-S27)</x:f>
       </x:c>
-      <x:c r="W27" s="44" t="str">
+      <x:c r="W27" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
       </x:c>
-      <x:c r="X27" s="44" t="str">
+      <x:c r="X27" s="46" t="str">
         <x:f>IF(OR(W27="",U27=""),"",W27-U27)</x:f>
       </x:c>
-      <x:c r="Y27" s="44" t="str">
+      <x:c r="Y27" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B27,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
       </x:c>
-      <x:c r="Z27" s="44" t="str">
+      <x:c r="Z27" s="46" t="str">
         <x:f>IF(OR(Y27="",W27=""),"",Y27-W27)</x:f>
       </x:c>
-      <x:c r="AA27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AB27" s="46" t="str">
+      <x:c r="AA27" s="48" t="str">
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AB27" s="48" t="str">
         <x:f>IF(OR(AA27="",Y27=""),"",AA27-Y27)</x:f>
       </x:c>
-      <x:c r="AC27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AD27" s="46" t="str">
+      <x:c r="AC27" s="48" t="str">
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AD27" s="48" t="str">
         <x:f>IF(OR(AC27="",AA27=""),"",AC27-AA27)</x:f>
       </x:c>
-      <x:c r="AE27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AF27" s="46" t="str">
+      <x:c r="AE27" s="48" t="str">
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AF27" s="48" t="str">
         <x:f>IF(OR(AE27="",AC27=""),"",AE27-AC27)</x:f>
       </x:c>
-      <x:c r="AG27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AH27" s="46" t="str">
+      <x:c r="AG27" s="48" t="str">
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AH27" s="48" t="str">
         <x:f>IF(OR(AG27="",AE27=""),"",AG27-AE27)</x:f>
       </x:c>
-      <x:c r="AI27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AJ27" s="46" t="str">
+      <x:c r="AI27" s="48" t="str">
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AJ27" s="48" t="str">
         <x:f>IF(OR(AI27="",AG27=""),"",AI27-AG27)</x:f>
       </x:c>
-      <x:c r="AK27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AL27" s="46" t="str">
+      <x:c r="AK27" s="48" t="str">
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AL27" s="48" t="str">
         <x:f>IF(OR(AK27="",AI27=""),"",AK27-AI27)</x:f>
       </x:c>
-      <x:c r="AM27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AN27" s="46" t="str">
+      <x:c r="AM27" s="48" t="str">
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AN27" s="48" t="str">
         <x:f>IF(OR(AM27="",AK27=""),"",AM27-AK27)</x:f>
       </x:c>
-      <x:c r="AO27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AP27" s="46" t="str">
+      <x:c r="AO27" s="48" t="str">
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AP27" s="48" t="str">
         <x:f>IF(OR(AO27="",AM27=""),"",AO27-AM27)</x:f>
       </x:c>
-      <x:c r="AQ27" s="46" t="str">
-        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-      </x:c>
-      <x:c r="AR27" s="46" t="str">
+      <x:c r="AQ27" s="48" t="str">
+        <x:f>IF('Model'!$D27=0,"",1-POWER(2,-('Model'!$M27+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+      </x:c>
+      <x:c r="AR27" s="48" t="str">
         <x:f>IF(OR(AQ27="",AO27=""),"",AQ27-AO27)</x:f>
       </x:c>
       <x:c r="AS27" s="24" t="str">
@@ -7033,18 +7070,18 @@
         <x:f>'Model'!S27</x:f>
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="AU27" s="26" t="str">
+      <x:c r="AU27" s="25" t="str">
         <x:f>IF('Model'!$D27=0,"",'Model'!T27)</x:f>
       </x:c>
-      <x:c r="AV27" s="26" t="n">
+      <x:c r="AV27" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW27" s="25" t="n">
+      <x:c r="AW27" s="26" t="n">
         <x:f>'Model'!N27</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX27" s="25" t="n">
+      <x:c r="AX27" s="26" t="n">
         <x:f>'Model'!P27</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -7066,148 +7103,148 @@
       <x:c r="D28" s="17" t="str">
         <x:v>Pass^3 on governed agent tasks</x:v>
       </x:c>
-      <x:c r="E28" s="44" t="str">
+      <x:c r="E28" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;1)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;1)))</x:f>
       </x:c>
-      <x:c r="F28" s="44" t="str">
+      <x:c r="F28" s="46" t="str">
         <x:f>""</x:f>
       </x:c>
-      <x:c r="G28" s="44" t="str">
+      <x:c r="G28" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;2)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;2)))</x:f>
       </x:c>
-      <x:c r="H28" s="44" t="str">
+      <x:c r="H28" s="46" t="str">
         <x:f>IF(OR(G28="",E28=""),"",G28-E28)</x:f>
       </x:c>
-      <x:c r="I28" s="44" t="str">
+      <x:c r="I28" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;3)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;3)))</x:f>
       </x:c>
-      <x:c r="J28" s="44" t="str">
+      <x:c r="J28" s="46" t="str">
         <x:f>IF(OR(I28="",G28=""),"",I28-G28)</x:f>
       </x:c>
-      <x:c r="K28" s="44" t="str">
+      <x:c r="K28" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;4)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;4)))</x:f>
       </x:c>
-      <x:c r="L28" s="44" t="str">
+      <x:c r="L28" s="46" t="str">
         <x:f>IF(OR(K28="",I28=""),"",K28-I28)</x:f>
       </x:c>
-      <x:c r="M28" s="44" t="str">
+      <x:c r="M28" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;5)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;5)))</x:f>
       </x:c>
-      <x:c r="N28" s="44" t="str">
+      <x:c r="N28" s="46" t="str">
         <x:f>IF(OR(M28="",K28=""),"",M28-K28)</x:f>
       </x:c>
-      <x:c r="O28" s="44" t="str">
+      <x:c r="O28" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;6)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;6)))</x:f>
       </x:c>
-      <x:c r="P28" s="44" t="str">
+      <x:c r="P28" s="46" t="str">
         <x:f>IF(OR(O28="",M28=""),"",O28-M28)</x:f>
       </x:c>
-      <x:c r="Q28" s="44" t="str">
+      <x:c r="Q28" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;7)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;7)))</x:f>
       </x:c>
-      <x:c r="R28" s="44" t="str">
+      <x:c r="R28" s="46" t="str">
         <x:f>IF(OR(Q28="",O28=""),"",Q28-O28)</x:f>
       </x:c>
-      <x:c r="S28" s="44" t="str">
+      <x:c r="S28" s="46" t="str">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;8)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;8)))</x:f>
       </x:c>
-      <x:c r="T28" s="44" t="str">
+      <x:c r="T28" s="46" t="str">
         <x:f>IF(OR(S28="",Q28=""),"",S28-Q28)</x:f>
       </x:c>
-      <x:c r="U28" s="45" t="n">
+      <x:c r="U28" s="47" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;9)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;9)))</x:f>
         <x:v>0.704</x:v>
       </x:c>
-      <x:c r="V28" s="45" t="str">
+      <x:c r="V28" s="47" t="str">
         <x:f>IF(OR(U28="",S28=""),"",U28-S28)</x:f>
       </x:c>
-      <x:c r="W28" s="44" t="n">
+      <x:c r="W28" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;10)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;10)))</x:f>
         <x:v>0.704</x:v>
       </x:c>
-      <x:c r="X28" s="44" t="n">
+      <x:c r="X28" s="46" t="n">
         <x:f>IF(OR(W28="",U28=""),"",W28-U28)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y28" s="44" t="n">
+      <x:c r="Y28" s="46" t="n">
         <x:f>IF(COUNTIFS('Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;11)=0,"",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,MAXIFS('Observations'!$F$6:$F$500,'Observations'!$A$6:$A$500,$B28,'Observations'!$F$6:$F$500,"&lt;="&amp;11)))</x:f>
         <x:v>0.704</x:v>
       </x:c>
-      <x:c r="Z28" s="44" t="n">
+      <x:c r="Z28" s="46" t="n">
         <x:f>IF(OR(Y28="",W28=""),"",Y28-W28)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(12-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7327078926195539</x:v>
-      </x:c>
-      <x:c r="AB28" s="46" t="n">
+      <x:c r="AA28" s="48" t="n">
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(12-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(12-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7314248234028913</x:v>
+      </x:c>
+      <x:c r="AB28" s="48" t="n">
         <x:f>IF(OR(AA28="",Y28=""),"",AA28-Y28)</x:f>
-        <x:v>0.028707892619553976</x:v>
-      </x:c>
-      <x:c r="AC28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(13-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.7699520732751727</x:v>
-      </x:c>
-      <x:c r="AD28" s="46" t="n">
+        <x:v>0.02742482340289132</x:v>
+      </x:c>
+      <x:c r="AC28" s="48" t="n">
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(13-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(13-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.7642999457427458</x:v>
+      </x:c>
+      <x:c r="AD28" s="48" t="n">
         <x:f>IF(OR(AC28="",AA28=""),"",AC28-AA28)</x:f>
-        <x:v>0.03724418065561874</x:v>
-      </x:c>
-      <x:c r="AE28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(14-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8155133930813762</x:v>
-      </x:c>
-      <x:c r="AF28" s="46" t="n">
+        <x:v>0.03287512233985457</x:v>
+      </x:c>
+      <x:c r="AE28" s="48" t="n">
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(14-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(14-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.802208575269019</x:v>
+      </x:c>
+      <x:c r="AF28" s="48" t="n">
         <x:f>IF(OR(AE28="",AC28=""),"",AE28-AC28)</x:f>
-        <x:v>0.04556131980620348</x:v>
-      </x:c>
-      <x:c r="AG28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(15-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.8666550153120273</x:v>
-      </x:c>
-      <x:c r="AH28" s="46" t="n">
+        <x:v>0.03790862952627316</x:v>
+      </x:c>
+      <x:c r="AG28" s="48" t="n">
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(15-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(15-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8437065981993416</x:v>
+      </x:c>
+      <x:c r="AH28" s="48" t="n">
         <x:f>IF(OR(AG28="",AE28=""),"",AG28-AE28)</x:f>
-        <x:v>0.05114162223065111</x:v>
-      </x:c>
-      <x:c r="AI28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(16-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9172817733463193</x:v>
-      </x:c>
-      <x:c r="AJ28" s="46" t="n">
+        <x:v>0.041498022930322565</x:v>
+      </x:c>
+      <x:c r="AI28" s="48" t="n">
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(16-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(16-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.8860789810294643</x:v>
+      </x:c>
+      <x:c r="AJ28" s="48" t="n">
         <x:f>IF(OR(AI28="",AG28=""),"",AI28-AG28)</x:f>
-        <x:v>0.05062675803429206</x:v>
-      </x:c>
-      <x:c r="AK28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(17-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9590193790828255</x:v>
-      </x:c>
-      <x:c r="AL28" s="46" t="n">
+        <x:v>0.04237238283012268</x:v>
+      </x:c>
+      <x:c r="AK28" s="48" t="n">
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(17-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(17-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.925497525160084</x:v>
+      </x:c>
+      <x:c r="AL28" s="48" t="n">
         <x:f>IF(OR(AK28="",AI28=""),"",AK28-AI28)</x:f>
-        <x:v>0.0417376057365062</x:v>
-      </x:c>
-      <x:c r="AM28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(18-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9854142303970646</x:v>
-      </x:c>
-      <x:c r="AN28" s="46" t="n">
+        <x:v>0.03941854413061974</x:v>
+      </x:c>
+      <x:c r="AM28" s="48" t="n">
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(18-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(18-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9578797850716189</x:v>
+      </x:c>
+      <x:c r="AN28" s="48" t="n">
         <x:f>IF(OR(AM28="",AK28=""),"",AM28-AK28)</x:f>
-        <x:v>0.02639485131423902</x:v>
-      </x:c>
-      <x:c r="AO28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(19-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9968082855901719</x:v>
-      </x:c>
-      <x:c r="AP28" s="46" t="n">
+        <x:v>0.03238225991153487</x:v>
+      </x:c>
+      <x:c r="AO28" s="48" t="n">
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(19-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(19-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9804172148082161</x:v>
+      </x:c>
+      <x:c r="AP28" s="48" t="n">
         <x:f>IF(OR(AO28="",AM28=""),"",AO28-AM28)</x:f>
-        <x:v>0.011394055193107322</x:v>
-      </x:c>
-      <x:c r="AQ28" s="46" t="n">
-        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('Summary'!$H$17/'Summary'!$G$17)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP(('Summary'!$H$17/'Summary'!$G$17)*(20-'Methodology'!$B$8))-1)/('Summary'!$H$17/'Summary'!$G$17)))))))</x:f>
-        <x:v>0.9996585020878515</x:v>
-      </x:c>
-      <x:c r="AR28" s="46" t="n">
+        <x:v>0.022537429736597225</x:v>
+      </x:c>
+      <x:c r="AQ28" s="48" t="n">
+        <x:f>IF('Model'!$D28=0,"",1-POWER(2,-('Model'!$M28+MAX(0,IF(ABS('Summary'!$G$17)&lt;0.000000001,0,IF(ABS('METR Horizon'!$O$14)&lt;0.000000001,'Summary'!$G$17*(20-'Methodology'!$B$8),'Summary'!$G$17*(EXP('METR Horizon'!$O$14*(20-'Methodology'!$B$8))-1)/'METR Horizon'!$O$14))))))</x:f>
+        <x:v>0.9929984278803496</x:v>
+      </x:c>
+      <x:c r="AR28" s="48" t="n">
         <x:f>IF(OR(AQ28="",AO28=""),"",AQ28-AO28)</x:f>
-        <x:v>0.0028502164976795807</x:v>
+        <x:v>0.012581213072133557</x:v>
       </x:c>
       <x:c r="AS28" s="24" t="n">
         <x:f>IF('Model'!$D28=0,"",Y28)</x:f>
@@ -7217,25 +7254,25 @@
         <x:f>'Model'!S28</x:f>
         <x:v>C</x:v>
       </x:c>
-      <x:c r="AU28" s="26" t="n">
+      <x:c r="AU28" s="25" t="n">
         <x:f>IF('Model'!$D28=0,"",'Model'!T28)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AV28" s="26" t="n">
+      <x:c r="AV28" s="25" t="n">
         <x:f>IFERROR((AVERAGEIF($A$6:$A$28,"Direct economic stewardship",$AU$6:$AU$28)*'Summary'!$K$13+AVERAGEIF($A$6:$A$28,"Operational execution",$AU$6:$AU$28)*'Summary'!$K$14+AVERAGEIF($A$6:$A$28,"Personal stewardship transfer",$AU$6:$AU$28)*'Summary'!$K$15+AVERAGEIF($A$6:$A$28,"Economic value &amp; governance",$AU$6:$AU$28)*'Summary'!$K$16)/SUM('Summary'!$K$13:$K$16),"")</x:f>
         <x:v>0.5796055796055796</x:v>
       </x:c>
-      <x:c r="AW28" s="25" t="n">
+      <x:c r="AW28" s="26" t="n">
         <x:f>'Model'!N28</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AX28" s="25" t="n">
+      <x:c r="AX28" s="26" t="n">
         <x:f>'Model'!P28</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AY28" s="17" t="str">
         <x:f>'Model'!Q28</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8794,7 +8831,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re173a23f1dac45fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04ea93be6f7b4b10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9610,7 +9647,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R304642bdcb484e1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb12ded54eb364aaf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9644,197 +9681,197 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="F1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="G1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="H1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="I1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="J1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="K1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="L1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="M1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="N1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="O1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="P1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="Q1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="R1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="S1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="T1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="U1" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="F2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="L2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="M2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="N2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="Q2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="R2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="S2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="T2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
       <x:c r="U2" s="3" t="str">
-        <x:v>Projection Model — Failure-Gap Velocity and Acceleration</x:v>
+        <x:v>Projection Model — Economic Benchmark Level and Transfer</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="B3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="C3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="H3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="I3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="J3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="K3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="L3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="M3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="N3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="O3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="P3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="Q3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="R3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="S3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="T3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
       <x:c r="U3" s="6" t="str">
-        <x:v>Helper sheet. Longitudinal series estimate the shared frontier velocity and initial acceleration. The forecast compounds their causal feedback across every graded benchmark; evidence credits preserve uncertainty.</x:v>
+        <x:v>Helper sheet. Economic benchmarks set the current level and initial gap velocity. Benchmark-local acceleration is diagnostic; METR H50/H80 controls the shared feedback applied to every graded benchmark.</x:v>
       </x:c>
     </x:row>
     <x:row r="4"/>
@@ -9885,7 +9922,7 @@
         <x:v>Prior gap velocity</x:v>
       </x:c>
       <x:c r="P5" s="13" t="str">
-        <x:v>Gap acceleration</x:v>
+        <x:v>Benchmark-local acceleration (diagnostic)</x:v>
       </x:c>
       <x:c r="Q5" s="13" t="str">
         <x:v>Projection basis</x:v>
@@ -9903,7 +9940,7 @@
         <x:v>Evidence credits</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
+    <x:row r="6" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A6" s="17" t="str">
         <x:v>DES-01</x:v>
       </x:c>
@@ -9941,33 +9978,33 @@
         <x:f>IF(G6="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A6,'Observations'!$F$6:$F$500,G6))</x:f>
         <x:v>0.17749</x:v>
       </x:c>
-      <x:c r="K6" s="25" t="n">
+      <x:c r="K6" s="26" t="n">
         <x:f>IF(H6="","",IF(H6&gt;=1,30,-LN(1-H6)/LN(2)))</x:f>
         <x:v>0.19638168387795835</x:v>
       </x:c>
-      <x:c r="L6" s="25" t="n">
+      <x:c r="L6" s="26" t="n">
         <x:f>IF(I6="","",IF(I6&gt;=1,30,-LN(1-I6)/LN(2)))</x:f>
         <x:v>0.27508673226655406</x:v>
       </x:c>
-      <x:c r="M6" s="25" t="n">
+      <x:c r="M6" s="26" t="n">
         <x:f>IF(J6="","",IF(J6&gt;=1,30,-LN(1-J6)/LN(2)))</x:f>
         <x:v>0.28189487578087197</x:v>
       </x:c>
-      <x:c r="N6" s="25" t="n">
+      <x:c r="N6" s="26" t="n">
         <x:f>IF(D6&lt;2,0,(M6-L6)/(G6-F6))</x:f>
         <x:v>0.00680814351431791</x:v>
       </x:c>
-      <x:c r="O6" s="25" t="n">
+      <x:c r="O6" s="26" t="n">
         <x:f>IF(D6&lt;3,0,(L6-K6)/(F6-E6))</x:f>
         <x:v>0.07870504838859571</x:v>
       </x:c>
-      <x:c r="P6" s="25" t="n">
+      <x:c r="P6" s="26" t="n">
         <x:f>IF(D6&lt;3,0,(N6-O6)/(((G6-F6)+(F6-E6))/2))</x:f>
         <x:v>-0.0718969048742778</x:v>
       </x:c>
       <x:c r="Q6" s="17" t="str">
-        <x:f>IF(D6=0,"Ungraded — no normalized observation",IF(D6=1,"Shared frontier transfer — one observation",IF(D6=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
+        <x:f>IF(D6=0,"Ungraded — no normalized observation",IF(D6=1,"METR feedback transfer — one economic observation",IF(D6=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — local acceleration retained as diagnostic</x:v>
       </x:c>
       <x:c r="R6" s="24" t="n">
         <x:f>IF(D6=0,"",J6)</x:f>
@@ -9977,11 +10014,11 @@
         <x:f>IF(R6="","N/A",IF(R6&gt;='Methodology'!$G$7,"A",IF(R6&gt;='Methodology'!$G$8,"B",IF(R6&gt;='Methodology'!$G$9,"C",IF(R6&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T6" s="26" t="n">
+      <x:c r="T6" s="25" t="n">
         <x:f>IF(R6="","",IF(R6&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R6&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R6&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R6&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U6" s="27" t="n">
+      <x:c r="U6" s="29" t="n">
         <x:f>MIN(D6,3)</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -10022,32 +10059,32 @@
         <x:f>IF(G7="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A7,'Observations'!$F$6:$F$500,G7))</x:f>
         <x:v>0.010067435</x:v>
       </x:c>
-      <x:c r="K7" s="25" t="str">
+      <x:c r="K7" s="26" t="str">
         <x:f>IF(H7="","",IF(H7&gt;=1,30,-LN(1-H7)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L7" s="25" t="n">
+      <x:c r="L7" s="26" t="n">
         <x:f>IF(I7="","",IF(I7&gt;=1,30,-LN(1-I7)/LN(2)))</x:f>
         <x:v>0.008306298103420784</x:v>
       </x:c>
-      <x:c r="M7" s="25" t="n">
+      <x:c r="M7" s="26" t="n">
         <x:f>IF(J7="","",IF(J7&gt;=1,30,-LN(1-J7)/LN(2)))</x:f>
         <x:v>0.01459784389075154</x:v>
       </x:c>
-      <x:c r="N7" s="25" t="n">
+      <x:c r="N7" s="26" t="n">
         <x:f>IF(D7&lt;2,0,(M7-L7)/(G7-F7))</x:f>
         <x:v>0.006291545787330755</x:v>
       </x:c>
-      <x:c r="O7" s="25" t="n">
+      <x:c r="O7" s="26" t="n">
         <x:f>IF(D7&lt;3,0,(L7-K7)/(F7-E7))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P7" s="25" t="n">
+      <x:c r="P7" s="26" t="n">
         <x:f>IF(D7&lt;3,0,(N7-O7)/(((G7-F7)+(F7-E7))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q7" s="17" t="str">
-        <x:f>IF(D7=0,"Ungraded — no normalized observation",IF(D7=1,"Shared frontier transfer — one observation",IF(D7=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — velocity contributor</x:v>
+        <x:f>IF(D7=0,"Ungraded — no normalized observation",IF(D7=1,"METR feedback transfer — one economic observation",IF(D7=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — economic velocity contributor</x:v>
       </x:c>
       <x:c r="R7" s="24" t="n">
         <x:f>IF(D7=0,"",J7)</x:f>
@@ -10057,11 +10094,11 @@
         <x:f>IF(R7="","N/A",IF(R7&gt;='Methodology'!$G$7,"A",IF(R7&gt;='Methodology'!$G$8,"B",IF(R7&gt;='Methodology'!$G$9,"C",IF(R7&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T7" s="26" t="n">
+      <x:c r="T7" s="25" t="n">
         <x:f>IF(R7="","",IF(R7&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R7&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R7&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R7&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U7" s="27" t="n">
+      <x:c r="U7" s="29" t="n">
         <x:f>MIN(D7,3)</x:f>
         <x:v>2</x:v>
       </x:c>
@@ -10100,31 +10137,31 @@
         <x:f>IF(G8="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A8,'Observations'!$F$6:$F$500,G8))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K8" s="25" t="str">
+      <x:c r="K8" s="26" t="str">
         <x:f>IF(H8="","",IF(H8&gt;=1,30,-LN(1-H8)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L8" s="25" t="str">
+      <x:c r="L8" s="26" t="str">
         <x:f>IF(I8="","",IF(I8&gt;=1,30,-LN(1-I8)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M8" s="25" t="n">
+      <x:c r="M8" s="26" t="n">
         <x:f>IF(J8="","",IF(J8&gt;=1,30,-LN(1-J8)/LN(2)))</x:f>
         <x:v>30</x:v>
       </x:c>
-      <x:c r="N8" s="25" t="n">
+      <x:c r="N8" s="26" t="n">
         <x:f>IF(D8&lt;2,0,(M8-L8)/(G8-F8))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O8" s="25" t="n">
+      <x:c r="O8" s="26" t="n">
         <x:f>IF(D8&lt;3,0,(L8-K8)/(F8-E8))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P8" s="25" t="n">
+      <x:c r="P8" s="26" t="n">
         <x:f>IF(D8&lt;3,0,(N8-O8)/(((G8-F8)+(F8-E8))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q8" s="17" t="str">
-        <x:f>IF(D8=0,"Ungraded — no normalized observation",IF(D8=1,"Shared frontier transfer — one observation",IF(D8=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:f>IF(D8=0,"Ungraded — no normalized observation",IF(D8=1,"METR feedback transfer — one economic observation",IF(D8=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
       <x:c r="R8" s="24" t="n">
         <x:f>IF(D8=0,"",J8)</x:f>
@@ -10134,11 +10171,11 @@
         <x:f>IF(R8="","N/A",IF(R8&gt;='Methodology'!$G$7,"A",IF(R8&gt;='Methodology'!$G$8,"B",IF(R8&gt;='Methodology'!$G$9,"C",IF(R8&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>A</x:v>
       </x:c>
-      <x:c r="T8" s="26" t="n">
+      <x:c r="T8" s="25" t="n">
         <x:f>IF(R8="","",IF(R8&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R8&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R8&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R8&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="U8" s="27" t="n">
+      <x:c r="U8" s="29" t="n">
         <x:f>MIN(D8,3)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -10177,31 +10214,31 @@
         <x:f>IF(G9="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A9,'Observations'!$F$6:$F$500,G9))</x:f>
         <x:v>0.4321186625247882</x:v>
       </x:c>
-      <x:c r="K9" s="25" t="str">
+      <x:c r="K9" s="26" t="str">
         <x:f>IF(H9="","",IF(H9&gt;=1,30,-LN(1-H9)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L9" s="25" t="str">
+      <x:c r="L9" s="26" t="str">
         <x:f>IF(I9="","",IF(I9&gt;=1,30,-LN(1-I9)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M9" s="25" t="n">
+      <x:c r="M9" s="26" t="n">
         <x:f>IF(J9="","",IF(J9&gt;=1,30,-LN(1-J9)/LN(2)))</x:f>
         <x:v>0.8163385942433947</x:v>
       </x:c>
-      <x:c r="N9" s="25" t="n">
+      <x:c r="N9" s="26" t="n">
         <x:f>IF(D9&lt;2,0,(M9-L9)/(G9-F9))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O9" s="25" t="n">
+      <x:c r="O9" s="26" t="n">
         <x:f>IF(D9&lt;3,0,(L9-K9)/(F9-E9))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P9" s="25" t="n">
+      <x:c r="P9" s="26" t="n">
         <x:f>IF(D9&lt;3,0,(N9-O9)/(((G9-F9)+(F9-E9))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q9" s="17" t="str">
-        <x:f>IF(D9=0,"Ungraded — no normalized observation",IF(D9=1,"Shared frontier transfer — one observation",IF(D9=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:f>IF(D9=0,"Ungraded — no normalized observation",IF(D9=1,"METR feedback transfer — one economic observation",IF(D9=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
       <x:c r="R9" s="24" t="n">
         <x:f>IF(D9=0,"",J9)</x:f>
@@ -10211,11 +10248,11 @@
         <x:f>IF(R9="","N/A",IF(R9&gt;='Methodology'!$G$7,"A",IF(R9&gt;='Methodology'!$G$8,"B",IF(R9&gt;='Methodology'!$G$9,"C",IF(R9&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T9" s="26" t="n">
+      <x:c r="T9" s="25" t="n">
         <x:f>IF(R9="","",IF(R9&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R9&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R9&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R9&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U9" s="27" t="n">
+      <x:c r="U9" s="29" t="n">
         <x:f>MIN(D9,3)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -10254,31 +10291,31 @@
         <x:f>IF(G10="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A10,'Observations'!$F$6:$F$500,G10))</x:f>
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="K10" s="25" t="str">
+      <x:c r="K10" s="26" t="str">
         <x:f>IF(H10="","",IF(H10&gt;=1,30,-LN(1-H10)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L10" s="25" t="str">
+      <x:c r="L10" s="26" t="str">
         <x:f>IF(I10="","",IF(I10&gt;=1,30,-LN(1-I10)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M10" s="25" t="n">
+      <x:c r="M10" s="26" t="n">
         <x:f>IF(J10="","",IF(J10&gt;=1,30,-LN(1-J10)/LN(2)))</x:f>
         <x:v>1.3219280948873622</x:v>
       </x:c>
-      <x:c r="N10" s="25" t="n">
+      <x:c r="N10" s="26" t="n">
         <x:f>IF(D10&lt;2,0,(M10-L10)/(G10-F10))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O10" s="25" t="n">
+      <x:c r="O10" s="26" t="n">
         <x:f>IF(D10&lt;3,0,(L10-K10)/(F10-E10))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P10" s="25" t="n">
+      <x:c r="P10" s="26" t="n">
         <x:f>IF(D10&lt;3,0,(N10-O10)/(((G10-F10)+(F10-E10))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q10" s="17" t="str">
-        <x:f>IF(D10=0,"Ungraded — no normalized observation",IF(D10=1,"Shared frontier transfer — one observation",IF(D10=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:f>IF(D10=0,"Ungraded — no normalized observation",IF(D10=1,"METR feedback transfer — one economic observation",IF(D10=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
       <x:c r="R10" s="24" t="n">
         <x:f>IF(D10=0,"",J10)</x:f>
@@ -10288,11 +10325,11 @@
         <x:f>IF(R10="","N/A",IF(R10&gt;='Methodology'!$G$7,"A",IF(R10&gt;='Methodology'!$G$8,"B",IF(R10&gt;='Methodology'!$G$9,"C",IF(R10&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>D</x:v>
       </x:c>
-      <x:c r="T10" s="26" t="n">
+      <x:c r="T10" s="25" t="n">
         <x:f>IF(R10="","",IF(R10&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R10&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R10&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R10&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="U10" s="27" t="n">
+      <x:c r="U10" s="29" t="n">
         <x:f>MIN(D10,3)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -10331,31 +10368,31 @@
         <x:f>IF(G11="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A11,'Observations'!$F$6:$F$500,G11))</x:f>
         <x:v>0.18516388283148968</x:v>
       </x:c>
-      <x:c r="K11" s="25" t="str">
+      <x:c r="K11" s="26" t="str">
         <x:f>IF(H11="","",IF(H11&gt;=1,30,-LN(1-H11)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L11" s="25" t="str">
+      <x:c r="L11" s="26" t="str">
         <x:f>IF(I11="","",IF(I11&gt;=1,30,-LN(1-I11)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M11" s="25" t="n">
+      <x:c r="M11" s="26" t="n">
         <x:f>IF(J11="","",IF(J11&gt;=1,30,-LN(1-J11)/LN(2)))</x:f>
         <x:v>0.29541816649188574</x:v>
       </x:c>
-      <x:c r="N11" s="25" t="n">
+      <x:c r="N11" s="26" t="n">
         <x:f>IF(D11&lt;2,0,(M11-L11)/(G11-F11))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O11" s="25" t="n">
+      <x:c r="O11" s="26" t="n">
         <x:f>IF(D11&lt;3,0,(L11-K11)/(F11-E11))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P11" s="25" t="n">
+      <x:c r="P11" s="26" t="n">
         <x:f>IF(D11&lt;3,0,(N11-O11)/(((G11-F11)+(F11-E11))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q11" s="17" t="str">
-        <x:f>IF(D11=0,"Ungraded — no normalized observation",IF(D11=1,"Shared frontier transfer — one observation",IF(D11=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:f>IF(D11=0,"Ungraded — no normalized observation",IF(D11=1,"METR feedback transfer — one economic observation",IF(D11=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
       <x:c r="R11" s="24" t="n">
         <x:f>IF(D11=0,"",J11)</x:f>
@@ -10365,11 +10402,11 @@
         <x:f>IF(R11="","N/A",IF(R11&gt;='Methodology'!$G$7,"A",IF(R11&gt;='Methodology'!$G$8,"B",IF(R11&gt;='Methodology'!$G$9,"C",IF(R11&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T11" s="26" t="n">
+      <x:c r="T11" s="25" t="n">
         <x:f>IF(R11="","",IF(R11&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R11&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R11&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R11&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U11" s="27" t="n">
+      <x:c r="U11" s="29" t="n">
         <x:f>MIN(D11,3)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -10408,31 +10445,31 @@
         <x:f>IF(G12="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A12,'Observations'!$F$6:$F$500,G12))</x:f>
         <x:v>0.273</x:v>
       </x:c>
-      <x:c r="K12" s="25" t="str">
+      <x:c r="K12" s="26" t="str">
         <x:f>IF(H12="","",IF(H12&gt;=1,30,-LN(1-H12)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L12" s="25" t="str">
+      <x:c r="L12" s="26" t="str">
         <x:f>IF(I12="","",IF(I12&gt;=1,30,-LN(1-I12)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M12" s="25" t="n">
+      <x:c r="M12" s="26" t="n">
         <x:f>IF(J12="","",IF(J12&gt;=1,30,-LN(1-J12)/LN(2)))</x:f>
         <x:v>0.45997273074249273</x:v>
       </x:c>
-      <x:c r="N12" s="25" t="n">
+      <x:c r="N12" s="26" t="n">
         <x:f>IF(D12&lt;2,0,(M12-L12)/(G12-F12))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O12" s="25" t="n">
+      <x:c r="O12" s="26" t="n">
         <x:f>IF(D12&lt;3,0,(L12-K12)/(F12-E12))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P12" s="25" t="n">
+      <x:c r="P12" s="26" t="n">
         <x:f>IF(D12&lt;3,0,(N12-O12)/(((G12-F12)+(F12-E12))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q12" s="17" t="str">
-        <x:f>IF(D12=0,"Ungraded — no normalized observation",IF(D12=1,"Shared frontier transfer — one observation",IF(D12=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:f>IF(D12=0,"Ungraded — no normalized observation",IF(D12=1,"METR feedback transfer — one economic observation",IF(D12=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
       <x:c r="R12" s="24" t="n">
         <x:f>IF(D12=0,"",J12)</x:f>
@@ -10442,11 +10479,11 @@
         <x:f>IF(R12="","N/A",IF(R12&gt;='Methodology'!$G$7,"A",IF(R12&gt;='Methodology'!$G$8,"B",IF(R12&gt;='Methodology'!$G$9,"C",IF(R12&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T12" s="26" t="n">
+      <x:c r="T12" s="25" t="n">
         <x:f>IF(R12="","",IF(R12&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R12&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R12&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R12&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U12" s="27" t="n">
+      <x:c r="U12" s="29" t="n">
         <x:f>MIN(D12,3)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -10485,31 +10522,31 @@
         <x:f>IF(G13="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A13,'Observations'!$F$6:$F$500,G13))</x:f>
         <x:v>0.3033</x:v>
       </x:c>
-      <x:c r="K13" s="25" t="str">
+      <x:c r="K13" s="26" t="str">
         <x:f>IF(H13="","",IF(H13&gt;=1,30,-LN(1-H13)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L13" s="25" t="str">
+      <x:c r="L13" s="26" t="str">
         <x:f>IF(I13="","",IF(I13&gt;=1,30,-LN(1-I13)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M13" s="25" t="n">
+      <x:c r="M13" s="26" t="n">
         <x:f>IF(J13="","",IF(J13&gt;=1,30,-LN(1-J13)/LN(2)))</x:f>
         <x:v>0.5213905315954884</x:v>
       </x:c>
-      <x:c r="N13" s="25" t="n">
+      <x:c r="N13" s="26" t="n">
         <x:f>IF(D13&lt;2,0,(M13-L13)/(G13-F13))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O13" s="25" t="n">
+      <x:c r="O13" s="26" t="n">
         <x:f>IF(D13&lt;3,0,(L13-K13)/(F13-E13))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P13" s="25" t="n">
+      <x:c r="P13" s="26" t="n">
         <x:f>IF(D13&lt;3,0,(N13-O13)/(((G13-F13)+(F13-E13))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q13" s="17" t="str">
-        <x:f>IF(D13=0,"Ungraded — no normalized observation",IF(D13=1,"Shared frontier transfer — one observation",IF(D13=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:f>IF(D13=0,"Ungraded — no normalized observation",IF(D13=1,"METR feedback transfer — one economic observation",IF(D13=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
       <x:c r="R13" s="24" t="n">
         <x:f>IF(D13=0,"",J13)</x:f>
@@ -10519,16 +10556,16 @@
         <x:f>IF(R13="","N/A",IF(R13&gt;='Methodology'!$G$7,"A",IF(R13&gt;='Methodology'!$G$8,"B",IF(R13&gt;='Methodology'!$G$9,"C",IF(R13&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T13" s="26" t="n">
+      <x:c r="T13" s="25" t="n">
         <x:f>IF(R13="","",IF(R13&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R13&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R13&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R13&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U13" s="27" t="n">
+      <x:c r="U13" s="29" t="n">
         <x:f>MIN(D13,3)</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
+    <x:row r="14" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A14" s="17" t="str">
         <x:v>OPS-02</x:v>
       </x:c>
@@ -10566,33 +10603,33 @@
         <x:f>IF(G14="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A14,'Observations'!$F$6:$F$500,G14))</x:f>
         <x:v>0.511</x:v>
       </x:c>
-      <x:c r="K14" s="25" t="n">
+      <x:c r="K14" s="26" t="n">
         <x:f>IF(H14="","",IF(H14&gt;=1,30,-LN(1-H14)/LN(2)))</x:f>
         <x:v>0.7226103011891362</x:v>
       </x:c>
-      <x:c r="L14" s="25" t="n">
+      <x:c r="L14" s="26" t="n">
         <x:f>IF(I14="","",IF(I14&gt;=1,30,-LN(1-I14)/LN(2)))</x:f>
         <x:v>0.8862995008352721</x:v>
       </x:c>
-      <x:c r="M14" s="25" t="n">
+      <x:c r="M14" s="26" t="n">
         <x:f>IF(J14="","",IF(J14&gt;=1,30,-LN(1-J14)/LN(2)))</x:f>
         <x:v>1.0320936297098533</x:v>
       </x:c>
-      <x:c r="N14" s="25" t="n">
+      <x:c r="N14" s="26" t="n">
         <x:f>IF(D14&lt;2,0,(M14-L14)/(G14-F14))</x:f>
         <x:v>0.0728970644372906</x:v>
       </x:c>
-      <x:c r="O14" s="25" t="n">
+      <x:c r="O14" s="26" t="n">
         <x:f>IF(D14&lt;3,0,(L14-K14)/(F14-E14))</x:f>
         <x:v>0.16368919964613593</x:v>
       </x:c>
-      <x:c r="P14" s="25" t="n">
+      <x:c r="P14" s="26" t="n">
         <x:f>IF(D14&lt;3,0,(N14-O14)/(((G14-F14)+(F14-E14))/2))</x:f>
         <x:v>-0.06052809013923022</x:v>
       </x:c>
       <x:c r="Q14" s="17" t="str">
-        <x:f>IF(D14=0,"Ungraded — no normalized observation",IF(D14=1,"Shared frontier transfer — one observation",IF(D14=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
+        <x:f>IF(D14=0,"Ungraded — no normalized observation",IF(D14=1,"METR feedback transfer — one economic observation",IF(D14=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — local acceleration retained as diagnostic</x:v>
       </x:c>
       <x:c r="R14" s="24" t="n">
         <x:f>IF(D14=0,"",J14)</x:f>
@@ -10602,16 +10639,16 @@
         <x:f>IF(R14="","N/A",IF(R14&gt;='Methodology'!$G$7,"A",IF(R14&gt;='Methodology'!$G$8,"B",IF(R14&gt;='Methodology'!$G$9,"C",IF(R14&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T14" s="26" t="n">
+      <x:c r="T14" s="25" t="n">
         <x:f>IF(R14="","",IF(R14&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R14&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R14&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R14&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U14" s="27" t="n">
+      <x:c r="U14" s="29" t="n">
         <x:f>MIN(D14,3)</x:f>
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="15" hidden="0" customHeight="1">
+    <x:row r="15" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A15" s="17" t="str">
         <x:v>OPS-03</x:v>
       </x:c>
@@ -10649,33 +10686,33 @@
         <x:f>IF(G15="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A15,'Observations'!$F$6:$F$500,G15))</x:f>
         <x:v>0.607</x:v>
       </x:c>
-      <x:c r="K15" s="25" t="n">
+      <x:c r="K15" s="26" t="n">
         <x:f>IF(H15="","",IF(H15&gt;=1,30,-LN(1-H15)/LN(2)))</x:f>
         <x:v>0.49410907027004275</x:v>
       </x:c>
-      <x:c r="L15" s="25" t="n">
+      <x:c r="L15" s="26" t="n">
         <x:f>IF(I15="","",IF(I15&gt;=1,30,-LN(1-I15)/LN(2)))</x:f>
         <x:v>1.0679388286565756</x:v>
       </x:c>
-      <x:c r="M15" s="25" t="n">
+      <x:c r="M15" s="26" t="n">
         <x:f>IF(J15="","",IF(J15&gt;=1,30,-LN(1-J15)/LN(2)))</x:f>
         <x:v>1.3473987824034805</x:v>
       </x:c>
-      <x:c r="N15" s="25" t="n">
+      <x:c r="N15" s="26" t="n">
         <x:f>IF(D15&lt;2,0,(M15-L15)/(G15-F15))</x:f>
         <x:v>0.2794599537469049</x:v>
       </x:c>
-      <x:c r="O15" s="25" t="n">
+      <x:c r="O15" s="26" t="n">
         <x:f>IF(D15&lt;3,0,(L15-K15)/(F15-E15))</x:f>
         <x:v>0.2869148791932664</x:v>
       </x:c>
-      <x:c r="P15" s="25" t="n">
+      <x:c r="P15" s="26" t="n">
         <x:f>IF(D15&lt;3,0,(N15-O15)/(((G15-F15)+(F15-E15))/2))</x:f>
         <x:v>-0.004969950297574337</x:v>
       </x:c>
       <x:c r="Q15" s="17" t="str">
-        <x:f>IF(D15=0,"Ungraded — no normalized observation",IF(D15=1,"Shared frontier transfer — one observation",IF(D15=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
+        <x:f>IF(D15=0,"Ungraded — no normalized observation",IF(D15=1,"METR feedback transfer — one economic observation",IF(D15=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — local acceleration retained as diagnostic</x:v>
       </x:c>
       <x:c r="R15" s="24" t="n">
         <x:f>IF(D15=0,"",J15)</x:f>
@@ -10685,11 +10722,11 @@
         <x:f>IF(R15="","N/A",IF(R15&gt;='Methodology'!$G$7,"A",IF(R15&gt;='Methodology'!$G$8,"B",IF(R15&gt;='Methodology'!$G$9,"C",IF(R15&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>D</x:v>
       </x:c>
-      <x:c r="T15" s="26" t="n">
+      <x:c r="T15" s="25" t="n">
         <x:f>IF(R15="","",IF(R15&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R15&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R15&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R15&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="U15" s="27" t="n">
+      <x:c r="U15" s="29" t="n">
         <x:f>MIN(D15,3)</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -10728,31 +10765,31 @@
         <x:f>IF(G16="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A16,'Observations'!$F$6:$F$500,G16))</x:f>
         <x:v>0.758</x:v>
       </x:c>
-      <x:c r="K16" s="25" t="str">
+      <x:c r="K16" s="26" t="str">
         <x:f>IF(H16="","",IF(H16&gt;=1,30,-LN(1-H16)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L16" s="25" t="str">
+      <x:c r="L16" s="26" t="str">
         <x:f>IF(I16="","",IF(I16&gt;=1,30,-LN(1-I16)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M16" s="25" t="n">
+      <x:c r="M16" s="26" t="n">
         <x:f>IF(J16="","",IF(J16&gt;=1,30,-LN(1-J16)/LN(2)))</x:f>
         <x:v>2.046921047387493</x:v>
       </x:c>
-      <x:c r="N16" s="25" t="n">
+      <x:c r="N16" s="26" t="n">
         <x:f>IF(D16&lt;2,0,(M16-L16)/(G16-F16))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O16" s="25" t="n">
+      <x:c r="O16" s="26" t="n">
         <x:f>IF(D16&lt;3,0,(L16-K16)/(F16-E16))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P16" s="25" t="n">
+      <x:c r="P16" s="26" t="n">
         <x:f>IF(D16&lt;3,0,(N16-O16)/(((G16-F16)+(F16-E16))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q16" s="17" t="str">
-        <x:f>IF(D16=0,"Ungraded — no normalized observation",IF(D16=1,"Shared frontier transfer — one observation",IF(D16=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:f>IF(D16=0,"Ungraded — no normalized observation",IF(D16=1,"METR feedback transfer — one economic observation",IF(D16=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
       <x:c r="R16" s="24" t="n">
         <x:f>IF(D16=0,"",J16)</x:f>
@@ -10762,16 +10799,16 @@
         <x:f>IF(R16="","N/A",IF(R16&gt;='Methodology'!$G$7,"A",IF(R16&gt;='Methodology'!$G$8,"B",IF(R16&gt;='Methodology'!$G$9,"C",IF(R16&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>C</x:v>
       </x:c>
-      <x:c r="T16" s="26" t="n">
+      <x:c r="T16" s="25" t="n">
         <x:f>IF(R16="","",IF(R16&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R16&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R16&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R16&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="U16" s="27" t="n">
+      <x:c r="U16" s="29" t="n">
         <x:f>MIN(D16,3)</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
+    <x:row r="17" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A17" s="17" t="str">
         <x:v>OPS-05</x:v>
       </x:c>
@@ -10809,33 +10846,33 @@
         <x:f>IF(G17="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A17,'Observations'!$F$6:$F$500,G17))</x:f>
         <x:v>0.429</x:v>
       </x:c>
-      <x:c r="K17" s="25" t="n">
+      <x:c r="K17" s="26" t="n">
         <x:f>IF(H17="","",IF(H17&gt;=1,30,-LN(1-H17)/LN(2)))</x:f>
         <x:v>0.3959286763311392</x:v>
       </x:c>
-      <x:c r="L17" s="25" t="n">
+      <x:c r="L17" s="26" t="n">
         <x:f>IF(I17="","",IF(I17&gt;=1,30,-LN(1-I17)/LN(2)))</x:f>
         <x:v>0.5207694387936639</x:v>
       </x:c>
-      <x:c r="M17" s="25" t="n">
+      <x:c r="M17" s="26" t="n">
         <x:f>IF(J17="","",IF(J17&gt;=1,30,-LN(1-J17)/LN(2)))</x:f>
         <x:v>0.8084373492992445</x:v>
       </x:c>
-      <x:c r="N17" s="25" t="n">
+      <x:c r="N17" s="26" t="n">
         <x:f>IF(D17&lt;2,0,(M17-L17)/(G17-F17))</x:f>
         <x:v>0.2876679105055806</x:v>
       </x:c>
-      <x:c r="O17" s="25" t="n">
+      <x:c r="O17" s="26" t="n">
         <x:f>IF(D17&lt;3,0,(L17-K17)/(F17-E17))</x:f>
         <x:v>0.06242038123126234</x:v>
       </x:c>
-      <x:c r="P17" s="25" t="n">
+      <x:c r="P17" s="26" t="n">
         <x:f>IF(D17&lt;3,0,(N17-O17)/(((G17-F17)+(F17-E17))/2))</x:f>
         <x:v>0.15016501951621217</x:v>
       </x:c>
       <x:c r="Q17" s="17" t="str">
-        <x:f>IF(D17=0,"Ungraded — no normalized observation",IF(D17=1,"Shared frontier transfer — one observation",IF(D17=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
+        <x:f>IF(D17=0,"Ungraded — no normalized observation",IF(D17=1,"METR feedback transfer — one economic observation",IF(D17=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — local acceleration retained as diagnostic</x:v>
       </x:c>
       <x:c r="R17" s="24" t="n">
         <x:f>IF(D17=0,"",J17)</x:f>
@@ -10845,11 +10882,11 @@
         <x:f>IF(R17="","N/A",IF(R17&gt;='Methodology'!$G$7,"A",IF(R17&gt;='Methodology'!$G$8,"B",IF(R17&gt;='Methodology'!$G$9,"C",IF(R17&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T17" s="26" t="n">
+      <x:c r="T17" s="25" t="n">
         <x:f>IF(R17="","",IF(R17&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R17&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R17&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R17&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U17" s="27" t="n">
+      <x:c r="U17" s="29" t="n">
         <x:f>MIN(D17,3)</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -10886,29 +10923,29 @@
       <x:c r="J18" s="24" t="str">
         <x:f>IF(G18="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A18,'Observations'!$F$6:$F$500,G18))</x:f>
       </x:c>
-      <x:c r="K18" s="25" t="str">
+      <x:c r="K18" s="26" t="str">
         <x:f>IF(H18="","",IF(H18&gt;=1,30,-LN(1-H18)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L18" s="25" t="str">
+      <x:c r="L18" s="26" t="str">
         <x:f>IF(I18="","",IF(I18&gt;=1,30,-LN(1-I18)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M18" s="25" t="str">
+      <x:c r="M18" s="26" t="str">
         <x:f>IF(J18="","",IF(J18&gt;=1,30,-LN(1-J18)/LN(2)))</x:f>
       </x:c>
-      <x:c r="N18" s="25" t="n">
+      <x:c r="N18" s="26" t="n">
         <x:f>IF(D18&lt;2,0,(M18-L18)/(G18-F18))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O18" s="25" t="n">
+      <x:c r="O18" s="26" t="n">
         <x:f>IF(D18&lt;3,0,(L18-K18)/(F18-E18))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P18" s="25" t="n">
+      <x:c r="P18" s="26" t="n">
         <x:f>IF(D18&lt;3,0,(N18-O18)/(((G18-F18)+(F18-E18))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q18" s="17" t="str">
-        <x:f>IF(D18=0,"Ungraded — no normalized observation",IF(D18=1,"Shared frontier transfer — one observation",IF(D18=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:f>IF(D18=0,"Ungraded — no normalized observation",IF(D18=1,"METR feedback transfer — one economic observation",IF(D18=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
         <x:v>Ungraded — no normalized observation</x:v>
       </x:c>
       <x:c r="R18" s="24" t="str">
@@ -10918,10 +10955,10 @@
         <x:f>IF(R18="","N/A",IF(R18&gt;='Methodology'!$G$7,"A",IF(R18&gt;='Methodology'!$G$8,"B",IF(R18&gt;='Methodology'!$G$9,"C",IF(R18&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="T18" s="26" t="str">
+      <x:c r="T18" s="25" t="str">
         <x:f>IF(R18="","",IF(R18&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R18&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R18&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R18&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
       </x:c>
-      <x:c r="U18" s="27" t="n">
+      <x:c r="U18" s="29" t="n">
         <x:f>MIN(D18,3)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -10960,31 +10997,31 @@
         <x:f>IF(G19="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A19,'Observations'!$F$6:$F$500,G19))</x:f>
         <x:v>0.384</x:v>
       </x:c>
-      <x:c r="K19" s="25" t="str">
+      <x:c r="K19" s="26" t="str">
         <x:f>IF(H19="","",IF(H19&gt;=1,30,-LN(1-H19)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L19" s="25" t="str">
+      <x:c r="L19" s="26" t="str">
         <x:f>IF(I19="","",IF(I19&gt;=1,30,-LN(1-I19)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M19" s="25" t="n">
+      <x:c r="M19" s="26" t="n">
         <x:f>IF(J19="","",IF(J19&gt;=1,30,-LN(1-J19)/LN(2)))</x:f>
         <x:v>0.6989977439671857</x:v>
       </x:c>
-      <x:c r="N19" s="25" t="n">
+      <x:c r="N19" s="26" t="n">
         <x:f>IF(D19&lt;2,0,(M19-L19)/(G19-F19))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O19" s="25" t="n">
+      <x:c r="O19" s="26" t="n">
         <x:f>IF(D19&lt;3,0,(L19-K19)/(F19-E19))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P19" s="25" t="n">
+      <x:c r="P19" s="26" t="n">
         <x:f>IF(D19&lt;3,0,(N19-O19)/(((G19-F19)+(F19-E19))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q19" s="17" t="str">
-        <x:f>IF(D19=0,"Ungraded — no normalized observation",IF(D19=1,"Shared frontier transfer — one observation",IF(D19=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:f>IF(D19=0,"Ungraded — no normalized observation",IF(D19=1,"METR feedback transfer — one economic observation",IF(D19=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
       <x:c r="R19" s="24" t="n">
         <x:f>IF(D19=0,"",J19)</x:f>
@@ -10994,16 +11031,16 @@
         <x:f>IF(R19="","N/A",IF(R19&gt;='Methodology'!$G$7,"A",IF(R19&gt;='Methodology'!$G$8,"B",IF(R19&gt;='Methodology'!$G$9,"C",IF(R19&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T19" s="26" t="n">
+      <x:c r="T19" s="25" t="n">
         <x:f>IF(R19="","",IF(R19&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R19&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R19&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R19&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U19" s="27" t="n">
+      <x:c r="U19" s="29" t="n">
         <x:f>MIN(D19,3)</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
+    <x:row r="20" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A20" s="17" t="str">
         <x:v>OPS-08</x:v>
       </x:c>
@@ -11041,33 +11078,33 @@
         <x:f>IF(G20="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A20,'Observations'!$F$6:$F$500,G20))</x:f>
         <x:v>0.552</x:v>
       </x:c>
-      <x:c r="K20" s="25" t="n">
+      <x:c r="K20" s="26" t="n">
         <x:f>IF(H20="","",IF(H20&gt;=1,30,-LN(1-H20)/LN(2)))</x:f>
         <x:v>0.7226103011891362</x:v>
       </x:c>
-      <x:c r="L20" s="25" t="n">
+      <x:c r="L20" s="26" t="n">
         <x:f>IF(I20="","",IF(I20&gt;=1,30,-LN(1-I20)/LN(2)))</x:f>
         <x:v>0.8520421186128986</x:v>
       </x:c>
-      <x:c r="M20" s="25" t="n">
+      <x:c r="M20" s="26" t="n">
         <x:f>IF(J20="","",IF(J20&gt;=1,30,-LN(1-J20)/LN(2)))</x:f>
         <x:v>1.158429362604483</x:v>
       </x:c>
-      <x:c r="N20" s="25" t="n">
+      <x:c r="N20" s="26" t="n">
         <x:f>IF(D20&lt;2,0,(M20-L20)/(G20-F20))</x:f>
         <x:v>0.30638724399158446</x:v>
       </x:c>
-      <x:c r="O20" s="25" t="n">
+      <x:c r="O20" s="26" t="n">
         <x:f>IF(D20&lt;3,0,(L20-K20)/(F20-E20))</x:f>
         <x:v>0.12943181742376242</x:v>
       </x:c>
-      <x:c r="P20" s="25" t="n">
+      <x:c r="P20" s="26" t="n">
         <x:f>IF(D20&lt;3,0,(N20-O20)/(((G20-F20)+(F20-E20))/2))</x:f>
         <x:v>0.17695542656782204</x:v>
       </x:c>
       <x:c r="Q20" s="17" t="str">
-        <x:f>IF(D20=0,"Ungraded — no normalized observation",IF(D20=1,"Shared frontier transfer — one observation",IF(D20=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
+        <x:f>IF(D20=0,"Ungraded — no normalized observation",IF(D20=1,"METR feedback transfer — one economic observation",IF(D20=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — local acceleration retained as diagnostic</x:v>
       </x:c>
       <x:c r="R20" s="24" t="n">
         <x:f>IF(D20=0,"",J20)</x:f>
@@ -11077,11 +11114,11 @@
         <x:f>IF(R20="","N/A",IF(R20&gt;='Methodology'!$G$7,"A",IF(R20&gt;='Methodology'!$G$8,"B",IF(R20&gt;='Methodology'!$G$9,"C",IF(R20&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T20" s="26" t="n">
+      <x:c r="T20" s="25" t="n">
         <x:f>IF(R20="","",IF(R20&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R20&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R20&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R20&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U20" s="27" t="n">
+      <x:c r="U20" s="29" t="n">
         <x:f>MIN(D20,3)</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -11120,31 +11157,31 @@
         <x:f>IF(G21="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A21,'Observations'!$F$6:$F$500,G21))</x:f>
         <x:v>0.582</x:v>
       </x:c>
-      <x:c r="K21" s="25" t="str">
+      <x:c r="K21" s="26" t="str">
         <x:f>IF(H21="","",IF(H21&gt;=1,30,-LN(1-H21)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L21" s="25" t="str">
+      <x:c r="L21" s="26" t="str">
         <x:f>IF(I21="","",IF(I21&gt;=1,30,-LN(1-I21)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M21" s="25" t="n">
+      <x:c r="M21" s="26" t="n">
         <x:f>IF(J21="","",IF(J21&gt;=1,30,-LN(1-J21)/LN(2)))</x:f>
         <x:v>1.2584251525812042</x:v>
       </x:c>
-      <x:c r="N21" s="25" t="n">
+      <x:c r="N21" s="26" t="n">
         <x:f>IF(D21&lt;2,0,(M21-L21)/(G21-F21))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O21" s="25" t="n">
+      <x:c r="O21" s="26" t="n">
         <x:f>IF(D21&lt;3,0,(L21-K21)/(F21-E21))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P21" s="25" t="n">
+      <x:c r="P21" s="26" t="n">
         <x:f>IF(D21&lt;3,0,(N21-O21)/(((G21-F21)+(F21-E21))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q21" s="17" t="str">
-        <x:f>IF(D21=0,"Ungraded — no normalized observation",IF(D21=1,"Shared frontier transfer — one observation",IF(D21=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:f>IF(D21=0,"Ungraded — no normalized observation",IF(D21=1,"METR feedback transfer — one economic observation",IF(D21=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
       <x:c r="R21" s="24" t="n">
         <x:f>IF(D21=0,"",J21)</x:f>
@@ -11154,11 +11191,11 @@
         <x:f>IF(R21="","N/A",IF(R21&gt;='Methodology'!$G$7,"A",IF(R21&gt;='Methodology'!$G$8,"B",IF(R21&gt;='Methodology'!$G$9,"C",IF(R21&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T21" s="26" t="n">
+      <x:c r="T21" s="25" t="n">
         <x:f>IF(R21="","",IF(R21&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R21&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R21&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R21&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U21" s="27" t="n">
+      <x:c r="U21" s="29" t="n">
         <x:f>MIN(D21,3)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -11197,31 +11234,31 @@
         <x:f>IF(G22="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A22,'Observations'!$F$6:$F$500,G22))</x:f>
         <x:v>0.676</x:v>
       </x:c>
-      <x:c r="K22" s="25" t="str">
+      <x:c r="K22" s="26" t="str">
         <x:f>IF(H22="","",IF(H22&gt;=1,30,-LN(1-H22)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L22" s="25" t="str">
+      <x:c r="L22" s="26" t="str">
         <x:f>IF(I22="","",IF(I22&gt;=1,30,-LN(1-I22)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M22" s="25" t="n">
+      <x:c r="M22" s="26" t="n">
         <x:f>IF(J22="","",IF(J22&gt;=1,30,-LN(1-J22)/LN(2)))</x:f>
         <x:v>1.6259342817774625</x:v>
       </x:c>
-      <x:c r="N22" s="25" t="n">
+      <x:c r="N22" s="26" t="n">
         <x:f>IF(D22&lt;2,0,(M22-L22)/(G22-F22))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O22" s="25" t="n">
+      <x:c r="O22" s="26" t="n">
         <x:f>IF(D22&lt;3,0,(L22-K22)/(F22-E22))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P22" s="25" t="n">
+      <x:c r="P22" s="26" t="n">
         <x:f>IF(D22&lt;3,0,(N22-O22)/(((G22-F22)+(F22-E22))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q22" s="17" t="str">
-        <x:f>IF(D22=0,"Ungraded — no normalized observation",IF(D22=1,"Shared frontier transfer — one observation",IF(D22=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:f>IF(D22=0,"Ungraded — no normalized observation",IF(D22=1,"METR feedback transfer — one economic observation",IF(D22=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
       <x:c r="R22" s="24" t="n">
         <x:f>IF(D22=0,"",J22)</x:f>
@@ -11231,11 +11268,11 @@
         <x:f>IF(R22="","N/A",IF(R22&gt;='Methodology'!$G$7,"A",IF(R22&gt;='Methodology'!$G$8,"B",IF(R22&gt;='Methodology'!$G$9,"C",IF(R22&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>D</x:v>
       </x:c>
-      <x:c r="T22" s="26" t="n">
+      <x:c r="T22" s="25" t="n">
         <x:f>IF(R22="","",IF(R22&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R22&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R22&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R22&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="U22" s="27" t="n">
+      <x:c r="U22" s="29" t="n">
         <x:f>MIN(D22,3)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -11274,31 +11311,31 @@
         <x:f>IF(G23="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A23,'Observations'!$F$6:$F$500,G23))</x:f>
         <x:v>0.333</x:v>
       </x:c>
-      <x:c r="K23" s="25" t="str">
+      <x:c r="K23" s="26" t="str">
         <x:f>IF(H23="","",IF(H23&gt;=1,30,-LN(1-H23)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L23" s="25" t="str">
+      <x:c r="L23" s="26" t="str">
         <x:f>IF(I23="","",IF(I23&gt;=1,30,-LN(1-I23)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M23" s="25" t="n">
+      <x:c r="M23" s="26" t="n">
         <x:f>IF(J23="","",IF(J23&gt;=1,30,-LN(1-J23)/LN(2)))</x:f>
         <x:v>0.584241333477502</x:v>
       </x:c>
-      <x:c r="N23" s="25" t="n">
+      <x:c r="N23" s="26" t="n">
         <x:f>IF(D23&lt;2,0,(M23-L23)/(G23-F23))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O23" s="25" t="n">
+      <x:c r="O23" s="26" t="n">
         <x:f>IF(D23&lt;3,0,(L23-K23)/(F23-E23))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P23" s="25" t="n">
+      <x:c r="P23" s="26" t="n">
         <x:f>IF(D23&lt;3,0,(N23-O23)/(((G23-F23)+(F23-E23))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q23" s="17" t="str">
-        <x:f>IF(D23=0,"Ungraded — no normalized observation",IF(D23=1,"Shared frontier transfer — one observation",IF(D23=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:f>IF(D23=0,"Ungraded — no normalized observation",IF(D23=1,"METR feedback transfer — one economic observation",IF(D23=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
       <x:c r="R23" s="24" t="n">
         <x:f>IF(D23=0,"",J23)</x:f>
@@ -11308,11 +11345,11 @@
         <x:f>IF(R23="","N/A",IF(R23&gt;='Methodology'!$G$7,"A",IF(R23&gt;='Methodology'!$G$8,"B",IF(R23&gt;='Methodology'!$G$9,"C",IF(R23&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T23" s="26" t="n">
+      <x:c r="T23" s="25" t="n">
         <x:f>IF(R23="","",IF(R23&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R23&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R23&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R23&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U23" s="27" t="n">
+      <x:c r="U23" s="29" t="n">
         <x:f>MIN(D23,3)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -11351,31 +11388,31 @@
         <x:f>IF(G24="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A24,'Observations'!$F$6:$F$500,G24))</x:f>
         <x:v>0.3881</x:v>
       </x:c>
-      <x:c r="K24" s="25" t="str">
+      <x:c r="K24" s="26" t="str">
         <x:f>IF(H24="","",IF(H24&gt;=1,30,-LN(1-H24)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L24" s="25" t="str">
+      <x:c r="L24" s="26" t="str">
         <x:f>IF(I24="","",IF(I24&gt;=1,30,-LN(1-I24)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M24" s="25" t="n">
+      <x:c r="M24" s="26" t="n">
         <x:f>IF(J24="","",IF(J24&gt;=1,30,-LN(1-J24)/LN(2)))</x:f>
         <x:v>0.7086321957146922</x:v>
       </x:c>
-      <x:c r="N24" s="25" t="n">
+      <x:c r="N24" s="26" t="n">
         <x:f>IF(D24&lt;2,0,(M24-L24)/(G24-F24))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O24" s="25" t="n">
+      <x:c r="O24" s="26" t="n">
         <x:f>IF(D24&lt;3,0,(L24-K24)/(F24-E24))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P24" s="25" t="n">
+      <x:c r="P24" s="26" t="n">
         <x:f>IF(D24&lt;3,0,(N24-O24)/(((G24-F24)+(F24-E24))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q24" s="17" t="str">
-        <x:f>IF(D24=0,"Ungraded — no normalized observation",IF(D24=1,"Shared frontier transfer — one observation",IF(D24=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:f>IF(D24=0,"Ungraded — no normalized observation",IF(D24=1,"METR feedback transfer — one economic observation",IF(D24=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
       <x:c r="R24" s="24" t="n">
         <x:f>IF(D24=0,"",J24)</x:f>
@@ -11385,11 +11422,11 @@
         <x:f>IF(R24="","N/A",IF(R24&gt;='Methodology'!$G$7,"A",IF(R24&gt;='Methodology'!$G$8,"B",IF(R24&gt;='Methodology'!$G$9,"C",IF(R24&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T24" s="26" t="n">
+      <x:c r="T24" s="25" t="n">
         <x:f>IF(R24="","",IF(R24&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R24&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R24&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R24&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U24" s="27" t="n">
+      <x:c r="U24" s="29" t="n">
         <x:f>MIN(D24,3)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -11426,29 +11463,29 @@
       <x:c r="J25" s="24" t="str">
         <x:f>IF(G25="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A25,'Observations'!$F$6:$F$500,G25))</x:f>
       </x:c>
-      <x:c r="K25" s="25" t="str">
+      <x:c r="K25" s="26" t="str">
         <x:f>IF(H25="","",IF(H25&gt;=1,30,-LN(1-H25)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L25" s="25" t="str">
+      <x:c r="L25" s="26" t="str">
         <x:f>IF(I25="","",IF(I25&gt;=1,30,-LN(1-I25)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M25" s="25" t="str">
+      <x:c r="M25" s="26" t="str">
         <x:f>IF(J25="","",IF(J25&gt;=1,30,-LN(1-J25)/LN(2)))</x:f>
       </x:c>
-      <x:c r="N25" s="25" t="n">
+      <x:c r="N25" s="26" t="n">
         <x:f>IF(D25&lt;2,0,(M25-L25)/(G25-F25))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O25" s="25" t="n">
+      <x:c r="O25" s="26" t="n">
         <x:f>IF(D25&lt;3,0,(L25-K25)/(F25-E25))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P25" s="25" t="n">
+      <x:c r="P25" s="26" t="n">
         <x:f>IF(D25&lt;3,0,(N25-O25)/(((G25-F25)+(F25-E25))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q25" s="17" t="str">
-        <x:f>IF(D25=0,"Ungraded — no normalized observation",IF(D25=1,"Shared frontier transfer — one observation",IF(D25=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:f>IF(D25=0,"Ungraded — no normalized observation",IF(D25=1,"METR feedback transfer — one economic observation",IF(D25=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
         <x:v>Ungraded — no normalized observation</x:v>
       </x:c>
       <x:c r="R25" s="24" t="str">
@@ -11458,15 +11495,15 @@
         <x:f>IF(R25="","N/A",IF(R25&gt;='Methodology'!$G$7,"A",IF(R25&gt;='Methodology'!$G$8,"B",IF(R25&gt;='Methodology'!$G$9,"C",IF(R25&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="T25" s="26" t="str">
+      <x:c r="T25" s="25" t="str">
         <x:f>IF(R25="","",IF(R25&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R25&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R25&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R25&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
       </x:c>
-      <x:c r="U25" s="27" t="n">
+      <x:c r="U25" s="29" t="n">
         <x:f>MIN(D25,3)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="15" hidden="0" customHeight="1">
+    <x:row r="26" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A26" s="17" t="str">
         <x:v>VAL-02</x:v>
       </x:c>
@@ -11504,33 +11541,33 @@
         <x:f>IF(G26="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A26,'Observations'!$F$6:$F$500,G26))</x:f>
         <x:v>0.158</x:v>
       </x:c>
-      <x:c r="K26" s="25" t="n">
+      <x:c r="K26" s="26" t="n">
         <x:f>IF(H26="","",IF(H26&gt;=1,30,-LN(1-H26)/LN(2)))</x:f>
         <x:v>0.05514155419246095</x:v>
       </x:c>
-      <x:c r="L26" s="25" t="n">
+      <x:c r="L26" s="26" t="n">
         <x:f>IF(I26="","",IF(I26&gt;=1,30,-LN(1-I26)/LN(2)))</x:f>
         <x:v>0.06145072623394566</x:v>
       </x:c>
-      <x:c r="M26" s="25" t="n">
+      <x:c r="M26" s="26" t="n">
         <x:f>IF(J26="","",IF(J26&gt;=1,30,-LN(1-J26)/LN(2)))</x:f>
         <x:v>0.24810786159569104</x:v>
       </x:c>
-      <x:c r="N26" s="25" t="n">
+      <x:c r="N26" s="26" t="n">
         <x:f>IF(D26&lt;2,0,(M26-L26)/(G26-F26))</x:f>
         <x:v>0.18665713536174539</x:v>
       </x:c>
-      <x:c r="O26" s="25" t="n">
+      <x:c r="O26" s="26" t="n">
         <x:f>IF(D26&lt;3,0,(L26-K26)/(F26-E26))</x:f>
         <x:v>0.006309172041484706</x:v>
       </x:c>
-      <x:c r="P26" s="25" t="n">
+      <x:c r="P26" s="26" t="n">
         <x:f>IF(D26&lt;3,0,(N26-O26)/(((G26-F26)+(F26-E26))/2))</x:f>
         <x:v>0.18034796332026068</x:v>
       </x:c>
       <x:c r="Q26" s="17" t="str">
-        <x:f>IF(D26=0,"Ungraded — no normalized observation",IF(D26=1,"Shared frontier transfer — one observation",IF(D26=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — velocity + acceleration contributor</x:v>
+        <x:f>IF(D26=0,"Ungraded — no normalized observation",IF(D26=1,"METR feedback transfer — one economic observation",IF(D26=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — local acceleration retained as diagnostic</x:v>
       </x:c>
       <x:c r="R26" s="24" t="n">
         <x:f>IF(D26=0,"",J26)</x:f>
@@ -11540,11 +11577,11 @@
         <x:f>IF(R26="","N/A",IF(R26&gt;='Methodology'!$G$7,"A",IF(R26&gt;='Methodology'!$G$8,"B",IF(R26&gt;='Methodology'!$G$9,"C",IF(R26&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>F</x:v>
       </x:c>
-      <x:c r="T26" s="26" t="n">
+      <x:c r="T26" s="25" t="n">
         <x:f>IF(R26="","",IF(R26&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R26&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R26&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R26&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U26" s="27" t="n">
+      <x:c r="U26" s="29" t="n">
         <x:f>MIN(D26,3)</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -11581,29 +11618,29 @@
       <x:c r="J27" s="24" t="str">
         <x:f>IF(G27="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A27,'Observations'!$F$6:$F$500,G27))</x:f>
       </x:c>
-      <x:c r="K27" s="25" t="str">
+      <x:c r="K27" s="26" t="str">
         <x:f>IF(H27="","",IF(H27&gt;=1,30,-LN(1-H27)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L27" s="25" t="str">
+      <x:c r="L27" s="26" t="str">
         <x:f>IF(I27="","",IF(I27&gt;=1,30,-LN(1-I27)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M27" s="25" t="str">
+      <x:c r="M27" s="26" t="str">
         <x:f>IF(J27="","",IF(J27&gt;=1,30,-LN(1-J27)/LN(2)))</x:f>
       </x:c>
-      <x:c r="N27" s="25" t="n">
+      <x:c r="N27" s="26" t="n">
         <x:f>IF(D27&lt;2,0,(M27-L27)/(G27-F27))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O27" s="25" t="n">
+      <x:c r="O27" s="26" t="n">
         <x:f>IF(D27&lt;3,0,(L27-K27)/(F27-E27))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P27" s="25" t="n">
+      <x:c r="P27" s="26" t="n">
         <x:f>IF(D27&lt;3,0,(N27-O27)/(((G27-F27)+(F27-E27))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q27" s="17" t="str">
-        <x:f>IF(D27=0,"Ungraded — no normalized observation",IF(D27=1,"Shared frontier transfer — one observation",IF(D27=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
+        <x:f>IF(D27=0,"Ungraded — no normalized observation",IF(D27=1,"METR feedback transfer — one economic observation",IF(D27=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
         <x:v>Ungraded — no normalized observation</x:v>
       </x:c>
       <x:c r="R27" s="24" t="str">
@@ -11613,10 +11650,10 @@
         <x:f>IF(R27="","N/A",IF(R27&gt;='Methodology'!$G$7,"A",IF(R27&gt;='Methodology'!$G$8,"B",IF(R27&gt;='Methodology'!$G$9,"C",IF(R27&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="T27" s="26" t="str">
+      <x:c r="T27" s="25" t="str">
         <x:f>IF(R27="","",IF(R27&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R27&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R27&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R27&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
       </x:c>
-      <x:c r="U27" s="27" t="n">
+      <x:c r="U27" s="29" t="n">
         <x:f>MIN(D27,3)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -11655,31 +11692,31 @@
         <x:f>IF(G28="","",SUMIFS('Observations'!$G$6:$G$500,'Observations'!$A$6:$A$500,A28,'Observations'!$F$6:$F$500,G28))</x:f>
         <x:v>0.704</x:v>
       </x:c>
-      <x:c r="K28" s="25" t="str">
+      <x:c r="K28" s="26" t="str">
         <x:f>IF(H28="","",IF(H28&gt;=1,30,-LN(1-H28)/LN(2)))</x:f>
       </x:c>
-      <x:c r="L28" s="25" t="str">
+      <x:c r="L28" s="26" t="str">
         <x:f>IF(I28="","",IF(I28&gt;=1,30,-LN(1-I28)/LN(2)))</x:f>
       </x:c>
-      <x:c r="M28" s="25" t="n">
+      <x:c r="M28" s="26" t="n">
         <x:f>IF(J28="","",IF(J28&gt;=1,30,-LN(1-J28)/LN(2)))</x:f>
         <x:v>1.756330919033137</x:v>
       </x:c>
-      <x:c r="N28" s="25" t="n">
+      <x:c r="N28" s="26" t="n">
         <x:f>IF(D28&lt;2,0,(M28-L28)/(G28-F28))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O28" s="25" t="n">
+      <x:c r="O28" s="26" t="n">
         <x:f>IF(D28&lt;3,0,(L28-K28)/(F28-E28))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P28" s="25" t="n">
+      <x:c r="P28" s="26" t="n">
         <x:f>IF(D28&lt;3,0,(N28-O28)/(((G28-F28)+(F28-E28))/2))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q28" s="17" t="str">
-        <x:f>IF(D28=0,"Ungraded — no normalized observation",IF(D28=1,"Shared frontier transfer — one observation",IF(D28=2,"Shared frontier transfer — velocity contributor","Shared frontier transfer — velocity + acceleration contributor")))</x:f>
-        <x:v>Shared frontier transfer — one observation</x:v>
+        <x:f>IF(D28=0,"Ungraded — no normalized observation",IF(D28=1,"METR feedback transfer — one economic observation",IF(D28=2,"METR feedback transfer — economic velocity contributor","METR feedback transfer — local acceleration retained as diagnostic")))</x:f>
+        <x:v>METR feedback transfer — one economic observation</x:v>
       </x:c>
       <x:c r="R28" s="24" t="n">
         <x:f>IF(D28=0,"",J28)</x:f>
@@ -11689,11 +11726,11 @@
         <x:f>IF(R28="","N/A",IF(R28&gt;='Methodology'!$G$7,"A",IF(R28&gt;='Methodology'!$G$8,"B",IF(R28&gt;='Methodology'!$G$9,"C",IF(R28&gt;='Methodology'!$G$10,"D","F")))))</x:f>
         <x:v>C</x:v>
       </x:c>
-      <x:c r="T28" s="26" t="n">
+      <x:c r="T28" s="25" t="n">
         <x:f>IF(R28="","",IF(R28&gt;='Methodology'!$G$7,'Methodology'!$H$7,IF(R28&gt;='Methodology'!$G$8,'Methodology'!$H$8,IF(R28&gt;='Methodology'!$G$9,'Methodology'!$H$9,IF(R28&gt;='Methodology'!$G$10,'Methodology'!$H$10,'Methodology'!$H$11)))))</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="U28" s="27" t="n">
+      <x:c r="U28" s="29" t="n">
         <x:f>MIN(D28,3)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -11705,12 +11742,1135 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec132fc97b6a466b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0aff542b9bca492d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="44" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="46" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="3" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="26" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="17" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="17" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="17" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="16" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="12" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="15" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="30" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="12" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="G1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="H1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="J1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="K1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="L1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="M1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="N1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="O1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="P1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="Q1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="R1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="S1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="T1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="U1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="V1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="W1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="X1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="Y1" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="D2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="E2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="F2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="H2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="I2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="K2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="L2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="M2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="N2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="O2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="P2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="Q2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="R2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="S2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="T2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="U2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="V2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="W2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="X2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+      <x:c r="Y2" s="3" t="str">
+        <x:v>METR Task Horizon — Capability Velocity and Acceleration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="M3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="N3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="O3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="P3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="Q3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="R3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="S3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="T3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="U3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="V3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="W3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="X3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+      <x:c r="Y3" s="6" t="str">
+        <x:v>The economic benchmark basket sets capability level. METR H50 determines how quickly the shared frontier velocity compounds; H80 checks that longer horizons are not purchased by abandoning reliability.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4"/>
+    <x:row r="5" ht="42" hidden="0" customHeight="1">
+      <x:c r="A5" s="13" t="str">
+        <x:v>Metric</x:v>
+      </x:c>
+      <x:c r="B5" s="13" t="str">
+        <x:v>Model / system</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="str">
+        <x:v>Release date</x:v>
+      </x:c>
+      <x:c r="D5" s="13" t="str">
+        <x:v>Horizon (minutes)</x:v>
+      </x:c>
+      <x:c r="E5" s="13" t="str">
+        <x:v>log₂ minutes</x:v>
+      </x:c>
+      <x:c r="F5" s="13" t="str">
+        <x:v>Elapsed quarters to latest</x:v>
+      </x:c>
+      <x:c r="G5" s="13" t="str">
+        <x:v>Fitted log₂ minutes</x:v>
+      </x:c>
+      <x:c r="H5" s="13" t="str">
+        <x:v>Residual</x:v>
+      </x:c>
+      <x:c r="I5" s="13" t="str">
+        <x:v>Harness</x:v>
+      </x:c>
+      <x:c r="J5" s="13" t="str">
+        <x:v>Source URL</x:v>
+      </x:c>
+      <x:c r="K5" s="13" t="str">
+        <x:v>Comparability note</x:v>
+      </x:c>
+      <x:c r="L5" s="13" t="str">
+        <x:v>Observation role</x:v>
+      </x:c>
+      <x:c r="N5" s="13" t="str">
+        <x:v>Metric</x:v>
+      </x:c>
+      <x:c r="O5" s="13" t="str">
+        <x:v>Observations</x:v>
+      </x:c>
+      <x:c r="P5" s="13" t="str">
+        <x:v>Source velocity (doublings/qtr)</x:v>
+      </x:c>
+      <x:c r="Q5" s="13" t="str">
+        <x:v>Quadratic current velocity</x:v>
+      </x:c>
+      <x:c r="R5" s="13" t="str">
+        <x:v>Quadratic acceleration</x:v>
+      </x:c>
+      <x:c r="S5" s="13" t="str">
+        <x:v>Relative acceleration k</x:v>
+      </x:c>
+      <x:c r="T5" s="13" t="str">
+        <x:v>Velocity growth / qtr</x:v>
+      </x:c>
+      <x:c r="U5" s="13" t="str">
+        <x:v>Fit R²</x:v>
+      </x:c>
+      <x:c r="V5" s="13" t="str">
+        <x:v>Evidence role</x:v>
+      </x:c>
+      <x:c r="W5" s="13" t="str">
+        <x:v>β₀</x:v>
+      </x:c>
+      <x:c r="X5" s="13" t="str">
+        <x:v>β₁</x:v>
+      </x:c>
+      <x:c r="Y5" s="13" t="str">
+        <x:v>β₂</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A6" s="17" t="str">
+        <x:v>H50</x:v>
+      </x:c>
+      <x:c r="B6" s="17" t="str">
+        <x:v>GPT-5</x:v>
+      </x:c>
+      <x:c r="C6" s="18" t="n">
+        <x:v>45876</x:v>
+      </x:c>
+      <x:c r="D6" s="25" t="n">
+        <x:v>203.012577</x:v>
+      </x:c>
+      <x:c r="E6" s="26" t="n">
+        <x:f>LN(D6)/LN(2)</x:f>
+        <x:v>7.665425297547081</x:v>
+      </x:c>
+      <x:c r="F6" s="26" t="n">
+        <x:v>-2.6612456107928293</x:v>
+      </x:c>
+      <x:c r="G6" s="26" t="n">
+        <x:f>IF(A6="H50",$W$6+$X$6*F6+$Y$6*F6^2,$W$7+$X$7*F6+$Y$7*F6^2)</x:f>
+        <x:v>7.621960370951646</x:v>
+      </x:c>
+      <x:c r="H6" s="26" t="n">
+        <x:f>E6-G6</x:f>
+        <x:v>0.043464926595435216</x:v>
+      </x:c>
+      <x:c r="I6" s="17" t="str">
+        <x:v>METR-selected Triframe scaffold</x:v>
+      </x:c>
+      <x:c r="J6" s="17" t="str">
+        <x:v>https://metr.org/time-horizons/</x:v>
+      </x:c>
+      <x:c r="K6" s="17" t="str">
+        <x:v>Mostly software/ML/cyber tasks; horizon is human task duration rather than agent runtime</x:v>
+      </x:c>
+      <x:c r="L6" s="17" t="str">
+        <x:v>frontier</x:v>
+      </x:c>
+      <x:c r="N6" s="17" t="str">
+        <x:v>H50</x:v>
+      </x:c>
+      <x:c r="O6" s="17" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P6" s="27" t="n">
+        <x:v>0.7092417899086559</x:v>
+      </x:c>
+      <x:c r="Q6" s="27" t="n">
+        <x:v>1.5581273436103493</x:v>
+      </x:c>
+      <x:c r="R6" s="27" t="n">
+        <x:v>0.459415326606668</x:v>
+      </x:c>
+      <x:c r="S6" s="27" t="n">
+        <x:v>0.2948509494366186</x:v>
+      </x:c>
+      <x:c r="T6" s="27" t="n">
+        <x:v>0.34292617986457585</x:v>
+      </x:c>
+      <x:c r="U6" s="24" t="n">
+        <x:v>0.9668331830828172</x:v>
+      </x:c>
+      <x:c r="V6" s="26" t="str">
+        <x:v>Primary capability-velocity signal</x:v>
+      </x:c>
+      <x:c r="W6" s="17" t="n">
+        <x:v>10.14167783416654</x:v>
+      </x:c>
+      <x:c r="X6" s="26" t="n">
+        <x:v>1.5581273436103493</x:v>
+      </x:c>
+      <x:c r="Y6" s="26" t="n">
+        <x:v>0.229707663303334</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="17" t="str">
+        <x:v>H50</x:v>
+      </x:c>
+      <x:c r="B7" s="17" t="str">
+        <x:v>Claude Opus 4.5</x:v>
+      </x:c>
+      <x:c r="C7" s="18" t="n">
+        <x:v>45985</x:v>
+      </x:c>
+      <x:c r="D7" s="25" t="n">
+        <x:v>292.994594</x:v>
+      </x:c>
+      <x:c r="E7" s="26" t="n">
+        <x:f>LN(D7)/LN(2)</x:f>
+        <x:v>8.194730235714598</x:v>
+      </x:c>
+      <x:c r="F7" s="26" t="n">
+        <x:v>-1.46751815574584</x:v>
+      </x:c>
+      <x:c r="G7" s="26" t="n">
+        <x:f>IF(A7="H50",$W$6+$X$6*F7+$Y$6*F7^2,$W$7+$X$7*F7+$Y$7*F7^2)</x:f>
+        <x:v>8.349798282968274</x:v>
+      </x:c>
+      <x:c r="H7" s="26" t="n">
+        <x:f>E7-G7</x:f>
+        <x:v>-0.1550680472536765</x:v>
+      </x:c>
+      <x:c r="I7" s="17" t="str">
+        <x:v>METR-selected ReAct scaffold</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="str">
+        <x:v>https://metr.org/time-horizons/</x:v>
+      </x:c>
+      <x:c r="K7" s="17" t="str">
+        <x:v>Scaffold differs by model family because METR elicits each model</x:v>
+      </x:c>
+      <x:c r="L7" s="17" t="str">
+        <x:v>frontier</x:v>
+      </x:c>
+      <x:c r="N7" s="17" t="str">
+        <x:v>H80</x:v>
+      </x:c>
+      <x:c r="O7" s="17" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P7" s="27" t="n">
+        <x:v>0.8562672311933832</x:v>
+      </x:c>
+      <x:c r="Q7" s="27" t="n">
+        <x:v>1.718976256750132</x:v>
+      </x:c>
+      <x:c r="R7" s="27" t="n">
+        <x:v>0.6884145326885791</x:v>
+      </x:c>
+      <x:c r="S7" s="27" t="n">
+        <x:v>0.4004793725249493</x:v>
+      </x:c>
+      <x:c r="T7" s="27" t="n">
+        <x:v>0.4925400088499324</x:v>
+      </x:c>
+      <x:c r="U7" s="24" t="n">
+        <x:v>0.9426761745795728</x:v>
+      </x:c>
+      <x:c r="V7" s="26" t="str">
+        <x:v>Reliability guardrail</x:v>
+      </x:c>
+      <x:c r="W7" s="17" t="n">
+        <x:v>7.429421481905298</x:v>
+      </x:c>
+      <x:c r="X7" s="26" t="n">
+        <x:v>1.718976256750132</x:v>
+      </x:c>
+      <x:c r="Y7" s="26" t="n">
+        <x:v>0.34420726634428955</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="17" t="str">
+        <x:v>H50</x:v>
+      </x:c>
+      <x:c r="B8" s="17" t="str">
+        <x:v>GPT-5.2</x:v>
+      </x:c>
+      <x:c r="C8" s="18" t="n">
+        <x:v>46002</x:v>
+      </x:c>
+      <x:c r="D8" s="25" t="n">
+        <x:v>352.249302</x:v>
+      </x:c>
+      <x:c r="E8" s="26" t="n">
+        <x:f>LN(D8)/LN(2)</x:f>
+        <x:v>8.46045303753849</x:v>
+      </x:c>
+      <x:c r="F8" s="26" t="n">
+        <x:v>-1.2813404792706216</x:v>
+      </x:c>
+      <x:c r="G8" s="26" t="n">
+        <x:f>IF(A8="H50",$W$6+$X$6*F8+$Y$6*F8^2,$W$7+$X$7*F8+$Y$7*F8^2)</x:f>
+        <x:v>8.522327916258618</x:v>
+      </x:c>
+      <x:c r="H8" s="26" t="n">
+        <x:f>E8-G8</x:f>
+        <x:v>-0.06187487872012731</x:v>
+      </x:c>
+      <x:c r="I8" s="17" t="str">
+        <x:v>METR-selected Triframe scaffold</x:v>
+      </x:c>
+      <x:c r="J8" s="17" t="str">
+        <x:v>https://metr.org/time-horizons/</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="str">
+        <x:v>Scaffold differs by model family because METR elicits each model</x:v>
+      </x:c>
+      <x:c r="L8" s="17" t="str">
+        <x:v>frontier</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="17" t="str">
+        <x:v>H50</x:v>
+      </x:c>
+      <x:c r="B9" s="17" t="str">
+        <x:v>Claude Opus 4.6</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="n">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="D9" s="25" t="n">
+        <x:v>718.80683</x:v>
+      </x:c>
+      <x:c r="E9" s="26" t="n">
+        <x:f>LN(D9)/LN(2)</x:f>
+        <x:v>9.489460306970264</x:v>
+      </x:c>
+      <x:c r="F9" s="26" t="n">
+        <x:v>-0.6680493097051958</x:v>
+      </x:c>
+      <x:c r="G9" s="26" t="n">
+        <x:f>IF(A9="H50",$W$6+$X$6*F9+$Y$6*F9^2,$W$7+$X$7*F9+$Y$7*F9^2)</x:f>
+        <x:v>9.203288143370967</x:v>
+      </x:c>
+      <x:c r="H9" s="26" t="n">
+        <x:f>E9-G9</x:f>
+        <x:v>0.2861721635992964</x:v>
+      </x:c>
+      <x:c r="I9" s="17" t="str">
+        <x:v>METR-selected ReAct scaffold</x:v>
+      </x:c>
+      <x:c r="J9" s="17" t="str">
+        <x:v>https://metr.org/time-horizons/</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="str">
+        <x:v>Point estimate has a wide confidence interval</x:v>
+      </x:c>
+      <x:c r="L9" s="17" t="str">
+        <x:v>frontier</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="17" t="str">
+        <x:v>H50</x:v>
+      </x:c>
+      <x:c r="B10" s="17" t="str">
+        <x:v>Claude Mythos Preview</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="n">
+        <x:v>46119</x:v>
+      </x:c>
+      <x:c r="D10" s="25" t="n">
+        <x:v>1044.780145</x:v>
+      </x:c>
+      <x:c r="E10" s="26" t="n">
+        <x:f>LN(D10)/LN(2)</x:f>
+        <x:v>10.028983669945614</x:v>
+      </x:c>
+      <x:c r="F10" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="26" t="n">
+        <x:f>IF(A10="H50",$W$6+$X$6*F10+$Y$6*F10^2,$W$7+$X$7*F10+$Y$7*F10^2)</x:f>
+        <x:v>10.14167783416654</x:v>
+      </x:c>
+      <x:c r="H10" s="26" t="n">
+        <x:f>E10-G10</x:f>
+        <x:v>-0.11269416422092604</x:v>
+      </x:c>
+      <x:c r="I10" s="17" t="str">
+        <x:v>METR-selected ReAct scaffold</x:v>
+      </x:c>
+      <x:c r="J10" s="17" t="str">
+        <x:v>https://metr.org/time-horizons/</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="str">
+        <x:v>METR warns that estimates above 16 hours are unreliable</x:v>
+      </x:c>
+      <x:c r="L10" s="17" t="str">
+        <x:v>frontier</x:v>
+      </x:c>
+      <x:c r="N10" s="9" t="str">
+        <x:v>FORECAST BRIDGE</x:v>
+      </x:c>
+      <x:c r="O10" s="9" t="str">
+        <x:v>FORECAST BRIDGE</x:v>
+      </x:c>
+      <x:c r="P10" s="9" t="str">
+        <x:v>FORECAST BRIDGE</x:v>
+      </x:c>
+      <x:c r="Q10" s="9" t="str">
+        <x:v>FORECAST BRIDGE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="38" hidden="0" customHeight="1">
+      <x:c r="A11" s="17" t="str">
+        <x:v>H80</x:v>
+      </x:c>
+      <x:c r="B11" s="17" t="str">
+        <x:v>GPT-5</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="n">
+        <x:v>45876</x:v>
+      </x:c>
+      <x:c r="D11" s="25" t="n">
+        <x:v>38.312431</x:v>
+      </x:c>
+      <x:c r="E11" s="26" t="n">
+        <x:f>LN(D11)/LN(2)</x:f>
+        <x:v>5.2597406654252685</x:v>
+      </x:c>
+      <x:c r="F11" s="26" t="n">
+        <x:v>-2.6612456107928293</x:v>
+      </x:c>
+      <x:c r="G11" s="26" t="n">
+        <x:f>IF(A11="H50",$W$6+$X$6*F11+$Y$6*F11^2,$W$7+$X$7*F11+$Y$7*F11^2)</x:f>
+        <x:v>5.29255787225221</x:v>
+      </x:c>
+      <x:c r="H11" s="26" t="n">
+        <x:f>E11-G11</x:f>
+        <x:v>-0.03281720682694189</x:v>
+      </x:c>
+      <x:c r="I11" s="17" t="str">
+        <x:v>METR-selected Triframe scaffold</x:v>
+      </x:c>
+      <x:c r="J11" s="17" t="str">
+        <x:v>https://metr.org/time-horizons/</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="str">
+        <x:v>Higher-reliability horizon on the same task suite</x:v>
+      </x:c>
+      <x:c r="L11" s="17" t="str">
+        <x:v>frontier</x:v>
+      </x:c>
+      <x:c r="N11" s="13" t="str">
+        <x:v>Parameter</x:v>
+      </x:c>
+      <x:c r="O11" s="13" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="P11" s="13" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="Q11" s="13" t="str">
+        <x:v>Rule</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A12" s="17" t="str">
+        <x:v>H80</x:v>
+      </x:c>
+      <x:c r="B12" s="17" t="str">
+        <x:v>Claude Opus 4.5</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="n">
+        <x:v>45985</x:v>
+      </x:c>
+      <x:c r="D12" s="25" t="n">
+        <x:v>49.430584</x:v>
+      </x:c>
+      <x:c r="E12" s="26" t="n">
+        <x:f>LN(D12)/LN(2)</x:f>
+        <x:v>5.627332046255334</x:v>
+      </x:c>
+      <x:c r="F12" s="26" t="n">
+        <x:v>-1.46751815574584</x:v>
+      </x:c>
+      <x:c r="G12" s="26" t="n">
+        <x:f>IF(A12="H50",$W$6+$X$6*F12+$Y$6*F12^2,$W$7+$X$7*F12+$Y$7*F12^2)</x:f>
+        <x:v>5.648080667484933</x:v>
+      </x:c>
+      <x:c r="H12" s="26" t="n">
+        <x:f>E12-G12</x:f>
+        <x:v>-0.02074862122959953</x:v>
+      </x:c>
+      <x:c r="I12" s="17" t="str">
+        <x:v>METR-selected ReAct scaffold</x:v>
+      </x:c>
+      <x:c r="J12" s="17" t="str">
+        <x:v>https://metr.org/time-horizons/</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="str">
+        <x:v>Higher-reliability horizon on the same task suite</x:v>
+      </x:c>
+      <x:c r="L12" s="17" t="str">
+        <x:v>frontier</x:v>
+      </x:c>
+      <x:c r="N12" s="17" t="str">
+        <x:v>Economic gap velocity</x:v>
+      </x:c>
+      <x:c r="O12" s="27" t="n">
+        <x:f>'Summary'!$G$17</x:f>
+        <x:v>0.12060641981551987</x:v>
+      </x:c>
+      <x:c r="P12" s="17" t="str">
+        <x:v>failure-gap halvings / qtr</x:v>
+      </x:c>
+      <x:c r="Q12" s="17" t="str">
+        <x:v>Confidence-weighted current benchmark velocity</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="A13" s="17" t="str">
+        <x:v>H80</x:v>
+      </x:c>
+      <x:c r="B13" s="17" t="str">
+        <x:v>GPT-5.2</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="n">
+        <x:v>46002</x:v>
+      </x:c>
+      <x:c r="D13" s="25" t="n">
+        <x:v>66.002649</x:v>
+      </x:c>
+      <x:c r="E13" s="26" t="n">
+        <x:f>LN(D13)/LN(2)</x:f>
+        <x:v>6.0444520227292236</x:v>
+      </x:c>
+      <x:c r="F13" s="26" t="n">
+        <x:v>-1.2813404792706216</x:v>
+      </x:c>
+      <x:c r="G13" s="26" t="n">
+        <x:f>IF(A13="H50",$W$6+$X$6*F13+$Y$6*F13^2,$W$7+$X$7*F13+$Y$7*F13^2)</x:f>
+        <x:v>5.7919586158311605</x:v>
+      </x:c>
+      <x:c r="H13" s="26" t="n">
+        <x:f>E13-G13</x:f>
+        <x:v>0.2524934068980631</x:v>
+      </x:c>
+      <x:c r="I13" s="17" t="str">
+        <x:v>METR-selected Triframe scaffold</x:v>
+      </x:c>
+      <x:c r="J13" s="17" t="str">
+        <x:v>https://metr.org/time-horizons/</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="str">
+        <x:v>Higher-reliability horizon on the same task suite</x:v>
+      </x:c>
+      <x:c r="L13" s="17" t="str">
+        <x:v>frontier</x:v>
+      </x:c>
+      <x:c r="N13" s="17" t="str">
+        <x:v>H50 source velocity</x:v>
+      </x:c>
+      <x:c r="O13" s="27" t="n">
+        <x:f>P6</x:f>
+        <x:v>0.7092417899086559</x:v>
+      </x:c>
+      <x:c r="P13" s="17" t="str">
+        <x:v>task-horizon doublings / qtr</x:v>
+      </x:c>
+      <x:c r="Q13" s="17" t="str">
+        <x:v>Published 128.744-day recent-fit doubling time</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="A14" s="17" t="str">
+        <x:v>H80</x:v>
+      </x:c>
+      <x:c r="B14" s="17" t="str">
+        <x:v>Claude Opus 4.6</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="n">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="D14" s="25" t="n">
+        <x:v>69.874587</x:v>
+      </x:c>
+      <x:c r="E14" s="26" t="n">
+        <x:f>LN(D14)/LN(2)</x:f>
+        <x:v>6.126695945690234</x:v>
+      </x:c>
+      <x:c r="F14" s="26" t="n">
+        <x:v>-0.6680493097051958</x:v>
+      </x:c>
+      <x:c r="G14" s="26" t="n">
+        <x:f>IF(A14="H50",$W$6+$X$6*F14+$Y$6*F14^2,$W$7+$X$7*F14+$Y$7*F14^2)</x:f>
+        <x:v>6.434676799843683</x:v>
+      </x:c>
+      <x:c r="H14" s="26" t="n">
+        <x:f>E14-G14</x:f>
+        <x:v>-0.307980854153449</x:v>
+      </x:c>
+      <x:c r="I14" s="17" t="str">
+        <x:v>METR-selected ReAct scaffold</x:v>
+      </x:c>
+      <x:c r="J14" s="17" t="str">
+        <x:v>https://metr.org/time-horizons/</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="str">
+        <x:v>Higher-reliability horizon on the same task suite</x:v>
+      </x:c>
+      <x:c r="L14" s="17" t="str">
+        <x:v>frontier</x:v>
+      </x:c>
+      <x:c r="N14" s="17" t="str">
+        <x:v>Effective relative acceleration</x:v>
+      </x:c>
+      <x:c r="O14" s="27" t="n">
+        <x:f>MAX(0,MIN(S6,S7))</x:f>
+        <x:v>0.2948509494366186</x:v>
+      </x:c>
+      <x:c r="P14" s="17" t="str">
+        <x:v>per qtr</x:v>
+      </x:c>
+      <x:c r="Q14" s="17" t="str">
+        <x:v>Slower positive k from H50 and H80 quadratic fits</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A15" s="17" t="str">
+        <x:v>H80</x:v>
+      </x:c>
+      <x:c r="B15" s="17" t="str">
+        <x:v>Claude Mythos Preview</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="n">
+        <x:v>46119</x:v>
+      </x:c>
+      <x:c r="D15" s="25" t="n">
+        <x:v>185.911829</x:v>
+      </x:c>
+      <x:c r="E15" s="26" t="n">
+        <x:f>LN(D15)/LN(2)</x:f>
+        <x:v>7.538474757217219</x:v>
+      </x:c>
+      <x:c r="F15" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="26" t="n">
+        <x:f>IF(A15="H50",$W$6+$X$6*F15+$Y$6*F15^2,$W$7+$X$7*F15+$Y$7*F15^2)</x:f>
+        <x:v>7.429421481905298</x:v>
+      </x:c>
+      <x:c r="H15" s="26" t="n">
+        <x:f>E15-G15</x:f>
+        <x:v>0.10905327531192022</x:v>
+      </x:c>
+      <x:c r="I15" s="17" t="str">
+        <x:v>METR-selected ReAct scaffold</x:v>
+      </x:c>
+      <x:c r="J15" s="17" t="str">
+        <x:v>https://metr.org/time-horizons/</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="str">
+        <x:v>Higher-reliability horizon on the same task suite</x:v>
+      </x:c>
+      <x:c r="L15" s="17" t="str">
+        <x:v>frontier</x:v>
+      </x:c>
+      <x:c r="N15" s="17" t="str">
+        <x:v>Default H50 acceleration</x:v>
+      </x:c>
+      <x:c r="O15" s="27" t="n">
+        <x:f>O13*O14</x:f>
+        <x:v>0.209120615134694</x:v>
+      </x:c>
+      <x:c r="P15" s="17" t="str">
+        <x:v>task-horizon doublings / qtr²</x:v>
+      </x:c>
+      <x:c r="Q15" s="17" t="str">
+        <x:v>H50 source velocity × effective relative acceleration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="N16" s="17" t="str">
+        <x:v>Economic transfer coefficient</x:v>
+      </x:c>
+      <x:c r="O16" s="27" t="n">
+        <x:f>O12/O13</x:f>
+        <x:v>0.17004979335897974</x:v>
+      </x:c>
+      <x:c r="P16" s="17" t="str">
+        <x:v>economic gap halvings / horizon doubling</x:v>
+      </x:c>
+      <x:c r="Q16" s="17" t="str">
+        <x:v>Economic velocity ÷ H50 velocity</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="N17" s="17" t="str">
+        <x:v>Initial economic acceleration</x:v>
+      </x:c>
+      <x:c r="O17" s="27" t="n">
+        <x:f>O12*O14</x:f>
+        <x:v>0.035560917390757445</x:v>
+      </x:c>
+      <x:c r="P17" s="17" t="str">
+        <x:v>failure-gap halvings / qtr²</x:v>
+      </x:c>
+      <x:c r="Q17" s="17" t="str">
+        <x:v>Economic velocity × effective relative acceleration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="N18" s="17" t="str">
+        <x:v>H80 implied acceleration</x:v>
+      </x:c>
+      <x:c r="O18" s="27" t="n">
+        <x:f>P7*S7</x:f>
+        <x:v>0.3429173634620018</x:v>
+      </x:c>
+      <x:c r="P18" s="17" t="str">
+        <x:v>task-horizon doublings / qtr²</x:v>
+      </x:c>
+      <x:c r="Q18" s="17" t="str">
+        <x:v>H80 source velocity × H80 relative acceleration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="N19" s="17" t="str">
+        <x:v>H80 / H50 feedback ratio</x:v>
+      </x:c>
+      <x:c r="O19" s="28" t="n">
+        <x:f>S7/S6</x:f>
+        <x:v>1.3582434558550969</x:v>
+      </x:c>
+      <x:c r="P19" s="17" t="str">
+        <x:v>ratio</x:v>
+      </x:c>
+      <x:c r="Q19" s="17" t="str">
+        <x:v>Values ≥1 confirm that the reliability horizon is not accelerating more slowly</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20"/>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="N21" s="9" t="str">
+        <x:v>INTERPRETATION / LIMITATIONS</x:v>
+      </x:c>
+      <x:c r="O21" s="9" t="str">
+        <x:v>INTERPRETATION / LIMITATIONS</x:v>
+      </x:c>
+      <x:c r="P21" s="9" t="str">
+        <x:v>INTERPRETATION / LIMITATIONS</x:v>
+      </x:c>
+      <x:c r="Q21" s="9" t="str">
+        <x:v>INTERPRETATION / LIMITATIONS</x:v>
+      </x:c>
+      <x:c r="R21" s="9" t="str">
+        <x:v>INTERPRETATION / LIMITATIONS</x:v>
+      </x:c>
+      <x:c r="S21" s="9" t="str">
+        <x:v>INTERPRETATION / LIMITATIONS</x:v>
+      </x:c>
+      <x:c r="T21" s="9" t="str">
+        <x:v>INTERPRETATION / LIMITATIONS</x:v>
+      </x:c>
+      <x:c r="U21" s="9" t="str">
+        <x:v>INTERPRETATION / LIMITATIONS</x:v>
+      </x:c>
+      <x:c r="V21" s="9" t="str">
+        <x:v>INTERPRETATION / LIMITATIONS</x:v>
+      </x:c>
+      <x:c r="W21" s="9" t="str">
+        <x:v>INTERPRETATION / LIMITATIONS</x:v>
+      </x:c>
+      <x:c r="X21" s="9" t="str">
+        <x:v>INTERPRETATION / LIMITATIONS</x:v>
+      </x:c>
+      <x:c r="Y21" s="9" t="str">
+        <x:v>INTERPRETATION / LIMITATIONS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="38" hidden="0" customHeight="1">
+      <x:c r="N22" s="17" t="str">
+        <x:v>Reading rule</x:v>
+      </x:c>
+      <x:c r="O22" s="17" t="str">
+        <x:v>The default acceleration is a real H50 task-horizon acceleration, not a multiplier. Raising it increases the feedback coefficient k = a/v and therefore brings the gate forward.</x:v>
+      </x:c>
+      <x:c r="P22" s="17"/>
+      <x:c r="Q22" s="17"/>
+      <x:c r="R22" s="17"/>
+      <x:c r="S22" s="17"/>
+      <x:c r="T22" s="17"/>
+      <x:c r="U22" s="17"/>
+      <x:c r="V22" s="17"/>
+      <x:c r="W22" s="17"/>
+      <x:c r="X22" s="17"/>
+      <x:c r="Y22" s="17"/>
+    </x:row>
+    <x:row r="23" ht="38" hidden="0" customHeight="1">
+      <x:c r="N23" s="17" t="str">
+        <x:v>H50 role</x:v>
+      </x:c>
+      <x:c r="O23" s="17" t="str">
+        <x:v>Primary measure of the length of tasks a model–harness system can complete at 50% success. The forecast uses the published recent-fit velocity rather than the noisy endpoint derivative.</x:v>
+      </x:c>
+      <x:c r="P23" s="17"/>
+      <x:c r="Q23" s="17"/>
+      <x:c r="R23" s="17"/>
+      <x:c r="S23" s="17"/>
+      <x:c r="T23" s="17"/>
+      <x:c r="U23" s="17"/>
+      <x:c r="V23" s="17"/>
+      <x:c r="W23" s="17"/>
+      <x:c r="X23" s="17"/>
+      <x:c r="Y23" s="17"/>
+    </x:row>
+    <x:row r="24" ht="38" hidden="0" customHeight="1">
+      <x:c r="N24" s="17" t="str">
+        <x:v>H80 role</x:v>
+      </x:c>
+      <x:c r="O24" s="17" t="str">
+        <x:v>Reliability guardrail on the same task suite. The default uses the slower positive relative-acceleration estimate; H80 currently accelerates faster, so H50 controls.</x:v>
+      </x:c>
+      <x:c r="P24" s="17"/>
+      <x:c r="Q24" s="17"/>
+      <x:c r="R24" s="17"/>
+      <x:c r="S24" s="17"/>
+      <x:c r="T24" s="17"/>
+      <x:c r="U24" s="17"/>
+      <x:c r="V24" s="17"/>
+      <x:c r="W24" s="17"/>
+      <x:c r="X24" s="17"/>
+      <x:c r="Y24" s="17"/>
+    </x:row>
+    <x:row r="25" ht="38" hidden="0" customHeight="1">
+      <x:c r="N25" s="17" t="str">
+        <x:v>Acceleration fit</x:v>
+      </x:c>
+      <x:c r="O25" s="17" t="str">
+        <x:v>Quadratic least squares on log₂ horizon versus elapsed quarters, centered at the latest release. Only five recent points exist, so the acceleration estimate is low confidence and scenario-sensitive.</x:v>
+      </x:c>
+      <x:c r="P25" s="17"/>
+      <x:c r="Q25" s="17"/>
+      <x:c r="R25" s="17"/>
+      <x:c r="S25" s="17"/>
+      <x:c r="T25" s="17"/>
+      <x:c r="U25" s="17"/>
+      <x:c r="V25" s="17"/>
+      <x:c r="W25" s="17"/>
+      <x:c r="X25" s="17"/>
+      <x:c r="Y25" s="17"/>
+    </x:row>
+    <x:row r="26" ht="38" hidden="0" customHeight="1">
+      <x:c r="N26" s="17" t="str">
+        <x:v>Ceiling warning</x:v>
+      </x:c>
+      <x:c r="O26" s="17" t="str">
+        <x:v>METR warns that central H50 estimates above 16 hours are unreliable. The final H50 point is retained for transparency; H80 and the published recent-fit velocity limit overinterpretation.</x:v>
+      </x:c>
+      <x:c r="P26" s="17"/>
+      <x:c r="Q26" s="17"/>
+      <x:c r="R26" s="17"/>
+      <x:c r="S26" s="17"/>
+      <x:c r="T26" s="17"/>
+      <x:c r="U26" s="17"/>
+      <x:c r="V26" s="17"/>
+      <x:c r="W26" s="17"/>
+      <x:c r="X26" s="17"/>
+      <x:c r="Y26" s="17"/>
+    </x:row>
+    <x:row r="27" ht="38" hidden="0" customHeight="1">
+      <x:c r="N27" s="17" t="str">
+        <x:v>Transfer assumption</x:v>
+      </x:c>
+      <x:c r="O27" s="17" t="str">
+        <x:v>Economic benchmarks measure whether systems can do useful work; METR measures how quickly task horizon advances. Applying METR's relative acceleration to economic gap velocity is the conjectural bridge and a direct target for refutation.</x:v>
+      </x:c>
+      <x:c r="P27" s="17"/>
+      <x:c r="Q27" s="17"/>
+      <x:c r="R27" s="17"/>
+      <x:c r="S27" s="17"/>
+      <x:c r="T27" s="17"/>
+      <x:c r="U27" s="17"/>
+      <x:c r="V27" s="17"/>
+      <x:c r="W27" s="17"/>
+      <x:c r="X27" s="17"/>
+      <x:c r="Y27" s="17"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:Y2"/>
+    <x:mergeCell ref="A3:Y3"/>
+    <x:mergeCell ref="N10:Q10"/>
+    <x:mergeCell ref="N21:Y21"/>
+    <x:mergeCell ref="O22:Y22"/>
+    <x:mergeCell ref="O23:Y23"/>
+    <x:mergeCell ref="O24:Y24"/>
+    <x:mergeCell ref="O25:Y25"/>
+    <x:mergeCell ref="O26:Y26"/>
+    <x:mergeCell ref="O27:Y27"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="2">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1856098b45854d7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0305d17902b541d2"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -12014,16 +13174,16 @@
     </x:row>
     <x:row r="14" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A14" s="17" t="str">
-        <x:v>Acceleration summary</x:v>
+        <x:v>Capability feedback</x:v>
       </x:c>
       <x:c r="B14" s="17" t="str">
-        <x:v>Observed series only</x:v>
+        <x:v>METR H50 + H80</x:v>
       </x:c>
       <x:c r="C14" s="17" t="str">
         <x:v>rule</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
-        <x:v>Average 3+ point acceleration estimates; coverage is reported separately</x:v>
+        <x:v>H50 sets task-horizon acceleration; H80 is a reliability guardrail. Benchmark-local acceleration remains diagnostic only.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -12078,13 +13238,13 @@
     </x:row>
     <x:row r="17" ht="38" hidden="0" customHeight="1">
       <x:c r="A17" s="17" t="str">
-        <x:v>Depth</x:v>
+        <x:v>Economic depth</x:v>
       </x:c>
       <x:c r="B17" s="17" t="str">
         <x:v>d = -LOG2(1 - score)</x:v>
       </x:c>
       <x:c r="C17" s="17" t="str">
-        <x:v>Transforms a bounded percentage into halvings of the remaining failure gap. Exact 100% is represented as 30 halvings for finite computation.</x:v>
+        <x:v>Transforms each bounded economic benchmark into halvings of its remaining failure gap. Exact 100% is represented as 30 halvings for finite computation.</x:v>
       </x:c>
       <x:c r="D17" s="17"/>
       <x:c r="E17" s="17"/>
@@ -12096,13 +13256,13 @@
     </x:row>
     <x:row r="18" ht="38" hidden="0" customHeight="1">
       <x:c r="A18" s="17" t="str">
-        <x:v>Velocity</x:v>
+        <x:v>Economic velocity</x:v>
       </x:c>
       <x:c r="B18" s="17" t="str">
-        <x:v>v = (d_t - d_t-1) / elapsed quarters</x:v>
+        <x:v>v_e = confidence-weighted mean of recent benchmark depth velocity</x:v>
       </x:c>
       <x:c r="C18" s="17" t="str">
-        <x:v>First derivative of failure-gap depth. Report-card Δ score cells separately show quarter-over-quarter percentage-point changes.</x:v>
+        <x:v>Anchors the current rate at which the economic-work composite is closing its remaining gap. Benchmark-local accelerations do not drive the forecast.</x:v>
       </x:c>
       <x:c r="D18" s="17"/>
       <x:c r="E18" s="17"/>
@@ -12114,13 +13274,13 @@
     </x:row>
     <x:row r="19" ht="38" hidden="0" customHeight="1">
       <x:c r="A19" s="17" t="str">
-        <x:v>Acceleration</x:v>
+        <x:v>METR acceleration</x:v>
       </x:c>
       <x:c r="B19" s="17" t="str">
-        <x:v>a = (v_recent - v_prior) / average interval</x:v>
+        <x:v>a_H50 = v_H50 · MIN(k_H50, k_H80)</x:v>
       </x:c>
       <x:c r="C19" s="17" t="str">
-        <x:v>Second derivative: whether gap-closing speed is rising or falling.</x:v>
+        <x:v>A quadratic fit of log2 task horizon supplies relative acceleration k. H50 is primary; the slower of positive H50/H80 feedback estimates is used so reliability cannot silently lag.</x:v>
       </x:c>
       <x:c r="D19" s="17"/>
       <x:c r="E19" s="17"/>
@@ -12132,13 +13292,13 @@
     </x:row>
     <x:row r="20" ht="38" hidden="0" customHeight="1">
       <x:c r="A20" s="17" t="str">
-        <x:v>Feedback</x:v>
+        <x:v>Transfer</x:v>
       </x:c>
       <x:c r="B20" s="17" t="str">
-        <x:v>k = a / v; dv/dh = k·v; v(h) = v·EXP(k·h)</x:v>
+        <x:v>τ = v_e / v_H50; k = a_H50 / v_H50</x:v>
       </x:c>
       <x:c r="C20" s="17" t="str">
-        <x:v>The conjectured causal loop: progress raises the next quarter's rate of progress. At h = 0, dv/dh equals the measured initial acceleration a.</x:v>
+        <x:v>The level comes from economic benchmarks; METR determines how quickly that level's velocity compounds. The transfer coefficient keeps the initial economic velocity anchored to observed economic data.</x:v>
       </x:c>
       <x:c r="D20" s="17"/>
       <x:c r="E20" s="17"/>
@@ -12153,10 +13313,10 @@
         <x:v>Projection</x:v>
       </x:c>
       <x:c r="B21" s="17" t="str">
-        <x:v>Δd(h) = v·(EXP(k·h) - 1) / k</x:v>
+        <x:v>Δd(h) = v_e·(EXP(k·h) - 1) / k</x:v>
       </x:c>
       <x:c r="C21" s="17" t="str">
-        <x:v>Continuous shared-frontier depth gain; when k = 0, Δd = v·h. Each graded benchmark receives the same gain from its current depth.</x:v>
+        <x:v>Continuous shared-frontier depth gain; when k = 0, Δd = v_e·h. Positive METR acceleration makes future progress raise the subsequent progress rate.</x:v>
       </x:c>
       <x:c r="D21" s="17"/>
       <x:c r="E21" s="17"/>
@@ -12174,7 +13334,7 @@
         <x:v>score_b(h) = 1 - 2^(-(d_b,now + MAX(0,Δd(h))))</x:v>
       </x:c>
       <x:c r="C22" s="17" t="str">
-        <x:v>Approaches 100% asymptotically. Evidence confidence reports uncertainty; it does not convert missing history into permanent zero progress.</x:v>
+        <x:v>Each graded benchmark receives the shared economic-depth gain, then categories are recomputed and confidence weighted. The score approaches 100% asymptotically.</x:v>
       </x:c>
       <x:c r="D22" s="17"/>
       <x:c r="E22" s="17"/>
@@ -12592,7 +13752,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B48" s="17" t="str">
-        <x:v>Refresh sources and inspect projected saturation. A projection is a scenario extrapolation, not a probability distribution.</x:v>
+        <x:v>Append new METR H50/H80 observations to the canonical CSV, refit the horizon curve, and inspect projected saturation. A projection is a scenario extrapolation, not a probability distribution.</x:v>
       </x:c>
       <x:c r="C48" s="17"/>
       <x:c r="D48" s="17"/>
